--- a/input/202509_Bao cao cong viec_thinhdv.xlsx
+++ b/input/202509_Bao cao cong viec_thinhdv.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bao\Desktop\Work\App\report_task\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\app\extract-work\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD14BB8-EB8F-4076-B15D-4BC890473C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B0E525-24D5-4843-AB2F-B20D94E116BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="3150" windowWidth="28800" windowHeight="15345" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Th6-T7" sheetId="267" state="hidden" r:id="rId1"/>
@@ -4089,16 +4089,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="dd/mm"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="dd/mm"/>
   </numFmts>
   <fonts count="45">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -4143,7 +4143,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4203,7 +4203,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4216,7 +4216,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4259,7 +4259,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4272,7 +4272,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF002060"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4330,7 +4330,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4344,7 +4344,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -4357,7 +4357,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4653,7 +4653,7 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -4688,7 +4688,7 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4821,7 +4821,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4882,25 +4882,25 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4932,7 +4932,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -5100,7 +5100,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5113,16 +5113,16 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="21" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5158,7 +5158,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5212,7 +5212,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5229,7 +5229,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5269,7 +5269,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5317,7 +5317,7 @@
     <xf numFmtId="14" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5329,7 +5329,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5380,16 +5380,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5473,13 +5473,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5509,16 +5509,16 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="38" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="38" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="38" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5545,20 +5545,20 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5567,16 +5567,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5717,7 +5717,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5834,10 +5834,10 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5972,10 +5972,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6035,10 +6035,10 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6580,587 +6580,587 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L342"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="40" customWidth="1"/>
-    <col min="2" max="2" width="43.7109375" style="379" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="40" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" style="334" customWidth="1"/>
-    <col min="6" max="6" width="52.5703125" style="379" customWidth="1"/>
-    <col min="7" max="7" width="43.7109375" style="40" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="43.75" style="379" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="40" customWidth="1"/>
+    <col min="4" max="5" width="11.25" style="334" customWidth="1"/>
+    <col min="6" max="6" width="52.58203125" style="379" customWidth="1"/>
+    <col min="7" max="7" width="43.75" style="40" customWidth="1"/>
     <col min="8" max="8" width="16" style="235" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.58203125" style="40" bestFit="1" customWidth="1"/>
     <col min="10" max="256" width="9" style="40"/>
-    <col min="257" max="257" width="5.85546875" style="40" customWidth="1"/>
-    <col min="258" max="258" width="62.42578125" style="40" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" style="40" customWidth="1"/>
-    <col min="260" max="260" width="17.28515625" style="40" customWidth="1"/>
-    <col min="261" max="261" width="20.7109375" style="40" customWidth="1"/>
-    <col min="262" max="262" width="33.85546875" style="40" customWidth="1"/>
-    <col min="263" max="263" width="37.28515625" style="40" customWidth="1"/>
-    <col min="264" max="264" width="18.5703125" style="40" customWidth="1"/>
+    <col min="257" max="257" width="5.83203125" style="40" customWidth="1"/>
+    <col min="258" max="258" width="62.4140625" style="40" customWidth="1"/>
+    <col min="259" max="259" width="14.83203125" style="40" customWidth="1"/>
+    <col min="260" max="260" width="17.25" style="40" customWidth="1"/>
+    <col min="261" max="261" width="20.75" style="40" customWidth="1"/>
+    <col min="262" max="262" width="33.83203125" style="40" customWidth="1"/>
+    <col min="263" max="263" width="37.25" style="40" customWidth="1"/>
+    <col min="264" max="264" width="18.58203125" style="40" customWidth="1"/>
     <col min="265" max="512" width="9" style="40"/>
-    <col min="513" max="513" width="5.85546875" style="40" customWidth="1"/>
-    <col min="514" max="514" width="62.42578125" style="40" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" style="40" customWidth="1"/>
-    <col min="516" max="516" width="17.28515625" style="40" customWidth="1"/>
-    <col min="517" max="517" width="20.7109375" style="40" customWidth="1"/>
-    <col min="518" max="518" width="33.85546875" style="40" customWidth="1"/>
-    <col min="519" max="519" width="37.28515625" style="40" customWidth="1"/>
-    <col min="520" max="520" width="18.5703125" style="40" customWidth="1"/>
+    <col min="513" max="513" width="5.83203125" style="40" customWidth="1"/>
+    <col min="514" max="514" width="62.4140625" style="40" customWidth="1"/>
+    <col min="515" max="515" width="14.83203125" style="40" customWidth="1"/>
+    <col min="516" max="516" width="17.25" style="40" customWidth="1"/>
+    <col min="517" max="517" width="20.75" style="40" customWidth="1"/>
+    <col min="518" max="518" width="33.83203125" style="40" customWidth="1"/>
+    <col min="519" max="519" width="37.25" style="40" customWidth="1"/>
+    <col min="520" max="520" width="18.58203125" style="40" customWidth="1"/>
     <col min="521" max="768" width="9" style="40"/>
-    <col min="769" max="769" width="5.85546875" style="40" customWidth="1"/>
-    <col min="770" max="770" width="62.42578125" style="40" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" style="40" customWidth="1"/>
-    <col min="772" max="772" width="17.28515625" style="40" customWidth="1"/>
-    <col min="773" max="773" width="20.7109375" style="40" customWidth="1"/>
-    <col min="774" max="774" width="33.85546875" style="40" customWidth="1"/>
-    <col min="775" max="775" width="37.28515625" style="40" customWidth="1"/>
-    <col min="776" max="776" width="18.5703125" style="40" customWidth="1"/>
+    <col min="769" max="769" width="5.83203125" style="40" customWidth="1"/>
+    <col min="770" max="770" width="62.4140625" style="40" customWidth="1"/>
+    <col min="771" max="771" width="14.83203125" style="40" customWidth="1"/>
+    <col min="772" max="772" width="17.25" style="40" customWidth="1"/>
+    <col min="773" max="773" width="20.75" style="40" customWidth="1"/>
+    <col min="774" max="774" width="33.83203125" style="40" customWidth="1"/>
+    <col min="775" max="775" width="37.25" style="40" customWidth="1"/>
+    <col min="776" max="776" width="18.58203125" style="40" customWidth="1"/>
     <col min="777" max="1024" width="9" style="40"/>
-    <col min="1025" max="1025" width="5.85546875" style="40" customWidth="1"/>
-    <col min="1026" max="1026" width="62.42578125" style="40" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" style="40" customWidth="1"/>
-    <col min="1028" max="1028" width="17.28515625" style="40" customWidth="1"/>
-    <col min="1029" max="1029" width="20.7109375" style="40" customWidth="1"/>
-    <col min="1030" max="1030" width="33.85546875" style="40" customWidth="1"/>
-    <col min="1031" max="1031" width="37.28515625" style="40" customWidth="1"/>
-    <col min="1032" max="1032" width="18.5703125" style="40" customWidth="1"/>
+    <col min="1025" max="1025" width="5.83203125" style="40" customWidth="1"/>
+    <col min="1026" max="1026" width="62.4140625" style="40" customWidth="1"/>
+    <col min="1027" max="1027" width="14.83203125" style="40" customWidth="1"/>
+    <col min="1028" max="1028" width="17.25" style="40" customWidth="1"/>
+    <col min="1029" max="1029" width="20.75" style="40" customWidth="1"/>
+    <col min="1030" max="1030" width="33.83203125" style="40" customWidth="1"/>
+    <col min="1031" max="1031" width="37.25" style="40" customWidth="1"/>
+    <col min="1032" max="1032" width="18.58203125" style="40" customWidth="1"/>
     <col min="1033" max="1280" width="9" style="40"/>
-    <col min="1281" max="1281" width="5.85546875" style="40" customWidth="1"/>
-    <col min="1282" max="1282" width="62.42578125" style="40" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" style="40" customWidth="1"/>
-    <col min="1284" max="1284" width="17.28515625" style="40" customWidth="1"/>
-    <col min="1285" max="1285" width="20.7109375" style="40" customWidth="1"/>
-    <col min="1286" max="1286" width="33.85546875" style="40" customWidth="1"/>
-    <col min="1287" max="1287" width="37.28515625" style="40" customWidth="1"/>
-    <col min="1288" max="1288" width="18.5703125" style="40" customWidth="1"/>
+    <col min="1281" max="1281" width="5.83203125" style="40" customWidth="1"/>
+    <col min="1282" max="1282" width="62.4140625" style="40" customWidth="1"/>
+    <col min="1283" max="1283" width="14.83203125" style="40" customWidth="1"/>
+    <col min="1284" max="1284" width="17.25" style="40" customWidth="1"/>
+    <col min="1285" max="1285" width="20.75" style="40" customWidth="1"/>
+    <col min="1286" max="1286" width="33.83203125" style="40" customWidth="1"/>
+    <col min="1287" max="1287" width="37.25" style="40" customWidth="1"/>
+    <col min="1288" max="1288" width="18.58203125" style="40" customWidth="1"/>
     <col min="1289" max="1536" width="9" style="40"/>
-    <col min="1537" max="1537" width="5.85546875" style="40" customWidth="1"/>
-    <col min="1538" max="1538" width="62.42578125" style="40" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" style="40" customWidth="1"/>
-    <col min="1540" max="1540" width="17.28515625" style="40" customWidth="1"/>
-    <col min="1541" max="1541" width="20.7109375" style="40" customWidth="1"/>
-    <col min="1542" max="1542" width="33.85546875" style="40" customWidth="1"/>
-    <col min="1543" max="1543" width="37.28515625" style="40" customWidth="1"/>
-    <col min="1544" max="1544" width="18.5703125" style="40" customWidth="1"/>
+    <col min="1537" max="1537" width="5.83203125" style="40" customWidth="1"/>
+    <col min="1538" max="1538" width="62.4140625" style="40" customWidth="1"/>
+    <col min="1539" max="1539" width="14.83203125" style="40" customWidth="1"/>
+    <col min="1540" max="1540" width="17.25" style="40" customWidth="1"/>
+    <col min="1541" max="1541" width="20.75" style="40" customWidth="1"/>
+    <col min="1542" max="1542" width="33.83203125" style="40" customWidth="1"/>
+    <col min="1543" max="1543" width="37.25" style="40" customWidth="1"/>
+    <col min="1544" max="1544" width="18.58203125" style="40" customWidth="1"/>
     <col min="1545" max="1792" width="9" style="40"/>
-    <col min="1793" max="1793" width="5.85546875" style="40" customWidth="1"/>
-    <col min="1794" max="1794" width="62.42578125" style="40" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" style="40" customWidth="1"/>
-    <col min="1796" max="1796" width="17.28515625" style="40" customWidth="1"/>
-    <col min="1797" max="1797" width="20.7109375" style="40" customWidth="1"/>
-    <col min="1798" max="1798" width="33.85546875" style="40" customWidth="1"/>
-    <col min="1799" max="1799" width="37.28515625" style="40" customWidth="1"/>
-    <col min="1800" max="1800" width="18.5703125" style="40" customWidth="1"/>
+    <col min="1793" max="1793" width="5.83203125" style="40" customWidth="1"/>
+    <col min="1794" max="1794" width="62.4140625" style="40" customWidth="1"/>
+    <col min="1795" max="1795" width="14.83203125" style="40" customWidth="1"/>
+    <col min="1796" max="1796" width="17.25" style="40" customWidth="1"/>
+    <col min="1797" max="1797" width="20.75" style="40" customWidth="1"/>
+    <col min="1798" max="1798" width="33.83203125" style="40" customWidth="1"/>
+    <col min="1799" max="1799" width="37.25" style="40" customWidth="1"/>
+    <col min="1800" max="1800" width="18.58203125" style="40" customWidth="1"/>
     <col min="1801" max="2048" width="9" style="40"/>
-    <col min="2049" max="2049" width="5.85546875" style="40" customWidth="1"/>
-    <col min="2050" max="2050" width="62.42578125" style="40" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" style="40" customWidth="1"/>
-    <col min="2052" max="2052" width="17.28515625" style="40" customWidth="1"/>
-    <col min="2053" max="2053" width="20.7109375" style="40" customWidth="1"/>
-    <col min="2054" max="2054" width="33.85546875" style="40" customWidth="1"/>
-    <col min="2055" max="2055" width="37.28515625" style="40" customWidth="1"/>
-    <col min="2056" max="2056" width="18.5703125" style="40" customWidth="1"/>
+    <col min="2049" max="2049" width="5.83203125" style="40" customWidth="1"/>
+    <col min="2050" max="2050" width="62.4140625" style="40" customWidth="1"/>
+    <col min="2051" max="2051" width="14.83203125" style="40" customWidth="1"/>
+    <col min="2052" max="2052" width="17.25" style="40" customWidth="1"/>
+    <col min="2053" max="2053" width="20.75" style="40" customWidth="1"/>
+    <col min="2054" max="2054" width="33.83203125" style="40" customWidth="1"/>
+    <col min="2055" max="2055" width="37.25" style="40" customWidth="1"/>
+    <col min="2056" max="2056" width="18.58203125" style="40" customWidth="1"/>
     <col min="2057" max="2304" width="9" style="40"/>
-    <col min="2305" max="2305" width="5.85546875" style="40" customWidth="1"/>
-    <col min="2306" max="2306" width="62.42578125" style="40" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" style="40" customWidth="1"/>
-    <col min="2308" max="2308" width="17.28515625" style="40" customWidth="1"/>
-    <col min="2309" max="2309" width="20.7109375" style="40" customWidth="1"/>
-    <col min="2310" max="2310" width="33.85546875" style="40" customWidth="1"/>
-    <col min="2311" max="2311" width="37.28515625" style="40" customWidth="1"/>
-    <col min="2312" max="2312" width="18.5703125" style="40" customWidth="1"/>
+    <col min="2305" max="2305" width="5.83203125" style="40" customWidth="1"/>
+    <col min="2306" max="2306" width="62.4140625" style="40" customWidth="1"/>
+    <col min="2307" max="2307" width="14.83203125" style="40" customWidth="1"/>
+    <col min="2308" max="2308" width="17.25" style="40" customWidth="1"/>
+    <col min="2309" max="2309" width="20.75" style="40" customWidth="1"/>
+    <col min="2310" max="2310" width="33.83203125" style="40" customWidth="1"/>
+    <col min="2311" max="2311" width="37.25" style="40" customWidth="1"/>
+    <col min="2312" max="2312" width="18.58203125" style="40" customWidth="1"/>
     <col min="2313" max="2560" width="9" style="40"/>
-    <col min="2561" max="2561" width="5.85546875" style="40" customWidth="1"/>
-    <col min="2562" max="2562" width="62.42578125" style="40" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" style="40" customWidth="1"/>
-    <col min="2564" max="2564" width="17.28515625" style="40" customWidth="1"/>
-    <col min="2565" max="2565" width="20.7109375" style="40" customWidth="1"/>
-    <col min="2566" max="2566" width="33.85546875" style="40" customWidth="1"/>
-    <col min="2567" max="2567" width="37.28515625" style="40" customWidth="1"/>
-    <col min="2568" max="2568" width="18.5703125" style="40" customWidth="1"/>
+    <col min="2561" max="2561" width="5.83203125" style="40" customWidth="1"/>
+    <col min="2562" max="2562" width="62.4140625" style="40" customWidth="1"/>
+    <col min="2563" max="2563" width="14.83203125" style="40" customWidth="1"/>
+    <col min="2564" max="2564" width="17.25" style="40" customWidth="1"/>
+    <col min="2565" max="2565" width="20.75" style="40" customWidth="1"/>
+    <col min="2566" max="2566" width="33.83203125" style="40" customWidth="1"/>
+    <col min="2567" max="2567" width="37.25" style="40" customWidth="1"/>
+    <col min="2568" max="2568" width="18.58203125" style="40" customWidth="1"/>
     <col min="2569" max="2816" width="9" style="40"/>
-    <col min="2817" max="2817" width="5.85546875" style="40" customWidth="1"/>
-    <col min="2818" max="2818" width="62.42578125" style="40" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" style="40" customWidth="1"/>
-    <col min="2820" max="2820" width="17.28515625" style="40" customWidth="1"/>
-    <col min="2821" max="2821" width="20.7109375" style="40" customWidth="1"/>
-    <col min="2822" max="2822" width="33.85546875" style="40" customWidth="1"/>
-    <col min="2823" max="2823" width="37.28515625" style="40" customWidth="1"/>
-    <col min="2824" max="2824" width="18.5703125" style="40" customWidth="1"/>
+    <col min="2817" max="2817" width="5.83203125" style="40" customWidth="1"/>
+    <col min="2818" max="2818" width="62.4140625" style="40" customWidth="1"/>
+    <col min="2819" max="2819" width="14.83203125" style="40" customWidth="1"/>
+    <col min="2820" max="2820" width="17.25" style="40" customWidth="1"/>
+    <col min="2821" max="2821" width="20.75" style="40" customWidth="1"/>
+    <col min="2822" max="2822" width="33.83203125" style="40" customWidth="1"/>
+    <col min="2823" max="2823" width="37.25" style="40" customWidth="1"/>
+    <col min="2824" max="2824" width="18.58203125" style="40" customWidth="1"/>
     <col min="2825" max="3072" width="9" style="40"/>
-    <col min="3073" max="3073" width="5.85546875" style="40" customWidth="1"/>
-    <col min="3074" max="3074" width="62.42578125" style="40" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" style="40" customWidth="1"/>
-    <col min="3076" max="3076" width="17.28515625" style="40" customWidth="1"/>
-    <col min="3077" max="3077" width="20.7109375" style="40" customWidth="1"/>
-    <col min="3078" max="3078" width="33.85546875" style="40" customWidth="1"/>
-    <col min="3079" max="3079" width="37.28515625" style="40" customWidth="1"/>
-    <col min="3080" max="3080" width="18.5703125" style="40" customWidth="1"/>
+    <col min="3073" max="3073" width="5.83203125" style="40" customWidth="1"/>
+    <col min="3074" max="3074" width="62.4140625" style="40" customWidth="1"/>
+    <col min="3075" max="3075" width="14.83203125" style="40" customWidth="1"/>
+    <col min="3076" max="3076" width="17.25" style="40" customWidth="1"/>
+    <col min="3077" max="3077" width="20.75" style="40" customWidth="1"/>
+    <col min="3078" max="3078" width="33.83203125" style="40" customWidth="1"/>
+    <col min="3079" max="3079" width="37.25" style="40" customWidth="1"/>
+    <col min="3080" max="3080" width="18.58203125" style="40" customWidth="1"/>
     <col min="3081" max="3328" width="9" style="40"/>
-    <col min="3329" max="3329" width="5.85546875" style="40" customWidth="1"/>
-    <col min="3330" max="3330" width="62.42578125" style="40" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" style="40" customWidth="1"/>
-    <col min="3332" max="3332" width="17.28515625" style="40" customWidth="1"/>
-    <col min="3333" max="3333" width="20.7109375" style="40" customWidth="1"/>
-    <col min="3334" max="3334" width="33.85546875" style="40" customWidth="1"/>
-    <col min="3335" max="3335" width="37.28515625" style="40" customWidth="1"/>
-    <col min="3336" max="3336" width="18.5703125" style="40" customWidth="1"/>
+    <col min="3329" max="3329" width="5.83203125" style="40" customWidth="1"/>
+    <col min="3330" max="3330" width="62.4140625" style="40" customWidth="1"/>
+    <col min="3331" max="3331" width="14.83203125" style="40" customWidth="1"/>
+    <col min="3332" max="3332" width="17.25" style="40" customWidth="1"/>
+    <col min="3333" max="3333" width="20.75" style="40" customWidth="1"/>
+    <col min="3334" max="3334" width="33.83203125" style="40" customWidth="1"/>
+    <col min="3335" max="3335" width="37.25" style="40" customWidth="1"/>
+    <col min="3336" max="3336" width="18.58203125" style="40" customWidth="1"/>
     <col min="3337" max="3584" width="9" style="40"/>
-    <col min="3585" max="3585" width="5.85546875" style="40" customWidth="1"/>
-    <col min="3586" max="3586" width="62.42578125" style="40" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" style="40" customWidth="1"/>
-    <col min="3588" max="3588" width="17.28515625" style="40" customWidth="1"/>
-    <col min="3589" max="3589" width="20.7109375" style="40" customWidth="1"/>
-    <col min="3590" max="3590" width="33.85546875" style="40" customWidth="1"/>
-    <col min="3591" max="3591" width="37.28515625" style="40" customWidth="1"/>
-    <col min="3592" max="3592" width="18.5703125" style="40" customWidth="1"/>
+    <col min="3585" max="3585" width="5.83203125" style="40" customWidth="1"/>
+    <col min="3586" max="3586" width="62.4140625" style="40" customWidth="1"/>
+    <col min="3587" max="3587" width="14.83203125" style="40" customWidth="1"/>
+    <col min="3588" max="3588" width="17.25" style="40" customWidth="1"/>
+    <col min="3589" max="3589" width="20.75" style="40" customWidth="1"/>
+    <col min="3590" max="3590" width="33.83203125" style="40" customWidth="1"/>
+    <col min="3591" max="3591" width="37.25" style="40" customWidth="1"/>
+    <col min="3592" max="3592" width="18.58203125" style="40" customWidth="1"/>
     <col min="3593" max="3840" width="9" style="40"/>
-    <col min="3841" max="3841" width="5.85546875" style="40" customWidth="1"/>
-    <col min="3842" max="3842" width="62.42578125" style="40" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" style="40" customWidth="1"/>
-    <col min="3844" max="3844" width="17.28515625" style="40" customWidth="1"/>
-    <col min="3845" max="3845" width="20.7109375" style="40" customWidth="1"/>
-    <col min="3846" max="3846" width="33.85546875" style="40" customWidth="1"/>
-    <col min="3847" max="3847" width="37.28515625" style="40" customWidth="1"/>
-    <col min="3848" max="3848" width="18.5703125" style="40" customWidth="1"/>
+    <col min="3841" max="3841" width="5.83203125" style="40" customWidth="1"/>
+    <col min="3842" max="3842" width="62.4140625" style="40" customWidth="1"/>
+    <col min="3843" max="3843" width="14.83203125" style="40" customWidth="1"/>
+    <col min="3844" max="3844" width="17.25" style="40" customWidth="1"/>
+    <col min="3845" max="3845" width="20.75" style="40" customWidth="1"/>
+    <col min="3846" max="3846" width="33.83203125" style="40" customWidth="1"/>
+    <col min="3847" max="3847" width="37.25" style="40" customWidth="1"/>
+    <col min="3848" max="3848" width="18.58203125" style="40" customWidth="1"/>
     <col min="3849" max="4096" width="9" style="40"/>
-    <col min="4097" max="4097" width="5.85546875" style="40" customWidth="1"/>
-    <col min="4098" max="4098" width="62.42578125" style="40" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" style="40" customWidth="1"/>
-    <col min="4100" max="4100" width="17.28515625" style="40" customWidth="1"/>
-    <col min="4101" max="4101" width="20.7109375" style="40" customWidth="1"/>
-    <col min="4102" max="4102" width="33.85546875" style="40" customWidth="1"/>
-    <col min="4103" max="4103" width="37.28515625" style="40" customWidth="1"/>
-    <col min="4104" max="4104" width="18.5703125" style="40" customWidth="1"/>
+    <col min="4097" max="4097" width="5.83203125" style="40" customWidth="1"/>
+    <col min="4098" max="4098" width="62.4140625" style="40" customWidth="1"/>
+    <col min="4099" max="4099" width="14.83203125" style="40" customWidth="1"/>
+    <col min="4100" max="4100" width="17.25" style="40" customWidth="1"/>
+    <col min="4101" max="4101" width="20.75" style="40" customWidth="1"/>
+    <col min="4102" max="4102" width="33.83203125" style="40" customWidth="1"/>
+    <col min="4103" max="4103" width="37.25" style="40" customWidth="1"/>
+    <col min="4104" max="4104" width="18.58203125" style="40" customWidth="1"/>
     <col min="4105" max="4352" width="9" style="40"/>
-    <col min="4353" max="4353" width="5.85546875" style="40" customWidth="1"/>
-    <col min="4354" max="4354" width="62.42578125" style="40" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" style="40" customWidth="1"/>
-    <col min="4356" max="4356" width="17.28515625" style="40" customWidth="1"/>
-    <col min="4357" max="4357" width="20.7109375" style="40" customWidth="1"/>
-    <col min="4358" max="4358" width="33.85546875" style="40" customWidth="1"/>
-    <col min="4359" max="4359" width="37.28515625" style="40" customWidth="1"/>
-    <col min="4360" max="4360" width="18.5703125" style="40" customWidth="1"/>
+    <col min="4353" max="4353" width="5.83203125" style="40" customWidth="1"/>
+    <col min="4354" max="4354" width="62.4140625" style="40" customWidth="1"/>
+    <col min="4355" max="4355" width="14.83203125" style="40" customWidth="1"/>
+    <col min="4356" max="4356" width="17.25" style="40" customWidth="1"/>
+    <col min="4357" max="4357" width="20.75" style="40" customWidth="1"/>
+    <col min="4358" max="4358" width="33.83203125" style="40" customWidth="1"/>
+    <col min="4359" max="4359" width="37.25" style="40" customWidth="1"/>
+    <col min="4360" max="4360" width="18.58203125" style="40" customWidth="1"/>
     <col min="4361" max="4608" width="9" style="40"/>
-    <col min="4609" max="4609" width="5.85546875" style="40" customWidth="1"/>
-    <col min="4610" max="4610" width="62.42578125" style="40" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" style="40" customWidth="1"/>
-    <col min="4612" max="4612" width="17.28515625" style="40" customWidth="1"/>
-    <col min="4613" max="4613" width="20.7109375" style="40" customWidth="1"/>
-    <col min="4614" max="4614" width="33.85546875" style="40" customWidth="1"/>
-    <col min="4615" max="4615" width="37.28515625" style="40" customWidth="1"/>
-    <col min="4616" max="4616" width="18.5703125" style="40" customWidth="1"/>
+    <col min="4609" max="4609" width="5.83203125" style="40" customWidth="1"/>
+    <col min="4610" max="4610" width="62.4140625" style="40" customWidth="1"/>
+    <col min="4611" max="4611" width="14.83203125" style="40" customWidth="1"/>
+    <col min="4612" max="4612" width="17.25" style="40" customWidth="1"/>
+    <col min="4613" max="4613" width="20.75" style="40" customWidth="1"/>
+    <col min="4614" max="4614" width="33.83203125" style="40" customWidth="1"/>
+    <col min="4615" max="4615" width="37.25" style="40" customWidth="1"/>
+    <col min="4616" max="4616" width="18.58203125" style="40" customWidth="1"/>
     <col min="4617" max="4864" width="9" style="40"/>
-    <col min="4865" max="4865" width="5.85546875" style="40" customWidth="1"/>
-    <col min="4866" max="4866" width="62.42578125" style="40" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" style="40" customWidth="1"/>
-    <col min="4868" max="4868" width="17.28515625" style="40" customWidth="1"/>
-    <col min="4869" max="4869" width="20.7109375" style="40" customWidth="1"/>
-    <col min="4870" max="4870" width="33.85546875" style="40" customWidth="1"/>
-    <col min="4871" max="4871" width="37.28515625" style="40" customWidth="1"/>
-    <col min="4872" max="4872" width="18.5703125" style="40" customWidth="1"/>
+    <col min="4865" max="4865" width="5.83203125" style="40" customWidth="1"/>
+    <col min="4866" max="4866" width="62.4140625" style="40" customWidth="1"/>
+    <col min="4867" max="4867" width="14.83203125" style="40" customWidth="1"/>
+    <col min="4868" max="4868" width="17.25" style="40" customWidth="1"/>
+    <col min="4869" max="4869" width="20.75" style="40" customWidth="1"/>
+    <col min="4870" max="4870" width="33.83203125" style="40" customWidth="1"/>
+    <col min="4871" max="4871" width="37.25" style="40" customWidth="1"/>
+    <col min="4872" max="4872" width="18.58203125" style="40" customWidth="1"/>
     <col min="4873" max="5120" width="9" style="40"/>
-    <col min="5121" max="5121" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5122" max="5122" width="62.42578125" style="40" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" style="40" customWidth="1"/>
-    <col min="5124" max="5124" width="17.28515625" style="40" customWidth="1"/>
-    <col min="5125" max="5125" width="20.7109375" style="40" customWidth="1"/>
-    <col min="5126" max="5126" width="33.85546875" style="40" customWidth="1"/>
-    <col min="5127" max="5127" width="37.28515625" style="40" customWidth="1"/>
-    <col min="5128" max="5128" width="18.5703125" style="40" customWidth="1"/>
+    <col min="5121" max="5121" width="5.83203125" style="40" customWidth="1"/>
+    <col min="5122" max="5122" width="62.4140625" style="40" customWidth="1"/>
+    <col min="5123" max="5123" width="14.83203125" style="40" customWidth="1"/>
+    <col min="5124" max="5124" width="17.25" style="40" customWidth="1"/>
+    <col min="5125" max="5125" width="20.75" style="40" customWidth="1"/>
+    <col min="5126" max="5126" width="33.83203125" style="40" customWidth="1"/>
+    <col min="5127" max="5127" width="37.25" style="40" customWidth="1"/>
+    <col min="5128" max="5128" width="18.58203125" style="40" customWidth="1"/>
     <col min="5129" max="5376" width="9" style="40"/>
-    <col min="5377" max="5377" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5378" max="5378" width="62.42578125" style="40" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" style="40" customWidth="1"/>
-    <col min="5380" max="5380" width="17.28515625" style="40" customWidth="1"/>
-    <col min="5381" max="5381" width="20.7109375" style="40" customWidth="1"/>
-    <col min="5382" max="5382" width="33.85546875" style="40" customWidth="1"/>
-    <col min="5383" max="5383" width="37.28515625" style="40" customWidth="1"/>
-    <col min="5384" max="5384" width="18.5703125" style="40" customWidth="1"/>
+    <col min="5377" max="5377" width="5.83203125" style="40" customWidth="1"/>
+    <col min="5378" max="5378" width="62.4140625" style="40" customWidth="1"/>
+    <col min="5379" max="5379" width="14.83203125" style="40" customWidth="1"/>
+    <col min="5380" max="5380" width="17.25" style="40" customWidth="1"/>
+    <col min="5381" max="5381" width="20.75" style="40" customWidth="1"/>
+    <col min="5382" max="5382" width="33.83203125" style="40" customWidth="1"/>
+    <col min="5383" max="5383" width="37.25" style="40" customWidth="1"/>
+    <col min="5384" max="5384" width="18.58203125" style="40" customWidth="1"/>
     <col min="5385" max="5632" width="9" style="40"/>
-    <col min="5633" max="5633" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5634" max="5634" width="62.42578125" style="40" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" style="40" customWidth="1"/>
-    <col min="5636" max="5636" width="17.28515625" style="40" customWidth="1"/>
-    <col min="5637" max="5637" width="20.7109375" style="40" customWidth="1"/>
-    <col min="5638" max="5638" width="33.85546875" style="40" customWidth="1"/>
-    <col min="5639" max="5639" width="37.28515625" style="40" customWidth="1"/>
-    <col min="5640" max="5640" width="18.5703125" style="40" customWidth="1"/>
+    <col min="5633" max="5633" width="5.83203125" style="40" customWidth="1"/>
+    <col min="5634" max="5634" width="62.4140625" style="40" customWidth="1"/>
+    <col min="5635" max="5635" width="14.83203125" style="40" customWidth="1"/>
+    <col min="5636" max="5636" width="17.25" style="40" customWidth="1"/>
+    <col min="5637" max="5637" width="20.75" style="40" customWidth="1"/>
+    <col min="5638" max="5638" width="33.83203125" style="40" customWidth="1"/>
+    <col min="5639" max="5639" width="37.25" style="40" customWidth="1"/>
+    <col min="5640" max="5640" width="18.58203125" style="40" customWidth="1"/>
     <col min="5641" max="5888" width="9" style="40"/>
-    <col min="5889" max="5889" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5890" max="5890" width="62.42578125" style="40" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" style="40" customWidth="1"/>
-    <col min="5892" max="5892" width="17.28515625" style="40" customWidth="1"/>
-    <col min="5893" max="5893" width="20.7109375" style="40" customWidth="1"/>
-    <col min="5894" max="5894" width="33.85546875" style="40" customWidth="1"/>
-    <col min="5895" max="5895" width="37.28515625" style="40" customWidth="1"/>
-    <col min="5896" max="5896" width="18.5703125" style="40" customWidth="1"/>
+    <col min="5889" max="5889" width="5.83203125" style="40" customWidth="1"/>
+    <col min="5890" max="5890" width="62.4140625" style="40" customWidth="1"/>
+    <col min="5891" max="5891" width="14.83203125" style="40" customWidth="1"/>
+    <col min="5892" max="5892" width="17.25" style="40" customWidth="1"/>
+    <col min="5893" max="5893" width="20.75" style="40" customWidth="1"/>
+    <col min="5894" max="5894" width="33.83203125" style="40" customWidth="1"/>
+    <col min="5895" max="5895" width="37.25" style="40" customWidth="1"/>
+    <col min="5896" max="5896" width="18.58203125" style="40" customWidth="1"/>
     <col min="5897" max="6144" width="9" style="40"/>
-    <col min="6145" max="6145" width="5.85546875" style="40" customWidth="1"/>
-    <col min="6146" max="6146" width="62.42578125" style="40" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" style="40" customWidth="1"/>
-    <col min="6148" max="6148" width="17.28515625" style="40" customWidth="1"/>
-    <col min="6149" max="6149" width="20.7109375" style="40" customWidth="1"/>
-    <col min="6150" max="6150" width="33.85546875" style="40" customWidth="1"/>
-    <col min="6151" max="6151" width="37.28515625" style="40" customWidth="1"/>
-    <col min="6152" max="6152" width="18.5703125" style="40" customWidth="1"/>
+    <col min="6145" max="6145" width="5.83203125" style="40" customWidth="1"/>
+    <col min="6146" max="6146" width="62.4140625" style="40" customWidth="1"/>
+    <col min="6147" max="6147" width="14.83203125" style="40" customWidth="1"/>
+    <col min="6148" max="6148" width="17.25" style="40" customWidth="1"/>
+    <col min="6149" max="6149" width="20.75" style="40" customWidth="1"/>
+    <col min="6150" max="6150" width="33.83203125" style="40" customWidth="1"/>
+    <col min="6151" max="6151" width="37.25" style="40" customWidth="1"/>
+    <col min="6152" max="6152" width="18.58203125" style="40" customWidth="1"/>
     <col min="6153" max="6400" width="9" style="40"/>
-    <col min="6401" max="6401" width="5.85546875" style="40" customWidth="1"/>
-    <col min="6402" max="6402" width="62.42578125" style="40" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" style="40" customWidth="1"/>
-    <col min="6404" max="6404" width="17.28515625" style="40" customWidth="1"/>
-    <col min="6405" max="6405" width="20.7109375" style="40" customWidth="1"/>
-    <col min="6406" max="6406" width="33.85546875" style="40" customWidth="1"/>
-    <col min="6407" max="6407" width="37.28515625" style="40" customWidth="1"/>
-    <col min="6408" max="6408" width="18.5703125" style="40" customWidth="1"/>
+    <col min="6401" max="6401" width="5.83203125" style="40" customWidth="1"/>
+    <col min="6402" max="6402" width="62.4140625" style="40" customWidth="1"/>
+    <col min="6403" max="6403" width="14.83203125" style="40" customWidth="1"/>
+    <col min="6404" max="6404" width="17.25" style="40" customWidth="1"/>
+    <col min="6405" max="6405" width="20.75" style="40" customWidth="1"/>
+    <col min="6406" max="6406" width="33.83203125" style="40" customWidth="1"/>
+    <col min="6407" max="6407" width="37.25" style="40" customWidth="1"/>
+    <col min="6408" max="6408" width="18.58203125" style="40" customWidth="1"/>
     <col min="6409" max="6656" width="9" style="40"/>
-    <col min="6657" max="6657" width="5.85546875" style="40" customWidth="1"/>
-    <col min="6658" max="6658" width="62.42578125" style="40" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" style="40" customWidth="1"/>
-    <col min="6660" max="6660" width="17.28515625" style="40" customWidth="1"/>
-    <col min="6661" max="6661" width="20.7109375" style="40" customWidth="1"/>
-    <col min="6662" max="6662" width="33.85546875" style="40" customWidth="1"/>
-    <col min="6663" max="6663" width="37.28515625" style="40" customWidth="1"/>
-    <col min="6664" max="6664" width="18.5703125" style="40" customWidth="1"/>
+    <col min="6657" max="6657" width="5.83203125" style="40" customWidth="1"/>
+    <col min="6658" max="6658" width="62.4140625" style="40" customWidth="1"/>
+    <col min="6659" max="6659" width="14.83203125" style="40" customWidth="1"/>
+    <col min="6660" max="6660" width="17.25" style="40" customWidth="1"/>
+    <col min="6661" max="6661" width="20.75" style="40" customWidth="1"/>
+    <col min="6662" max="6662" width="33.83203125" style="40" customWidth="1"/>
+    <col min="6663" max="6663" width="37.25" style="40" customWidth="1"/>
+    <col min="6664" max="6664" width="18.58203125" style="40" customWidth="1"/>
     <col min="6665" max="6912" width="9" style="40"/>
-    <col min="6913" max="6913" width="5.85546875" style="40" customWidth="1"/>
-    <col min="6914" max="6914" width="62.42578125" style="40" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" style="40" customWidth="1"/>
-    <col min="6916" max="6916" width="17.28515625" style="40" customWidth="1"/>
-    <col min="6917" max="6917" width="20.7109375" style="40" customWidth="1"/>
-    <col min="6918" max="6918" width="33.85546875" style="40" customWidth="1"/>
-    <col min="6919" max="6919" width="37.28515625" style="40" customWidth="1"/>
-    <col min="6920" max="6920" width="18.5703125" style="40" customWidth="1"/>
+    <col min="6913" max="6913" width="5.83203125" style="40" customWidth="1"/>
+    <col min="6914" max="6914" width="62.4140625" style="40" customWidth="1"/>
+    <col min="6915" max="6915" width="14.83203125" style="40" customWidth="1"/>
+    <col min="6916" max="6916" width="17.25" style="40" customWidth="1"/>
+    <col min="6917" max="6917" width="20.75" style="40" customWidth="1"/>
+    <col min="6918" max="6918" width="33.83203125" style="40" customWidth="1"/>
+    <col min="6919" max="6919" width="37.25" style="40" customWidth="1"/>
+    <col min="6920" max="6920" width="18.58203125" style="40" customWidth="1"/>
     <col min="6921" max="7168" width="9" style="40"/>
-    <col min="7169" max="7169" width="5.85546875" style="40" customWidth="1"/>
-    <col min="7170" max="7170" width="62.42578125" style="40" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" style="40" customWidth="1"/>
-    <col min="7172" max="7172" width="17.28515625" style="40" customWidth="1"/>
-    <col min="7173" max="7173" width="20.7109375" style="40" customWidth="1"/>
-    <col min="7174" max="7174" width="33.85546875" style="40" customWidth="1"/>
-    <col min="7175" max="7175" width="37.28515625" style="40" customWidth="1"/>
-    <col min="7176" max="7176" width="18.5703125" style="40" customWidth="1"/>
+    <col min="7169" max="7169" width="5.83203125" style="40" customWidth="1"/>
+    <col min="7170" max="7170" width="62.4140625" style="40" customWidth="1"/>
+    <col min="7171" max="7171" width="14.83203125" style="40" customWidth="1"/>
+    <col min="7172" max="7172" width="17.25" style="40" customWidth="1"/>
+    <col min="7173" max="7173" width="20.75" style="40" customWidth="1"/>
+    <col min="7174" max="7174" width="33.83203125" style="40" customWidth="1"/>
+    <col min="7175" max="7175" width="37.25" style="40" customWidth="1"/>
+    <col min="7176" max="7176" width="18.58203125" style="40" customWidth="1"/>
     <col min="7177" max="7424" width="9" style="40"/>
-    <col min="7425" max="7425" width="5.85546875" style="40" customWidth="1"/>
-    <col min="7426" max="7426" width="62.42578125" style="40" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" style="40" customWidth="1"/>
-    <col min="7428" max="7428" width="17.28515625" style="40" customWidth="1"/>
-    <col min="7429" max="7429" width="20.7109375" style="40" customWidth="1"/>
-    <col min="7430" max="7430" width="33.85546875" style="40" customWidth="1"/>
-    <col min="7431" max="7431" width="37.28515625" style="40" customWidth="1"/>
-    <col min="7432" max="7432" width="18.5703125" style="40" customWidth="1"/>
+    <col min="7425" max="7425" width="5.83203125" style="40" customWidth="1"/>
+    <col min="7426" max="7426" width="62.4140625" style="40" customWidth="1"/>
+    <col min="7427" max="7427" width="14.83203125" style="40" customWidth="1"/>
+    <col min="7428" max="7428" width="17.25" style="40" customWidth="1"/>
+    <col min="7429" max="7429" width="20.75" style="40" customWidth="1"/>
+    <col min="7430" max="7430" width="33.83203125" style="40" customWidth="1"/>
+    <col min="7431" max="7431" width="37.25" style="40" customWidth="1"/>
+    <col min="7432" max="7432" width="18.58203125" style="40" customWidth="1"/>
     <col min="7433" max="7680" width="9" style="40"/>
-    <col min="7681" max="7681" width="5.85546875" style="40" customWidth="1"/>
-    <col min="7682" max="7682" width="62.42578125" style="40" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" style="40" customWidth="1"/>
-    <col min="7684" max="7684" width="17.28515625" style="40" customWidth="1"/>
-    <col min="7685" max="7685" width="20.7109375" style="40" customWidth="1"/>
-    <col min="7686" max="7686" width="33.85546875" style="40" customWidth="1"/>
-    <col min="7687" max="7687" width="37.28515625" style="40" customWidth="1"/>
-    <col min="7688" max="7688" width="18.5703125" style="40" customWidth="1"/>
+    <col min="7681" max="7681" width="5.83203125" style="40" customWidth="1"/>
+    <col min="7682" max="7682" width="62.4140625" style="40" customWidth="1"/>
+    <col min="7683" max="7683" width="14.83203125" style="40" customWidth="1"/>
+    <col min="7684" max="7684" width="17.25" style="40" customWidth="1"/>
+    <col min="7685" max="7685" width="20.75" style="40" customWidth="1"/>
+    <col min="7686" max="7686" width="33.83203125" style="40" customWidth="1"/>
+    <col min="7687" max="7687" width="37.25" style="40" customWidth="1"/>
+    <col min="7688" max="7688" width="18.58203125" style="40" customWidth="1"/>
     <col min="7689" max="7936" width="9" style="40"/>
-    <col min="7937" max="7937" width="5.85546875" style="40" customWidth="1"/>
-    <col min="7938" max="7938" width="62.42578125" style="40" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" style="40" customWidth="1"/>
-    <col min="7940" max="7940" width="17.28515625" style="40" customWidth="1"/>
-    <col min="7941" max="7941" width="20.7109375" style="40" customWidth="1"/>
-    <col min="7942" max="7942" width="33.85546875" style="40" customWidth="1"/>
-    <col min="7943" max="7943" width="37.28515625" style="40" customWidth="1"/>
-    <col min="7944" max="7944" width="18.5703125" style="40" customWidth="1"/>
+    <col min="7937" max="7937" width="5.83203125" style="40" customWidth="1"/>
+    <col min="7938" max="7938" width="62.4140625" style="40" customWidth="1"/>
+    <col min="7939" max="7939" width="14.83203125" style="40" customWidth="1"/>
+    <col min="7940" max="7940" width="17.25" style="40" customWidth="1"/>
+    <col min="7941" max="7941" width="20.75" style="40" customWidth="1"/>
+    <col min="7942" max="7942" width="33.83203125" style="40" customWidth="1"/>
+    <col min="7943" max="7943" width="37.25" style="40" customWidth="1"/>
+    <col min="7944" max="7944" width="18.58203125" style="40" customWidth="1"/>
     <col min="7945" max="8192" width="9" style="40"/>
-    <col min="8193" max="8193" width="5.85546875" style="40" customWidth="1"/>
-    <col min="8194" max="8194" width="62.42578125" style="40" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" style="40" customWidth="1"/>
-    <col min="8196" max="8196" width="17.28515625" style="40" customWidth="1"/>
-    <col min="8197" max="8197" width="20.7109375" style="40" customWidth="1"/>
-    <col min="8198" max="8198" width="33.85546875" style="40" customWidth="1"/>
-    <col min="8199" max="8199" width="37.28515625" style="40" customWidth="1"/>
-    <col min="8200" max="8200" width="18.5703125" style="40" customWidth="1"/>
+    <col min="8193" max="8193" width="5.83203125" style="40" customWidth="1"/>
+    <col min="8194" max="8194" width="62.4140625" style="40" customWidth="1"/>
+    <col min="8195" max="8195" width="14.83203125" style="40" customWidth="1"/>
+    <col min="8196" max="8196" width="17.25" style="40" customWidth="1"/>
+    <col min="8197" max="8197" width="20.75" style="40" customWidth="1"/>
+    <col min="8198" max="8198" width="33.83203125" style="40" customWidth="1"/>
+    <col min="8199" max="8199" width="37.25" style="40" customWidth="1"/>
+    <col min="8200" max="8200" width="18.58203125" style="40" customWidth="1"/>
     <col min="8201" max="8448" width="9" style="40"/>
-    <col min="8449" max="8449" width="5.85546875" style="40" customWidth="1"/>
-    <col min="8450" max="8450" width="62.42578125" style="40" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" style="40" customWidth="1"/>
-    <col min="8452" max="8452" width="17.28515625" style="40" customWidth="1"/>
-    <col min="8453" max="8453" width="20.7109375" style="40" customWidth="1"/>
-    <col min="8454" max="8454" width="33.85546875" style="40" customWidth="1"/>
-    <col min="8455" max="8455" width="37.28515625" style="40" customWidth="1"/>
-    <col min="8456" max="8456" width="18.5703125" style="40" customWidth="1"/>
+    <col min="8449" max="8449" width="5.83203125" style="40" customWidth="1"/>
+    <col min="8450" max="8450" width="62.4140625" style="40" customWidth="1"/>
+    <col min="8451" max="8451" width="14.83203125" style="40" customWidth="1"/>
+    <col min="8452" max="8452" width="17.25" style="40" customWidth="1"/>
+    <col min="8453" max="8453" width="20.75" style="40" customWidth="1"/>
+    <col min="8454" max="8454" width="33.83203125" style="40" customWidth="1"/>
+    <col min="8455" max="8455" width="37.25" style="40" customWidth="1"/>
+    <col min="8456" max="8456" width="18.58203125" style="40" customWidth="1"/>
     <col min="8457" max="8704" width="9" style="40"/>
-    <col min="8705" max="8705" width="5.85546875" style="40" customWidth="1"/>
-    <col min="8706" max="8706" width="62.42578125" style="40" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" style="40" customWidth="1"/>
-    <col min="8708" max="8708" width="17.28515625" style="40" customWidth="1"/>
-    <col min="8709" max="8709" width="20.7109375" style="40" customWidth="1"/>
-    <col min="8710" max="8710" width="33.85546875" style="40" customWidth="1"/>
-    <col min="8711" max="8711" width="37.28515625" style="40" customWidth="1"/>
-    <col min="8712" max="8712" width="18.5703125" style="40" customWidth="1"/>
+    <col min="8705" max="8705" width="5.83203125" style="40" customWidth="1"/>
+    <col min="8706" max="8706" width="62.4140625" style="40" customWidth="1"/>
+    <col min="8707" max="8707" width="14.83203125" style="40" customWidth="1"/>
+    <col min="8708" max="8708" width="17.25" style="40" customWidth="1"/>
+    <col min="8709" max="8709" width="20.75" style="40" customWidth="1"/>
+    <col min="8710" max="8710" width="33.83203125" style="40" customWidth="1"/>
+    <col min="8711" max="8711" width="37.25" style="40" customWidth="1"/>
+    <col min="8712" max="8712" width="18.58203125" style="40" customWidth="1"/>
     <col min="8713" max="8960" width="9" style="40"/>
-    <col min="8961" max="8961" width="5.85546875" style="40" customWidth="1"/>
-    <col min="8962" max="8962" width="62.42578125" style="40" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" style="40" customWidth="1"/>
-    <col min="8964" max="8964" width="17.28515625" style="40" customWidth="1"/>
-    <col min="8965" max="8965" width="20.7109375" style="40" customWidth="1"/>
-    <col min="8966" max="8966" width="33.85546875" style="40" customWidth="1"/>
-    <col min="8967" max="8967" width="37.28515625" style="40" customWidth="1"/>
-    <col min="8968" max="8968" width="18.5703125" style="40" customWidth="1"/>
+    <col min="8961" max="8961" width="5.83203125" style="40" customWidth="1"/>
+    <col min="8962" max="8962" width="62.4140625" style="40" customWidth="1"/>
+    <col min="8963" max="8963" width="14.83203125" style="40" customWidth="1"/>
+    <col min="8964" max="8964" width="17.25" style="40" customWidth="1"/>
+    <col min="8965" max="8965" width="20.75" style="40" customWidth="1"/>
+    <col min="8966" max="8966" width="33.83203125" style="40" customWidth="1"/>
+    <col min="8967" max="8967" width="37.25" style="40" customWidth="1"/>
+    <col min="8968" max="8968" width="18.58203125" style="40" customWidth="1"/>
     <col min="8969" max="9216" width="9" style="40"/>
-    <col min="9217" max="9217" width="5.85546875" style="40" customWidth="1"/>
-    <col min="9218" max="9218" width="62.42578125" style="40" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" style="40" customWidth="1"/>
-    <col min="9220" max="9220" width="17.28515625" style="40" customWidth="1"/>
-    <col min="9221" max="9221" width="20.7109375" style="40" customWidth="1"/>
-    <col min="9222" max="9222" width="33.85546875" style="40" customWidth="1"/>
-    <col min="9223" max="9223" width="37.28515625" style="40" customWidth="1"/>
-    <col min="9224" max="9224" width="18.5703125" style="40" customWidth="1"/>
+    <col min="9217" max="9217" width="5.83203125" style="40" customWidth="1"/>
+    <col min="9218" max="9218" width="62.4140625" style="40" customWidth="1"/>
+    <col min="9219" max="9219" width="14.83203125" style="40" customWidth="1"/>
+    <col min="9220" max="9220" width="17.25" style="40" customWidth="1"/>
+    <col min="9221" max="9221" width="20.75" style="40" customWidth="1"/>
+    <col min="9222" max="9222" width="33.83203125" style="40" customWidth="1"/>
+    <col min="9223" max="9223" width="37.25" style="40" customWidth="1"/>
+    <col min="9224" max="9224" width="18.58203125" style="40" customWidth="1"/>
     <col min="9225" max="9472" width="9" style="40"/>
-    <col min="9473" max="9473" width="5.85546875" style="40" customWidth="1"/>
-    <col min="9474" max="9474" width="62.42578125" style="40" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" style="40" customWidth="1"/>
-    <col min="9476" max="9476" width="17.28515625" style="40" customWidth="1"/>
-    <col min="9477" max="9477" width="20.7109375" style="40" customWidth="1"/>
-    <col min="9478" max="9478" width="33.85546875" style="40" customWidth="1"/>
-    <col min="9479" max="9479" width="37.28515625" style="40" customWidth="1"/>
-    <col min="9480" max="9480" width="18.5703125" style="40" customWidth="1"/>
+    <col min="9473" max="9473" width="5.83203125" style="40" customWidth="1"/>
+    <col min="9474" max="9474" width="62.4140625" style="40" customWidth="1"/>
+    <col min="9475" max="9475" width="14.83203125" style="40" customWidth="1"/>
+    <col min="9476" max="9476" width="17.25" style="40" customWidth="1"/>
+    <col min="9477" max="9477" width="20.75" style="40" customWidth="1"/>
+    <col min="9478" max="9478" width="33.83203125" style="40" customWidth="1"/>
+    <col min="9479" max="9479" width="37.25" style="40" customWidth="1"/>
+    <col min="9480" max="9480" width="18.58203125" style="40" customWidth="1"/>
     <col min="9481" max="9728" width="9" style="40"/>
-    <col min="9729" max="9729" width="5.85546875" style="40" customWidth="1"/>
-    <col min="9730" max="9730" width="62.42578125" style="40" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" style="40" customWidth="1"/>
-    <col min="9732" max="9732" width="17.28515625" style="40" customWidth="1"/>
-    <col min="9733" max="9733" width="20.7109375" style="40" customWidth="1"/>
-    <col min="9734" max="9734" width="33.85546875" style="40" customWidth="1"/>
-    <col min="9735" max="9735" width="37.28515625" style="40" customWidth="1"/>
-    <col min="9736" max="9736" width="18.5703125" style="40" customWidth="1"/>
+    <col min="9729" max="9729" width="5.83203125" style="40" customWidth="1"/>
+    <col min="9730" max="9730" width="62.4140625" style="40" customWidth="1"/>
+    <col min="9731" max="9731" width="14.83203125" style="40" customWidth="1"/>
+    <col min="9732" max="9732" width="17.25" style="40" customWidth="1"/>
+    <col min="9733" max="9733" width="20.75" style="40" customWidth="1"/>
+    <col min="9734" max="9734" width="33.83203125" style="40" customWidth="1"/>
+    <col min="9735" max="9735" width="37.25" style="40" customWidth="1"/>
+    <col min="9736" max="9736" width="18.58203125" style="40" customWidth="1"/>
     <col min="9737" max="9984" width="9" style="40"/>
-    <col min="9985" max="9985" width="5.85546875" style="40" customWidth="1"/>
-    <col min="9986" max="9986" width="62.42578125" style="40" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" style="40" customWidth="1"/>
-    <col min="9988" max="9988" width="17.28515625" style="40" customWidth="1"/>
-    <col min="9989" max="9989" width="20.7109375" style="40" customWidth="1"/>
-    <col min="9990" max="9990" width="33.85546875" style="40" customWidth="1"/>
-    <col min="9991" max="9991" width="37.28515625" style="40" customWidth="1"/>
-    <col min="9992" max="9992" width="18.5703125" style="40" customWidth="1"/>
+    <col min="9985" max="9985" width="5.83203125" style="40" customWidth="1"/>
+    <col min="9986" max="9986" width="62.4140625" style="40" customWidth="1"/>
+    <col min="9987" max="9987" width="14.83203125" style="40" customWidth="1"/>
+    <col min="9988" max="9988" width="17.25" style="40" customWidth="1"/>
+    <col min="9989" max="9989" width="20.75" style="40" customWidth="1"/>
+    <col min="9990" max="9990" width="33.83203125" style="40" customWidth="1"/>
+    <col min="9991" max="9991" width="37.25" style="40" customWidth="1"/>
+    <col min="9992" max="9992" width="18.58203125" style="40" customWidth="1"/>
     <col min="9993" max="10240" width="9" style="40"/>
-    <col min="10241" max="10241" width="5.85546875" style="40" customWidth="1"/>
-    <col min="10242" max="10242" width="62.42578125" style="40" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" style="40" customWidth="1"/>
-    <col min="10244" max="10244" width="17.28515625" style="40" customWidth="1"/>
-    <col min="10245" max="10245" width="20.7109375" style="40" customWidth="1"/>
-    <col min="10246" max="10246" width="33.85546875" style="40" customWidth="1"/>
-    <col min="10247" max="10247" width="37.28515625" style="40" customWidth="1"/>
-    <col min="10248" max="10248" width="18.5703125" style="40" customWidth="1"/>
+    <col min="10241" max="10241" width="5.83203125" style="40" customWidth="1"/>
+    <col min="10242" max="10242" width="62.4140625" style="40" customWidth="1"/>
+    <col min="10243" max="10243" width="14.83203125" style="40" customWidth="1"/>
+    <col min="10244" max="10244" width="17.25" style="40" customWidth="1"/>
+    <col min="10245" max="10245" width="20.75" style="40" customWidth="1"/>
+    <col min="10246" max="10246" width="33.83203125" style="40" customWidth="1"/>
+    <col min="10247" max="10247" width="37.25" style="40" customWidth="1"/>
+    <col min="10248" max="10248" width="18.58203125" style="40" customWidth="1"/>
     <col min="10249" max="10496" width="9" style="40"/>
-    <col min="10497" max="10497" width="5.85546875" style="40" customWidth="1"/>
-    <col min="10498" max="10498" width="62.42578125" style="40" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" style="40" customWidth="1"/>
-    <col min="10500" max="10500" width="17.28515625" style="40" customWidth="1"/>
-    <col min="10501" max="10501" width="20.7109375" style="40" customWidth="1"/>
-    <col min="10502" max="10502" width="33.85546875" style="40" customWidth="1"/>
-    <col min="10503" max="10503" width="37.28515625" style="40" customWidth="1"/>
-    <col min="10504" max="10504" width="18.5703125" style="40" customWidth="1"/>
+    <col min="10497" max="10497" width="5.83203125" style="40" customWidth="1"/>
+    <col min="10498" max="10498" width="62.4140625" style="40" customWidth="1"/>
+    <col min="10499" max="10499" width="14.83203125" style="40" customWidth="1"/>
+    <col min="10500" max="10500" width="17.25" style="40" customWidth="1"/>
+    <col min="10501" max="10501" width="20.75" style="40" customWidth="1"/>
+    <col min="10502" max="10502" width="33.83203125" style="40" customWidth="1"/>
+    <col min="10503" max="10503" width="37.25" style="40" customWidth="1"/>
+    <col min="10504" max="10504" width="18.58203125" style="40" customWidth="1"/>
     <col min="10505" max="10752" width="9" style="40"/>
-    <col min="10753" max="10753" width="5.85546875" style="40" customWidth="1"/>
-    <col min="10754" max="10754" width="62.42578125" style="40" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" style="40" customWidth="1"/>
-    <col min="10756" max="10756" width="17.28515625" style="40" customWidth="1"/>
-    <col min="10757" max="10757" width="20.7109375" style="40" customWidth="1"/>
-    <col min="10758" max="10758" width="33.85546875" style="40" customWidth="1"/>
-    <col min="10759" max="10759" width="37.28515625" style="40" customWidth="1"/>
-    <col min="10760" max="10760" width="18.5703125" style="40" customWidth="1"/>
+    <col min="10753" max="10753" width="5.83203125" style="40" customWidth="1"/>
+    <col min="10754" max="10754" width="62.4140625" style="40" customWidth="1"/>
+    <col min="10755" max="10755" width="14.83203125" style="40" customWidth="1"/>
+    <col min="10756" max="10756" width="17.25" style="40" customWidth="1"/>
+    <col min="10757" max="10757" width="20.75" style="40" customWidth="1"/>
+    <col min="10758" max="10758" width="33.83203125" style="40" customWidth="1"/>
+    <col min="10759" max="10759" width="37.25" style="40" customWidth="1"/>
+    <col min="10760" max="10760" width="18.58203125" style="40" customWidth="1"/>
     <col min="10761" max="11008" width="9" style="40"/>
-    <col min="11009" max="11009" width="5.85546875" style="40" customWidth="1"/>
-    <col min="11010" max="11010" width="62.42578125" style="40" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" style="40" customWidth="1"/>
-    <col min="11012" max="11012" width="17.28515625" style="40" customWidth="1"/>
-    <col min="11013" max="11013" width="20.7109375" style="40" customWidth="1"/>
-    <col min="11014" max="11014" width="33.85546875" style="40" customWidth="1"/>
-    <col min="11015" max="11015" width="37.28515625" style="40" customWidth="1"/>
-    <col min="11016" max="11016" width="18.5703125" style="40" customWidth="1"/>
+    <col min="11009" max="11009" width="5.83203125" style="40" customWidth="1"/>
+    <col min="11010" max="11010" width="62.4140625" style="40" customWidth="1"/>
+    <col min="11011" max="11011" width="14.83203125" style="40" customWidth="1"/>
+    <col min="11012" max="11012" width="17.25" style="40" customWidth="1"/>
+    <col min="11013" max="11013" width="20.75" style="40" customWidth="1"/>
+    <col min="11014" max="11014" width="33.83203125" style="40" customWidth="1"/>
+    <col min="11015" max="11015" width="37.25" style="40" customWidth="1"/>
+    <col min="11016" max="11016" width="18.58203125" style="40" customWidth="1"/>
     <col min="11017" max="11264" width="9" style="40"/>
-    <col min="11265" max="11265" width="5.85546875" style="40" customWidth="1"/>
-    <col min="11266" max="11266" width="62.42578125" style="40" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" style="40" customWidth="1"/>
-    <col min="11268" max="11268" width="17.28515625" style="40" customWidth="1"/>
-    <col min="11269" max="11269" width="20.7109375" style="40" customWidth="1"/>
-    <col min="11270" max="11270" width="33.85546875" style="40" customWidth="1"/>
-    <col min="11271" max="11271" width="37.28515625" style="40" customWidth="1"/>
-    <col min="11272" max="11272" width="18.5703125" style="40" customWidth="1"/>
+    <col min="11265" max="11265" width="5.83203125" style="40" customWidth="1"/>
+    <col min="11266" max="11266" width="62.4140625" style="40" customWidth="1"/>
+    <col min="11267" max="11267" width="14.83203125" style="40" customWidth="1"/>
+    <col min="11268" max="11268" width="17.25" style="40" customWidth="1"/>
+    <col min="11269" max="11269" width="20.75" style="40" customWidth="1"/>
+    <col min="11270" max="11270" width="33.83203125" style="40" customWidth="1"/>
+    <col min="11271" max="11271" width="37.25" style="40" customWidth="1"/>
+    <col min="11272" max="11272" width="18.58203125" style="40" customWidth="1"/>
     <col min="11273" max="11520" width="9" style="40"/>
-    <col min="11521" max="11521" width="5.85546875" style="40" customWidth="1"/>
-    <col min="11522" max="11522" width="62.42578125" style="40" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" style="40" customWidth="1"/>
-    <col min="11524" max="11524" width="17.28515625" style="40" customWidth="1"/>
-    <col min="11525" max="11525" width="20.7109375" style="40" customWidth="1"/>
-    <col min="11526" max="11526" width="33.85546875" style="40" customWidth="1"/>
-    <col min="11527" max="11527" width="37.28515625" style="40" customWidth="1"/>
-    <col min="11528" max="11528" width="18.5703125" style="40" customWidth="1"/>
+    <col min="11521" max="11521" width="5.83203125" style="40" customWidth="1"/>
+    <col min="11522" max="11522" width="62.4140625" style="40" customWidth="1"/>
+    <col min="11523" max="11523" width="14.83203125" style="40" customWidth="1"/>
+    <col min="11524" max="11524" width="17.25" style="40" customWidth="1"/>
+    <col min="11525" max="11525" width="20.75" style="40" customWidth="1"/>
+    <col min="11526" max="11526" width="33.83203125" style="40" customWidth="1"/>
+    <col min="11527" max="11527" width="37.25" style="40" customWidth="1"/>
+    <col min="11528" max="11528" width="18.58203125" style="40" customWidth="1"/>
     <col min="11529" max="11776" width="9" style="40"/>
-    <col min="11777" max="11777" width="5.85546875" style="40" customWidth="1"/>
-    <col min="11778" max="11778" width="62.42578125" style="40" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" style="40" customWidth="1"/>
-    <col min="11780" max="11780" width="17.28515625" style="40" customWidth="1"/>
-    <col min="11781" max="11781" width="20.7109375" style="40" customWidth="1"/>
-    <col min="11782" max="11782" width="33.85546875" style="40" customWidth="1"/>
-    <col min="11783" max="11783" width="37.28515625" style="40" customWidth="1"/>
-    <col min="11784" max="11784" width="18.5703125" style="40" customWidth="1"/>
+    <col min="11777" max="11777" width="5.83203125" style="40" customWidth="1"/>
+    <col min="11778" max="11778" width="62.4140625" style="40" customWidth="1"/>
+    <col min="11779" max="11779" width="14.83203125" style="40" customWidth="1"/>
+    <col min="11780" max="11780" width="17.25" style="40" customWidth="1"/>
+    <col min="11781" max="11781" width="20.75" style="40" customWidth="1"/>
+    <col min="11782" max="11782" width="33.83203125" style="40" customWidth="1"/>
+    <col min="11783" max="11783" width="37.25" style="40" customWidth="1"/>
+    <col min="11784" max="11784" width="18.58203125" style="40" customWidth="1"/>
     <col min="11785" max="12032" width="9" style="40"/>
-    <col min="12033" max="12033" width="5.85546875" style="40" customWidth="1"/>
-    <col min="12034" max="12034" width="62.42578125" style="40" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" style="40" customWidth="1"/>
-    <col min="12036" max="12036" width="17.28515625" style="40" customWidth="1"/>
-    <col min="12037" max="12037" width="20.7109375" style="40" customWidth="1"/>
-    <col min="12038" max="12038" width="33.85546875" style="40" customWidth="1"/>
-    <col min="12039" max="12039" width="37.28515625" style="40" customWidth="1"/>
-    <col min="12040" max="12040" width="18.5703125" style="40" customWidth="1"/>
+    <col min="12033" max="12033" width="5.83203125" style="40" customWidth="1"/>
+    <col min="12034" max="12034" width="62.4140625" style="40" customWidth="1"/>
+    <col min="12035" max="12035" width="14.83203125" style="40" customWidth="1"/>
+    <col min="12036" max="12036" width="17.25" style="40" customWidth="1"/>
+    <col min="12037" max="12037" width="20.75" style="40" customWidth="1"/>
+    <col min="12038" max="12038" width="33.83203125" style="40" customWidth="1"/>
+    <col min="12039" max="12039" width="37.25" style="40" customWidth="1"/>
+    <col min="12040" max="12040" width="18.58203125" style="40" customWidth="1"/>
     <col min="12041" max="12288" width="9" style="40"/>
-    <col min="12289" max="12289" width="5.85546875" style="40" customWidth="1"/>
-    <col min="12290" max="12290" width="62.42578125" style="40" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" style="40" customWidth="1"/>
-    <col min="12292" max="12292" width="17.28515625" style="40" customWidth="1"/>
-    <col min="12293" max="12293" width="20.7109375" style="40" customWidth="1"/>
-    <col min="12294" max="12294" width="33.85546875" style="40" customWidth="1"/>
-    <col min="12295" max="12295" width="37.28515625" style="40" customWidth="1"/>
-    <col min="12296" max="12296" width="18.5703125" style="40" customWidth="1"/>
+    <col min="12289" max="12289" width="5.83203125" style="40" customWidth="1"/>
+    <col min="12290" max="12290" width="62.4140625" style="40" customWidth="1"/>
+    <col min="12291" max="12291" width="14.83203125" style="40" customWidth="1"/>
+    <col min="12292" max="12292" width="17.25" style="40" customWidth="1"/>
+    <col min="12293" max="12293" width="20.75" style="40" customWidth="1"/>
+    <col min="12294" max="12294" width="33.83203125" style="40" customWidth="1"/>
+    <col min="12295" max="12295" width="37.25" style="40" customWidth="1"/>
+    <col min="12296" max="12296" width="18.58203125" style="40" customWidth="1"/>
     <col min="12297" max="12544" width="9" style="40"/>
-    <col min="12545" max="12545" width="5.85546875" style="40" customWidth="1"/>
-    <col min="12546" max="12546" width="62.42578125" style="40" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" style="40" customWidth="1"/>
-    <col min="12548" max="12548" width="17.28515625" style="40" customWidth="1"/>
-    <col min="12549" max="12549" width="20.7109375" style="40" customWidth="1"/>
-    <col min="12550" max="12550" width="33.85546875" style="40" customWidth="1"/>
-    <col min="12551" max="12551" width="37.28515625" style="40" customWidth="1"/>
-    <col min="12552" max="12552" width="18.5703125" style="40" customWidth="1"/>
+    <col min="12545" max="12545" width="5.83203125" style="40" customWidth="1"/>
+    <col min="12546" max="12546" width="62.4140625" style="40" customWidth="1"/>
+    <col min="12547" max="12547" width="14.83203125" style="40" customWidth="1"/>
+    <col min="12548" max="12548" width="17.25" style="40" customWidth="1"/>
+    <col min="12549" max="12549" width="20.75" style="40" customWidth="1"/>
+    <col min="12550" max="12550" width="33.83203125" style="40" customWidth="1"/>
+    <col min="12551" max="12551" width="37.25" style="40" customWidth="1"/>
+    <col min="12552" max="12552" width="18.58203125" style="40" customWidth="1"/>
     <col min="12553" max="12800" width="9" style="40"/>
-    <col min="12801" max="12801" width="5.85546875" style="40" customWidth="1"/>
-    <col min="12802" max="12802" width="62.42578125" style="40" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" style="40" customWidth="1"/>
-    <col min="12804" max="12804" width="17.28515625" style="40" customWidth="1"/>
-    <col min="12805" max="12805" width="20.7109375" style="40" customWidth="1"/>
-    <col min="12806" max="12806" width="33.85546875" style="40" customWidth="1"/>
-    <col min="12807" max="12807" width="37.28515625" style="40" customWidth="1"/>
-    <col min="12808" max="12808" width="18.5703125" style="40" customWidth="1"/>
+    <col min="12801" max="12801" width="5.83203125" style="40" customWidth="1"/>
+    <col min="12802" max="12802" width="62.4140625" style="40" customWidth="1"/>
+    <col min="12803" max="12803" width="14.83203125" style="40" customWidth="1"/>
+    <col min="12804" max="12804" width="17.25" style="40" customWidth="1"/>
+    <col min="12805" max="12805" width="20.75" style="40" customWidth="1"/>
+    <col min="12806" max="12806" width="33.83203125" style="40" customWidth="1"/>
+    <col min="12807" max="12807" width="37.25" style="40" customWidth="1"/>
+    <col min="12808" max="12808" width="18.58203125" style="40" customWidth="1"/>
     <col min="12809" max="13056" width="9" style="40"/>
-    <col min="13057" max="13057" width="5.85546875" style="40" customWidth="1"/>
-    <col min="13058" max="13058" width="62.42578125" style="40" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" style="40" customWidth="1"/>
-    <col min="13060" max="13060" width="17.28515625" style="40" customWidth="1"/>
-    <col min="13061" max="13061" width="20.7109375" style="40" customWidth="1"/>
-    <col min="13062" max="13062" width="33.85546875" style="40" customWidth="1"/>
-    <col min="13063" max="13063" width="37.28515625" style="40" customWidth="1"/>
-    <col min="13064" max="13064" width="18.5703125" style="40" customWidth="1"/>
+    <col min="13057" max="13057" width="5.83203125" style="40" customWidth="1"/>
+    <col min="13058" max="13058" width="62.4140625" style="40" customWidth="1"/>
+    <col min="13059" max="13059" width="14.83203125" style="40" customWidth="1"/>
+    <col min="13060" max="13060" width="17.25" style="40" customWidth="1"/>
+    <col min="13061" max="13061" width="20.75" style="40" customWidth="1"/>
+    <col min="13062" max="13062" width="33.83203125" style="40" customWidth="1"/>
+    <col min="13063" max="13063" width="37.25" style="40" customWidth="1"/>
+    <col min="13064" max="13064" width="18.58203125" style="40" customWidth="1"/>
     <col min="13065" max="13312" width="9" style="40"/>
-    <col min="13313" max="13313" width="5.85546875" style="40" customWidth="1"/>
-    <col min="13314" max="13314" width="62.42578125" style="40" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" style="40" customWidth="1"/>
-    <col min="13316" max="13316" width="17.28515625" style="40" customWidth="1"/>
-    <col min="13317" max="13317" width="20.7109375" style="40" customWidth="1"/>
-    <col min="13318" max="13318" width="33.85546875" style="40" customWidth="1"/>
-    <col min="13319" max="13319" width="37.28515625" style="40" customWidth="1"/>
-    <col min="13320" max="13320" width="18.5703125" style="40" customWidth="1"/>
+    <col min="13313" max="13313" width="5.83203125" style="40" customWidth="1"/>
+    <col min="13314" max="13314" width="62.4140625" style="40" customWidth="1"/>
+    <col min="13315" max="13315" width="14.83203125" style="40" customWidth="1"/>
+    <col min="13316" max="13316" width="17.25" style="40" customWidth="1"/>
+    <col min="13317" max="13317" width="20.75" style="40" customWidth="1"/>
+    <col min="13318" max="13318" width="33.83203125" style="40" customWidth="1"/>
+    <col min="13319" max="13319" width="37.25" style="40" customWidth="1"/>
+    <col min="13320" max="13320" width="18.58203125" style="40" customWidth="1"/>
     <col min="13321" max="13568" width="9" style="40"/>
-    <col min="13569" max="13569" width="5.85546875" style="40" customWidth="1"/>
-    <col min="13570" max="13570" width="62.42578125" style="40" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" style="40" customWidth="1"/>
-    <col min="13572" max="13572" width="17.28515625" style="40" customWidth="1"/>
-    <col min="13573" max="13573" width="20.7109375" style="40" customWidth="1"/>
-    <col min="13574" max="13574" width="33.85546875" style="40" customWidth="1"/>
-    <col min="13575" max="13575" width="37.28515625" style="40" customWidth="1"/>
-    <col min="13576" max="13576" width="18.5703125" style="40" customWidth="1"/>
+    <col min="13569" max="13569" width="5.83203125" style="40" customWidth="1"/>
+    <col min="13570" max="13570" width="62.4140625" style="40" customWidth="1"/>
+    <col min="13571" max="13571" width="14.83203125" style="40" customWidth="1"/>
+    <col min="13572" max="13572" width="17.25" style="40" customWidth="1"/>
+    <col min="13573" max="13573" width="20.75" style="40" customWidth="1"/>
+    <col min="13574" max="13574" width="33.83203125" style="40" customWidth="1"/>
+    <col min="13575" max="13575" width="37.25" style="40" customWidth="1"/>
+    <col min="13576" max="13576" width="18.58203125" style="40" customWidth="1"/>
     <col min="13577" max="13824" width="9" style="40"/>
-    <col min="13825" max="13825" width="5.85546875" style="40" customWidth="1"/>
-    <col min="13826" max="13826" width="62.42578125" style="40" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" style="40" customWidth="1"/>
-    <col min="13828" max="13828" width="17.28515625" style="40" customWidth="1"/>
-    <col min="13829" max="13829" width="20.7109375" style="40" customWidth="1"/>
-    <col min="13830" max="13830" width="33.85546875" style="40" customWidth="1"/>
-    <col min="13831" max="13831" width="37.28515625" style="40" customWidth="1"/>
-    <col min="13832" max="13832" width="18.5703125" style="40" customWidth="1"/>
+    <col min="13825" max="13825" width="5.83203125" style="40" customWidth="1"/>
+    <col min="13826" max="13826" width="62.4140625" style="40" customWidth="1"/>
+    <col min="13827" max="13827" width="14.83203125" style="40" customWidth="1"/>
+    <col min="13828" max="13828" width="17.25" style="40" customWidth="1"/>
+    <col min="13829" max="13829" width="20.75" style="40" customWidth="1"/>
+    <col min="13830" max="13830" width="33.83203125" style="40" customWidth="1"/>
+    <col min="13831" max="13831" width="37.25" style="40" customWidth="1"/>
+    <col min="13832" max="13832" width="18.58203125" style="40" customWidth="1"/>
     <col min="13833" max="14080" width="9" style="40"/>
-    <col min="14081" max="14081" width="5.85546875" style="40" customWidth="1"/>
-    <col min="14082" max="14082" width="62.42578125" style="40" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" style="40" customWidth="1"/>
-    <col min="14084" max="14084" width="17.28515625" style="40" customWidth="1"/>
-    <col min="14085" max="14085" width="20.7109375" style="40" customWidth="1"/>
-    <col min="14086" max="14086" width="33.85546875" style="40" customWidth="1"/>
-    <col min="14087" max="14087" width="37.28515625" style="40" customWidth="1"/>
-    <col min="14088" max="14088" width="18.5703125" style="40" customWidth="1"/>
+    <col min="14081" max="14081" width="5.83203125" style="40" customWidth="1"/>
+    <col min="14082" max="14082" width="62.4140625" style="40" customWidth="1"/>
+    <col min="14083" max="14083" width="14.83203125" style="40" customWidth="1"/>
+    <col min="14084" max="14084" width="17.25" style="40" customWidth="1"/>
+    <col min="14085" max="14085" width="20.75" style="40" customWidth="1"/>
+    <col min="14086" max="14086" width="33.83203125" style="40" customWidth="1"/>
+    <col min="14087" max="14087" width="37.25" style="40" customWidth="1"/>
+    <col min="14088" max="14088" width="18.58203125" style="40" customWidth="1"/>
     <col min="14089" max="14336" width="9" style="40"/>
-    <col min="14337" max="14337" width="5.85546875" style="40" customWidth="1"/>
-    <col min="14338" max="14338" width="62.42578125" style="40" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" style="40" customWidth="1"/>
-    <col min="14340" max="14340" width="17.28515625" style="40" customWidth="1"/>
-    <col min="14341" max="14341" width="20.7109375" style="40" customWidth="1"/>
-    <col min="14342" max="14342" width="33.85546875" style="40" customWidth="1"/>
-    <col min="14343" max="14343" width="37.28515625" style="40" customWidth="1"/>
-    <col min="14344" max="14344" width="18.5703125" style="40" customWidth="1"/>
+    <col min="14337" max="14337" width="5.83203125" style="40" customWidth="1"/>
+    <col min="14338" max="14338" width="62.4140625" style="40" customWidth="1"/>
+    <col min="14339" max="14339" width="14.83203125" style="40" customWidth="1"/>
+    <col min="14340" max="14340" width="17.25" style="40" customWidth="1"/>
+    <col min="14341" max="14341" width="20.75" style="40" customWidth="1"/>
+    <col min="14342" max="14342" width="33.83203125" style="40" customWidth="1"/>
+    <col min="14343" max="14343" width="37.25" style="40" customWidth="1"/>
+    <col min="14344" max="14344" width="18.58203125" style="40" customWidth="1"/>
     <col min="14345" max="14592" width="9" style="40"/>
-    <col min="14593" max="14593" width="5.85546875" style="40" customWidth="1"/>
-    <col min="14594" max="14594" width="62.42578125" style="40" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" style="40" customWidth="1"/>
-    <col min="14596" max="14596" width="17.28515625" style="40" customWidth="1"/>
-    <col min="14597" max="14597" width="20.7109375" style="40" customWidth="1"/>
-    <col min="14598" max="14598" width="33.85546875" style="40" customWidth="1"/>
-    <col min="14599" max="14599" width="37.28515625" style="40" customWidth="1"/>
-    <col min="14600" max="14600" width="18.5703125" style="40" customWidth="1"/>
+    <col min="14593" max="14593" width="5.83203125" style="40" customWidth="1"/>
+    <col min="14594" max="14594" width="62.4140625" style="40" customWidth="1"/>
+    <col min="14595" max="14595" width="14.83203125" style="40" customWidth="1"/>
+    <col min="14596" max="14596" width="17.25" style="40" customWidth="1"/>
+    <col min="14597" max="14597" width="20.75" style="40" customWidth="1"/>
+    <col min="14598" max="14598" width="33.83203125" style="40" customWidth="1"/>
+    <col min="14599" max="14599" width="37.25" style="40" customWidth="1"/>
+    <col min="14600" max="14600" width="18.58203125" style="40" customWidth="1"/>
     <col min="14601" max="14848" width="9" style="40"/>
-    <col min="14849" max="14849" width="5.85546875" style="40" customWidth="1"/>
-    <col min="14850" max="14850" width="62.42578125" style="40" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" style="40" customWidth="1"/>
-    <col min="14852" max="14852" width="17.28515625" style="40" customWidth="1"/>
-    <col min="14853" max="14853" width="20.7109375" style="40" customWidth="1"/>
-    <col min="14854" max="14854" width="33.85546875" style="40" customWidth="1"/>
-    <col min="14855" max="14855" width="37.28515625" style="40" customWidth="1"/>
-    <col min="14856" max="14856" width="18.5703125" style="40" customWidth="1"/>
+    <col min="14849" max="14849" width="5.83203125" style="40" customWidth="1"/>
+    <col min="14850" max="14850" width="62.4140625" style="40" customWidth="1"/>
+    <col min="14851" max="14851" width="14.83203125" style="40" customWidth="1"/>
+    <col min="14852" max="14852" width="17.25" style="40" customWidth="1"/>
+    <col min="14853" max="14853" width="20.75" style="40" customWidth="1"/>
+    <col min="14854" max="14854" width="33.83203125" style="40" customWidth="1"/>
+    <col min="14855" max="14855" width="37.25" style="40" customWidth="1"/>
+    <col min="14856" max="14856" width="18.58203125" style="40" customWidth="1"/>
     <col min="14857" max="15104" width="9" style="40"/>
-    <col min="15105" max="15105" width="5.85546875" style="40" customWidth="1"/>
-    <col min="15106" max="15106" width="62.42578125" style="40" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" style="40" customWidth="1"/>
-    <col min="15108" max="15108" width="17.28515625" style="40" customWidth="1"/>
-    <col min="15109" max="15109" width="20.7109375" style="40" customWidth="1"/>
-    <col min="15110" max="15110" width="33.85546875" style="40" customWidth="1"/>
-    <col min="15111" max="15111" width="37.28515625" style="40" customWidth="1"/>
-    <col min="15112" max="15112" width="18.5703125" style="40" customWidth="1"/>
+    <col min="15105" max="15105" width="5.83203125" style="40" customWidth="1"/>
+    <col min="15106" max="15106" width="62.4140625" style="40" customWidth="1"/>
+    <col min="15107" max="15107" width="14.83203125" style="40" customWidth="1"/>
+    <col min="15108" max="15108" width="17.25" style="40" customWidth="1"/>
+    <col min="15109" max="15109" width="20.75" style="40" customWidth="1"/>
+    <col min="15110" max="15110" width="33.83203125" style="40" customWidth="1"/>
+    <col min="15111" max="15111" width="37.25" style="40" customWidth="1"/>
+    <col min="15112" max="15112" width="18.58203125" style="40" customWidth="1"/>
     <col min="15113" max="15360" width="9" style="40"/>
-    <col min="15361" max="15361" width="5.85546875" style="40" customWidth="1"/>
-    <col min="15362" max="15362" width="62.42578125" style="40" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" style="40" customWidth="1"/>
-    <col min="15364" max="15364" width="17.28515625" style="40" customWidth="1"/>
-    <col min="15365" max="15365" width="20.7109375" style="40" customWidth="1"/>
-    <col min="15366" max="15366" width="33.85546875" style="40" customWidth="1"/>
-    <col min="15367" max="15367" width="37.28515625" style="40" customWidth="1"/>
-    <col min="15368" max="15368" width="18.5703125" style="40" customWidth="1"/>
+    <col min="15361" max="15361" width="5.83203125" style="40" customWidth="1"/>
+    <col min="15362" max="15362" width="62.4140625" style="40" customWidth="1"/>
+    <col min="15363" max="15363" width="14.83203125" style="40" customWidth="1"/>
+    <col min="15364" max="15364" width="17.25" style="40" customWidth="1"/>
+    <col min="15365" max="15365" width="20.75" style="40" customWidth="1"/>
+    <col min="15366" max="15366" width="33.83203125" style="40" customWidth="1"/>
+    <col min="15367" max="15367" width="37.25" style="40" customWidth="1"/>
+    <col min="15368" max="15368" width="18.58203125" style="40" customWidth="1"/>
     <col min="15369" max="15616" width="9" style="40"/>
-    <col min="15617" max="15617" width="5.85546875" style="40" customWidth="1"/>
-    <col min="15618" max="15618" width="62.42578125" style="40" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" style="40" customWidth="1"/>
-    <col min="15620" max="15620" width="17.28515625" style="40" customWidth="1"/>
-    <col min="15621" max="15621" width="20.7109375" style="40" customWidth="1"/>
-    <col min="15622" max="15622" width="33.85546875" style="40" customWidth="1"/>
-    <col min="15623" max="15623" width="37.28515625" style="40" customWidth="1"/>
-    <col min="15624" max="15624" width="18.5703125" style="40" customWidth="1"/>
+    <col min="15617" max="15617" width="5.83203125" style="40" customWidth="1"/>
+    <col min="15618" max="15618" width="62.4140625" style="40" customWidth="1"/>
+    <col min="15619" max="15619" width="14.83203125" style="40" customWidth="1"/>
+    <col min="15620" max="15620" width="17.25" style="40" customWidth="1"/>
+    <col min="15621" max="15621" width="20.75" style="40" customWidth="1"/>
+    <col min="15622" max="15622" width="33.83203125" style="40" customWidth="1"/>
+    <col min="15623" max="15623" width="37.25" style="40" customWidth="1"/>
+    <col min="15624" max="15624" width="18.58203125" style="40" customWidth="1"/>
     <col min="15625" max="15872" width="9" style="40"/>
-    <col min="15873" max="15873" width="5.85546875" style="40" customWidth="1"/>
-    <col min="15874" max="15874" width="62.42578125" style="40" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" style="40" customWidth="1"/>
-    <col min="15876" max="15876" width="17.28515625" style="40" customWidth="1"/>
-    <col min="15877" max="15877" width="20.7109375" style="40" customWidth="1"/>
-    <col min="15878" max="15878" width="33.85546875" style="40" customWidth="1"/>
-    <col min="15879" max="15879" width="37.28515625" style="40" customWidth="1"/>
-    <col min="15880" max="15880" width="18.5703125" style="40" customWidth="1"/>
+    <col min="15873" max="15873" width="5.83203125" style="40" customWidth="1"/>
+    <col min="15874" max="15874" width="62.4140625" style="40" customWidth="1"/>
+    <col min="15875" max="15875" width="14.83203125" style="40" customWidth="1"/>
+    <col min="15876" max="15876" width="17.25" style="40" customWidth="1"/>
+    <col min="15877" max="15877" width="20.75" style="40" customWidth="1"/>
+    <col min="15878" max="15878" width="33.83203125" style="40" customWidth="1"/>
+    <col min="15879" max="15879" width="37.25" style="40" customWidth="1"/>
+    <col min="15880" max="15880" width="18.58203125" style="40" customWidth="1"/>
     <col min="15881" max="16128" width="9" style="40"/>
-    <col min="16129" max="16129" width="5.85546875" style="40" customWidth="1"/>
-    <col min="16130" max="16130" width="62.42578125" style="40" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" style="40" customWidth="1"/>
-    <col min="16132" max="16132" width="17.28515625" style="40" customWidth="1"/>
-    <col min="16133" max="16133" width="20.7109375" style="40" customWidth="1"/>
-    <col min="16134" max="16134" width="33.85546875" style="40" customWidth="1"/>
-    <col min="16135" max="16135" width="37.28515625" style="40" customWidth="1"/>
-    <col min="16136" max="16136" width="18.5703125" style="40" customWidth="1"/>
+    <col min="16129" max="16129" width="5.83203125" style="40" customWidth="1"/>
+    <col min="16130" max="16130" width="62.4140625" style="40" customWidth="1"/>
+    <col min="16131" max="16131" width="14.83203125" style="40" customWidth="1"/>
+    <col min="16132" max="16132" width="17.25" style="40" customWidth="1"/>
+    <col min="16133" max="16133" width="20.75" style="40" customWidth="1"/>
+    <col min="16134" max="16134" width="33.83203125" style="40" customWidth="1"/>
+    <col min="16135" max="16135" width="37.25" style="40" customWidth="1"/>
+    <col min="16136" max="16136" width="18.58203125" style="40" customWidth="1"/>
     <col min="16137" max="16384" width="9" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="17.5">
       <c r="A1" s="420" t="s">
         <v>0</v>
       </c>
@@ -7174,7 +7174,7 @@
       <c r="G1" s="421"/>
       <c r="H1" s="421"/>
     </row>
-    <row r="2" spans="1:10" ht="16.5" thickBot="1">
+    <row r="2" spans="1:10" ht="15.5" thickBot="1">
       <c r="A2" s="422" t="s">
         <v>18</v>
       </c>
@@ -7188,7 +7188,7 @@
       <c r="G2" s="422"/>
       <c r="H2" s="422"/>
     </row>
-    <row r="3" spans="1:10" ht="16.5" thickTop="1">
+    <row r="3" spans="1:10" ht="16" thickTop="1">
       <c r="A3" s="219"/>
       <c r="B3" s="350"/>
       <c r="C3" s="219"/>
@@ -7198,7 +7198,7 @@
       <c r="G3" s="219"/>
       <c r="H3" s="221"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75">
+    <row r="4" spans="1:10" ht="15.5">
       <c r="A4" s="219"/>
       <c r="B4" s="351"/>
       <c r="C4" s="423"/>
@@ -7210,7 +7210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="20.25">
+    <row r="5" spans="1:10" ht="20">
       <c r="A5" s="425" t="s">
         <v>22</v>
       </c>
@@ -7222,7 +7222,7 @@
       <c r="G5" s="425"/>
       <c r="H5" s="426"/>
     </row>
-    <row r="6" spans="1:10" s="34" customFormat="1" ht="15.75">
+    <row r="6" spans="1:10" s="34" customFormat="1" ht="15.5">
       <c r="A6" s="433" t="s">
         <v>2</v>
       </c>
@@ -7246,7 +7246,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="34" customFormat="1" ht="15.75">
+    <row r="7" spans="1:10" s="34" customFormat="1" ht="15.5">
       <c r="A7" s="433"/>
       <c r="B7" s="440"/>
       <c r="C7" s="433"/>
@@ -7274,7 +7274,7 @@
       <c r="G8" s="37"/>
       <c r="H8" s="44"/>
     </row>
-    <row r="9" spans="1:10" s="52" customFormat="1" ht="47.25">
+    <row r="9" spans="1:10" s="52" customFormat="1" ht="30">
       <c r="A9" s="104">
         <v>1</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="52" customFormat="1" ht="31.5">
+    <row r="14" spans="1:10" s="52" customFormat="1" ht="15.5">
       <c r="A14" s="104">
         <v>6</v>
       </c>
@@ -7500,7 +7500,7 @@
       <c r="G18" s="193"/>
       <c r="H18" s="198"/>
     </row>
-    <row r="19" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="19" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A19" s="44" t="s">
         <v>428</v>
       </c>
@@ -7520,7 +7520,7 @@
       <c r="G19" s="193"/>
       <c r="H19" s="198"/>
     </row>
-    <row r="20" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="20" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A20" s="44" t="s">
         <v>616</v>
       </c>
@@ -7540,7 +7540,7 @@
       <c r="G20" s="193"/>
       <c r="H20" s="198"/>
     </row>
-    <row r="21" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="21" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A21" s="44" t="s">
         <v>617</v>
       </c>
@@ -7560,7 +7560,7 @@
       <c r="G21" s="193"/>
       <c r="H21" s="198"/>
     </row>
-    <row r="22" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="22" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A22" s="44" t="s">
         <v>618</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="G22" s="193"/>
       <c r="H22" s="198"/>
     </row>
-    <row r="23" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="23" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A23" s="44" t="s">
         <v>619</v>
       </c>
@@ -7596,7 +7596,7 @@
       <c r="G24" s="193"/>
       <c r="H24" s="198"/>
     </row>
-    <row r="25" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="25" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A25" s="44" t="s">
         <v>621</v>
       </c>
@@ -7608,7 +7608,7 @@
       <c r="G25" s="193"/>
       <c r="H25" s="198"/>
     </row>
-    <row r="26" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="26" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A26" s="44" t="s">
         <v>622</v>
       </c>
@@ -7620,7 +7620,7 @@
       <c r="G26" s="193"/>
       <c r="H26" s="198"/>
     </row>
-    <row r="27" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="27" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A27" s="44" t="s">
         <v>623</v>
       </c>
@@ -7644,7 +7644,7 @@
       <c r="G28" s="311"/>
       <c r="H28" s="198"/>
     </row>
-    <row r="29" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="29" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A29" s="44" t="s">
         <v>625</v>
       </c>
@@ -7680,7 +7680,7 @@
       <c r="G31" s="193"/>
       <c r="H31" s="198"/>
     </row>
-    <row r="32" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="32" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A32" s="44" t="s">
         <v>628</v>
       </c>
@@ -7692,7 +7692,7 @@
       <c r="G32" s="193"/>
       <c r="H32" s="198"/>
     </row>
-    <row r="33" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="33" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A33" s="44" t="s">
         <v>629</v>
       </c>
@@ -7752,7 +7752,7 @@
       <c r="G37" s="193"/>
       <c r="H37" s="198"/>
     </row>
-    <row r="38" spans="1:8" ht="15.75">
+    <row r="38" spans="1:8" ht="15.5">
       <c r="A38" s="35" t="s">
         <v>13</v>
       </c>
@@ -7780,7 +7780,7 @@
       <c r="G39" s="196"/>
       <c r="H39" s="44"/>
     </row>
-    <row r="40" spans="1:8" ht="47.25">
+    <row r="40" spans="1:8" ht="46.5">
       <c r="A40" s="44" t="s">
         <v>552</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75">
+    <row r="45" spans="1:8" ht="15.5">
       <c r="A45" s="41">
         <v>2</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="49" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A49" s="104">
         <v>5</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="52" customFormat="1" ht="94.5">
+    <row r="51" spans="1:8" s="52" customFormat="1" ht="93">
       <c r="A51" s="44" t="s">
         <v>349</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="52" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A52" s="36" t="s">
         <v>174</v>
       </c>
@@ -8102,7 +8102,7 @@
       <c r="G54" s="439"/>
       <c r="H54" s="439"/>
     </row>
-    <row r="55" spans="1:8" ht="15.75">
+    <row r="55" spans="1:8" ht="15.5">
       <c r="A55" s="113" t="s">
         <v>634</v>
       </c>
@@ -8150,7 +8150,7 @@
       <c r="G57" s="427"/>
       <c r="H57" s="432"/>
     </row>
-    <row r="58" spans="1:8" ht="31.5">
+    <row r="58" spans="1:8" ht="15.5">
       <c r="A58" s="35" t="s">
         <v>10</v>
       </c>
@@ -8186,7 +8186,7 @@
       <c r="G59" s="446"/>
       <c r="H59" s="198"/>
     </row>
-    <row r="60" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="60" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A60" s="44">
         <v>2</v>
       </c>
@@ -8208,7 +8208,7 @@
       <c r="G60" s="446"/>
       <c r="H60" s="198"/>
     </row>
-    <row r="61" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="61" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A61" s="44">
         <v>3</v>
       </c>
@@ -8230,7 +8230,7 @@
       <c r="G61" s="446"/>
       <c r="H61" s="198"/>
     </row>
-    <row r="62" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="62" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A62" s="44">
         <v>4</v>
       </c>
@@ -8252,7 +8252,7 @@
       <c r="G62" s="446"/>
       <c r="H62" s="198"/>
     </row>
-    <row r="63" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="63" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A63" s="44">
         <v>5</v>
       </c>
@@ -8274,7 +8274,7 @@
       <c r="G63" s="446"/>
       <c r="H63" s="198"/>
     </row>
-    <row r="64" spans="1:8" ht="15.75">
+    <row r="64" spans="1:8" ht="15.5">
       <c r="A64" s="35" t="s">
         <v>13</v>
       </c>
@@ -8366,7 +8366,7 @@
       <c r="G68" s="444"/>
       <c r="H68" s="44"/>
     </row>
-    <row r="69" spans="1:8" ht="15.75">
+    <row r="69" spans="1:8" ht="15.5">
       <c r="A69" s="104">
         <v>2</v>
       </c>
@@ -8402,7 +8402,7 @@
       <c r="G70" s="446"/>
       <c r="H70" s="216"/>
     </row>
-    <row r="71" spans="1:8" ht="31.5">
+    <row r="71" spans="1:8" ht="30">
       <c r="A71" s="104">
         <v>3</v>
       </c>
@@ -8470,7 +8470,7 @@
       <c r="G73" s="446"/>
       <c r="H73" s="44"/>
     </row>
-    <row r="74" spans="1:8" ht="15.75">
+    <row r="74" spans="1:8" ht="15.5">
       <c r="A74" s="132"/>
       <c r="B74" s="359"/>
       <c r="C74" s="134"/>
@@ -8492,7 +8492,7 @@
       <c r="G75" s="425"/>
       <c r="H75" s="426"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75">
+    <row r="76" spans="1:8" ht="15">
       <c r="A76" s="447" t="s">
         <v>478</v>
       </c>
@@ -8504,7 +8504,7 @@
       <c r="G76" s="447"/>
       <c r="H76" s="447"/>
     </row>
-    <row r="77" spans="1:8" s="34" customFormat="1" ht="15.75">
+    <row r="77" spans="1:8" s="34" customFormat="1" ht="15.5">
       <c r="A77" s="433" t="s">
         <v>2</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="34" customFormat="1" ht="15.75">
+    <row r="78" spans="1:8" s="34" customFormat="1" ht="15.5">
       <c r="A78" s="433"/>
       <c r="B78" s="440"/>
       <c r="C78" s="433"/>
@@ -8556,7 +8556,7 @@
       <c r="G79" s="209"/>
       <c r="H79" s="211"/>
     </row>
-    <row r="80" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="80" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A80" s="41">
         <v>1</v>
       </c>
@@ -8608,7 +8608,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:8" s="52" customFormat="1" ht="47.25" hidden="1">
+    <row r="82" spans="1:8" s="52" customFormat="1" ht="46.5" hidden="1">
       <c r="A82" s="41">
         <v>3</v>
       </c>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H86" s="64"/>
     </row>
-    <row r="87" spans="1:8" s="52" customFormat="1" ht="47.25" hidden="1">
+    <row r="87" spans="1:8" s="52" customFormat="1" ht="46.5" hidden="1">
       <c r="A87" s="48" t="s">
         <v>349</v>
       </c>
@@ -8754,7 +8754,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="89" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A89" s="48" t="s">
         <v>431</v>
       </c>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="H89" s="50"/>
     </row>
-    <row r="90" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="90" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A90" s="48" t="s">
         <v>435</v>
       </c>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="H90" s="50"/>
     </row>
-    <row r="91" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="91" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A91" s="48" t="s">
         <v>436</v>
       </c>
@@ -8826,7 +8826,7 @@
       </c>
       <c r="H91" s="50"/>
     </row>
-    <row r="92" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="92" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A92" s="48" t="s">
         <v>437</v>
       </c>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="H92" s="50"/>
     </row>
-    <row r="93" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="93" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A93" s="48" t="s">
         <v>438</v>
       </c>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="H93" s="50"/>
     </row>
-    <row r="94" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="94" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A94" s="48" t="s">
         <v>444</v>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H96" s="50"/>
     </row>
-    <row r="97" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="97" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A97" s="48" t="s">
         <v>441</v>
       </c>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H97" s="44"/>
     </row>
-    <row r="98" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="98" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A98" s="48" t="s">
         <v>446</v>
       </c>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H98" s="50"/>
     </row>
-    <row r="99" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="99" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A99" s="48" t="s">
         <v>451</v>
       </c>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H99" s="50"/>
     </row>
-    <row r="100" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="100" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A100" s="48" t="s">
         <v>452</v>
       </c>
@@ -9034,7 +9034,7 @@
       </c>
       <c r="H100" s="50"/>
     </row>
-    <row r="101" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="101" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A101" s="48" t="s">
         <v>453</v>
       </c>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="H101" s="50"/>
     </row>
-    <row r="102" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="102" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A102" s="48" t="s">
         <v>454</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="105" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A105" s="48" t="s">
         <v>424</v>
       </c>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="H105" s="50"/>
     </row>
-    <row r="106" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="106" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A106" s="48" t="s">
         <v>426</v>
       </c>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="H106" s="50"/>
     </row>
-    <row r="107" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="107" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A107" s="48" t="s">
         <v>428</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="109" spans="1:8" s="241" customFormat="1" ht="63" hidden="1">
+    <row r="109" spans="1:8" s="241" customFormat="1" ht="62" hidden="1">
       <c r="A109" s="238" t="s">
         <v>433</v>
       </c>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="H109" s="244"/>
     </row>
-    <row r="110" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="110" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A110" s="44" t="s">
         <v>455</v>
       </c>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="H110" s="50"/>
     </row>
-    <row r="111" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="111" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A111" s="44" t="s">
         <v>455</v>
       </c>
@@ -9296,7 +9296,7 @@
       <c r="G112" s="209"/>
       <c r="H112" s="210"/>
     </row>
-    <row r="113" spans="1:8" s="241" customFormat="1" ht="126" hidden="1">
+    <row r="113" spans="1:8" s="241" customFormat="1" ht="124" hidden="1">
       <c r="A113" s="238">
         <v>1</v>
       </c>
@@ -9322,7 +9322,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="31.5" hidden="1">
+    <row r="114" spans="1:8" ht="31" hidden="1">
       <c r="A114" s="44">
         <v>2</v>
       </c>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="H114" s="50"/>
     </row>
-    <row r="115" spans="1:8" s="52" customFormat="1" ht="47.25" hidden="1">
+    <row r="115" spans="1:8" s="52" customFormat="1" ht="46.5" hidden="1">
       <c r="A115" s="44">
         <v>3</v>
       </c>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="H115" s="50"/>
     </row>
-    <row r="116" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="116" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A116" s="36" t="s">
         <v>174</v>
       </c>
@@ -9392,7 +9392,7 @@
       <c r="G117" s="448"/>
       <c r="H117" s="448"/>
     </row>
-    <row r="118" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="118" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A118" s="104">
         <v>2</v>
       </c>
@@ -9408,7 +9408,7 @@
       <c r="G118" s="442"/>
       <c r="H118" s="442"/>
     </row>
-    <row r="119" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="119" spans="1:8" s="52" customFormat="1" ht="15" hidden="1">
       <c r="A119" s="105"/>
       <c r="B119" s="351"/>
       <c r="C119" s="107"/>
@@ -9418,7 +9418,7 @@
       <c r="G119" s="107"/>
       <c r="H119" s="200"/>
     </row>
-    <row r="120" spans="1:8" ht="15.75" hidden="1">
+    <row r="120" spans="1:8" ht="15.5" hidden="1">
       <c r="A120" s="113" t="s">
         <v>480</v>
       </c>
@@ -9466,7 +9466,7 @@
       <c r="G122" s="449"/>
       <c r="H122" s="433"/>
     </row>
-    <row r="123" spans="1:8" ht="15.75" hidden="1">
+    <row r="123" spans="1:8" ht="15.5" hidden="1">
       <c r="A123" s="68" t="s">
         <v>10</v>
       </c>
@@ -9482,7 +9482,7 @@
       <c r="G123" s="458"/>
       <c r="H123" s="57"/>
     </row>
-    <row r="124" spans="1:8" ht="47.25" hidden="1">
+    <row r="124" spans="1:8" ht="46.5" hidden="1">
       <c r="A124" s="48">
         <v>1</v>
       </c>
@@ -9504,7 +9504,7 @@
       <c r="G124" s="457"/>
       <c r="H124" s="44"/>
     </row>
-    <row r="125" spans="1:8" ht="31.5" hidden="1">
+    <row r="125" spans="1:8" ht="31" hidden="1">
       <c r="A125" s="44">
         <v>2</v>
       </c>
@@ -9524,7 +9524,7 @@
       <c r="G125" s="460"/>
       <c r="H125" s="44"/>
     </row>
-    <row r="126" spans="1:8" ht="15.75" hidden="1">
+    <row r="126" spans="1:8" ht="15.5" hidden="1">
       <c r="A126" s="48">
         <v>3</v>
       </c>
@@ -9588,7 +9588,7 @@
       <c r="G128" s="455"/>
       <c r="H128" s="37"/>
     </row>
-    <row r="129" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="129" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A129" s="44">
         <v>6</v>
       </c>
@@ -9632,7 +9632,7 @@
       <c r="G130" s="453"/>
       <c r="H130" s="44"/>
     </row>
-    <row r="131" spans="1:8" ht="15.75" hidden="1">
+    <row r="131" spans="1:8" ht="15.5" hidden="1">
       <c r="A131" s="35" t="s">
         <v>13</v>
       </c>
@@ -9668,7 +9668,7 @@
       <c r="G132" s="446"/>
       <c r="H132" s="44"/>
     </row>
-    <row r="133" spans="1:8" ht="31.5" hidden="1">
+    <row r="133" spans="1:8" ht="31" hidden="1">
       <c r="A133" s="44">
         <v>2</v>
       </c>
@@ -9712,7 +9712,7 @@
       <c r="G134" s="457"/>
       <c r="H134" s="198"/>
     </row>
-    <row r="135" spans="1:8" ht="15.75">
+    <row r="135" spans="1:8" ht="15.5">
       <c r="A135" s="44"/>
       <c r="B135" s="73"/>
       <c r="C135" s="44"/>
@@ -9722,7 +9722,7 @@
       <c r="G135" s="442"/>
       <c r="H135" s="44"/>
     </row>
-    <row r="136" spans="1:8" ht="20.25">
+    <row r="136" spans="1:8" ht="20">
       <c r="A136" s="425" t="s">
         <v>24</v>
       </c>
@@ -9734,7 +9734,7 @@
       <c r="G136" s="425"/>
       <c r="H136" s="426"/>
     </row>
-    <row r="137" spans="1:8" ht="15.75">
+    <row r="137" spans="1:8" ht="15">
       <c r="A137" s="463" t="s">
         <v>659</v>
       </c>
@@ -9784,7 +9784,7 @@
       <c r="G139" s="433"/>
       <c r="H139" s="433"/>
     </row>
-    <row r="140" spans="1:8" ht="15.75" hidden="1">
+    <row r="140" spans="1:8" ht="15.5" hidden="1">
       <c r="A140" s="35" t="s">
         <v>10</v>
       </c>
@@ -9868,7 +9868,7 @@
       <c r="G143" s="56"/>
       <c r="H143" s="44"/>
     </row>
-    <row r="144" spans="1:8" ht="15.75" hidden="1">
+    <row r="144" spans="1:8" ht="15.5" hidden="1">
       <c r="A144" s="48" t="s">
         <v>555</v>
       </c>
@@ -9890,7 +9890,7 @@
       <c r="G144" s="56"/>
       <c r="H144" s="37"/>
     </row>
-    <row r="145" spans="1:8" ht="78.75" hidden="1">
+    <row r="145" spans="1:8" ht="62" hidden="1">
       <c r="A145" s="48" t="s">
         <v>562</v>
       </c>
@@ -9956,7 +9956,7 @@
       <c r="G147" s="56"/>
       <c r="H147" s="37"/>
     </row>
-    <row r="148" spans="1:8" ht="47.25" hidden="1">
+    <row r="148" spans="1:8" ht="46.5" hidden="1">
       <c r="A148" s="48" t="s">
         <v>777</v>
       </c>
@@ -9978,7 +9978,7 @@
       <c r="G148" s="56"/>
       <c r="H148" s="37"/>
     </row>
-    <row r="149" spans="1:8" ht="15.75" hidden="1">
+    <row r="149" spans="1:8" ht="15.5" hidden="1">
       <c r="A149" s="48" t="s">
         <v>780</v>
       </c>
@@ -10000,7 +10000,7 @@
       <c r="G149" s="56"/>
       <c r="H149" s="37"/>
     </row>
-    <row r="150" spans="1:8" ht="47.25" hidden="1">
+    <row r="150" spans="1:8" ht="46.5" hidden="1">
       <c r="A150" s="48" t="s">
         <v>781</v>
       </c>
@@ -10200,7 +10200,7 @@
       <c r="G158" s="338"/>
       <c r="H158" s="339"/>
     </row>
-    <row r="159" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="159" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A159" s="336" t="s">
         <v>569</v>
       </c>
@@ -10266,7 +10266,7 @@
       <c r="G161" s="338"/>
       <c r="H161" s="339"/>
     </row>
-    <row r="162" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="162" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A162" s="336" t="s">
         <v>789</v>
       </c>
@@ -10356,7 +10356,7 @@
       <c r="G165" s="56"/>
       <c r="H165" s="44"/>
     </row>
-    <row r="166" spans="1:8" ht="31.5" hidden="1">
+    <row r="166" spans="1:8" ht="30" hidden="1">
       <c r="A166" s="41">
         <v>4</v>
       </c>
@@ -10488,7 +10488,7 @@
       <c r="G171" s="338"/>
       <c r="H171" s="339"/>
     </row>
-    <row r="172" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="172" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A172" s="336" t="s">
         <v>359</v>
       </c>
@@ -10510,7 +10510,7 @@
       <c r="G172" s="338"/>
       <c r="H172" s="339"/>
     </row>
-    <row r="173" spans="1:8" s="90" customFormat="1" ht="15.75" hidden="1">
+    <row r="173" spans="1:8" s="90" customFormat="1" ht="15.5" hidden="1">
       <c r="A173" s="336" t="s">
         <v>360</v>
       </c>
@@ -10532,7 +10532,7 @@
       <c r="G173" s="338"/>
       <c r="H173" s="339"/>
     </row>
-    <row r="174" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="174" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A174" s="336" t="s">
         <v>362</v>
       </c>
@@ -10554,7 +10554,7 @@
       <c r="G174" s="338"/>
       <c r="H174" s="339"/>
     </row>
-    <row r="175" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="175" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A175" s="336" t="s">
         <v>363</v>
       </c>
@@ -10598,7 +10598,7 @@
       <c r="G176" s="338"/>
       <c r="H176" s="339"/>
     </row>
-    <row r="177" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="177" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A177" s="336" t="s">
         <v>365</v>
       </c>
@@ -10620,7 +10620,7 @@
       <c r="G177" s="338"/>
       <c r="H177" s="339"/>
     </row>
-    <row r="178" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="178" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A178" s="336" t="s">
         <v>366</v>
       </c>
@@ -10642,7 +10642,7 @@
       <c r="G178" s="338"/>
       <c r="H178" s="339"/>
     </row>
-    <row r="179" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="179" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A179" s="336" t="s">
         <v>367</v>
       </c>
@@ -10664,7 +10664,7 @@
       <c r="G179" s="338"/>
       <c r="H179" s="339"/>
     </row>
-    <row r="180" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="180" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A180" s="336" t="s">
         <v>368</v>
       </c>
@@ -10708,7 +10708,7 @@
       <c r="G181" s="338"/>
       <c r="H181" s="339"/>
     </row>
-    <row r="182" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="182" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A182" s="336" t="s">
         <v>372</v>
       </c>
@@ -10730,7 +10730,7 @@
       <c r="G182" s="141"/>
       <c r="H182" s="339"/>
     </row>
-    <row r="183" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="183" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A183" s="336" t="s">
         <v>373</v>
       </c>
@@ -10774,7 +10774,7 @@
       <c r="G184" s="338"/>
       <c r="H184" s="339"/>
     </row>
-    <row r="185" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="185" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A185" s="336" t="s">
         <v>377</v>
       </c>
@@ -10842,7 +10842,7 @@
       <c r="G187" s="338"/>
       <c r="H187" s="339"/>
     </row>
-    <row r="188" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="188" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A188" s="336" t="s">
         <v>349</v>
       </c>
@@ -10864,7 +10864,7 @@
       <c r="G188" s="338"/>
       <c r="H188" s="339"/>
     </row>
-    <row r="189" spans="1:12" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="189" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A189" s="336" t="s">
         <v>538</v>
       </c>
@@ -10886,7 +10886,7 @@
       <c r="G189" s="338"/>
       <c r="H189" s="339"/>
     </row>
-    <row r="190" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="190" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A190" s="336" t="s">
         <v>539</v>
       </c>
@@ -10908,7 +10908,7 @@
       <c r="G190" s="338"/>
       <c r="H190" s="339"/>
     </row>
-    <row r="191" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="191" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A191" s="336" t="s">
         <v>540</v>
       </c>
@@ -10930,7 +10930,7 @@
       <c r="G191" s="338"/>
       <c r="H191" s="339"/>
     </row>
-    <row r="192" spans="1:12" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="192" spans="1:12" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A192" s="336" t="s">
         <v>541</v>
       </c>
@@ -10953,7 +10953,7 @@
       <c r="H192" s="339"/>
       <c r="L192" s="347"/>
     </row>
-    <row r="193" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="193" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A193" s="336" t="s">
         <v>542</v>
       </c>
@@ -10975,7 +10975,7 @@
       <c r="G193" s="338"/>
       <c r="H193" s="339"/>
     </row>
-    <row r="194" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="194" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A194" s="336" t="s">
         <v>543</v>
       </c>
@@ -10997,7 +10997,7 @@
       <c r="G194" s="338"/>
       <c r="H194" s="339"/>
     </row>
-    <row r="195" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="195" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A195" s="336" t="s">
         <v>544</v>
       </c>
@@ -11063,7 +11063,7 @@
       <c r="G197" s="338"/>
       <c r="H197" s="339"/>
     </row>
-    <row r="198" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="198" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A198" s="336" t="s">
         <v>805</v>
       </c>
@@ -11107,7 +11107,7 @@
       <c r="G199" s="338"/>
       <c r="H199" s="339"/>
     </row>
-    <row r="200" spans="1:8" s="90" customFormat="1" ht="15.75" hidden="1">
+    <row r="200" spans="1:8" s="90" customFormat="1" ht="15.5" hidden="1">
       <c r="A200" s="336" t="s">
         <v>807</v>
       </c>
@@ -11151,7 +11151,7 @@
       <c r="G201" s="338"/>
       <c r="H201" s="339"/>
     </row>
-    <row r="202" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="202" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A202" s="336" t="s">
         <v>809</v>
       </c>
@@ -11171,7 +11171,7 @@
       <c r="G202" s="338"/>
       <c r="H202" s="339"/>
     </row>
-    <row r="203" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="203" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A203" s="336" t="s">
         <v>810</v>
       </c>
@@ -11193,7 +11193,7 @@
       <c r="G203" s="338"/>
       <c r="H203" s="339"/>
     </row>
-    <row r="204" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="204" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A204" s="336" t="s">
         <v>811</v>
       </c>
@@ -11237,7 +11237,7 @@
       <c r="G205" s="338"/>
       <c r="H205" s="339"/>
     </row>
-    <row r="206" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="206" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A206" s="336" t="s">
         <v>813</v>
       </c>
@@ -11259,7 +11259,7 @@
       <c r="G206" s="338"/>
       <c r="H206" s="339"/>
     </row>
-    <row r="207" spans="1:8" s="90" customFormat="1" ht="63" hidden="1">
+    <row r="207" spans="1:8" s="90" customFormat="1" ht="62" hidden="1">
       <c r="A207" s="336" t="s">
         <v>814</v>
       </c>
@@ -11303,7 +11303,7 @@
       <c r="G208" s="338"/>
       <c r="H208" s="339"/>
     </row>
-    <row r="209" spans="1:8" s="90" customFormat="1" ht="63" hidden="1">
+    <row r="209" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A209" s="336" t="s">
         <v>816</v>
       </c>
@@ -11391,7 +11391,7 @@
       <c r="G212" s="338"/>
       <c r="H212" s="339"/>
     </row>
-    <row r="213" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="213" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A213" s="336" t="s">
         <v>820</v>
       </c>
@@ -11413,7 +11413,7 @@
       <c r="G213" s="338"/>
       <c r="H213" s="339"/>
     </row>
-    <row r="214" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="214" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A214" s="336" t="s">
         <v>821</v>
       </c>
@@ -11435,7 +11435,7 @@
       <c r="G214" s="338"/>
       <c r="H214" s="339"/>
     </row>
-    <row r="215" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="215" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A215" s="336" t="s">
         <v>822</v>
       </c>
@@ -11457,7 +11457,7 @@
       <c r="G215" s="338"/>
       <c r="H215" s="339"/>
     </row>
-    <row r="216" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="216" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A216" s="336" t="s">
         <v>823</v>
       </c>
@@ -11501,7 +11501,7 @@
       <c r="G217" s="338"/>
       <c r="H217" s="339"/>
     </row>
-    <row r="218" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="218" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A218" s="336" t="s">
         <v>825</v>
       </c>
@@ -11545,7 +11545,7 @@
       <c r="G219" s="338"/>
       <c r="H219" s="339"/>
     </row>
-    <row r="220" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="220" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A220" s="336" t="s">
         <v>827</v>
       </c>
@@ -11567,7 +11567,7 @@
       <c r="G220" s="338"/>
       <c r="H220" s="339"/>
     </row>
-    <row r="221" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="221" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A221" s="336" t="s">
         <v>828</v>
       </c>
@@ -11589,7 +11589,7 @@
       <c r="G221" s="338"/>
       <c r="H221" s="339"/>
     </row>
-    <row r="222" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="222" spans="1:8" s="90" customFormat="1" ht="15.5" hidden="1">
       <c r="A222" s="336" t="s">
         <v>829</v>
       </c>
@@ -11611,7 +11611,7 @@
       <c r="G222" s="338"/>
       <c r="H222" s="339"/>
     </row>
-    <row r="223" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="223" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A223" s="336" t="s">
         <v>830</v>
       </c>
@@ -11633,7 +11633,7 @@
       <c r="G223" s="338"/>
       <c r="H223" s="339"/>
     </row>
-    <row r="224" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="224" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A224" s="336" t="s">
         <v>831</v>
       </c>
@@ -11655,7 +11655,7 @@
       <c r="G224" s="338"/>
       <c r="H224" s="339"/>
     </row>
-    <row r="225" spans="1:8" s="90" customFormat="1" ht="63" hidden="1">
+    <row r="225" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A225" s="336" t="s">
         <v>832</v>
       </c>
@@ -11677,7 +11677,7 @@
       <c r="G225" s="338"/>
       <c r="H225" s="339"/>
     </row>
-    <row r="226" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="226" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A226" s="336" t="s">
         <v>833</v>
       </c>
@@ -11739,7 +11739,7 @@
       <c r="G228" s="338"/>
       <c r="H228" s="339"/>
     </row>
-    <row r="229" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="229" spans="1:8" s="90" customFormat="1" ht="15.5" hidden="1">
       <c r="A229" s="336" t="s">
         <v>435</v>
       </c>
@@ -11761,7 +11761,7 @@
       <c r="G229" s="338"/>
       <c r="H229" s="339"/>
     </row>
-    <row r="230" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="230" spans="1:8" s="90" customFormat="1" ht="15.5" hidden="1">
       <c r="A230" s="336" t="s">
         <v>436</v>
       </c>
@@ -11849,7 +11849,7 @@
       <c r="G233" s="338"/>
       <c r="H233" s="339"/>
     </row>
-    <row r="234" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="234" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A234" s="336" t="s">
         <v>834</v>
       </c>
@@ -11871,7 +11871,7 @@
       <c r="G234" s="338"/>
       <c r="H234" s="339"/>
     </row>
-    <row r="235" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="235" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A235" s="336" t="s">
         <v>835</v>
       </c>
@@ -11915,7 +11915,7 @@
       <c r="G236" s="338"/>
       <c r="H236" s="339"/>
     </row>
-    <row r="237" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="237" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A237" s="336" t="s">
         <v>837</v>
       </c>
@@ -11937,7 +11937,7 @@
       <c r="G237" s="141"/>
       <c r="H237" s="339"/>
     </row>
-    <row r="238" spans="1:8" s="90" customFormat="1" ht="47.25" hidden="1">
+    <row r="238" spans="1:8" s="90" customFormat="1" ht="46.5" hidden="1">
       <c r="A238" s="336" t="s">
         <v>838</v>
       </c>
@@ -11981,7 +11981,7 @@
       <c r="G239" s="338"/>
       <c r="H239" s="339"/>
     </row>
-    <row r="240" spans="1:8" s="90" customFormat="1" ht="31.5" hidden="1">
+    <row r="240" spans="1:8" s="90" customFormat="1" ht="31" hidden="1">
       <c r="A240" s="336" t="s">
         <v>840</v>
       </c>
@@ -12025,7 +12025,7 @@
       <c r="G241" s="338"/>
       <c r="H241" s="339"/>
     </row>
-    <row r="242" spans="1:12" ht="31.5" hidden="1">
+    <row r="242" spans="1:12" ht="15.5" hidden="1">
       <c r="A242" s="41">
         <v>7</v>
       </c>
@@ -12150,7 +12150,7 @@
       <c r="G247" s="56"/>
       <c r="H247" s="44"/>
     </row>
-    <row r="248" spans="1:12" ht="15.75" hidden="1">
+    <row r="248" spans="1:12" ht="15.5" hidden="1">
       <c r="A248" s="104">
         <v>1</v>
       </c>
@@ -12267,7 +12267,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="15.75" hidden="1">
+    <row r="253" spans="1:12" ht="15.5" hidden="1">
       <c r="A253" s="41">
         <v>4</v>
       </c>
@@ -12329,7 +12329,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="63" hidden="1">
+    <row r="256" spans="1:12" ht="45.5" hidden="1">
       <c r="A256" s="104">
         <v>5</v>
       </c>
@@ -12351,7 +12351,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="257" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="257" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A257" s="36" t="s">
         <v>174</v>
       </c>
@@ -12397,7 +12397,7 @@
       <c r="G259" s="469"/>
       <c r="H259" s="469"/>
     </row>
-    <row r="260" spans="1:8" ht="15.75" hidden="1">
+    <row r="260" spans="1:8" ht="15.5" hidden="1">
       <c r="A260" s="110" t="s">
         <v>634</v>
       </c>
@@ -12445,7 +12445,7 @@
       <c r="G262" s="470"/>
       <c r="H262" s="475"/>
     </row>
-    <row r="263" spans="1:8" ht="15.75" hidden="1">
+    <row r="263" spans="1:8" ht="15.5" hidden="1">
       <c r="A263" s="35" t="s">
         <v>10</v>
       </c>
@@ -12505,7 +12505,7 @@
         <v>26000000</v>
       </c>
     </row>
-    <row r="266" spans="1:8" ht="15.75" hidden="1">
+    <row r="266" spans="1:8" ht="15.5" hidden="1">
       <c r="A266" s="35" t="s">
         <v>13</v>
       </c>
@@ -12519,7 +12519,7 @@
       <c r="G266" s="457"/>
       <c r="H266" s="44"/>
     </row>
-    <row r="267" spans="1:8" ht="15.75" hidden="1">
+    <row r="267" spans="1:8" ht="15.5" hidden="1">
       <c r="A267" s="63">
         <v>1</v>
       </c>
@@ -12717,7 +12717,7 @@
       <c r="G276" s="457"/>
       <c r="H276" s="318"/>
     </row>
-    <row r="277" spans="1:8" ht="16.5" thickBot="1">
+    <row r="277" spans="1:8" ht="16" thickBot="1">
       <c r="A277" s="124"/>
       <c r="B277" s="371"/>
       <c r="C277" s="229"/>
@@ -12739,7 +12739,7 @@
       <c r="G278" s="233"/>
       <c r="H278" s="234"/>
     </row>
-    <row r="279" spans="1:8" ht="15.75">
+    <row r="279" spans="1:8" ht="15">
       <c r="A279" s="463" t="s">
         <v>478</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="281" spans="1:8" s="34" customFormat="1" ht="15.75">
+    <row r="281" spans="1:8" s="34" customFormat="1" ht="15.5">
       <c r="A281" s="432"/>
       <c r="B281" s="487"/>
       <c r="C281" s="432"/>
@@ -12789,7 +12789,7 @@
       <c r="G281" s="432"/>
       <c r="H281" s="433"/>
     </row>
-    <row r="282" spans="1:8" ht="15.75" hidden="1">
+    <row r="282" spans="1:8" ht="15.5" hidden="1">
       <c r="A282" s="35" t="s">
         <v>10</v>
       </c>
@@ -12803,7 +12803,7 @@
       <c r="G282" s="38"/>
       <c r="H282" s="48"/>
     </row>
-    <row r="283" spans="1:8" ht="47.25" hidden="1">
+    <row r="283" spans="1:8" ht="46.5" hidden="1">
       <c r="A283" s="41">
         <v>1</v>
       </c>
@@ -12829,7 +12829,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="284" spans="1:8" ht="63" hidden="1">
+    <row r="284" spans="1:8" ht="46.5" hidden="1">
       <c r="A284" s="41">
         <v>2</v>
       </c>
@@ -12897,7 +12897,7 @@
       </c>
       <c r="H286" s="51"/>
     </row>
-    <row r="287" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="287" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A287" s="44" t="s">
         <v>78</v>
       </c>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="H287" s="51"/>
     </row>
-    <row r="288" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="288" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A288" s="48" t="s">
         <v>82</v>
       </c>
@@ -12945,7 +12945,7 @@
       </c>
       <c r="H288" s="51"/>
     </row>
-    <row r="289" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="289" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A289" s="44" t="s">
         <v>85</v>
       </c>
@@ -12969,7 +12969,7 @@
       </c>
       <c r="H289" s="51"/>
     </row>
-    <row r="290" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="290" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A290" s="48" t="s">
         <v>88</v>
       </c>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H290" s="51"/>
     </row>
-    <row r="291" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="291" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A291" s="44" t="s">
         <v>92</v>
       </c>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="H291" s="51"/>
     </row>
-    <row r="292" spans="1:8" s="52" customFormat="1" ht="47.25" hidden="1">
+    <row r="292" spans="1:8" s="52" customFormat="1" ht="46.5" hidden="1">
       <c r="A292" s="48" t="s">
         <v>94</v>
       </c>
@@ -13041,7 +13041,7 @@
       </c>
       <c r="H292" s="51"/>
     </row>
-    <row r="293" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="293" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A293" s="44" t="s">
         <v>96</v>
       </c>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="H293" s="51"/>
     </row>
-    <row r="294" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="294" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A294" s="44" t="s">
         <v>100</v>
       </c>
@@ -13113,7 +13113,7 @@
       </c>
       <c r="H295" s="51"/>
     </row>
-    <row r="296" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="296" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A296" s="253" t="s">
         <v>319</v>
       </c>
@@ -13137,7 +13137,7 @@
       </c>
       <c r="H296" s="257"/>
     </row>
-    <row r="297" spans="1:8" s="52" customFormat="1" ht="63" hidden="1">
+    <row r="297" spans="1:8" s="52" customFormat="1" ht="62" hidden="1">
       <c r="A297" s="57" t="s">
         <v>322</v>
       </c>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="H297" s="51"/>
     </row>
-    <row r="298" spans="1:8" s="52" customFormat="1" ht="47.25" hidden="1">
+    <row r="298" spans="1:8" s="52" customFormat="1" ht="46.5" hidden="1">
       <c r="A298" s="48" t="s">
         <v>325</v>
       </c>
@@ -13257,7 +13257,7 @@
       </c>
       <c r="H301" s="51"/>
     </row>
-    <row r="302" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="302" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A302" s="48" t="s">
         <v>511</v>
       </c>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="H302" s="51"/>
     </row>
-    <row r="303" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="303" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A303" s="44" t="s">
         <v>513</v>
       </c>
@@ -13305,7 +13305,7 @@
       </c>
       <c r="H303" s="51"/>
     </row>
-    <row r="304" spans="1:8" s="52" customFormat="1" ht="31.5" hidden="1">
+    <row r="304" spans="1:8" s="52" customFormat="1" ht="31" hidden="1">
       <c r="A304" s="48" t="s">
         <v>515</v>
       </c>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="H304" s="51"/>
     </row>
-    <row r="305" spans="1:8" s="52" customFormat="1" ht="78.75" hidden="1">
+    <row r="305" spans="1:8" s="52" customFormat="1" ht="77.5" hidden="1">
       <c r="A305" s="44" t="s">
         <v>517</v>
       </c>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="H305" s="51"/>
     </row>
-    <row r="306" spans="1:8" s="52" customFormat="1" ht="126" hidden="1">
+    <row r="306" spans="1:8" s="52" customFormat="1" ht="124" hidden="1">
       <c r="A306" s="104">
         <v>4</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="15.75" hidden="1">
+    <row r="307" spans="1:8" ht="15.5" hidden="1">
       <c r="A307" s="58" t="s">
         <v>13</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="313" spans="1:8" s="52" customFormat="1" ht="15.75" hidden="1">
+    <row r="313" spans="1:8" s="52" customFormat="1" ht="15.5" hidden="1">
       <c r="A313" s="36" t="s">
         <v>174</v>
       </c>
@@ -13569,7 +13569,7 @@
       <c r="G315" s="457"/>
       <c r="H315" s="457"/>
     </row>
-    <row r="316" spans="1:8" ht="15.75" hidden="1">
+    <row r="316" spans="1:8" ht="15.5" hidden="1">
       <c r="A316" s="110" t="s">
         <v>480</v>
       </c>
@@ -13617,7 +13617,7 @@
       <c r="G318" s="470"/>
       <c r="H318" s="475"/>
     </row>
-    <row r="319" spans="1:8" ht="15.75" hidden="1">
+    <row r="319" spans="1:8" ht="15.5" hidden="1">
       <c r="A319" s="35" t="s">
         <v>10</v>
       </c>
@@ -13699,7 +13699,7 @@
       <c r="G322" s="461"/>
       <c r="H322" s="44"/>
     </row>
-    <row r="323" spans="1:10" ht="31.5" hidden="1">
+    <row r="323" spans="1:10" ht="15.5" hidden="1">
       <c r="A323" s="48">
         <v>4</v>
       </c>
@@ -14142,7 +14142,7 @@
     <mergeCell ref="G6:G7"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="74" max="16383" man="1"/>
     <brk id="135" max="16383" man="1"/>
@@ -14158,587 +14158,587 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L106"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" style="52" customWidth="1"/>
-    <col min="2" max="2" width="43.7109375" style="401" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="52" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" style="235" customWidth="1"/>
-    <col min="6" max="6" width="52.5703125" style="401" customWidth="1"/>
-    <col min="7" max="7" width="43.7109375" style="52" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" style="52" customWidth="1"/>
+    <col min="2" max="2" width="43.75" style="401" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="52" customWidth="1"/>
+    <col min="4" max="5" width="11.25" style="235" customWidth="1"/>
+    <col min="6" max="6" width="52.58203125" style="401" customWidth="1"/>
+    <col min="7" max="7" width="43.75" style="52" customWidth="1"/>
     <col min="8" max="8" width="16" style="235" customWidth="1"/>
-    <col min="9" max="9" width="26.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.58203125" style="52" bestFit="1" customWidth="1"/>
     <col min="10" max="256" width="9" style="52"/>
-    <col min="257" max="257" width="5.85546875" style="52" customWidth="1"/>
-    <col min="258" max="258" width="62.42578125" style="52" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" style="52" customWidth="1"/>
-    <col min="260" max="260" width="17.28515625" style="52" customWidth="1"/>
-    <col min="261" max="261" width="20.7109375" style="52" customWidth="1"/>
-    <col min="262" max="262" width="33.85546875" style="52" customWidth="1"/>
-    <col min="263" max="263" width="37.28515625" style="52" customWidth="1"/>
-    <col min="264" max="264" width="18.5703125" style="52" customWidth="1"/>
+    <col min="257" max="257" width="5.83203125" style="52" customWidth="1"/>
+    <col min="258" max="258" width="62.4140625" style="52" customWidth="1"/>
+    <col min="259" max="259" width="14.83203125" style="52" customWidth="1"/>
+    <col min="260" max="260" width="17.25" style="52" customWidth="1"/>
+    <col min="261" max="261" width="20.75" style="52" customWidth="1"/>
+    <col min="262" max="262" width="33.83203125" style="52" customWidth="1"/>
+    <col min="263" max="263" width="37.25" style="52" customWidth="1"/>
+    <col min="264" max="264" width="18.58203125" style="52" customWidth="1"/>
     <col min="265" max="512" width="9" style="52"/>
-    <col min="513" max="513" width="5.85546875" style="52" customWidth="1"/>
-    <col min="514" max="514" width="62.42578125" style="52" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" style="52" customWidth="1"/>
-    <col min="516" max="516" width="17.28515625" style="52" customWidth="1"/>
-    <col min="517" max="517" width="20.7109375" style="52" customWidth="1"/>
-    <col min="518" max="518" width="33.85546875" style="52" customWidth="1"/>
-    <col min="519" max="519" width="37.28515625" style="52" customWidth="1"/>
-    <col min="520" max="520" width="18.5703125" style="52" customWidth="1"/>
+    <col min="513" max="513" width="5.83203125" style="52" customWidth="1"/>
+    <col min="514" max="514" width="62.4140625" style="52" customWidth="1"/>
+    <col min="515" max="515" width="14.83203125" style="52" customWidth="1"/>
+    <col min="516" max="516" width="17.25" style="52" customWidth="1"/>
+    <col min="517" max="517" width="20.75" style="52" customWidth="1"/>
+    <col min="518" max="518" width="33.83203125" style="52" customWidth="1"/>
+    <col min="519" max="519" width="37.25" style="52" customWidth="1"/>
+    <col min="520" max="520" width="18.58203125" style="52" customWidth="1"/>
     <col min="521" max="768" width="9" style="52"/>
-    <col min="769" max="769" width="5.85546875" style="52" customWidth="1"/>
-    <col min="770" max="770" width="62.42578125" style="52" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" style="52" customWidth="1"/>
-    <col min="772" max="772" width="17.28515625" style="52" customWidth="1"/>
-    <col min="773" max="773" width="20.7109375" style="52" customWidth="1"/>
-    <col min="774" max="774" width="33.85546875" style="52" customWidth="1"/>
-    <col min="775" max="775" width="37.28515625" style="52" customWidth="1"/>
-    <col min="776" max="776" width="18.5703125" style="52" customWidth="1"/>
+    <col min="769" max="769" width="5.83203125" style="52" customWidth="1"/>
+    <col min="770" max="770" width="62.4140625" style="52" customWidth="1"/>
+    <col min="771" max="771" width="14.83203125" style="52" customWidth="1"/>
+    <col min="772" max="772" width="17.25" style="52" customWidth="1"/>
+    <col min="773" max="773" width="20.75" style="52" customWidth="1"/>
+    <col min="774" max="774" width="33.83203125" style="52" customWidth="1"/>
+    <col min="775" max="775" width="37.25" style="52" customWidth="1"/>
+    <col min="776" max="776" width="18.58203125" style="52" customWidth="1"/>
     <col min="777" max="1024" width="9" style="52"/>
-    <col min="1025" max="1025" width="5.85546875" style="52" customWidth="1"/>
-    <col min="1026" max="1026" width="62.42578125" style="52" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" style="52" customWidth="1"/>
-    <col min="1028" max="1028" width="17.28515625" style="52" customWidth="1"/>
-    <col min="1029" max="1029" width="20.7109375" style="52" customWidth="1"/>
-    <col min="1030" max="1030" width="33.85546875" style="52" customWidth="1"/>
-    <col min="1031" max="1031" width="37.28515625" style="52" customWidth="1"/>
-    <col min="1032" max="1032" width="18.5703125" style="52" customWidth="1"/>
+    <col min="1025" max="1025" width="5.83203125" style="52" customWidth="1"/>
+    <col min="1026" max="1026" width="62.4140625" style="52" customWidth="1"/>
+    <col min="1027" max="1027" width="14.83203125" style="52" customWidth="1"/>
+    <col min="1028" max="1028" width="17.25" style="52" customWidth="1"/>
+    <col min="1029" max="1029" width="20.75" style="52" customWidth="1"/>
+    <col min="1030" max="1030" width="33.83203125" style="52" customWidth="1"/>
+    <col min="1031" max="1031" width="37.25" style="52" customWidth="1"/>
+    <col min="1032" max="1032" width="18.58203125" style="52" customWidth="1"/>
     <col min="1033" max="1280" width="9" style="52"/>
-    <col min="1281" max="1281" width="5.85546875" style="52" customWidth="1"/>
-    <col min="1282" max="1282" width="62.42578125" style="52" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" style="52" customWidth="1"/>
-    <col min="1284" max="1284" width="17.28515625" style="52" customWidth="1"/>
-    <col min="1285" max="1285" width="20.7109375" style="52" customWidth="1"/>
-    <col min="1286" max="1286" width="33.85546875" style="52" customWidth="1"/>
-    <col min="1287" max="1287" width="37.28515625" style="52" customWidth="1"/>
-    <col min="1288" max="1288" width="18.5703125" style="52" customWidth="1"/>
+    <col min="1281" max="1281" width="5.83203125" style="52" customWidth="1"/>
+    <col min="1282" max="1282" width="62.4140625" style="52" customWidth="1"/>
+    <col min="1283" max="1283" width="14.83203125" style="52" customWidth="1"/>
+    <col min="1284" max="1284" width="17.25" style="52" customWidth="1"/>
+    <col min="1285" max="1285" width="20.75" style="52" customWidth="1"/>
+    <col min="1286" max="1286" width="33.83203125" style="52" customWidth="1"/>
+    <col min="1287" max="1287" width="37.25" style="52" customWidth="1"/>
+    <col min="1288" max="1288" width="18.58203125" style="52" customWidth="1"/>
     <col min="1289" max="1536" width="9" style="52"/>
-    <col min="1537" max="1537" width="5.85546875" style="52" customWidth="1"/>
-    <col min="1538" max="1538" width="62.42578125" style="52" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" style="52" customWidth="1"/>
-    <col min="1540" max="1540" width="17.28515625" style="52" customWidth="1"/>
-    <col min="1541" max="1541" width="20.7109375" style="52" customWidth="1"/>
-    <col min="1542" max="1542" width="33.85546875" style="52" customWidth="1"/>
-    <col min="1543" max="1543" width="37.28515625" style="52" customWidth="1"/>
-    <col min="1544" max="1544" width="18.5703125" style="52" customWidth="1"/>
+    <col min="1537" max="1537" width="5.83203125" style="52" customWidth="1"/>
+    <col min="1538" max="1538" width="62.4140625" style="52" customWidth="1"/>
+    <col min="1539" max="1539" width="14.83203125" style="52" customWidth="1"/>
+    <col min="1540" max="1540" width="17.25" style="52" customWidth="1"/>
+    <col min="1541" max="1541" width="20.75" style="52" customWidth="1"/>
+    <col min="1542" max="1542" width="33.83203125" style="52" customWidth="1"/>
+    <col min="1543" max="1543" width="37.25" style="52" customWidth="1"/>
+    <col min="1544" max="1544" width="18.58203125" style="52" customWidth="1"/>
     <col min="1545" max="1792" width="9" style="52"/>
-    <col min="1793" max="1793" width="5.85546875" style="52" customWidth="1"/>
-    <col min="1794" max="1794" width="62.42578125" style="52" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" style="52" customWidth="1"/>
-    <col min="1796" max="1796" width="17.28515625" style="52" customWidth="1"/>
-    <col min="1797" max="1797" width="20.7109375" style="52" customWidth="1"/>
-    <col min="1798" max="1798" width="33.85546875" style="52" customWidth="1"/>
-    <col min="1799" max="1799" width="37.28515625" style="52" customWidth="1"/>
-    <col min="1800" max="1800" width="18.5703125" style="52" customWidth="1"/>
+    <col min="1793" max="1793" width="5.83203125" style="52" customWidth="1"/>
+    <col min="1794" max="1794" width="62.4140625" style="52" customWidth="1"/>
+    <col min="1795" max="1795" width="14.83203125" style="52" customWidth="1"/>
+    <col min="1796" max="1796" width="17.25" style="52" customWidth="1"/>
+    <col min="1797" max="1797" width="20.75" style="52" customWidth="1"/>
+    <col min="1798" max="1798" width="33.83203125" style="52" customWidth="1"/>
+    <col min="1799" max="1799" width="37.25" style="52" customWidth="1"/>
+    <col min="1800" max="1800" width="18.58203125" style="52" customWidth="1"/>
     <col min="1801" max="2048" width="9" style="52"/>
-    <col min="2049" max="2049" width="5.85546875" style="52" customWidth="1"/>
-    <col min="2050" max="2050" width="62.42578125" style="52" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" style="52" customWidth="1"/>
-    <col min="2052" max="2052" width="17.28515625" style="52" customWidth="1"/>
-    <col min="2053" max="2053" width="20.7109375" style="52" customWidth="1"/>
-    <col min="2054" max="2054" width="33.85546875" style="52" customWidth="1"/>
-    <col min="2055" max="2055" width="37.28515625" style="52" customWidth="1"/>
-    <col min="2056" max="2056" width="18.5703125" style="52" customWidth="1"/>
+    <col min="2049" max="2049" width="5.83203125" style="52" customWidth="1"/>
+    <col min="2050" max="2050" width="62.4140625" style="52" customWidth="1"/>
+    <col min="2051" max="2051" width="14.83203125" style="52" customWidth="1"/>
+    <col min="2052" max="2052" width="17.25" style="52" customWidth="1"/>
+    <col min="2053" max="2053" width="20.75" style="52" customWidth="1"/>
+    <col min="2054" max="2054" width="33.83203125" style="52" customWidth="1"/>
+    <col min="2055" max="2055" width="37.25" style="52" customWidth="1"/>
+    <col min="2056" max="2056" width="18.58203125" style="52" customWidth="1"/>
     <col min="2057" max="2304" width="9" style="52"/>
-    <col min="2305" max="2305" width="5.85546875" style="52" customWidth="1"/>
-    <col min="2306" max="2306" width="62.42578125" style="52" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" style="52" customWidth="1"/>
-    <col min="2308" max="2308" width="17.28515625" style="52" customWidth="1"/>
-    <col min="2309" max="2309" width="20.7109375" style="52" customWidth="1"/>
-    <col min="2310" max="2310" width="33.85546875" style="52" customWidth="1"/>
-    <col min="2311" max="2311" width="37.28515625" style="52" customWidth="1"/>
-    <col min="2312" max="2312" width="18.5703125" style="52" customWidth="1"/>
+    <col min="2305" max="2305" width="5.83203125" style="52" customWidth="1"/>
+    <col min="2306" max="2306" width="62.4140625" style="52" customWidth="1"/>
+    <col min="2307" max="2307" width="14.83203125" style="52" customWidth="1"/>
+    <col min="2308" max="2308" width="17.25" style="52" customWidth="1"/>
+    <col min="2309" max="2309" width="20.75" style="52" customWidth="1"/>
+    <col min="2310" max="2310" width="33.83203125" style="52" customWidth="1"/>
+    <col min="2311" max="2311" width="37.25" style="52" customWidth="1"/>
+    <col min="2312" max="2312" width="18.58203125" style="52" customWidth="1"/>
     <col min="2313" max="2560" width="9" style="52"/>
-    <col min="2561" max="2561" width="5.85546875" style="52" customWidth="1"/>
-    <col min="2562" max="2562" width="62.42578125" style="52" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" style="52" customWidth="1"/>
-    <col min="2564" max="2564" width="17.28515625" style="52" customWidth="1"/>
-    <col min="2565" max="2565" width="20.7109375" style="52" customWidth="1"/>
-    <col min="2566" max="2566" width="33.85546875" style="52" customWidth="1"/>
-    <col min="2567" max="2567" width="37.28515625" style="52" customWidth="1"/>
-    <col min="2568" max="2568" width="18.5703125" style="52" customWidth="1"/>
+    <col min="2561" max="2561" width="5.83203125" style="52" customWidth="1"/>
+    <col min="2562" max="2562" width="62.4140625" style="52" customWidth="1"/>
+    <col min="2563" max="2563" width="14.83203125" style="52" customWidth="1"/>
+    <col min="2564" max="2564" width="17.25" style="52" customWidth="1"/>
+    <col min="2565" max="2565" width="20.75" style="52" customWidth="1"/>
+    <col min="2566" max="2566" width="33.83203125" style="52" customWidth="1"/>
+    <col min="2567" max="2567" width="37.25" style="52" customWidth="1"/>
+    <col min="2568" max="2568" width="18.58203125" style="52" customWidth="1"/>
     <col min="2569" max="2816" width="9" style="52"/>
-    <col min="2817" max="2817" width="5.85546875" style="52" customWidth="1"/>
-    <col min="2818" max="2818" width="62.42578125" style="52" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" style="52" customWidth="1"/>
-    <col min="2820" max="2820" width="17.28515625" style="52" customWidth="1"/>
-    <col min="2821" max="2821" width="20.7109375" style="52" customWidth="1"/>
-    <col min="2822" max="2822" width="33.85546875" style="52" customWidth="1"/>
-    <col min="2823" max="2823" width="37.28515625" style="52" customWidth="1"/>
-    <col min="2824" max="2824" width="18.5703125" style="52" customWidth="1"/>
+    <col min="2817" max="2817" width="5.83203125" style="52" customWidth="1"/>
+    <col min="2818" max="2818" width="62.4140625" style="52" customWidth="1"/>
+    <col min="2819" max="2819" width="14.83203125" style="52" customWidth="1"/>
+    <col min="2820" max="2820" width="17.25" style="52" customWidth="1"/>
+    <col min="2821" max="2821" width="20.75" style="52" customWidth="1"/>
+    <col min="2822" max="2822" width="33.83203125" style="52" customWidth="1"/>
+    <col min="2823" max="2823" width="37.25" style="52" customWidth="1"/>
+    <col min="2824" max="2824" width="18.58203125" style="52" customWidth="1"/>
     <col min="2825" max="3072" width="9" style="52"/>
-    <col min="3073" max="3073" width="5.85546875" style="52" customWidth="1"/>
-    <col min="3074" max="3074" width="62.42578125" style="52" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" style="52" customWidth="1"/>
-    <col min="3076" max="3076" width="17.28515625" style="52" customWidth="1"/>
-    <col min="3077" max="3077" width="20.7109375" style="52" customWidth="1"/>
-    <col min="3078" max="3078" width="33.85546875" style="52" customWidth="1"/>
-    <col min="3079" max="3079" width="37.28515625" style="52" customWidth="1"/>
-    <col min="3080" max="3080" width="18.5703125" style="52" customWidth="1"/>
+    <col min="3073" max="3073" width="5.83203125" style="52" customWidth="1"/>
+    <col min="3074" max="3074" width="62.4140625" style="52" customWidth="1"/>
+    <col min="3075" max="3075" width="14.83203125" style="52" customWidth="1"/>
+    <col min="3076" max="3076" width="17.25" style="52" customWidth="1"/>
+    <col min="3077" max="3077" width="20.75" style="52" customWidth="1"/>
+    <col min="3078" max="3078" width="33.83203125" style="52" customWidth="1"/>
+    <col min="3079" max="3079" width="37.25" style="52" customWidth="1"/>
+    <col min="3080" max="3080" width="18.58203125" style="52" customWidth="1"/>
     <col min="3081" max="3328" width="9" style="52"/>
-    <col min="3329" max="3329" width="5.85546875" style="52" customWidth="1"/>
-    <col min="3330" max="3330" width="62.42578125" style="52" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" style="52" customWidth="1"/>
-    <col min="3332" max="3332" width="17.28515625" style="52" customWidth="1"/>
-    <col min="3333" max="3333" width="20.7109375" style="52" customWidth="1"/>
-    <col min="3334" max="3334" width="33.85546875" style="52" customWidth="1"/>
-    <col min="3335" max="3335" width="37.28515625" style="52" customWidth="1"/>
-    <col min="3336" max="3336" width="18.5703125" style="52" customWidth="1"/>
+    <col min="3329" max="3329" width="5.83203125" style="52" customWidth="1"/>
+    <col min="3330" max="3330" width="62.4140625" style="52" customWidth="1"/>
+    <col min="3331" max="3331" width="14.83203125" style="52" customWidth="1"/>
+    <col min="3332" max="3332" width="17.25" style="52" customWidth="1"/>
+    <col min="3333" max="3333" width="20.75" style="52" customWidth="1"/>
+    <col min="3334" max="3334" width="33.83203125" style="52" customWidth="1"/>
+    <col min="3335" max="3335" width="37.25" style="52" customWidth="1"/>
+    <col min="3336" max="3336" width="18.58203125" style="52" customWidth="1"/>
     <col min="3337" max="3584" width="9" style="52"/>
-    <col min="3585" max="3585" width="5.85546875" style="52" customWidth="1"/>
-    <col min="3586" max="3586" width="62.42578125" style="52" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" style="52" customWidth="1"/>
-    <col min="3588" max="3588" width="17.28515625" style="52" customWidth="1"/>
-    <col min="3589" max="3589" width="20.7109375" style="52" customWidth="1"/>
-    <col min="3590" max="3590" width="33.85546875" style="52" customWidth="1"/>
-    <col min="3591" max="3591" width="37.28515625" style="52" customWidth="1"/>
-    <col min="3592" max="3592" width="18.5703125" style="52" customWidth="1"/>
+    <col min="3585" max="3585" width="5.83203125" style="52" customWidth="1"/>
+    <col min="3586" max="3586" width="62.4140625" style="52" customWidth="1"/>
+    <col min="3587" max="3587" width="14.83203125" style="52" customWidth="1"/>
+    <col min="3588" max="3588" width="17.25" style="52" customWidth="1"/>
+    <col min="3589" max="3589" width="20.75" style="52" customWidth="1"/>
+    <col min="3590" max="3590" width="33.83203125" style="52" customWidth="1"/>
+    <col min="3591" max="3591" width="37.25" style="52" customWidth="1"/>
+    <col min="3592" max="3592" width="18.58203125" style="52" customWidth="1"/>
     <col min="3593" max="3840" width="9" style="52"/>
-    <col min="3841" max="3841" width="5.85546875" style="52" customWidth="1"/>
-    <col min="3842" max="3842" width="62.42578125" style="52" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" style="52" customWidth="1"/>
-    <col min="3844" max="3844" width="17.28515625" style="52" customWidth="1"/>
-    <col min="3845" max="3845" width="20.7109375" style="52" customWidth="1"/>
-    <col min="3846" max="3846" width="33.85546875" style="52" customWidth="1"/>
-    <col min="3847" max="3847" width="37.28515625" style="52" customWidth="1"/>
-    <col min="3848" max="3848" width="18.5703125" style="52" customWidth="1"/>
+    <col min="3841" max="3841" width="5.83203125" style="52" customWidth="1"/>
+    <col min="3842" max="3842" width="62.4140625" style="52" customWidth="1"/>
+    <col min="3843" max="3843" width="14.83203125" style="52" customWidth="1"/>
+    <col min="3844" max="3844" width="17.25" style="52" customWidth="1"/>
+    <col min="3845" max="3845" width="20.75" style="52" customWidth="1"/>
+    <col min="3846" max="3846" width="33.83203125" style="52" customWidth="1"/>
+    <col min="3847" max="3847" width="37.25" style="52" customWidth="1"/>
+    <col min="3848" max="3848" width="18.58203125" style="52" customWidth="1"/>
     <col min="3849" max="4096" width="9" style="52"/>
-    <col min="4097" max="4097" width="5.85546875" style="52" customWidth="1"/>
-    <col min="4098" max="4098" width="62.42578125" style="52" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" style="52" customWidth="1"/>
-    <col min="4100" max="4100" width="17.28515625" style="52" customWidth="1"/>
-    <col min="4101" max="4101" width="20.7109375" style="52" customWidth="1"/>
-    <col min="4102" max="4102" width="33.85546875" style="52" customWidth="1"/>
-    <col min="4103" max="4103" width="37.28515625" style="52" customWidth="1"/>
-    <col min="4104" max="4104" width="18.5703125" style="52" customWidth="1"/>
+    <col min="4097" max="4097" width="5.83203125" style="52" customWidth="1"/>
+    <col min="4098" max="4098" width="62.4140625" style="52" customWidth="1"/>
+    <col min="4099" max="4099" width="14.83203125" style="52" customWidth="1"/>
+    <col min="4100" max="4100" width="17.25" style="52" customWidth="1"/>
+    <col min="4101" max="4101" width="20.75" style="52" customWidth="1"/>
+    <col min="4102" max="4102" width="33.83203125" style="52" customWidth="1"/>
+    <col min="4103" max="4103" width="37.25" style="52" customWidth="1"/>
+    <col min="4104" max="4104" width="18.58203125" style="52" customWidth="1"/>
     <col min="4105" max="4352" width="9" style="52"/>
-    <col min="4353" max="4353" width="5.85546875" style="52" customWidth="1"/>
-    <col min="4354" max="4354" width="62.42578125" style="52" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" style="52" customWidth="1"/>
-    <col min="4356" max="4356" width="17.28515625" style="52" customWidth="1"/>
-    <col min="4357" max="4357" width="20.7109375" style="52" customWidth="1"/>
-    <col min="4358" max="4358" width="33.85546875" style="52" customWidth="1"/>
-    <col min="4359" max="4359" width="37.28515625" style="52" customWidth="1"/>
-    <col min="4360" max="4360" width="18.5703125" style="52" customWidth="1"/>
+    <col min="4353" max="4353" width="5.83203125" style="52" customWidth="1"/>
+    <col min="4354" max="4354" width="62.4140625" style="52" customWidth="1"/>
+    <col min="4355" max="4355" width="14.83203125" style="52" customWidth="1"/>
+    <col min="4356" max="4356" width="17.25" style="52" customWidth="1"/>
+    <col min="4357" max="4357" width="20.75" style="52" customWidth="1"/>
+    <col min="4358" max="4358" width="33.83203125" style="52" customWidth="1"/>
+    <col min="4359" max="4359" width="37.25" style="52" customWidth="1"/>
+    <col min="4360" max="4360" width="18.58203125" style="52" customWidth="1"/>
     <col min="4361" max="4608" width="9" style="52"/>
-    <col min="4609" max="4609" width="5.85546875" style="52" customWidth="1"/>
-    <col min="4610" max="4610" width="62.42578125" style="52" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" style="52" customWidth="1"/>
-    <col min="4612" max="4612" width="17.28515625" style="52" customWidth="1"/>
-    <col min="4613" max="4613" width="20.7109375" style="52" customWidth="1"/>
-    <col min="4614" max="4614" width="33.85546875" style="52" customWidth="1"/>
-    <col min="4615" max="4615" width="37.28515625" style="52" customWidth="1"/>
-    <col min="4616" max="4616" width="18.5703125" style="52" customWidth="1"/>
+    <col min="4609" max="4609" width="5.83203125" style="52" customWidth="1"/>
+    <col min="4610" max="4610" width="62.4140625" style="52" customWidth="1"/>
+    <col min="4611" max="4611" width="14.83203125" style="52" customWidth="1"/>
+    <col min="4612" max="4612" width="17.25" style="52" customWidth="1"/>
+    <col min="4613" max="4613" width="20.75" style="52" customWidth="1"/>
+    <col min="4614" max="4614" width="33.83203125" style="52" customWidth="1"/>
+    <col min="4615" max="4615" width="37.25" style="52" customWidth="1"/>
+    <col min="4616" max="4616" width="18.58203125" style="52" customWidth="1"/>
     <col min="4617" max="4864" width="9" style="52"/>
-    <col min="4865" max="4865" width="5.85546875" style="52" customWidth="1"/>
-    <col min="4866" max="4866" width="62.42578125" style="52" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" style="52" customWidth="1"/>
-    <col min="4868" max="4868" width="17.28515625" style="52" customWidth="1"/>
-    <col min="4869" max="4869" width="20.7109375" style="52" customWidth="1"/>
-    <col min="4870" max="4870" width="33.85546875" style="52" customWidth="1"/>
-    <col min="4871" max="4871" width="37.28515625" style="52" customWidth="1"/>
-    <col min="4872" max="4872" width="18.5703125" style="52" customWidth="1"/>
+    <col min="4865" max="4865" width="5.83203125" style="52" customWidth="1"/>
+    <col min="4866" max="4866" width="62.4140625" style="52" customWidth="1"/>
+    <col min="4867" max="4867" width="14.83203125" style="52" customWidth="1"/>
+    <col min="4868" max="4868" width="17.25" style="52" customWidth="1"/>
+    <col min="4869" max="4869" width="20.75" style="52" customWidth="1"/>
+    <col min="4870" max="4870" width="33.83203125" style="52" customWidth="1"/>
+    <col min="4871" max="4871" width="37.25" style="52" customWidth="1"/>
+    <col min="4872" max="4872" width="18.58203125" style="52" customWidth="1"/>
     <col min="4873" max="5120" width="9" style="52"/>
-    <col min="5121" max="5121" width="5.85546875" style="52" customWidth="1"/>
-    <col min="5122" max="5122" width="62.42578125" style="52" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" style="52" customWidth="1"/>
-    <col min="5124" max="5124" width="17.28515625" style="52" customWidth="1"/>
-    <col min="5125" max="5125" width="20.7109375" style="52" customWidth="1"/>
-    <col min="5126" max="5126" width="33.85546875" style="52" customWidth="1"/>
-    <col min="5127" max="5127" width="37.28515625" style="52" customWidth="1"/>
-    <col min="5128" max="5128" width="18.5703125" style="52" customWidth="1"/>
+    <col min="5121" max="5121" width="5.83203125" style="52" customWidth="1"/>
+    <col min="5122" max="5122" width="62.4140625" style="52" customWidth="1"/>
+    <col min="5123" max="5123" width="14.83203125" style="52" customWidth="1"/>
+    <col min="5124" max="5124" width="17.25" style="52" customWidth="1"/>
+    <col min="5125" max="5125" width="20.75" style="52" customWidth="1"/>
+    <col min="5126" max="5126" width="33.83203125" style="52" customWidth="1"/>
+    <col min="5127" max="5127" width="37.25" style="52" customWidth="1"/>
+    <col min="5128" max="5128" width="18.58203125" style="52" customWidth="1"/>
     <col min="5129" max="5376" width="9" style="52"/>
-    <col min="5377" max="5377" width="5.85546875" style="52" customWidth="1"/>
-    <col min="5378" max="5378" width="62.42578125" style="52" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" style="52" customWidth="1"/>
-    <col min="5380" max="5380" width="17.28515625" style="52" customWidth="1"/>
-    <col min="5381" max="5381" width="20.7109375" style="52" customWidth="1"/>
-    <col min="5382" max="5382" width="33.85546875" style="52" customWidth="1"/>
-    <col min="5383" max="5383" width="37.28515625" style="52" customWidth="1"/>
-    <col min="5384" max="5384" width="18.5703125" style="52" customWidth="1"/>
+    <col min="5377" max="5377" width="5.83203125" style="52" customWidth="1"/>
+    <col min="5378" max="5378" width="62.4140625" style="52" customWidth="1"/>
+    <col min="5379" max="5379" width="14.83203125" style="52" customWidth="1"/>
+    <col min="5380" max="5380" width="17.25" style="52" customWidth="1"/>
+    <col min="5381" max="5381" width="20.75" style="52" customWidth="1"/>
+    <col min="5382" max="5382" width="33.83203125" style="52" customWidth="1"/>
+    <col min="5383" max="5383" width="37.25" style="52" customWidth="1"/>
+    <col min="5384" max="5384" width="18.58203125" style="52" customWidth="1"/>
     <col min="5385" max="5632" width="9" style="52"/>
-    <col min="5633" max="5633" width="5.85546875" style="52" customWidth="1"/>
-    <col min="5634" max="5634" width="62.42578125" style="52" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" style="52" customWidth="1"/>
-    <col min="5636" max="5636" width="17.28515625" style="52" customWidth="1"/>
-    <col min="5637" max="5637" width="20.7109375" style="52" customWidth="1"/>
-    <col min="5638" max="5638" width="33.85546875" style="52" customWidth="1"/>
-    <col min="5639" max="5639" width="37.28515625" style="52" customWidth="1"/>
-    <col min="5640" max="5640" width="18.5703125" style="52" customWidth="1"/>
+    <col min="5633" max="5633" width="5.83203125" style="52" customWidth="1"/>
+    <col min="5634" max="5634" width="62.4140625" style="52" customWidth="1"/>
+    <col min="5635" max="5635" width="14.83203125" style="52" customWidth="1"/>
+    <col min="5636" max="5636" width="17.25" style="52" customWidth="1"/>
+    <col min="5637" max="5637" width="20.75" style="52" customWidth="1"/>
+    <col min="5638" max="5638" width="33.83203125" style="52" customWidth="1"/>
+    <col min="5639" max="5639" width="37.25" style="52" customWidth="1"/>
+    <col min="5640" max="5640" width="18.58203125" style="52" customWidth="1"/>
     <col min="5641" max="5888" width="9" style="52"/>
-    <col min="5889" max="5889" width="5.85546875" style="52" customWidth="1"/>
-    <col min="5890" max="5890" width="62.42578125" style="52" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" style="52" customWidth="1"/>
-    <col min="5892" max="5892" width="17.28515625" style="52" customWidth="1"/>
-    <col min="5893" max="5893" width="20.7109375" style="52" customWidth="1"/>
-    <col min="5894" max="5894" width="33.85546875" style="52" customWidth="1"/>
-    <col min="5895" max="5895" width="37.28515625" style="52" customWidth="1"/>
-    <col min="5896" max="5896" width="18.5703125" style="52" customWidth="1"/>
+    <col min="5889" max="5889" width="5.83203125" style="52" customWidth="1"/>
+    <col min="5890" max="5890" width="62.4140625" style="52" customWidth="1"/>
+    <col min="5891" max="5891" width="14.83203125" style="52" customWidth="1"/>
+    <col min="5892" max="5892" width="17.25" style="52" customWidth="1"/>
+    <col min="5893" max="5893" width="20.75" style="52" customWidth="1"/>
+    <col min="5894" max="5894" width="33.83203125" style="52" customWidth="1"/>
+    <col min="5895" max="5895" width="37.25" style="52" customWidth="1"/>
+    <col min="5896" max="5896" width="18.58203125" style="52" customWidth="1"/>
     <col min="5897" max="6144" width="9" style="52"/>
-    <col min="6145" max="6145" width="5.85546875" style="52" customWidth="1"/>
-    <col min="6146" max="6146" width="62.42578125" style="52" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" style="52" customWidth="1"/>
-    <col min="6148" max="6148" width="17.28515625" style="52" customWidth="1"/>
-    <col min="6149" max="6149" width="20.7109375" style="52" customWidth="1"/>
-    <col min="6150" max="6150" width="33.85546875" style="52" customWidth="1"/>
-    <col min="6151" max="6151" width="37.28515625" style="52" customWidth="1"/>
-    <col min="6152" max="6152" width="18.5703125" style="52" customWidth="1"/>
+    <col min="6145" max="6145" width="5.83203125" style="52" customWidth="1"/>
+    <col min="6146" max="6146" width="62.4140625" style="52" customWidth="1"/>
+    <col min="6147" max="6147" width="14.83203125" style="52" customWidth="1"/>
+    <col min="6148" max="6148" width="17.25" style="52" customWidth="1"/>
+    <col min="6149" max="6149" width="20.75" style="52" customWidth="1"/>
+    <col min="6150" max="6150" width="33.83203125" style="52" customWidth="1"/>
+    <col min="6151" max="6151" width="37.25" style="52" customWidth="1"/>
+    <col min="6152" max="6152" width="18.58203125" style="52" customWidth="1"/>
     <col min="6153" max="6400" width="9" style="52"/>
-    <col min="6401" max="6401" width="5.85546875" style="52" customWidth="1"/>
-    <col min="6402" max="6402" width="62.42578125" style="52" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" style="52" customWidth="1"/>
-    <col min="6404" max="6404" width="17.28515625" style="52" customWidth="1"/>
-    <col min="6405" max="6405" width="20.7109375" style="52" customWidth="1"/>
-    <col min="6406" max="6406" width="33.85546875" style="52" customWidth="1"/>
-    <col min="6407" max="6407" width="37.28515625" style="52" customWidth="1"/>
-    <col min="6408" max="6408" width="18.5703125" style="52" customWidth="1"/>
+    <col min="6401" max="6401" width="5.83203125" style="52" customWidth="1"/>
+    <col min="6402" max="6402" width="62.4140625" style="52" customWidth="1"/>
+    <col min="6403" max="6403" width="14.83203125" style="52" customWidth="1"/>
+    <col min="6404" max="6404" width="17.25" style="52" customWidth="1"/>
+    <col min="6405" max="6405" width="20.75" style="52" customWidth="1"/>
+    <col min="6406" max="6406" width="33.83203125" style="52" customWidth="1"/>
+    <col min="6407" max="6407" width="37.25" style="52" customWidth="1"/>
+    <col min="6408" max="6408" width="18.58203125" style="52" customWidth="1"/>
     <col min="6409" max="6656" width="9" style="52"/>
-    <col min="6657" max="6657" width="5.85546875" style="52" customWidth="1"/>
-    <col min="6658" max="6658" width="62.42578125" style="52" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" style="52" customWidth="1"/>
-    <col min="6660" max="6660" width="17.28515625" style="52" customWidth="1"/>
-    <col min="6661" max="6661" width="20.7109375" style="52" customWidth="1"/>
-    <col min="6662" max="6662" width="33.85546875" style="52" customWidth="1"/>
-    <col min="6663" max="6663" width="37.28515625" style="52" customWidth="1"/>
-    <col min="6664" max="6664" width="18.5703125" style="52" customWidth="1"/>
+    <col min="6657" max="6657" width="5.83203125" style="52" customWidth="1"/>
+    <col min="6658" max="6658" width="62.4140625" style="52" customWidth="1"/>
+    <col min="6659" max="6659" width="14.83203125" style="52" customWidth="1"/>
+    <col min="6660" max="6660" width="17.25" style="52" customWidth="1"/>
+    <col min="6661" max="6661" width="20.75" style="52" customWidth="1"/>
+    <col min="6662" max="6662" width="33.83203125" style="52" customWidth="1"/>
+    <col min="6663" max="6663" width="37.25" style="52" customWidth="1"/>
+    <col min="6664" max="6664" width="18.58203125" style="52" customWidth="1"/>
     <col min="6665" max="6912" width="9" style="52"/>
-    <col min="6913" max="6913" width="5.85546875" style="52" customWidth="1"/>
-    <col min="6914" max="6914" width="62.42578125" style="52" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" style="52" customWidth="1"/>
-    <col min="6916" max="6916" width="17.28515625" style="52" customWidth="1"/>
-    <col min="6917" max="6917" width="20.7109375" style="52" customWidth="1"/>
-    <col min="6918" max="6918" width="33.85546875" style="52" customWidth="1"/>
-    <col min="6919" max="6919" width="37.28515625" style="52" customWidth="1"/>
-    <col min="6920" max="6920" width="18.5703125" style="52" customWidth="1"/>
+    <col min="6913" max="6913" width="5.83203125" style="52" customWidth="1"/>
+    <col min="6914" max="6914" width="62.4140625" style="52" customWidth="1"/>
+    <col min="6915" max="6915" width="14.83203125" style="52" customWidth="1"/>
+    <col min="6916" max="6916" width="17.25" style="52" customWidth="1"/>
+    <col min="6917" max="6917" width="20.75" style="52" customWidth="1"/>
+    <col min="6918" max="6918" width="33.83203125" style="52" customWidth="1"/>
+    <col min="6919" max="6919" width="37.25" style="52" customWidth="1"/>
+    <col min="6920" max="6920" width="18.58203125" style="52" customWidth="1"/>
     <col min="6921" max="7168" width="9" style="52"/>
-    <col min="7169" max="7169" width="5.85546875" style="52" customWidth="1"/>
-    <col min="7170" max="7170" width="62.42578125" style="52" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" style="52" customWidth="1"/>
-    <col min="7172" max="7172" width="17.28515625" style="52" customWidth="1"/>
-    <col min="7173" max="7173" width="20.7109375" style="52" customWidth="1"/>
-    <col min="7174" max="7174" width="33.85546875" style="52" customWidth="1"/>
-    <col min="7175" max="7175" width="37.28515625" style="52" customWidth="1"/>
-    <col min="7176" max="7176" width="18.5703125" style="52" customWidth="1"/>
+    <col min="7169" max="7169" width="5.83203125" style="52" customWidth="1"/>
+    <col min="7170" max="7170" width="62.4140625" style="52" customWidth="1"/>
+    <col min="7171" max="7171" width="14.83203125" style="52" customWidth="1"/>
+    <col min="7172" max="7172" width="17.25" style="52" customWidth="1"/>
+    <col min="7173" max="7173" width="20.75" style="52" customWidth="1"/>
+    <col min="7174" max="7174" width="33.83203125" style="52" customWidth="1"/>
+    <col min="7175" max="7175" width="37.25" style="52" customWidth="1"/>
+    <col min="7176" max="7176" width="18.58203125" style="52" customWidth="1"/>
     <col min="7177" max="7424" width="9" style="52"/>
-    <col min="7425" max="7425" width="5.85546875" style="52" customWidth="1"/>
-    <col min="7426" max="7426" width="62.42578125" style="52" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" style="52" customWidth="1"/>
-    <col min="7428" max="7428" width="17.28515625" style="52" customWidth="1"/>
-    <col min="7429" max="7429" width="20.7109375" style="52" customWidth="1"/>
-    <col min="7430" max="7430" width="33.85546875" style="52" customWidth="1"/>
-    <col min="7431" max="7431" width="37.28515625" style="52" customWidth="1"/>
-    <col min="7432" max="7432" width="18.5703125" style="52" customWidth="1"/>
+    <col min="7425" max="7425" width="5.83203125" style="52" customWidth="1"/>
+    <col min="7426" max="7426" width="62.4140625" style="52" customWidth="1"/>
+    <col min="7427" max="7427" width="14.83203125" style="52" customWidth="1"/>
+    <col min="7428" max="7428" width="17.25" style="52" customWidth="1"/>
+    <col min="7429" max="7429" width="20.75" style="52" customWidth="1"/>
+    <col min="7430" max="7430" width="33.83203125" style="52" customWidth="1"/>
+    <col min="7431" max="7431" width="37.25" style="52" customWidth="1"/>
+    <col min="7432" max="7432" width="18.58203125" style="52" customWidth="1"/>
     <col min="7433" max="7680" width="9" style="52"/>
-    <col min="7681" max="7681" width="5.85546875" style="52" customWidth="1"/>
-    <col min="7682" max="7682" width="62.42578125" style="52" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" style="52" customWidth="1"/>
-    <col min="7684" max="7684" width="17.28515625" style="52" customWidth="1"/>
-    <col min="7685" max="7685" width="20.7109375" style="52" customWidth="1"/>
-    <col min="7686" max="7686" width="33.85546875" style="52" customWidth="1"/>
-    <col min="7687" max="7687" width="37.28515625" style="52" customWidth="1"/>
-    <col min="7688" max="7688" width="18.5703125" style="52" customWidth="1"/>
+    <col min="7681" max="7681" width="5.83203125" style="52" customWidth="1"/>
+    <col min="7682" max="7682" width="62.4140625" style="52" customWidth="1"/>
+    <col min="7683" max="7683" width="14.83203125" style="52" customWidth="1"/>
+    <col min="7684" max="7684" width="17.25" style="52" customWidth="1"/>
+    <col min="7685" max="7685" width="20.75" style="52" customWidth="1"/>
+    <col min="7686" max="7686" width="33.83203125" style="52" customWidth="1"/>
+    <col min="7687" max="7687" width="37.25" style="52" customWidth="1"/>
+    <col min="7688" max="7688" width="18.58203125" style="52" customWidth="1"/>
     <col min="7689" max="7936" width="9" style="52"/>
-    <col min="7937" max="7937" width="5.85546875" style="52" customWidth="1"/>
-    <col min="7938" max="7938" width="62.42578125" style="52" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" style="52" customWidth="1"/>
-    <col min="7940" max="7940" width="17.28515625" style="52" customWidth="1"/>
-    <col min="7941" max="7941" width="20.7109375" style="52" customWidth="1"/>
-    <col min="7942" max="7942" width="33.85546875" style="52" customWidth="1"/>
-    <col min="7943" max="7943" width="37.28515625" style="52" customWidth="1"/>
-    <col min="7944" max="7944" width="18.5703125" style="52" customWidth="1"/>
+    <col min="7937" max="7937" width="5.83203125" style="52" customWidth="1"/>
+    <col min="7938" max="7938" width="62.4140625" style="52" customWidth="1"/>
+    <col min="7939" max="7939" width="14.83203125" style="52" customWidth="1"/>
+    <col min="7940" max="7940" width="17.25" style="52" customWidth="1"/>
+    <col min="7941" max="7941" width="20.75" style="52" customWidth="1"/>
+    <col min="7942" max="7942" width="33.83203125" style="52" customWidth="1"/>
+    <col min="7943" max="7943" width="37.25" style="52" customWidth="1"/>
+    <col min="7944" max="7944" width="18.58203125" style="52" customWidth="1"/>
     <col min="7945" max="8192" width="9" style="52"/>
-    <col min="8193" max="8193" width="5.85546875" style="52" customWidth="1"/>
-    <col min="8194" max="8194" width="62.42578125" style="52" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" style="52" customWidth="1"/>
-    <col min="8196" max="8196" width="17.28515625" style="52" customWidth="1"/>
-    <col min="8197" max="8197" width="20.7109375" style="52" customWidth="1"/>
-    <col min="8198" max="8198" width="33.85546875" style="52" customWidth="1"/>
-    <col min="8199" max="8199" width="37.28515625" style="52" customWidth="1"/>
-    <col min="8200" max="8200" width="18.5703125" style="52" customWidth="1"/>
+    <col min="8193" max="8193" width="5.83203125" style="52" customWidth="1"/>
+    <col min="8194" max="8194" width="62.4140625" style="52" customWidth="1"/>
+    <col min="8195" max="8195" width="14.83203125" style="52" customWidth="1"/>
+    <col min="8196" max="8196" width="17.25" style="52" customWidth="1"/>
+    <col min="8197" max="8197" width="20.75" style="52" customWidth="1"/>
+    <col min="8198" max="8198" width="33.83203125" style="52" customWidth="1"/>
+    <col min="8199" max="8199" width="37.25" style="52" customWidth="1"/>
+    <col min="8200" max="8200" width="18.58203125" style="52" customWidth="1"/>
     <col min="8201" max="8448" width="9" style="52"/>
-    <col min="8449" max="8449" width="5.85546875" style="52" customWidth="1"/>
-    <col min="8450" max="8450" width="62.42578125" style="52" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" style="52" customWidth="1"/>
-    <col min="8452" max="8452" width="17.28515625" style="52" customWidth="1"/>
-    <col min="8453" max="8453" width="20.7109375" style="52" customWidth="1"/>
-    <col min="8454" max="8454" width="33.85546875" style="52" customWidth="1"/>
-    <col min="8455" max="8455" width="37.28515625" style="52" customWidth="1"/>
-    <col min="8456" max="8456" width="18.5703125" style="52" customWidth="1"/>
+    <col min="8449" max="8449" width="5.83203125" style="52" customWidth="1"/>
+    <col min="8450" max="8450" width="62.4140625" style="52" customWidth="1"/>
+    <col min="8451" max="8451" width="14.83203125" style="52" customWidth="1"/>
+    <col min="8452" max="8452" width="17.25" style="52" customWidth="1"/>
+    <col min="8453" max="8453" width="20.75" style="52" customWidth="1"/>
+    <col min="8454" max="8454" width="33.83203125" style="52" customWidth="1"/>
+    <col min="8455" max="8455" width="37.25" style="52" customWidth="1"/>
+    <col min="8456" max="8456" width="18.58203125" style="52" customWidth="1"/>
     <col min="8457" max="8704" width="9" style="52"/>
-    <col min="8705" max="8705" width="5.85546875" style="52" customWidth="1"/>
-    <col min="8706" max="8706" width="62.42578125" style="52" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" style="52" customWidth="1"/>
-    <col min="8708" max="8708" width="17.28515625" style="52" customWidth="1"/>
-    <col min="8709" max="8709" width="20.7109375" style="52" customWidth="1"/>
-    <col min="8710" max="8710" width="33.85546875" style="52" customWidth="1"/>
-    <col min="8711" max="8711" width="37.28515625" style="52" customWidth="1"/>
-    <col min="8712" max="8712" width="18.5703125" style="52" customWidth="1"/>
+    <col min="8705" max="8705" width="5.83203125" style="52" customWidth="1"/>
+    <col min="8706" max="8706" width="62.4140625" style="52" customWidth="1"/>
+    <col min="8707" max="8707" width="14.83203125" style="52" customWidth="1"/>
+    <col min="8708" max="8708" width="17.25" style="52" customWidth="1"/>
+    <col min="8709" max="8709" width="20.75" style="52" customWidth="1"/>
+    <col min="8710" max="8710" width="33.83203125" style="52" customWidth="1"/>
+    <col min="8711" max="8711" width="37.25" style="52" customWidth="1"/>
+    <col min="8712" max="8712" width="18.58203125" style="52" customWidth="1"/>
     <col min="8713" max="8960" width="9" style="52"/>
-    <col min="8961" max="8961" width="5.85546875" style="52" customWidth="1"/>
-    <col min="8962" max="8962" width="62.42578125" style="52" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" style="52" customWidth="1"/>
-    <col min="8964" max="8964" width="17.28515625" style="52" customWidth="1"/>
-    <col min="8965" max="8965" width="20.7109375" style="52" customWidth="1"/>
-    <col min="8966" max="8966" width="33.85546875" style="52" customWidth="1"/>
-    <col min="8967" max="8967" width="37.28515625" style="52" customWidth="1"/>
-    <col min="8968" max="8968" width="18.5703125" style="52" customWidth="1"/>
+    <col min="8961" max="8961" width="5.83203125" style="52" customWidth="1"/>
+    <col min="8962" max="8962" width="62.4140625" style="52" customWidth="1"/>
+    <col min="8963" max="8963" width="14.83203125" style="52" customWidth="1"/>
+    <col min="8964" max="8964" width="17.25" style="52" customWidth="1"/>
+    <col min="8965" max="8965" width="20.75" style="52" customWidth="1"/>
+    <col min="8966" max="8966" width="33.83203125" style="52" customWidth="1"/>
+    <col min="8967" max="8967" width="37.25" style="52" customWidth="1"/>
+    <col min="8968" max="8968" width="18.58203125" style="52" customWidth="1"/>
     <col min="8969" max="9216" width="9" style="52"/>
-    <col min="9217" max="9217" width="5.85546875" style="52" customWidth="1"/>
-    <col min="9218" max="9218" width="62.42578125" style="52" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" style="52" customWidth="1"/>
-    <col min="9220" max="9220" width="17.28515625" style="52" customWidth="1"/>
-    <col min="9221" max="9221" width="20.7109375" style="52" customWidth="1"/>
-    <col min="9222" max="9222" width="33.85546875" style="52" customWidth="1"/>
-    <col min="9223" max="9223" width="37.28515625" style="52" customWidth="1"/>
-    <col min="9224" max="9224" width="18.5703125" style="52" customWidth="1"/>
+    <col min="9217" max="9217" width="5.83203125" style="52" customWidth="1"/>
+    <col min="9218" max="9218" width="62.4140625" style="52" customWidth="1"/>
+    <col min="9219" max="9219" width="14.83203125" style="52" customWidth="1"/>
+    <col min="9220" max="9220" width="17.25" style="52" customWidth="1"/>
+    <col min="9221" max="9221" width="20.75" style="52" customWidth="1"/>
+    <col min="9222" max="9222" width="33.83203125" style="52" customWidth="1"/>
+    <col min="9223" max="9223" width="37.25" style="52" customWidth="1"/>
+    <col min="9224" max="9224" width="18.58203125" style="52" customWidth="1"/>
     <col min="9225" max="9472" width="9" style="52"/>
-    <col min="9473" max="9473" width="5.85546875" style="52" customWidth="1"/>
-    <col min="9474" max="9474" width="62.42578125" style="52" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" style="52" customWidth="1"/>
-    <col min="9476" max="9476" width="17.28515625" style="52" customWidth="1"/>
-    <col min="9477" max="9477" width="20.7109375" style="52" customWidth="1"/>
-    <col min="9478" max="9478" width="33.85546875" style="52" customWidth="1"/>
-    <col min="9479" max="9479" width="37.28515625" style="52" customWidth="1"/>
-    <col min="9480" max="9480" width="18.5703125" style="52" customWidth="1"/>
+    <col min="9473" max="9473" width="5.83203125" style="52" customWidth="1"/>
+    <col min="9474" max="9474" width="62.4140625" style="52" customWidth="1"/>
+    <col min="9475" max="9475" width="14.83203125" style="52" customWidth="1"/>
+    <col min="9476" max="9476" width="17.25" style="52" customWidth="1"/>
+    <col min="9477" max="9477" width="20.75" style="52" customWidth="1"/>
+    <col min="9478" max="9478" width="33.83203125" style="52" customWidth="1"/>
+    <col min="9479" max="9479" width="37.25" style="52" customWidth="1"/>
+    <col min="9480" max="9480" width="18.58203125" style="52" customWidth="1"/>
     <col min="9481" max="9728" width="9" style="52"/>
-    <col min="9729" max="9729" width="5.85546875" style="52" customWidth="1"/>
-    <col min="9730" max="9730" width="62.42578125" style="52" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" style="52" customWidth="1"/>
-    <col min="9732" max="9732" width="17.28515625" style="52" customWidth="1"/>
-    <col min="9733" max="9733" width="20.7109375" style="52" customWidth="1"/>
-    <col min="9734" max="9734" width="33.85546875" style="52" customWidth="1"/>
-    <col min="9735" max="9735" width="37.28515625" style="52" customWidth="1"/>
-    <col min="9736" max="9736" width="18.5703125" style="52" customWidth="1"/>
+    <col min="9729" max="9729" width="5.83203125" style="52" customWidth="1"/>
+    <col min="9730" max="9730" width="62.4140625" style="52" customWidth="1"/>
+    <col min="9731" max="9731" width="14.83203125" style="52" customWidth="1"/>
+    <col min="9732" max="9732" width="17.25" style="52" customWidth="1"/>
+    <col min="9733" max="9733" width="20.75" style="52" customWidth="1"/>
+    <col min="9734" max="9734" width="33.83203125" style="52" customWidth="1"/>
+    <col min="9735" max="9735" width="37.25" style="52" customWidth="1"/>
+    <col min="9736" max="9736" width="18.58203125" style="52" customWidth="1"/>
     <col min="9737" max="9984" width="9" style="52"/>
-    <col min="9985" max="9985" width="5.85546875" style="52" customWidth="1"/>
-    <col min="9986" max="9986" width="62.42578125" style="52" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" style="52" customWidth="1"/>
-    <col min="9988" max="9988" width="17.28515625" style="52" customWidth="1"/>
-    <col min="9989" max="9989" width="20.7109375" style="52" customWidth="1"/>
-    <col min="9990" max="9990" width="33.85546875" style="52" customWidth="1"/>
-    <col min="9991" max="9991" width="37.28515625" style="52" customWidth="1"/>
-    <col min="9992" max="9992" width="18.5703125" style="52" customWidth="1"/>
+    <col min="9985" max="9985" width="5.83203125" style="52" customWidth="1"/>
+    <col min="9986" max="9986" width="62.4140625" style="52" customWidth="1"/>
+    <col min="9987" max="9987" width="14.83203125" style="52" customWidth="1"/>
+    <col min="9988" max="9988" width="17.25" style="52" customWidth="1"/>
+    <col min="9989" max="9989" width="20.75" style="52" customWidth="1"/>
+    <col min="9990" max="9990" width="33.83203125" style="52" customWidth="1"/>
+    <col min="9991" max="9991" width="37.25" style="52" customWidth="1"/>
+    <col min="9992" max="9992" width="18.58203125" style="52" customWidth="1"/>
     <col min="9993" max="10240" width="9" style="52"/>
-    <col min="10241" max="10241" width="5.85546875" style="52" customWidth="1"/>
-    <col min="10242" max="10242" width="62.42578125" style="52" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" style="52" customWidth="1"/>
-    <col min="10244" max="10244" width="17.28515625" style="52" customWidth="1"/>
-    <col min="10245" max="10245" width="20.7109375" style="52" customWidth="1"/>
-    <col min="10246" max="10246" width="33.85546875" style="52" customWidth="1"/>
-    <col min="10247" max="10247" width="37.28515625" style="52" customWidth="1"/>
-    <col min="10248" max="10248" width="18.5703125" style="52" customWidth="1"/>
+    <col min="10241" max="10241" width="5.83203125" style="52" customWidth="1"/>
+    <col min="10242" max="10242" width="62.4140625" style="52" customWidth="1"/>
+    <col min="10243" max="10243" width="14.83203125" style="52" customWidth="1"/>
+    <col min="10244" max="10244" width="17.25" style="52" customWidth="1"/>
+    <col min="10245" max="10245" width="20.75" style="52" customWidth="1"/>
+    <col min="10246" max="10246" width="33.83203125" style="52" customWidth="1"/>
+    <col min="10247" max="10247" width="37.25" style="52" customWidth="1"/>
+    <col min="10248" max="10248" width="18.58203125" style="52" customWidth="1"/>
     <col min="10249" max="10496" width="9" style="52"/>
-    <col min="10497" max="10497" width="5.85546875" style="52" customWidth="1"/>
-    <col min="10498" max="10498" width="62.42578125" style="52" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" style="52" customWidth="1"/>
-    <col min="10500" max="10500" width="17.28515625" style="52" customWidth="1"/>
-    <col min="10501" max="10501" width="20.7109375" style="52" customWidth="1"/>
-    <col min="10502" max="10502" width="33.85546875" style="52" customWidth="1"/>
-    <col min="10503" max="10503" width="37.28515625" style="52" customWidth="1"/>
-    <col min="10504" max="10504" width="18.5703125" style="52" customWidth="1"/>
+    <col min="10497" max="10497" width="5.83203125" style="52" customWidth="1"/>
+    <col min="10498" max="10498" width="62.4140625" style="52" customWidth="1"/>
+    <col min="10499" max="10499" width="14.83203125" style="52" customWidth="1"/>
+    <col min="10500" max="10500" width="17.25" style="52" customWidth="1"/>
+    <col min="10501" max="10501" width="20.75" style="52" customWidth="1"/>
+    <col min="10502" max="10502" width="33.83203125" style="52" customWidth="1"/>
+    <col min="10503" max="10503" width="37.25" style="52" customWidth="1"/>
+    <col min="10504" max="10504" width="18.58203125" style="52" customWidth="1"/>
     <col min="10505" max="10752" width="9" style="52"/>
-    <col min="10753" max="10753" width="5.85546875" style="52" customWidth="1"/>
-    <col min="10754" max="10754" width="62.42578125" style="52" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" style="52" customWidth="1"/>
-    <col min="10756" max="10756" width="17.28515625" style="52" customWidth="1"/>
-    <col min="10757" max="10757" width="20.7109375" style="52" customWidth="1"/>
-    <col min="10758" max="10758" width="33.85546875" style="52" customWidth="1"/>
-    <col min="10759" max="10759" width="37.28515625" style="52" customWidth="1"/>
-    <col min="10760" max="10760" width="18.5703125" style="52" customWidth="1"/>
+    <col min="10753" max="10753" width="5.83203125" style="52" customWidth="1"/>
+    <col min="10754" max="10754" width="62.4140625" style="52" customWidth="1"/>
+    <col min="10755" max="10755" width="14.83203125" style="52" customWidth="1"/>
+    <col min="10756" max="10756" width="17.25" style="52" customWidth="1"/>
+    <col min="10757" max="10757" width="20.75" style="52" customWidth="1"/>
+    <col min="10758" max="10758" width="33.83203125" style="52" customWidth="1"/>
+    <col min="10759" max="10759" width="37.25" style="52" customWidth="1"/>
+    <col min="10760" max="10760" width="18.58203125" style="52" customWidth="1"/>
     <col min="10761" max="11008" width="9" style="52"/>
-    <col min="11009" max="11009" width="5.85546875" style="52" customWidth="1"/>
-    <col min="11010" max="11010" width="62.42578125" style="52" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" style="52" customWidth="1"/>
-    <col min="11012" max="11012" width="17.28515625" style="52" customWidth="1"/>
-    <col min="11013" max="11013" width="20.7109375" style="52" customWidth="1"/>
-    <col min="11014" max="11014" width="33.85546875" style="52" customWidth="1"/>
-    <col min="11015" max="11015" width="37.28515625" style="52" customWidth="1"/>
-    <col min="11016" max="11016" width="18.5703125" style="52" customWidth="1"/>
+    <col min="11009" max="11009" width="5.83203125" style="52" customWidth="1"/>
+    <col min="11010" max="11010" width="62.4140625" style="52" customWidth="1"/>
+    <col min="11011" max="11011" width="14.83203125" style="52" customWidth="1"/>
+    <col min="11012" max="11012" width="17.25" style="52" customWidth="1"/>
+    <col min="11013" max="11013" width="20.75" style="52" customWidth="1"/>
+    <col min="11014" max="11014" width="33.83203125" style="52" customWidth="1"/>
+    <col min="11015" max="11015" width="37.25" style="52" customWidth="1"/>
+    <col min="11016" max="11016" width="18.58203125" style="52" customWidth="1"/>
     <col min="11017" max="11264" width="9" style="52"/>
-    <col min="11265" max="11265" width="5.85546875" style="52" customWidth="1"/>
-    <col min="11266" max="11266" width="62.42578125" style="52" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" style="52" customWidth="1"/>
-    <col min="11268" max="11268" width="17.28515625" style="52" customWidth="1"/>
-    <col min="11269" max="11269" width="20.7109375" style="52" customWidth="1"/>
-    <col min="11270" max="11270" width="33.85546875" style="52" customWidth="1"/>
-    <col min="11271" max="11271" width="37.28515625" style="52" customWidth="1"/>
-    <col min="11272" max="11272" width="18.5703125" style="52" customWidth="1"/>
+    <col min="11265" max="11265" width="5.83203125" style="52" customWidth="1"/>
+    <col min="11266" max="11266" width="62.4140625" style="52" customWidth="1"/>
+    <col min="11267" max="11267" width="14.83203125" style="52" customWidth="1"/>
+    <col min="11268" max="11268" width="17.25" style="52" customWidth="1"/>
+    <col min="11269" max="11269" width="20.75" style="52" customWidth="1"/>
+    <col min="11270" max="11270" width="33.83203125" style="52" customWidth="1"/>
+    <col min="11271" max="11271" width="37.25" style="52" customWidth="1"/>
+    <col min="11272" max="11272" width="18.58203125" style="52" customWidth="1"/>
     <col min="11273" max="11520" width="9" style="52"/>
-    <col min="11521" max="11521" width="5.85546875" style="52" customWidth="1"/>
-    <col min="11522" max="11522" width="62.42578125" style="52" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" style="52" customWidth="1"/>
-    <col min="11524" max="11524" width="17.28515625" style="52" customWidth="1"/>
-    <col min="11525" max="11525" width="20.7109375" style="52" customWidth="1"/>
-    <col min="11526" max="11526" width="33.85546875" style="52" customWidth="1"/>
-    <col min="11527" max="11527" width="37.28515625" style="52" customWidth="1"/>
-    <col min="11528" max="11528" width="18.5703125" style="52" customWidth="1"/>
+    <col min="11521" max="11521" width="5.83203125" style="52" customWidth="1"/>
+    <col min="11522" max="11522" width="62.4140625" style="52" customWidth="1"/>
+    <col min="11523" max="11523" width="14.83203125" style="52" customWidth="1"/>
+    <col min="11524" max="11524" width="17.25" style="52" customWidth="1"/>
+    <col min="11525" max="11525" width="20.75" style="52" customWidth="1"/>
+    <col min="11526" max="11526" width="33.83203125" style="52" customWidth="1"/>
+    <col min="11527" max="11527" width="37.25" style="52" customWidth="1"/>
+    <col min="11528" max="11528" width="18.58203125" style="52" customWidth="1"/>
     <col min="11529" max="11776" width="9" style="52"/>
-    <col min="11777" max="11777" width="5.85546875" style="52" customWidth="1"/>
-    <col min="11778" max="11778" width="62.42578125" style="52" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" style="52" customWidth="1"/>
-    <col min="11780" max="11780" width="17.28515625" style="52" customWidth="1"/>
-    <col min="11781" max="11781" width="20.7109375" style="52" customWidth="1"/>
-    <col min="11782" max="11782" width="33.85546875" style="52" customWidth="1"/>
-    <col min="11783" max="11783" width="37.28515625" style="52" customWidth="1"/>
-    <col min="11784" max="11784" width="18.5703125" style="52" customWidth="1"/>
+    <col min="11777" max="11777" width="5.83203125" style="52" customWidth="1"/>
+    <col min="11778" max="11778" width="62.4140625" style="52" customWidth="1"/>
+    <col min="11779" max="11779" width="14.83203125" style="52" customWidth="1"/>
+    <col min="11780" max="11780" width="17.25" style="52" customWidth="1"/>
+    <col min="11781" max="11781" width="20.75" style="52" customWidth="1"/>
+    <col min="11782" max="11782" width="33.83203125" style="52" customWidth="1"/>
+    <col min="11783" max="11783" width="37.25" style="52" customWidth="1"/>
+    <col min="11784" max="11784" width="18.58203125" style="52" customWidth="1"/>
     <col min="11785" max="12032" width="9" style="52"/>
-    <col min="12033" max="12033" width="5.85546875" style="52" customWidth="1"/>
-    <col min="12034" max="12034" width="62.42578125" style="52" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" style="52" customWidth="1"/>
-    <col min="12036" max="12036" width="17.28515625" style="52" customWidth="1"/>
-    <col min="12037" max="12037" width="20.7109375" style="52" customWidth="1"/>
-    <col min="12038" max="12038" width="33.85546875" style="52" customWidth="1"/>
-    <col min="12039" max="12039" width="37.28515625" style="52" customWidth="1"/>
-    <col min="12040" max="12040" width="18.5703125" style="52" customWidth="1"/>
+    <col min="12033" max="12033" width="5.83203125" style="52" customWidth="1"/>
+    <col min="12034" max="12034" width="62.4140625" style="52" customWidth="1"/>
+    <col min="12035" max="12035" width="14.83203125" style="52" customWidth="1"/>
+    <col min="12036" max="12036" width="17.25" style="52" customWidth="1"/>
+    <col min="12037" max="12037" width="20.75" style="52" customWidth="1"/>
+    <col min="12038" max="12038" width="33.83203125" style="52" customWidth="1"/>
+    <col min="12039" max="12039" width="37.25" style="52" customWidth="1"/>
+    <col min="12040" max="12040" width="18.58203125" style="52" customWidth="1"/>
     <col min="12041" max="12288" width="9" style="52"/>
-    <col min="12289" max="12289" width="5.85546875" style="52" customWidth="1"/>
-    <col min="12290" max="12290" width="62.42578125" style="52" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" style="52" customWidth="1"/>
-    <col min="12292" max="12292" width="17.28515625" style="52" customWidth="1"/>
-    <col min="12293" max="12293" width="20.7109375" style="52" customWidth="1"/>
-    <col min="12294" max="12294" width="33.85546875" style="52" customWidth="1"/>
-    <col min="12295" max="12295" width="37.28515625" style="52" customWidth="1"/>
-    <col min="12296" max="12296" width="18.5703125" style="52" customWidth="1"/>
+    <col min="12289" max="12289" width="5.83203125" style="52" customWidth="1"/>
+    <col min="12290" max="12290" width="62.4140625" style="52" customWidth="1"/>
+    <col min="12291" max="12291" width="14.83203125" style="52" customWidth="1"/>
+    <col min="12292" max="12292" width="17.25" style="52" customWidth="1"/>
+    <col min="12293" max="12293" width="20.75" style="52" customWidth="1"/>
+    <col min="12294" max="12294" width="33.83203125" style="52" customWidth="1"/>
+    <col min="12295" max="12295" width="37.25" style="52" customWidth="1"/>
+    <col min="12296" max="12296" width="18.58203125" style="52" customWidth="1"/>
     <col min="12297" max="12544" width="9" style="52"/>
-    <col min="12545" max="12545" width="5.85546875" style="52" customWidth="1"/>
-    <col min="12546" max="12546" width="62.42578125" style="52" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" style="52" customWidth="1"/>
-    <col min="12548" max="12548" width="17.28515625" style="52" customWidth="1"/>
-    <col min="12549" max="12549" width="20.7109375" style="52" customWidth="1"/>
-    <col min="12550" max="12550" width="33.85546875" style="52" customWidth="1"/>
-    <col min="12551" max="12551" width="37.28515625" style="52" customWidth="1"/>
-    <col min="12552" max="12552" width="18.5703125" style="52" customWidth="1"/>
+    <col min="12545" max="12545" width="5.83203125" style="52" customWidth="1"/>
+    <col min="12546" max="12546" width="62.4140625" style="52" customWidth="1"/>
+    <col min="12547" max="12547" width="14.83203125" style="52" customWidth="1"/>
+    <col min="12548" max="12548" width="17.25" style="52" customWidth="1"/>
+    <col min="12549" max="12549" width="20.75" style="52" customWidth="1"/>
+    <col min="12550" max="12550" width="33.83203125" style="52" customWidth="1"/>
+    <col min="12551" max="12551" width="37.25" style="52" customWidth="1"/>
+    <col min="12552" max="12552" width="18.58203125" style="52" customWidth="1"/>
     <col min="12553" max="12800" width="9" style="52"/>
-    <col min="12801" max="12801" width="5.85546875" style="52" customWidth="1"/>
-    <col min="12802" max="12802" width="62.42578125" style="52" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" style="52" customWidth="1"/>
-    <col min="12804" max="12804" width="17.28515625" style="52" customWidth="1"/>
-    <col min="12805" max="12805" width="20.7109375" style="52" customWidth="1"/>
-    <col min="12806" max="12806" width="33.85546875" style="52" customWidth="1"/>
-    <col min="12807" max="12807" width="37.28515625" style="52" customWidth="1"/>
-    <col min="12808" max="12808" width="18.5703125" style="52" customWidth="1"/>
+    <col min="12801" max="12801" width="5.83203125" style="52" customWidth="1"/>
+    <col min="12802" max="12802" width="62.4140625" style="52" customWidth="1"/>
+    <col min="12803" max="12803" width="14.83203125" style="52" customWidth="1"/>
+    <col min="12804" max="12804" width="17.25" style="52" customWidth="1"/>
+    <col min="12805" max="12805" width="20.75" style="52" customWidth="1"/>
+    <col min="12806" max="12806" width="33.83203125" style="52" customWidth="1"/>
+    <col min="12807" max="12807" width="37.25" style="52" customWidth="1"/>
+    <col min="12808" max="12808" width="18.58203125" style="52" customWidth="1"/>
     <col min="12809" max="13056" width="9" style="52"/>
-    <col min="13057" max="13057" width="5.85546875" style="52" customWidth="1"/>
-    <col min="13058" max="13058" width="62.42578125" style="52" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" style="52" customWidth="1"/>
-    <col min="13060" max="13060" width="17.28515625" style="52" customWidth="1"/>
-    <col min="13061" max="13061" width="20.7109375" style="52" customWidth="1"/>
-    <col min="13062" max="13062" width="33.85546875" style="52" customWidth="1"/>
-    <col min="13063" max="13063" width="37.28515625" style="52" customWidth="1"/>
-    <col min="13064" max="13064" width="18.5703125" style="52" customWidth="1"/>
+    <col min="13057" max="13057" width="5.83203125" style="52" customWidth="1"/>
+    <col min="13058" max="13058" width="62.4140625" style="52" customWidth="1"/>
+    <col min="13059" max="13059" width="14.83203125" style="52" customWidth="1"/>
+    <col min="13060" max="13060" width="17.25" style="52" customWidth="1"/>
+    <col min="13061" max="13061" width="20.75" style="52" customWidth="1"/>
+    <col min="13062" max="13062" width="33.83203125" style="52" customWidth="1"/>
+    <col min="13063" max="13063" width="37.25" style="52" customWidth="1"/>
+    <col min="13064" max="13064" width="18.58203125" style="52" customWidth="1"/>
     <col min="13065" max="13312" width="9" style="52"/>
-    <col min="13313" max="13313" width="5.85546875" style="52" customWidth="1"/>
-    <col min="13314" max="13314" width="62.42578125" style="52" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" style="52" customWidth="1"/>
-    <col min="13316" max="13316" width="17.28515625" style="52" customWidth="1"/>
-    <col min="13317" max="13317" width="20.7109375" style="52" customWidth="1"/>
-    <col min="13318" max="13318" width="33.85546875" style="52" customWidth="1"/>
-    <col min="13319" max="13319" width="37.28515625" style="52" customWidth="1"/>
-    <col min="13320" max="13320" width="18.5703125" style="52" customWidth="1"/>
+    <col min="13313" max="13313" width="5.83203125" style="52" customWidth="1"/>
+    <col min="13314" max="13314" width="62.4140625" style="52" customWidth="1"/>
+    <col min="13315" max="13315" width="14.83203125" style="52" customWidth="1"/>
+    <col min="13316" max="13316" width="17.25" style="52" customWidth="1"/>
+    <col min="13317" max="13317" width="20.75" style="52" customWidth="1"/>
+    <col min="13318" max="13318" width="33.83203125" style="52" customWidth="1"/>
+    <col min="13319" max="13319" width="37.25" style="52" customWidth="1"/>
+    <col min="13320" max="13320" width="18.58203125" style="52" customWidth="1"/>
     <col min="13321" max="13568" width="9" style="52"/>
-    <col min="13569" max="13569" width="5.85546875" style="52" customWidth="1"/>
-    <col min="13570" max="13570" width="62.42578125" style="52" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" style="52" customWidth="1"/>
-    <col min="13572" max="13572" width="17.28515625" style="52" customWidth="1"/>
-    <col min="13573" max="13573" width="20.7109375" style="52" customWidth="1"/>
-    <col min="13574" max="13574" width="33.85546875" style="52" customWidth="1"/>
-    <col min="13575" max="13575" width="37.28515625" style="52" customWidth="1"/>
-    <col min="13576" max="13576" width="18.5703125" style="52" customWidth="1"/>
+    <col min="13569" max="13569" width="5.83203125" style="52" customWidth="1"/>
+    <col min="13570" max="13570" width="62.4140625" style="52" customWidth="1"/>
+    <col min="13571" max="13571" width="14.83203125" style="52" customWidth="1"/>
+    <col min="13572" max="13572" width="17.25" style="52" customWidth="1"/>
+    <col min="13573" max="13573" width="20.75" style="52" customWidth="1"/>
+    <col min="13574" max="13574" width="33.83203125" style="52" customWidth="1"/>
+    <col min="13575" max="13575" width="37.25" style="52" customWidth="1"/>
+    <col min="13576" max="13576" width="18.58203125" style="52" customWidth="1"/>
     <col min="13577" max="13824" width="9" style="52"/>
-    <col min="13825" max="13825" width="5.85546875" style="52" customWidth="1"/>
-    <col min="13826" max="13826" width="62.42578125" style="52" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" style="52" customWidth="1"/>
-    <col min="13828" max="13828" width="17.28515625" style="52" customWidth="1"/>
-    <col min="13829" max="13829" width="20.7109375" style="52" customWidth="1"/>
-    <col min="13830" max="13830" width="33.85546875" style="52" customWidth="1"/>
-    <col min="13831" max="13831" width="37.28515625" style="52" customWidth="1"/>
-    <col min="13832" max="13832" width="18.5703125" style="52" customWidth="1"/>
+    <col min="13825" max="13825" width="5.83203125" style="52" customWidth="1"/>
+    <col min="13826" max="13826" width="62.4140625" style="52" customWidth="1"/>
+    <col min="13827" max="13827" width="14.83203125" style="52" customWidth="1"/>
+    <col min="13828" max="13828" width="17.25" style="52" customWidth="1"/>
+    <col min="13829" max="13829" width="20.75" style="52" customWidth="1"/>
+    <col min="13830" max="13830" width="33.83203125" style="52" customWidth="1"/>
+    <col min="13831" max="13831" width="37.25" style="52" customWidth="1"/>
+    <col min="13832" max="13832" width="18.58203125" style="52" customWidth="1"/>
     <col min="13833" max="14080" width="9" style="52"/>
-    <col min="14081" max="14081" width="5.85546875" style="52" customWidth="1"/>
-    <col min="14082" max="14082" width="62.42578125" style="52" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" style="52" customWidth="1"/>
-    <col min="14084" max="14084" width="17.28515625" style="52" customWidth="1"/>
-    <col min="14085" max="14085" width="20.7109375" style="52" customWidth="1"/>
-    <col min="14086" max="14086" width="33.85546875" style="52" customWidth="1"/>
-    <col min="14087" max="14087" width="37.28515625" style="52" customWidth="1"/>
-    <col min="14088" max="14088" width="18.5703125" style="52" customWidth="1"/>
+    <col min="14081" max="14081" width="5.83203125" style="52" customWidth="1"/>
+    <col min="14082" max="14082" width="62.4140625" style="52" customWidth="1"/>
+    <col min="14083" max="14083" width="14.83203125" style="52" customWidth="1"/>
+    <col min="14084" max="14084" width="17.25" style="52" customWidth="1"/>
+    <col min="14085" max="14085" width="20.75" style="52" customWidth="1"/>
+    <col min="14086" max="14086" width="33.83203125" style="52" customWidth="1"/>
+    <col min="14087" max="14087" width="37.25" style="52" customWidth="1"/>
+    <col min="14088" max="14088" width="18.58203125" style="52" customWidth="1"/>
     <col min="14089" max="14336" width="9" style="52"/>
-    <col min="14337" max="14337" width="5.85546875" style="52" customWidth="1"/>
-    <col min="14338" max="14338" width="62.42578125" style="52" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" style="52" customWidth="1"/>
-    <col min="14340" max="14340" width="17.28515625" style="52" customWidth="1"/>
-    <col min="14341" max="14341" width="20.7109375" style="52" customWidth="1"/>
-    <col min="14342" max="14342" width="33.85546875" style="52" customWidth="1"/>
-    <col min="14343" max="14343" width="37.28515625" style="52" customWidth="1"/>
-    <col min="14344" max="14344" width="18.5703125" style="52" customWidth="1"/>
+    <col min="14337" max="14337" width="5.83203125" style="52" customWidth="1"/>
+    <col min="14338" max="14338" width="62.4140625" style="52" customWidth="1"/>
+    <col min="14339" max="14339" width="14.83203125" style="52" customWidth="1"/>
+    <col min="14340" max="14340" width="17.25" style="52" customWidth="1"/>
+    <col min="14341" max="14341" width="20.75" style="52" customWidth="1"/>
+    <col min="14342" max="14342" width="33.83203125" style="52" customWidth="1"/>
+    <col min="14343" max="14343" width="37.25" style="52" customWidth="1"/>
+    <col min="14344" max="14344" width="18.58203125" style="52" customWidth="1"/>
     <col min="14345" max="14592" width="9" style="52"/>
-    <col min="14593" max="14593" width="5.85546875" style="52" customWidth="1"/>
-    <col min="14594" max="14594" width="62.42578125" style="52" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" style="52" customWidth="1"/>
-    <col min="14596" max="14596" width="17.28515625" style="52" customWidth="1"/>
-    <col min="14597" max="14597" width="20.7109375" style="52" customWidth="1"/>
-    <col min="14598" max="14598" width="33.85546875" style="52" customWidth="1"/>
-    <col min="14599" max="14599" width="37.28515625" style="52" customWidth="1"/>
-    <col min="14600" max="14600" width="18.5703125" style="52" customWidth="1"/>
+    <col min="14593" max="14593" width="5.83203125" style="52" customWidth="1"/>
+    <col min="14594" max="14594" width="62.4140625" style="52" customWidth="1"/>
+    <col min="14595" max="14595" width="14.83203125" style="52" customWidth="1"/>
+    <col min="14596" max="14596" width="17.25" style="52" customWidth="1"/>
+    <col min="14597" max="14597" width="20.75" style="52" customWidth="1"/>
+    <col min="14598" max="14598" width="33.83203125" style="52" customWidth="1"/>
+    <col min="14599" max="14599" width="37.25" style="52" customWidth="1"/>
+    <col min="14600" max="14600" width="18.58203125" style="52" customWidth="1"/>
     <col min="14601" max="14848" width="9" style="52"/>
-    <col min="14849" max="14849" width="5.85546875" style="52" customWidth="1"/>
-    <col min="14850" max="14850" width="62.42578125" style="52" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" style="52" customWidth="1"/>
-    <col min="14852" max="14852" width="17.28515625" style="52" customWidth="1"/>
-    <col min="14853" max="14853" width="20.7109375" style="52" customWidth="1"/>
-    <col min="14854" max="14854" width="33.85546875" style="52" customWidth="1"/>
-    <col min="14855" max="14855" width="37.28515625" style="52" customWidth="1"/>
-    <col min="14856" max="14856" width="18.5703125" style="52" customWidth="1"/>
+    <col min="14849" max="14849" width="5.83203125" style="52" customWidth="1"/>
+    <col min="14850" max="14850" width="62.4140625" style="52" customWidth="1"/>
+    <col min="14851" max="14851" width="14.83203125" style="52" customWidth="1"/>
+    <col min="14852" max="14852" width="17.25" style="52" customWidth="1"/>
+    <col min="14853" max="14853" width="20.75" style="52" customWidth="1"/>
+    <col min="14854" max="14854" width="33.83203125" style="52" customWidth="1"/>
+    <col min="14855" max="14855" width="37.25" style="52" customWidth="1"/>
+    <col min="14856" max="14856" width="18.58203125" style="52" customWidth="1"/>
     <col min="14857" max="15104" width="9" style="52"/>
-    <col min="15105" max="15105" width="5.85546875" style="52" customWidth="1"/>
-    <col min="15106" max="15106" width="62.42578125" style="52" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" style="52" customWidth="1"/>
-    <col min="15108" max="15108" width="17.28515625" style="52" customWidth="1"/>
-    <col min="15109" max="15109" width="20.7109375" style="52" customWidth="1"/>
-    <col min="15110" max="15110" width="33.85546875" style="52" customWidth="1"/>
-    <col min="15111" max="15111" width="37.28515625" style="52" customWidth="1"/>
-    <col min="15112" max="15112" width="18.5703125" style="52" customWidth="1"/>
+    <col min="15105" max="15105" width="5.83203125" style="52" customWidth="1"/>
+    <col min="15106" max="15106" width="62.4140625" style="52" customWidth="1"/>
+    <col min="15107" max="15107" width="14.83203125" style="52" customWidth="1"/>
+    <col min="15108" max="15108" width="17.25" style="52" customWidth="1"/>
+    <col min="15109" max="15109" width="20.75" style="52" customWidth="1"/>
+    <col min="15110" max="15110" width="33.83203125" style="52" customWidth="1"/>
+    <col min="15111" max="15111" width="37.25" style="52" customWidth="1"/>
+    <col min="15112" max="15112" width="18.58203125" style="52" customWidth="1"/>
     <col min="15113" max="15360" width="9" style="52"/>
-    <col min="15361" max="15361" width="5.85546875" style="52" customWidth="1"/>
-    <col min="15362" max="15362" width="62.42578125" style="52" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" style="52" customWidth="1"/>
-    <col min="15364" max="15364" width="17.28515625" style="52" customWidth="1"/>
-    <col min="15365" max="15365" width="20.7109375" style="52" customWidth="1"/>
-    <col min="15366" max="15366" width="33.85546875" style="52" customWidth="1"/>
-    <col min="15367" max="15367" width="37.28515625" style="52" customWidth="1"/>
-    <col min="15368" max="15368" width="18.5703125" style="52" customWidth="1"/>
+    <col min="15361" max="15361" width="5.83203125" style="52" customWidth="1"/>
+    <col min="15362" max="15362" width="62.4140625" style="52" customWidth="1"/>
+    <col min="15363" max="15363" width="14.83203125" style="52" customWidth="1"/>
+    <col min="15364" max="15364" width="17.25" style="52" customWidth="1"/>
+    <col min="15365" max="15365" width="20.75" style="52" customWidth="1"/>
+    <col min="15366" max="15366" width="33.83203125" style="52" customWidth="1"/>
+    <col min="15367" max="15367" width="37.25" style="52" customWidth="1"/>
+    <col min="15368" max="15368" width="18.58203125" style="52" customWidth="1"/>
     <col min="15369" max="15616" width="9" style="52"/>
-    <col min="15617" max="15617" width="5.85546875" style="52" customWidth="1"/>
-    <col min="15618" max="15618" width="62.42578125" style="52" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" style="52" customWidth="1"/>
-    <col min="15620" max="15620" width="17.28515625" style="52" customWidth="1"/>
-    <col min="15621" max="15621" width="20.7109375" style="52" customWidth="1"/>
-    <col min="15622" max="15622" width="33.85546875" style="52" customWidth="1"/>
-    <col min="15623" max="15623" width="37.28515625" style="52" customWidth="1"/>
-    <col min="15624" max="15624" width="18.5703125" style="52" customWidth="1"/>
+    <col min="15617" max="15617" width="5.83203125" style="52" customWidth="1"/>
+    <col min="15618" max="15618" width="62.4140625" style="52" customWidth="1"/>
+    <col min="15619" max="15619" width="14.83203125" style="52" customWidth="1"/>
+    <col min="15620" max="15620" width="17.25" style="52" customWidth="1"/>
+    <col min="15621" max="15621" width="20.75" style="52" customWidth="1"/>
+    <col min="15622" max="15622" width="33.83203125" style="52" customWidth="1"/>
+    <col min="15623" max="15623" width="37.25" style="52" customWidth="1"/>
+    <col min="15624" max="15624" width="18.58203125" style="52" customWidth="1"/>
     <col min="15625" max="15872" width="9" style="52"/>
-    <col min="15873" max="15873" width="5.85546875" style="52" customWidth="1"/>
-    <col min="15874" max="15874" width="62.42578125" style="52" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" style="52" customWidth="1"/>
-    <col min="15876" max="15876" width="17.28515625" style="52" customWidth="1"/>
-    <col min="15877" max="15877" width="20.7109375" style="52" customWidth="1"/>
-    <col min="15878" max="15878" width="33.85546875" style="52" customWidth="1"/>
-    <col min="15879" max="15879" width="37.28515625" style="52" customWidth="1"/>
-    <col min="15880" max="15880" width="18.5703125" style="52" customWidth="1"/>
+    <col min="15873" max="15873" width="5.83203125" style="52" customWidth="1"/>
+    <col min="15874" max="15874" width="62.4140625" style="52" customWidth="1"/>
+    <col min="15875" max="15875" width="14.83203125" style="52" customWidth="1"/>
+    <col min="15876" max="15876" width="17.25" style="52" customWidth="1"/>
+    <col min="15877" max="15877" width="20.75" style="52" customWidth="1"/>
+    <col min="15878" max="15878" width="33.83203125" style="52" customWidth="1"/>
+    <col min="15879" max="15879" width="37.25" style="52" customWidth="1"/>
+    <col min="15880" max="15880" width="18.58203125" style="52" customWidth="1"/>
     <col min="15881" max="16128" width="9" style="52"/>
-    <col min="16129" max="16129" width="5.85546875" style="52" customWidth="1"/>
-    <col min="16130" max="16130" width="62.42578125" style="52" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" style="52" customWidth="1"/>
-    <col min="16132" max="16132" width="17.28515625" style="52" customWidth="1"/>
-    <col min="16133" max="16133" width="20.7109375" style="52" customWidth="1"/>
-    <col min="16134" max="16134" width="33.85546875" style="52" customWidth="1"/>
-    <col min="16135" max="16135" width="37.28515625" style="52" customWidth="1"/>
-    <col min="16136" max="16136" width="18.5703125" style="52" customWidth="1"/>
+    <col min="16129" max="16129" width="5.83203125" style="52" customWidth="1"/>
+    <col min="16130" max="16130" width="62.4140625" style="52" customWidth="1"/>
+    <col min="16131" max="16131" width="14.83203125" style="52" customWidth="1"/>
+    <col min="16132" max="16132" width="17.25" style="52" customWidth="1"/>
+    <col min="16133" max="16133" width="20.75" style="52" customWidth="1"/>
+    <col min="16134" max="16134" width="33.83203125" style="52" customWidth="1"/>
+    <col min="16135" max="16135" width="37.25" style="52" customWidth="1"/>
+    <col min="16136" max="16136" width="18.58203125" style="52" customWidth="1"/>
     <col min="16137" max="16384" width="9" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="35.25" customHeight="1">
+    <row r="1" spans="1:8" ht="35" customHeight="1">
       <c r="A1" s="490" t="s">
         <v>867</v>
       </c>
@@ -14752,7 +14752,7 @@
       <c r="G1" s="493"/>
       <c r="H1" s="493"/>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickBot="1">
+    <row r="2" spans="1:8" ht="15.5" thickBot="1">
       <c r="A2" s="494" t="s">
         <v>18</v>
       </c>
@@ -14766,7 +14766,7 @@
       <c r="G2" s="494"/>
       <c r="H2" s="494"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" thickTop="1">
+    <row r="3" spans="1:8" ht="16" thickTop="1">
       <c r="A3" s="229"/>
       <c r="B3" s="397"/>
       <c r="C3" s="229"/>
@@ -14776,7 +14776,7 @@
       <c r="G3" s="229"/>
       <c r="H3" s="221"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="4" spans="1:8" ht="15.5">
       <c r="A4" s="229"/>
       <c r="B4" s="398"/>
       <c r="C4" s="496"/>
@@ -14788,7 +14788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.25">
+    <row r="5" spans="1:8" ht="20">
       <c r="A5" s="425" t="s">
         <v>24</v>
       </c>
@@ -14800,7 +14800,7 @@
       <c r="G5" s="425"/>
       <c r="H5" s="426"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6" s="498" t="s">
         <v>881</v>
       </c>
@@ -14850,7 +14850,7 @@
       <c r="G8" s="433"/>
       <c r="H8" s="433"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75">
+    <row r="9" spans="1:8" ht="15.5">
       <c r="A9" s="104" t="s">
         <v>10</v>
       </c>
@@ -14866,7 +14866,7 @@
       <c r="G9" s="50"/>
       <c r="H9" s="44"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75">
+    <row r="10" spans="1:8" ht="15.5">
       <c r="A10" s="41">
         <v>1</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="31.5">
+    <row r="11" spans="1:8" ht="31">
       <c r="A11" s="48" t="s">
         <v>552</v>
       </c>
@@ -14910,7 +14910,7 @@
       <c r="G11" s="403"/>
       <c r="H11" s="44"/>
     </row>
-    <row r="12" spans="1:8" ht="47.25">
+    <row r="12" spans="1:8" ht="46.5">
       <c r="A12" s="48" t="s">
         <v>553</v>
       </c>
@@ -14932,7 +14932,7 @@
       <c r="G12" s="403"/>
       <c r="H12" s="44"/>
     </row>
-    <row r="13" spans="1:8" ht="31.5">
+    <row r="13" spans="1:8" ht="31">
       <c r="A13" s="48" t="s">
         <v>555</v>
       </c>
@@ -14954,7 +14954,7 @@
       <c r="G13" s="403"/>
       <c r="H13" s="50"/>
     </row>
-    <row r="14" spans="1:8" ht="31.5">
+    <row r="14" spans="1:8" ht="31">
       <c r="A14" s="48" t="s">
         <v>562</v>
       </c>
@@ -14976,7 +14976,7 @@
       <c r="G14" s="403"/>
       <c r="H14" s="50"/>
     </row>
-    <row r="15" spans="1:8" ht="31.5">
+    <row r="15" spans="1:8" ht="31">
       <c r="A15" s="48" t="s">
         <v>632</v>
       </c>
@@ -14998,7 +14998,7 @@
       <c r="G15" s="403"/>
       <c r="H15" s="50"/>
     </row>
-    <row r="16" spans="1:8" ht="31.5">
+    <row r="16" spans="1:8" ht="30">
       <c r="A16" s="41">
         <v>2</v>
       </c>
@@ -15020,7 +15020,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="17" spans="1:12" s="409" customFormat="1" ht="15.75">
+    <row r="17" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A17" s="336" t="s">
         <v>567</v>
       </c>
@@ -15032,7 +15032,7 @@
       <c r="G17" s="403"/>
       <c r="H17" s="408"/>
     </row>
-    <row r="18" spans="1:12" ht="31.5">
+    <row r="18" spans="1:12" ht="31">
       <c r="A18" s="41">
         <v>3</v>
       </c>
@@ -15056,7 +15056,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="31.5">
+    <row r="19" spans="1:12" ht="31">
       <c r="A19" s="48" t="s">
         <v>75</v>
       </c>
@@ -15078,7 +15078,7 @@
       <c r="G19" s="153"/>
       <c r="H19" s="44"/>
     </row>
-    <row r="20" spans="1:12" ht="31.5">
+    <row r="20" spans="1:12" ht="30">
       <c r="A20" s="41">
         <v>4</v>
       </c>
@@ -15100,7 +15100,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:12" s="409" customFormat="1" ht="15.75">
+    <row r="21" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A21" s="336" t="s">
         <v>346</v>
       </c>
@@ -15122,7 +15122,7 @@
       <c r="G21" s="403"/>
       <c r="H21" s="408"/>
     </row>
-    <row r="22" spans="1:12" ht="126">
+    <row r="22" spans="1:12" ht="93">
       <c r="A22" s="248">
         <v>5</v>
       </c>
@@ -15146,7 +15146,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="23" spans="1:12" s="409" customFormat="1" ht="15.75">
+    <row r="23" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A23" s="336" t="s">
         <v>348</v>
       </c>
@@ -15168,7 +15168,7 @@
       <c r="G23" s="403"/>
       <c r="H23" s="408"/>
     </row>
-    <row r="24" spans="1:12" s="409" customFormat="1" ht="47.25">
+    <row r="24" spans="1:12" s="409" customFormat="1" ht="31">
       <c r="A24" s="336" t="s">
         <v>349</v>
       </c>
@@ -15191,7 +15191,7 @@
       <c r="H24" s="408"/>
       <c r="L24" s="411"/>
     </row>
-    <row r="25" spans="1:12" s="409" customFormat="1" ht="47.25">
+    <row r="25" spans="1:12" s="409" customFormat="1" ht="46.5">
       <c r="A25" s="336" t="s">
         <v>538</v>
       </c>
@@ -15213,7 +15213,7 @@
       <c r="G25" s="403"/>
       <c r="H25" s="408"/>
     </row>
-    <row r="26" spans="1:12" s="409" customFormat="1" ht="31.5">
+    <row r="26" spans="1:12" s="409" customFormat="1" ht="31">
       <c r="A26" s="336" t="s">
         <v>539</v>
       </c>
@@ -15235,7 +15235,7 @@
       <c r="G26" s="403"/>
       <c r="H26" s="408"/>
     </row>
-    <row r="27" spans="1:12" s="409" customFormat="1" ht="31.5">
+    <row r="27" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A27" s="336" t="s">
         <v>540</v>
       </c>
@@ -15257,7 +15257,7 @@
       <c r="G27" s="403"/>
       <c r="H27" s="408"/>
     </row>
-    <row r="28" spans="1:12" s="409" customFormat="1" ht="31.5">
+    <row r="28" spans="1:12" s="409" customFormat="1" ht="31">
       <c r="A28" s="336" t="s">
         <v>541</v>
       </c>
@@ -15279,7 +15279,7 @@
       <c r="G28" s="403"/>
       <c r="H28" s="408"/>
     </row>
-    <row r="29" spans="1:12" s="409" customFormat="1" ht="47.25">
+    <row r="29" spans="1:12" s="409" customFormat="1" ht="46.5">
       <c r="A29" s="336" t="s">
         <v>542</v>
       </c>
@@ -15301,7 +15301,7 @@
       <c r="G29" s="403"/>
       <c r="H29" s="408"/>
     </row>
-    <row r="30" spans="1:12" s="409" customFormat="1" ht="31.5">
+    <row r="30" spans="1:12" s="409" customFormat="1" ht="31">
       <c r="A30" s="336" t="s">
         <v>543</v>
       </c>
@@ -15323,7 +15323,7 @@
       <c r="G30" s="403"/>
       <c r="H30" s="408"/>
     </row>
-    <row r="31" spans="1:12" s="409" customFormat="1" ht="15.75">
+    <row r="31" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A31" s="336" t="s">
         <v>544</v>
       </c>
@@ -15345,7 +15345,7 @@
       <c r="G31" s="403"/>
       <c r="H31" s="408"/>
     </row>
-    <row r="32" spans="1:12" s="409" customFormat="1" ht="31.5">
+    <row r="32" spans="1:12" s="409" customFormat="1" ht="31">
       <c r="A32" s="336" t="s">
         <v>545</v>
       </c>
@@ -15367,7 +15367,7 @@
       <c r="G32" s="403"/>
       <c r="H32" s="408"/>
     </row>
-    <row r="33" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="33" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A33" s="336" t="s">
         <v>546</v>
       </c>
@@ -15389,7 +15389,7 @@
       <c r="G33" s="403"/>
       <c r="H33" s="408"/>
     </row>
-    <row r="34" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="34" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A34" s="336" t="s">
         <v>805</v>
       </c>
@@ -15411,7 +15411,7 @@
       <c r="G34" s="403"/>
       <c r="H34" s="408"/>
     </row>
-    <row r="35" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="35" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A35" s="336" t="s">
         <v>806</v>
       </c>
@@ -15433,7 +15433,7 @@
       <c r="G35" s="403"/>
       <c r="H35" s="408"/>
     </row>
-    <row r="36" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="36" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A36" s="336" t="s">
         <v>807</v>
       </c>
@@ -15455,7 +15455,7 @@
       <c r="G36" s="403"/>
       <c r="H36" s="408"/>
     </row>
-    <row r="37" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="37" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A37" s="336" t="s">
         <v>808</v>
       </c>
@@ -15477,7 +15477,7 @@
       <c r="G37" s="403"/>
       <c r="H37" s="408"/>
     </row>
-    <row r="38" spans="1:8" s="409" customFormat="1" ht="47.25">
+    <row r="38" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A38" s="336" t="s">
         <v>809</v>
       </c>
@@ -15499,7 +15499,7 @@
       <c r="G38" s="403"/>
       <c r="H38" s="408"/>
     </row>
-    <row r="39" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="39" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A39" s="336" t="s">
         <v>810</v>
       </c>
@@ -15521,7 +15521,7 @@
       <c r="G39" s="403"/>
       <c r="H39" s="408"/>
     </row>
-    <row r="40" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="40" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A40" s="336" t="s">
         <v>811</v>
       </c>
@@ -15543,7 +15543,7 @@
       <c r="G40" s="403"/>
       <c r="H40" s="408"/>
     </row>
-    <row r="41" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="41" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A41" s="336" t="s">
         <v>812</v>
       </c>
@@ -15565,7 +15565,7 @@
       <c r="G41" s="403"/>
       <c r="H41" s="408"/>
     </row>
-    <row r="42" spans="1:8" s="224" customFormat="1" ht="15.75">
+    <row r="42" spans="1:8" s="224" customFormat="1" ht="15.5">
       <c r="A42" s="265">
         <v>6</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="43" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A43" s="336" t="s">
         <v>431</v>
       </c>
@@ -15603,7 +15603,7 @@
       <c r="G43" s="403"/>
       <c r="H43" s="408"/>
     </row>
-    <row r="44" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="44" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A44" s="336" t="s">
         <v>435</v>
       </c>
@@ -15625,7 +15625,7 @@
       <c r="G44" s="403"/>
       <c r="H44" s="408"/>
     </row>
-    <row r="45" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="45" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A45" s="336" t="s">
         <v>436</v>
       </c>
@@ -15647,7 +15647,7 @@
       <c r="G45" s="403"/>
       <c r="H45" s="408"/>
     </row>
-    <row r="46" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="46" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A46" s="336" t="s">
         <v>437</v>
       </c>
@@ -15669,7 +15669,7 @@
       <c r="G46" s="403"/>
       <c r="H46" s="408"/>
     </row>
-    <row r="47" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="47" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A47" s="336" t="s">
         <v>438</v>
       </c>
@@ -15691,7 +15691,7 @@
       <c r="G47" s="403"/>
       <c r="H47" s="408"/>
     </row>
-    <row r="48" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="48" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A48" s="336" t="s">
         <v>444</v>
       </c>
@@ -15713,7 +15713,7 @@
       <c r="G48" s="403"/>
       <c r="H48" s="408"/>
     </row>
-    <row r="49" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="49" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A49" s="336" t="s">
         <v>834</v>
       </c>
@@ -15735,7 +15735,7 @@
       <c r="G49" s="403"/>
       <c r="H49" s="408"/>
     </row>
-    <row r="50" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="50" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A50" s="336" t="s">
         <v>835</v>
       </c>
@@ -15757,7 +15757,7 @@
       <c r="G50" s="403"/>
       <c r="H50" s="408"/>
     </row>
-    <row r="51" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="51" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A51" s="336" t="s">
         <v>836</v>
       </c>
@@ -15779,7 +15779,7 @@
       <c r="G51" s="403"/>
       <c r="H51" s="408"/>
     </row>
-    <row r="52" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="52" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A52" s="336" t="s">
         <v>837</v>
       </c>
@@ -15801,7 +15801,7 @@
       <c r="G52" s="403"/>
       <c r="H52" s="408"/>
     </row>
-    <row r="53" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="53" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A53" s="336" t="s">
         <v>838</v>
       </c>
@@ -15823,7 +15823,7 @@
       <c r="G53" s="403"/>
       <c r="H53" s="408"/>
     </row>
-    <row r="54" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="54" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A54" s="336" t="s">
         <v>839</v>
       </c>
@@ -15845,7 +15845,7 @@
       <c r="G54" s="403"/>
       <c r="H54" s="408"/>
     </row>
-    <row r="55" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="55" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A55" s="336" t="s">
         <v>840</v>
       </c>
@@ -15867,7 +15867,7 @@
       <c r="G55" s="403"/>
       <c r="H55" s="408"/>
     </row>
-    <row r="56" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="56" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A56" s="336" t="s">
         <v>841</v>
       </c>
@@ -15889,7 +15889,7 @@
       <c r="G56" s="403"/>
       <c r="H56" s="408"/>
     </row>
-    <row r="57" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="57" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A57" s="336">
         <v>6.15</v>
       </c>
@@ -15911,7 +15911,7 @@
       <c r="G57" s="403"/>
       <c r="H57" s="408"/>
     </row>
-    <row r="58" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="58" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A58" s="336">
         <v>6.16</v>
       </c>
@@ -15933,7 +15933,7 @@
       <c r="G58" s="403"/>
       <c r="H58" s="408"/>
     </row>
-    <row r="59" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="59" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A59" s="336">
         <v>6.17</v>
       </c>
@@ -15955,7 +15955,7 @@
       <c r="G59" s="403"/>
       <c r="H59" s="408"/>
     </row>
-    <row r="60" spans="1:8" s="409" customFormat="1" ht="47.25">
+    <row r="60" spans="1:8" s="409" customFormat="1" ht="46.5">
       <c r="A60" s="336">
         <v>6.18</v>
       </c>
@@ -15977,7 +15977,7 @@
       <c r="G60" s="403"/>
       <c r="H60" s="408"/>
     </row>
-    <row r="61" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="61" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A61" s="336" t="s">
         <v>873</v>
       </c>
@@ -15999,7 +15999,7 @@
       <c r="G61" s="403"/>
       <c r="H61" s="408"/>
     </row>
-    <row r="62" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="62" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A62" s="336" t="s">
         <v>874</v>
       </c>
@@ -16021,7 +16021,7 @@
       <c r="G62" s="403"/>
       <c r="H62" s="408"/>
     </row>
-    <row r="63" spans="1:8" s="409" customFormat="1" ht="15.75">
+    <row r="63" spans="1:8" s="409" customFormat="1" ht="15.5">
       <c r="A63" s="336" t="s">
         <v>875</v>
       </c>
@@ -16043,7 +16043,7 @@
       <c r="G63" s="403"/>
       <c r="H63" s="408"/>
     </row>
-    <row r="64" spans="1:8" s="409" customFormat="1" ht="31.5">
+    <row r="64" spans="1:8" s="409" customFormat="1" ht="31">
       <c r="A64" s="336" t="s">
         <v>876</v>
       </c>
@@ -16065,7 +16065,7 @@
       <c r="G64" s="403"/>
       <c r="H64" s="408"/>
     </row>
-    <row r="65" spans="1:12" s="409" customFormat="1" ht="15.75">
+    <row r="65" spans="1:12" s="409" customFormat="1" ht="15.5">
       <c r="A65" s="336"/>
       <c r="B65" s="405"/>
       <c r="C65" s="403"/>
@@ -16075,7 +16075,7 @@
       <c r="G65" s="403"/>
       <c r="H65" s="408"/>
     </row>
-    <row r="66" spans="1:12" ht="31.5">
+    <row r="66" spans="1:12" ht="15.5">
       <c r="A66" s="41">
         <v>7</v>
       </c>
@@ -16090,7 +16090,7 @@
       <c r="H66" s="50"/>
       <c r="L66" s="413"/>
     </row>
-    <row r="67" spans="1:12" ht="31.5">
+    <row r="67" spans="1:12" ht="31">
       <c r="A67" s="48" t="s">
         <v>440</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="G67" s="403"/>
       <c r="H67" s="104"/>
     </row>
-    <row r="68" spans="1:12" s="414" customFormat="1" ht="15.75">
+    <row r="68" spans="1:12" s="414" customFormat="1" ht="15.5">
       <c r="A68" s="44" t="s">
         <v>441</v>
       </c>
@@ -16126,7 +16126,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="31.5">
+    <row r="69" spans="1:12" ht="31">
       <c r="A69" s="41">
         <v>8</v>
       </c>
@@ -16152,7 +16152,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="15.75">
+    <row r="70" spans="1:12" ht="15.5">
       <c r="A70" s="104" t="s">
         <v>13</v>
       </c>
@@ -16166,7 +16166,7 @@
       <c r="G70" s="56"/>
       <c r="H70" s="44"/>
     </row>
-    <row r="71" spans="1:12" ht="15.75">
+    <row r="71" spans="1:12" ht="15.5">
       <c r="A71" s="104">
         <v>1</v>
       </c>
@@ -16180,7 +16180,7 @@
       <c r="G71" s="446"/>
       <c r="H71" s="51"/>
     </row>
-    <row r="72" spans="1:12" ht="63">
+    <row r="72" spans="1:12" ht="62">
       <c r="A72" s="48" t="s">
         <v>552</v>
       </c>
@@ -16204,7 +16204,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:12" s="62" customFormat="1" ht="94.5">
+    <row r="73" spans="1:12" s="62" customFormat="1" ht="93">
       <c r="A73" s="48" t="s">
         <v>553</v>
       </c>
@@ -16228,7 +16228,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="110.25">
+    <row r="74" spans="1:12" ht="93">
       <c r="A74" s="41">
         <v>2</v>
       </c>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="L74" s="415"/>
     </row>
-    <row r="75" spans="1:12" ht="94.5">
+    <row r="75" spans="1:12" ht="93">
       <c r="A75" s="41">
         <v>3</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="15.75">
+    <row r="76" spans="1:12" ht="15.5">
       <c r="A76" s="41">
         <v>4</v>
       </c>
@@ -16291,7 +16291,7 @@
       <c r="G76" s="56"/>
       <c r="H76" s="50"/>
     </row>
-    <row r="77" spans="1:12" ht="78.75">
+    <row r="77" spans="1:12" ht="62">
       <c r="A77" s="44" t="s">
         <v>346</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="78.75">
+    <row r="78" spans="1:12" ht="46.5">
       <c r="A78" s="48" t="s">
         <v>347</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="63">
+    <row r="79" spans="1:12" ht="45.5">
       <c r="A79" s="104">
         <v>5</v>
       </c>
@@ -16361,7 +16361,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="15.75">
+    <row r="80" spans="1:12" ht="15.5">
       <c r="A80" s="206" t="s">
         <v>174</v>
       </c>
@@ -16375,7 +16375,7 @@
       <c r="G80" s="50"/>
       <c r="H80" s="218"/>
     </row>
-    <row r="81" spans="1:12" ht="15.75">
+    <row r="81" spans="1:12" ht="15.5">
       <c r="A81" s="104">
         <v>1</v>
       </c>
@@ -16389,7 +16389,7 @@
       <c r="G81" s="467"/>
       <c r="H81" s="467"/>
     </row>
-    <row r="82" spans="1:12" ht="15.75">
+    <row r="82" spans="1:12" ht="15.5">
       <c r="A82" s="104">
         <v>2</v>
       </c>
@@ -16403,7 +16403,7 @@
       <c r="G82" s="469"/>
       <c r="H82" s="469"/>
     </row>
-    <row r="83" spans="1:12" ht="15.75">
+    <row r="83" spans="1:12" ht="15.5">
       <c r="A83" s="416" t="s">
         <v>934</v>
       </c>
@@ -16451,7 +16451,7 @@
       <c r="G85" s="470"/>
       <c r="H85" s="475"/>
     </row>
-    <row r="86" spans="1:12" ht="15.75">
+    <row r="86" spans="1:12" ht="15.5">
       <c r="A86" s="104" t="s">
         <v>10</v>
       </c>
@@ -16465,7 +16465,7 @@
       <c r="G86" s="457"/>
       <c r="H86" s="44"/>
     </row>
-    <row r="87" spans="1:12" ht="15.75">
+    <row r="87" spans="1:12" ht="15.5">
       <c r="A87" s="48">
         <v>1</v>
       </c>
@@ -16532,7 +16532,7 @@
       <c r="G89" s="482"/>
       <c r="H89" s="44"/>
     </row>
-    <row r="90" spans="1:12" ht="15.75">
+    <row r="90" spans="1:12" ht="15.5">
       <c r="A90" s="104" t="s">
         <v>13</v>
       </c>
@@ -16546,7 +16546,7 @@
       <c r="G90" s="457"/>
       <c r="H90" s="44"/>
     </row>
-    <row r="91" spans="1:12" ht="15.75">
+    <row r="91" spans="1:12" ht="15.5">
       <c r="A91" s="44">
         <v>1</v>
       </c>
@@ -16604,7 +16604,7 @@
       <c r="G93" s="482"/>
       <c r="H93" s="313"/>
     </row>
-    <row r="94" spans="1:12" s="409" customFormat="1" ht="47.25">
+    <row r="94" spans="1:12" s="409" customFormat="1" ht="46.5">
       <c r="A94" s="177" t="s">
         <v>555</v>
       </c>
@@ -16626,7 +16626,7 @@
       <c r="G94" s="482"/>
       <c r="H94" s="320"/>
     </row>
-    <row r="95" spans="1:12" ht="47.25">
+    <row r="95" spans="1:12" ht="46.5">
       <c r="A95" s="44" t="s">
         <v>562</v>
       </c>
@@ -16648,7 +16648,7 @@
       <c r="G95" s="482"/>
       <c r="H95" s="51"/>
     </row>
-    <row r="96" spans="1:12" ht="31.5">
+    <row r="96" spans="1:12" ht="31">
       <c r="A96" s="44" t="s">
         <v>632</v>
       </c>
@@ -16670,7 +16670,7 @@
       <c r="G96" s="446"/>
       <c r="H96" s="51"/>
     </row>
-    <row r="97" spans="1:10" ht="15.75">
+    <row r="97" spans="1:10" ht="15.5">
       <c r="A97" s="44" t="s">
         <v>721</v>
       </c>
@@ -16692,7 +16692,7 @@
       <c r="G97" s="446"/>
       <c r="H97" s="51"/>
     </row>
-    <row r="98" spans="1:10" ht="15.75">
+    <row r="98" spans="1:10" ht="15.5">
       <c r="A98" s="104">
         <v>2</v>
       </c>
@@ -16728,7 +16728,7 @@
       <c r="G99" s="446"/>
       <c r="H99" s="216"/>
     </row>
-    <row r="100" spans="1:10" ht="63">
+    <row r="100" spans="1:10" ht="45.5">
       <c r="A100" s="104">
         <v>3</v>
       </c>
@@ -16746,7 +16746,7 @@
       <c r="G100" s="457"/>
       <c r="H100" s="318"/>
     </row>
-    <row r="101" spans="1:10" ht="15.75">
+    <row r="101" spans="1:10" ht="15.5">
       <c r="A101" s="419"/>
       <c r="B101" s="400"/>
       <c r="C101" s="229"/>
@@ -16858,7 +16858,7 @@
   </mergeCells>
   <phoneticPr fontId="41" type="noConversion"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="4" max="16383" man="1"/>
   </rowBreaks>
@@ -16872,519 +16872,519 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L199"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="44.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="5" width="10.42578125" style="90" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.28515625" customWidth="1"/>
-    <col min="7" max="7" width="40.42578125" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="44.58203125" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="5" width="10.4140625" style="90" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.25" customWidth="1"/>
+    <col min="7" max="7" width="40.4140625" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="257" max="257" width="5.85546875" customWidth="1"/>
-    <col min="258" max="258" width="62.42578125" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" customWidth="1"/>
-    <col min="260" max="260" width="17.28515625" customWidth="1"/>
-    <col min="261" max="261" width="20.7109375" customWidth="1"/>
-    <col min="262" max="262" width="33.85546875" customWidth="1"/>
-    <col min="263" max="263" width="37.28515625" customWidth="1"/>
-    <col min="264" max="264" width="18.5703125" customWidth="1"/>
-    <col min="513" max="513" width="5.85546875" customWidth="1"/>
-    <col min="514" max="514" width="62.42578125" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" customWidth="1"/>
-    <col min="516" max="516" width="17.28515625" customWidth="1"/>
-    <col min="517" max="517" width="20.7109375" customWidth="1"/>
-    <col min="518" max="518" width="33.85546875" customWidth="1"/>
-    <col min="519" max="519" width="37.28515625" customWidth="1"/>
-    <col min="520" max="520" width="18.5703125" customWidth="1"/>
-    <col min="769" max="769" width="5.85546875" customWidth="1"/>
-    <col min="770" max="770" width="62.42578125" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" customWidth="1"/>
-    <col min="772" max="772" width="17.28515625" customWidth="1"/>
-    <col min="773" max="773" width="20.7109375" customWidth="1"/>
-    <col min="774" max="774" width="33.85546875" customWidth="1"/>
-    <col min="775" max="775" width="37.28515625" customWidth="1"/>
-    <col min="776" max="776" width="18.5703125" customWidth="1"/>
-    <col min="1025" max="1025" width="5.85546875" customWidth="1"/>
-    <col min="1026" max="1026" width="62.42578125" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" customWidth="1"/>
-    <col min="1028" max="1028" width="17.28515625" customWidth="1"/>
-    <col min="1029" max="1029" width="20.7109375" customWidth="1"/>
-    <col min="1030" max="1030" width="33.85546875" customWidth="1"/>
-    <col min="1031" max="1031" width="37.28515625" customWidth="1"/>
-    <col min="1032" max="1032" width="18.5703125" customWidth="1"/>
-    <col min="1281" max="1281" width="5.85546875" customWidth="1"/>
-    <col min="1282" max="1282" width="62.42578125" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" customWidth="1"/>
-    <col min="1284" max="1284" width="17.28515625" customWidth="1"/>
-    <col min="1285" max="1285" width="20.7109375" customWidth="1"/>
-    <col min="1286" max="1286" width="33.85546875" customWidth="1"/>
-    <col min="1287" max="1287" width="37.28515625" customWidth="1"/>
-    <col min="1288" max="1288" width="18.5703125" customWidth="1"/>
-    <col min="1537" max="1537" width="5.85546875" customWidth="1"/>
-    <col min="1538" max="1538" width="62.42578125" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" customWidth="1"/>
-    <col min="1540" max="1540" width="17.28515625" customWidth="1"/>
-    <col min="1541" max="1541" width="20.7109375" customWidth="1"/>
-    <col min="1542" max="1542" width="33.85546875" customWidth="1"/>
-    <col min="1543" max="1543" width="37.28515625" customWidth="1"/>
-    <col min="1544" max="1544" width="18.5703125" customWidth="1"/>
-    <col min="1793" max="1793" width="5.85546875" customWidth="1"/>
-    <col min="1794" max="1794" width="62.42578125" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" customWidth="1"/>
-    <col min="1796" max="1796" width="17.28515625" customWidth="1"/>
-    <col min="1797" max="1797" width="20.7109375" customWidth="1"/>
-    <col min="1798" max="1798" width="33.85546875" customWidth="1"/>
-    <col min="1799" max="1799" width="37.28515625" customWidth="1"/>
-    <col min="1800" max="1800" width="18.5703125" customWidth="1"/>
-    <col min="2049" max="2049" width="5.85546875" customWidth="1"/>
-    <col min="2050" max="2050" width="62.42578125" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" customWidth="1"/>
-    <col min="2052" max="2052" width="17.28515625" customWidth="1"/>
-    <col min="2053" max="2053" width="20.7109375" customWidth="1"/>
-    <col min="2054" max="2054" width="33.85546875" customWidth="1"/>
-    <col min="2055" max="2055" width="37.28515625" customWidth="1"/>
-    <col min="2056" max="2056" width="18.5703125" customWidth="1"/>
-    <col min="2305" max="2305" width="5.85546875" customWidth="1"/>
-    <col min="2306" max="2306" width="62.42578125" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" customWidth="1"/>
-    <col min="2308" max="2308" width="17.28515625" customWidth="1"/>
-    <col min="2309" max="2309" width="20.7109375" customWidth="1"/>
-    <col min="2310" max="2310" width="33.85546875" customWidth="1"/>
-    <col min="2311" max="2311" width="37.28515625" customWidth="1"/>
-    <col min="2312" max="2312" width="18.5703125" customWidth="1"/>
-    <col min="2561" max="2561" width="5.85546875" customWidth="1"/>
-    <col min="2562" max="2562" width="62.42578125" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" customWidth="1"/>
-    <col min="2564" max="2564" width="17.28515625" customWidth="1"/>
-    <col min="2565" max="2565" width="20.7109375" customWidth="1"/>
-    <col min="2566" max="2566" width="33.85546875" customWidth="1"/>
-    <col min="2567" max="2567" width="37.28515625" customWidth="1"/>
-    <col min="2568" max="2568" width="18.5703125" customWidth="1"/>
-    <col min="2817" max="2817" width="5.85546875" customWidth="1"/>
-    <col min="2818" max="2818" width="62.42578125" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" customWidth="1"/>
-    <col min="2820" max="2820" width="17.28515625" customWidth="1"/>
-    <col min="2821" max="2821" width="20.7109375" customWidth="1"/>
-    <col min="2822" max="2822" width="33.85546875" customWidth="1"/>
-    <col min="2823" max="2823" width="37.28515625" customWidth="1"/>
-    <col min="2824" max="2824" width="18.5703125" customWidth="1"/>
-    <col min="3073" max="3073" width="5.85546875" customWidth="1"/>
-    <col min="3074" max="3074" width="62.42578125" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" customWidth="1"/>
-    <col min="3076" max="3076" width="17.28515625" customWidth="1"/>
-    <col min="3077" max="3077" width="20.7109375" customWidth="1"/>
-    <col min="3078" max="3078" width="33.85546875" customWidth="1"/>
-    <col min="3079" max="3079" width="37.28515625" customWidth="1"/>
-    <col min="3080" max="3080" width="18.5703125" customWidth="1"/>
-    <col min="3329" max="3329" width="5.85546875" customWidth="1"/>
-    <col min="3330" max="3330" width="62.42578125" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" customWidth="1"/>
-    <col min="3332" max="3332" width="17.28515625" customWidth="1"/>
-    <col min="3333" max="3333" width="20.7109375" customWidth="1"/>
-    <col min="3334" max="3334" width="33.85546875" customWidth="1"/>
-    <col min="3335" max="3335" width="37.28515625" customWidth="1"/>
-    <col min="3336" max="3336" width="18.5703125" customWidth="1"/>
-    <col min="3585" max="3585" width="5.85546875" customWidth="1"/>
-    <col min="3586" max="3586" width="62.42578125" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" customWidth="1"/>
-    <col min="3588" max="3588" width="17.28515625" customWidth="1"/>
-    <col min="3589" max="3589" width="20.7109375" customWidth="1"/>
-    <col min="3590" max="3590" width="33.85546875" customWidth="1"/>
-    <col min="3591" max="3591" width="37.28515625" customWidth="1"/>
-    <col min="3592" max="3592" width="18.5703125" customWidth="1"/>
-    <col min="3841" max="3841" width="5.85546875" customWidth="1"/>
-    <col min="3842" max="3842" width="62.42578125" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" customWidth="1"/>
-    <col min="3844" max="3844" width="17.28515625" customWidth="1"/>
-    <col min="3845" max="3845" width="20.7109375" customWidth="1"/>
-    <col min="3846" max="3846" width="33.85546875" customWidth="1"/>
-    <col min="3847" max="3847" width="37.28515625" customWidth="1"/>
-    <col min="3848" max="3848" width="18.5703125" customWidth="1"/>
-    <col min="4097" max="4097" width="5.85546875" customWidth="1"/>
-    <col min="4098" max="4098" width="62.42578125" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" customWidth="1"/>
-    <col min="4100" max="4100" width="17.28515625" customWidth="1"/>
-    <col min="4101" max="4101" width="20.7109375" customWidth="1"/>
-    <col min="4102" max="4102" width="33.85546875" customWidth="1"/>
-    <col min="4103" max="4103" width="37.28515625" customWidth="1"/>
-    <col min="4104" max="4104" width="18.5703125" customWidth="1"/>
-    <col min="4353" max="4353" width="5.85546875" customWidth="1"/>
-    <col min="4354" max="4354" width="62.42578125" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" customWidth="1"/>
-    <col min="4356" max="4356" width="17.28515625" customWidth="1"/>
-    <col min="4357" max="4357" width="20.7109375" customWidth="1"/>
-    <col min="4358" max="4358" width="33.85546875" customWidth="1"/>
-    <col min="4359" max="4359" width="37.28515625" customWidth="1"/>
-    <col min="4360" max="4360" width="18.5703125" customWidth="1"/>
-    <col min="4609" max="4609" width="5.85546875" customWidth="1"/>
-    <col min="4610" max="4610" width="62.42578125" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" customWidth="1"/>
-    <col min="4612" max="4612" width="17.28515625" customWidth="1"/>
-    <col min="4613" max="4613" width="20.7109375" customWidth="1"/>
-    <col min="4614" max="4614" width="33.85546875" customWidth="1"/>
-    <col min="4615" max="4615" width="37.28515625" customWidth="1"/>
-    <col min="4616" max="4616" width="18.5703125" customWidth="1"/>
-    <col min="4865" max="4865" width="5.85546875" customWidth="1"/>
-    <col min="4866" max="4866" width="62.42578125" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" customWidth="1"/>
-    <col min="4868" max="4868" width="17.28515625" customWidth="1"/>
-    <col min="4869" max="4869" width="20.7109375" customWidth="1"/>
-    <col min="4870" max="4870" width="33.85546875" customWidth="1"/>
-    <col min="4871" max="4871" width="37.28515625" customWidth="1"/>
-    <col min="4872" max="4872" width="18.5703125" customWidth="1"/>
-    <col min="5121" max="5121" width="5.85546875" customWidth="1"/>
-    <col min="5122" max="5122" width="62.42578125" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" customWidth="1"/>
-    <col min="5124" max="5124" width="17.28515625" customWidth="1"/>
-    <col min="5125" max="5125" width="20.7109375" customWidth="1"/>
-    <col min="5126" max="5126" width="33.85546875" customWidth="1"/>
-    <col min="5127" max="5127" width="37.28515625" customWidth="1"/>
-    <col min="5128" max="5128" width="18.5703125" customWidth="1"/>
-    <col min="5377" max="5377" width="5.85546875" customWidth="1"/>
-    <col min="5378" max="5378" width="62.42578125" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" customWidth="1"/>
-    <col min="5380" max="5380" width="17.28515625" customWidth="1"/>
-    <col min="5381" max="5381" width="20.7109375" customWidth="1"/>
-    <col min="5382" max="5382" width="33.85546875" customWidth="1"/>
-    <col min="5383" max="5383" width="37.28515625" customWidth="1"/>
-    <col min="5384" max="5384" width="18.5703125" customWidth="1"/>
-    <col min="5633" max="5633" width="5.85546875" customWidth="1"/>
-    <col min="5634" max="5634" width="62.42578125" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" customWidth="1"/>
-    <col min="5636" max="5636" width="17.28515625" customWidth="1"/>
-    <col min="5637" max="5637" width="20.7109375" customWidth="1"/>
-    <col min="5638" max="5638" width="33.85546875" customWidth="1"/>
-    <col min="5639" max="5639" width="37.28515625" customWidth="1"/>
-    <col min="5640" max="5640" width="18.5703125" customWidth="1"/>
-    <col min="5889" max="5889" width="5.85546875" customWidth="1"/>
-    <col min="5890" max="5890" width="62.42578125" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" customWidth="1"/>
-    <col min="5892" max="5892" width="17.28515625" customWidth="1"/>
-    <col min="5893" max="5893" width="20.7109375" customWidth="1"/>
-    <col min="5894" max="5894" width="33.85546875" customWidth="1"/>
-    <col min="5895" max="5895" width="37.28515625" customWidth="1"/>
-    <col min="5896" max="5896" width="18.5703125" customWidth="1"/>
-    <col min="6145" max="6145" width="5.85546875" customWidth="1"/>
-    <col min="6146" max="6146" width="62.42578125" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" customWidth="1"/>
-    <col min="6148" max="6148" width="17.28515625" customWidth="1"/>
-    <col min="6149" max="6149" width="20.7109375" customWidth="1"/>
-    <col min="6150" max="6150" width="33.85546875" customWidth="1"/>
-    <col min="6151" max="6151" width="37.28515625" customWidth="1"/>
-    <col min="6152" max="6152" width="18.5703125" customWidth="1"/>
-    <col min="6401" max="6401" width="5.85546875" customWidth="1"/>
-    <col min="6402" max="6402" width="62.42578125" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" customWidth="1"/>
-    <col min="6404" max="6404" width="17.28515625" customWidth="1"/>
-    <col min="6405" max="6405" width="20.7109375" customWidth="1"/>
-    <col min="6406" max="6406" width="33.85546875" customWidth="1"/>
-    <col min="6407" max="6407" width="37.28515625" customWidth="1"/>
-    <col min="6408" max="6408" width="18.5703125" customWidth="1"/>
-    <col min="6657" max="6657" width="5.85546875" customWidth="1"/>
-    <col min="6658" max="6658" width="62.42578125" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" customWidth="1"/>
-    <col min="6660" max="6660" width="17.28515625" customWidth="1"/>
-    <col min="6661" max="6661" width="20.7109375" customWidth="1"/>
-    <col min="6662" max="6662" width="33.85546875" customWidth="1"/>
-    <col min="6663" max="6663" width="37.28515625" customWidth="1"/>
-    <col min="6664" max="6664" width="18.5703125" customWidth="1"/>
-    <col min="6913" max="6913" width="5.85546875" customWidth="1"/>
-    <col min="6914" max="6914" width="62.42578125" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" customWidth="1"/>
-    <col min="6916" max="6916" width="17.28515625" customWidth="1"/>
-    <col min="6917" max="6917" width="20.7109375" customWidth="1"/>
-    <col min="6918" max="6918" width="33.85546875" customWidth="1"/>
-    <col min="6919" max="6919" width="37.28515625" customWidth="1"/>
-    <col min="6920" max="6920" width="18.5703125" customWidth="1"/>
-    <col min="7169" max="7169" width="5.85546875" customWidth="1"/>
-    <col min="7170" max="7170" width="62.42578125" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" customWidth="1"/>
-    <col min="7172" max="7172" width="17.28515625" customWidth="1"/>
-    <col min="7173" max="7173" width="20.7109375" customWidth="1"/>
-    <col min="7174" max="7174" width="33.85546875" customWidth="1"/>
-    <col min="7175" max="7175" width="37.28515625" customWidth="1"/>
-    <col min="7176" max="7176" width="18.5703125" customWidth="1"/>
-    <col min="7425" max="7425" width="5.85546875" customWidth="1"/>
-    <col min="7426" max="7426" width="62.42578125" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" customWidth="1"/>
-    <col min="7428" max="7428" width="17.28515625" customWidth="1"/>
-    <col min="7429" max="7429" width="20.7109375" customWidth="1"/>
-    <col min="7430" max="7430" width="33.85546875" customWidth="1"/>
-    <col min="7431" max="7431" width="37.28515625" customWidth="1"/>
-    <col min="7432" max="7432" width="18.5703125" customWidth="1"/>
-    <col min="7681" max="7681" width="5.85546875" customWidth="1"/>
-    <col min="7682" max="7682" width="62.42578125" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" customWidth="1"/>
-    <col min="7684" max="7684" width="17.28515625" customWidth="1"/>
-    <col min="7685" max="7685" width="20.7109375" customWidth="1"/>
-    <col min="7686" max="7686" width="33.85546875" customWidth="1"/>
-    <col min="7687" max="7687" width="37.28515625" customWidth="1"/>
-    <col min="7688" max="7688" width="18.5703125" customWidth="1"/>
-    <col min="7937" max="7937" width="5.85546875" customWidth="1"/>
-    <col min="7938" max="7938" width="62.42578125" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" customWidth="1"/>
-    <col min="7940" max="7940" width="17.28515625" customWidth="1"/>
-    <col min="7941" max="7941" width="20.7109375" customWidth="1"/>
-    <col min="7942" max="7942" width="33.85546875" customWidth="1"/>
-    <col min="7943" max="7943" width="37.28515625" customWidth="1"/>
-    <col min="7944" max="7944" width="18.5703125" customWidth="1"/>
-    <col min="8193" max="8193" width="5.85546875" customWidth="1"/>
-    <col min="8194" max="8194" width="62.42578125" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" customWidth="1"/>
-    <col min="8196" max="8196" width="17.28515625" customWidth="1"/>
-    <col min="8197" max="8197" width="20.7109375" customWidth="1"/>
-    <col min="8198" max="8198" width="33.85546875" customWidth="1"/>
-    <col min="8199" max="8199" width="37.28515625" customWidth="1"/>
-    <col min="8200" max="8200" width="18.5703125" customWidth="1"/>
-    <col min="8449" max="8449" width="5.85546875" customWidth="1"/>
-    <col min="8450" max="8450" width="62.42578125" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" customWidth="1"/>
-    <col min="8452" max="8452" width="17.28515625" customWidth="1"/>
-    <col min="8453" max="8453" width="20.7109375" customWidth="1"/>
-    <col min="8454" max="8454" width="33.85546875" customWidth="1"/>
-    <col min="8455" max="8455" width="37.28515625" customWidth="1"/>
-    <col min="8456" max="8456" width="18.5703125" customWidth="1"/>
-    <col min="8705" max="8705" width="5.85546875" customWidth="1"/>
-    <col min="8706" max="8706" width="62.42578125" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" customWidth="1"/>
-    <col min="8708" max="8708" width="17.28515625" customWidth="1"/>
-    <col min="8709" max="8709" width="20.7109375" customWidth="1"/>
-    <col min="8710" max="8710" width="33.85546875" customWidth="1"/>
-    <col min="8711" max="8711" width="37.28515625" customWidth="1"/>
-    <col min="8712" max="8712" width="18.5703125" customWidth="1"/>
-    <col min="8961" max="8961" width="5.85546875" customWidth="1"/>
-    <col min="8962" max="8962" width="62.42578125" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" customWidth="1"/>
-    <col min="8964" max="8964" width="17.28515625" customWidth="1"/>
-    <col min="8965" max="8965" width="20.7109375" customWidth="1"/>
-    <col min="8966" max="8966" width="33.85546875" customWidth="1"/>
-    <col min="8967" max="8967" width="37.28515625" customWidth="1"/>
-    <col min="8968" max="8968" width="18.5703125" customWidth="1"/>
-    <col min="9217" max="9217" width="5.85546875" customWidth="1"/>
-    <col min="9218" max="9218" width="62.42578125" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" customWidth="1"/>
-    <col min="9220" max="9220" width="17.28515625" customWidth="1"/>
-    <col min="9221" max="9221" width="20.7109375" customWidth="1"/>
-    <col min="9222" max="9222" width="33.85546875" customWidth="1"/>
-    <col min="9223" max="9223" width="37.28515625" customWidth="1"/>
-    <col min="9224" max="9224" width="18.5703125" customWidth="1"/>
-    <col min="9473" max="9473" width="5.85546875" customWidth="1"/>
-    <col min="9474" max="9474" width="62.42578125" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" customWidth="1"/>
-    <col min="9476" max="9476" width="17.28515625" customWidth="1"/>
-    <col min="9477" max="9477" width="20.7109375" customWidth="1"/>
-    <col min="9478" max="9478" width="33.85546875" customWidth="1"/>
-    <col min="9479" max="9479" width="37.28515625" customWidth="1"/>
-    <col min="9480" max="9480" width="18.5703125" customWidth="1"/>
-    <col min="9729" max="9729" width="5.85546875" customWidth="1"/>
-    <col min="9730" max="9730" width="62.42578125" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" customWidth="1"/>
-    <col min="9732" max="9732" width="17.28515625" customWidth="1"/>
-    <col min="9733" max="9733" width="20.7109375" customWidth="1"/>
-    <col min="9734" max="9734" width="33.85546875" customWidth="1"/>
-    <col min="9735" max="9735" width="37.28515625" customWidth="1"/>
-    <col min="9736" max="9736" width="18.5703125" customWidth="1"/>
-    <col min="9985" max="9985" width="5.85546875" customWidth="1"/>
-    <col min="9986" max="9986" width="62.42578125" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" customWidth="1"/>
-    <col min="9988" max="9988" width="17.28515625" customWidth="1"/>
-    <col min="9989" max="9989" width="20.7109375" customWidth="1"/>
-    <col min="9990" max="9990" width="33.85546875" customWidth="1"/>
-    <col min="9991" max="9991" width="37.28515625" customWidth="1"/>
-    <col min="9992" max="9992" width="18.5703125" customWidth="1"/>
-    <col min="10241" max="10241" width="5.85546875" customWidth="1"/>
-    <col min="10242" max="10242" width="62.42578125" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" customWidth="1"/>
-    <col min="10244" max="10244" width="17.28515625" customWidth="1"/>
-    <col min="10245" max="10245" width="20.7109375" customWidth="1"/>
-    <col min="10246" max="10246" width="33.85546875" customWidth="1"/>
-    <col min="10247" max="10247" width="37.28515625" customWidth="1"/>
-    <col min="10248" max="10248" width="18.5703125" customWidth="1"/>
-    <col min="10497" max="10497" width="5.85546875" customWidth="1"/>
-    <col min="10498" max="10498" width="62.42578125" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" customWidth="1"/>
-    <col min="10500" max="10500" width="17.28515625" customWidth="1"/>
-    <col min="10501" max="10501" width="20.7109375" customWidth="1"/>
-    <col min="10502" max="10502" width="33.85546875" customWidth="1"/>
-    <col min="10503" max="10503" width="37.28515625" customWidth="1"/>
-    <col min="10504" max="10504" width="18.5703125" customWidth="1"/>
-    <col min="10753" max="10753" width="5.85546875" customWidth="1"/>
-    <col min="10754" max="10754" width="62.42578125" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" customWidth="1"/>
-    <col min="10756" max="10756" width="17.28515625" customWidth="1"/>
-    <col min="10757" max="10757" width="20.7109375" customWidth="1"/>
-    <col min="10758" max="10758" width="33.85546875" customWidth="1"/>
-    <col min="10759" max="10759" width="37.28515625" customWidth="1"/>
-    <col min="10760" max="10760" width="18.5703125" customWidth="1"/>
-    <col min="11009" max="11009" width="5.85546875" customWidth="1"/>
-    <col min="11010" max="11010" width="62.42578125" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" customWidth="1"/>
-    <col min="11012" max="11012" width="17.28515625" customWidth="1"/>
-    <col min="11013" max="11013" width="20.7109375" customWidth="1"/>
-    <col min="11014" max="11014" width="33.85546875" customWidth="1"/>
-    <col min="11015" max="11015" width="37.28515625" customWidth="1"/>
-    <col min="11016" max="11016" width="18.5703125" customWidth="1"/>
-    <col min="11265" max="11265" width="5.85546875" customWidth="1"/>
-    <col min="11266" max="11266" width="62.42578125" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" customWidth="1"/>
-    <col min="11268" max="11268" width="17.28515625" customWidth="1"/>
-    <col min="11269" max="11269" width="20.7109375" customWidth="1"/>
-    <col min="11270" max="11270" width="33.85546875" customWidth="1"/>
-    <col min="11271" max="11271" width="37.28515625" customWidth="1"/>
-    <col min="11272" max="11272" width="18.5703125" customWidth="1"/>
-    <col min="11521" max="11521" width="5.85546875" customWidth="1"/>
-    <col min="11522" max="11522" width="62.42578125" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" customWidth="1"/>
-    <col min="11524" max="11524" width="17.28515625" customWidth="1"/>
-    <col min="11525" max="11525" width="20.7109375" customWidth="1"/>
-    <col min="11526" max="11526" width="33.85546875" customWidth="1"/>
-    <col min="11527" max="11527" width="37.28515625" customWidth="1"/>
-    <col min="11528" max="11528" width="18.5703125" customWidth="1"/>
-    <col min="11777" max="11777" width="5.85546875" customWidth="1"/>
-    <col min="11778" max="11778" width="62.42578125" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" customWidth="1"/>
-    <col min="11780" max="11780" width="17.28515625" customWidth="1"/>
-    <col min="11781" max="11781" width="20.7109375" customWidth="1"/>
-    <col min="11782" max="11782" width="33.85546875" customWidth="1"/>
-    <col min="11783" max="11783" width="37.28515625" customWidth="1"/>
-    <col min="11784" max="11784" width="18.5703125" customWidth="1"/>
-    <col min="12033" max="12033" width="5.85546875" customWidth="1"/>
-    <col min="12034" max="12034" width="62.42578125" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" customWidth="1"/>
-    <col min="12036" max="12036" width="17.28515625" customWidth="1"/>
-    <col min="12037" max="12037" width="20.7109375" customWidth="1"/>
-    <col min="12038" max="12038" width="33.85546875" customWidth="1"/>
-    <col min="12039" max="12039" width="37.28515625" customWidth="1"/>
-    <col min="12040" max="12040" width="18.5703125" customWidth="1"/>
-    <col min="12289" max="12289" width="5.85546875" customWidth="1"/>
-    <col min="12290" max="12290" width="62.42578125" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" customWidth="1"/>
-    <col min="12292" max="12292" width="17.28515625" customWidth="1"/>
-    <col min="12293" max="12293" width="20.7109375" customWidth="1"/>
-    <col min="12294" max="12294" width="33.85546875" customWidth="1"/>
-    <col min="12295" max="12295" width="37.28515625" customWidth="1"/>
-    <col min="12296" max="12296" width="18.5703125" customWidth="1"/>
-    <col min="12545" max="12545" width="5.85546875" customWidth="1"/>
-    <col min="12546" max="12546" width="62.42578125" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" customWidth="1"/>
-    <col min="12548" max="12548" width="17.28515625" customWidth="1"/>
-    <col min="12549" max="12549" width="20.7109375" customWidth="1"/>
-    <col min="12550" max="12550" width="33.85546875" customWidth="1"/>
-    <col min="12551" max="12551" width="37.28515625" customWidth="1"/>
-    <col min="12552" max="12552" width="18.5703125" customWidth="1"/>
-    <col min="12801" max="12801" width="5.85546875" customWidth="1"/>
-    <col min="12802" max="12802" width="62.42578125" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" customWidth="1"/>
-    <col min="12804" max="12804" width="17.28515625" customWidth="1"/>
-    <col min="12805" max="12805" width="20.7109375" customWidth="1"/>
-    <col min="12806" max="12806" width="33.85546875" customWidth="1"/>
-    <col min="12807" max="12807" width="37.28515625" customWidth="1"/>
-    <col min="12808" max="12808" width="18.5703125" customWidth="1"/>
-    <col min="13057" max="13057" width="5.85546875" customWidth="1"/>
-    <col min="13058" max="13058" width="62.42578125" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" customWidth="1"/>
-    <col min="13060" max="13060" width="17.28515625" customWidth="1"/>
-    <col min="13061" max="13061" width="20.7109375" customWidth="1"/>
-    <col min="13062" max="13062" width="33.85546875" customWidth="1"/>
-    <col min="13063" max="13063" width="37.28515625" customWidth="1"/>
-    <col min="13064" max="13064" width="18.5703125" customWidth="1"/>
-    <col min="13313" max="13313" width="5.85546875" customWidth="1"/>
-    <col min="13314" max="13314" width="62.42578125" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" customWidth="1"/>
-    <col min="13316" max="13316" width="17.28515625" customWidth="1"/>
-    <col min="13317" max="13317" width="20.7109375" customWidth="1"/>
-    <col min="13318" max="13318" width="33.85546875" customWidth="1"/>
-    <col min="13319" max="13319" width="37.28515625" customWidth="1"/>
-    <col min="13320" max="13320" width="18.5703125" customWidth="1"/>
-    <col min="13569" max="13569" width="5.85546875" customWidth="1"/>
-    <col min="13570" max="13570" width="62.42578125" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" customWidth="1"/>
-    <col min="13572" max="13572" width="17.28515625" customWidth="1"/>
-    <col min="13573" max="13573" width="20.7109375" customWidth="1"/>
-    <col min="13574" max="13574" width="33.85546875" customWidth="1"/>
-    <col min="13575" max="13575" width="37.28515625" customWidth="1"/>
-    <col min="13576" max="13576" width="18.5703125" customWidth="1"/>
-    <col min="13825" max="13825" width="5.85546875" customWidth="1"/>
-    <col min="13826" max="13826" width="62.42578125" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" customWidth="1"/>
-    <col min="13828" max="13828" width="17.28515625" customWidth="1"/>
-    <col min="13829" max="13829" width="20.7109375" customWidth="1"/>
-    <col min="13830" max="13830" width="33.85546875" customWidth="1"/>
-    <col min="13831" max="13831" width="37.28515625" customWidth="1"/>
-    <col min="13832" max="13832" width="18.5703125" customWidth="1"/>
-    <col min="14081" max="14081" width="5.85546875" customWidth="1"/>
-    <col min="14082" max="14082" width="62.42578125" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" customWidth="1"/>
-    <col min="14084" max="14084" width="17.28515625" customWidth="1"/>
-    <col min="14085" max="14085" width="20.7109375" customWidth="1"/>
-    <col min="14086" max="14086" width="33.85546875" customWidth="1"/>
-    <col min="14087" max="14087" width="37.28515625" customWidth="1"/>
-    <col min="14088" max="14088" width="18.5703125" customWidth="1"/>
-    <col min="14337" max="14337" width="5.85546875" customWidth="1"/>
-    <col min="14338" max="14338" width="62.42578125" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" customWidth="1"/>
-    <col min="14340" max="14340" width="17.28515625" customWidth="1"/>
-    <col min="14341" max="14341" width="20.7109375" customWidth="1"/>
-    <col min="14342" max="14342" width="33.85546875" customWidth="1"/>
-    <col min="14343" max="14343" width="37.28515625" customWidth="1"/>
-    <col min="14344" max="14344" width="18.5703125" customWidth="1"/>
-    <col min="14593" max="14593" width="5.85546875" customWidth="1"/>
-    <col min="14594" max="14594" width="62.42578125" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" customWidth="1"/>
-    <col min="14596" max="14596" width="17.28515625" customWidth="1"/>
-    <col min="14597" max="14597" width="20.7109375" customWidth="1"/>
-    <col min="14598" max="14598" width="33.85546875" customWidth="1"/>
-    <col min="14599" max="14599" width="37.28515625" customWidth="1"/>
-    <col min="14600" max="14600" width="18.5703125" customWidth="1"/>
-    <col min="14849" max="14849" width="5.85546875" customWidth="1"/>
-    <col min="14850" max="14850" width="62.42578125" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" customWidth="1"/>
-    <col min="14852" max="14852" width="17.28515625" customWidth="1"/>
-    <col min="14853" max="14853" width="20.7109375" customWidth="1"/>
-    <col min="14854" max="14854" width="33.85546875" customWidth="1"/>
-    <col min="14855" max="14855" width="37.28515625" customWidth="1"/>
-    <col min="14856" max="14856" width="18.5703125" customWidth="1"/>
-    <col min="15105" max="15105" width="5.85546875" customWidth="1"/>
-    <col min="15106" max="15106" width="62.42578125" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" customWidth="1"/>
-    <col min="15108" max="15108" width="17.28515625" customWidth="1"/>
-    <col min="15109" max="15109" width="20.7109375" customWidth="1"/>
-    <col min="15110" max="15110" width="33.85546875" customWidth="1"/>
-    <col min="15111" max="15111" width="37.28515625" customWidth="1"/>
-    <col min="15112" max="15112" width="18.5703125" customWidth="1"/>
-    <col min="15361" max="15361" width="5.85546875" customWidth="1"/>
-    <col min="15362" max="15362" width="62.42578125" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" customWidth="1"/>
-    <col min="15364" max="15364" width="17.28515625" customWidth="1"/>
-    <col min="15365" max="15365" width="20.7109375" customWidth="1"/>
-    <col min="15366" max="15366" width="33.85546875" customWidth="1"/>
-    <col min="15367" max="15367" width="37.28515625" customWidth="1"/>
-    <col min="15368" max="15368" width="18.5703125" customWidth="1"/>
-    <col min="15617" max="15617" width="5.85546875" customWidth="1"/>
-    <col min="15618" max="15618" width="62.42578125" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" customWidth="1"/>
-    <col min="15620" max="15620" width="17.28515625" customWidth="1"/>
-    <col min="15621" max="15621" width="20.7109375" customWidth="1"/>
-    <col min="15622" max="15622" width="33.85546875" customWidth="1"/>
-    <col min="15623" max="15623" width="37.28515625" customWidth="1"/>
-    <col min="15624" max="15624" width="18.5703125" customWidth="1"/>
-    <col min="15873" max="15873" width="5.85546875" customWidth="1"/>
-    <col min="15874" max="15874" width="62.42578125" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" customWidth="1"/>
-    <col min="15876" max="15876" width="17.28515625" customWidth="1"/>
-    <col min="15877" max="15877" width="20.7109375" customWidth="1"/>
-    <col min="15878" max="15878" width="33.85546875" customWidth="1"/>
-    <col min="15879" max="15879" width="37.28515625" customWidth="1"/>
-    <col min="15880" max="15880" width="18.5703125" customWidth="1"/>
-    <col min="16129" max="16129" width="5.85546875" customWidth="1"/>
-    <col min="16130" max="16130" width="62.42578125" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" customWidth="1"/>
-    <col min="16132" max="16132" width="17.28515625" customWidth="1"/>
-    <col min="16133" max="16133" width="20.7109375" customWidth="1"/>
-    <col min="16134" max="16134" width="33.85546875" customWidth="1"/>
-    <col min="16135" max="16135" width="37.28515625" customWidth="1"/>
-    <col min="16136" max="16136" width="18.5703125" customWidth="1"/>
+    <col min="257" max="257" width="5.83203125" customWidth="1"/>
+    <col min="258" max="258" width="62.4140625" customWidth="1"/>
+    <col min="259" max="259" width="14.83203125" customWidth="1"/>
+    <col min="260" max="260" width="17.25" customWidth="1"/>
+    <col min="261" max="261" width="20.75" customWidth="1"/>
+    <col min="262" max="262" width="33.83203125" customWidth="1"/>
+    <col min="263" max="263" width="37.25" customWidth="1"/>
+    <col min="264" max="264" width="18.58203125" customWidth="1"/>
+    <col min="513" max="513" width="5.83203125" customWidth="1"/>
+    <col min="514" max="514" width="62.4140625" customWidth="1"/>
+    <col min="515" max="515" width="14.83203125" customWidth="1"/>
+    <col min="516" max="516" width="17.25" customWidth="1"/>
+    <col min="517" max="517" width="20.75" customWidth="1"/>
+    <col min="518" max="518" width="33.83203125" customWidth="1"/>
+    <col min="519" max="519" width="37.25" customWidth="1"/>
+    <col min="520" max="520" width="18.58203125" customWidth="1"/>
+    <col min="769" max="769" width="5.83203125" customWidth="1"/>
+    <col min="770" max="770" width="62.4140625" customWidth="1"/>
+    <col min="771" max="771" width="14.83203125" customWidth="1"/>
+    <col min="772" max="772" width="17.25" customWidth="1"/>
+    <col min="773" max="773" width="20.75" customWidth="1"/>
+    <col min="774" max="774" width="33.83203125" customWidth="1"/>
+    <col min="775" max="775" width="37.25" customWidth="1"/>
+    <col min="776" max="776" width="18.58203125" customWidth="1"/>
+    <col min="1025" max="1025" width="5.83203125" customWidth="1"/>
+    <col min="1026" max="1026" width="62.4140625" customWidth="1"/>
+    <col min="1027" max="1027" width="14.83203125" customWidth="1"/>
+    <col min="1028" max="1028" width="17.25" customWidth="1"/>
+    <col min="1029" max="1029" width="20.75" customWidth="1"/>
+    <col min="1030" max="1030" width="33.83203125" customWidth="1"/>
+    <col min="1031" max="1031" width="37.25" customWidth="1"/>
+    <col min="1032" max="1032" width="18.58203125" customWidth="1"/>
+    <col min="1281" max="1281" width="5.83203125" customWidth="1"/>
+    <col min="1282" max="1282" width="62.4140625" customWidth="1"/>
+    <col min="1283" max="1283" width="14.83203125" customWidth="1"/>
+    <col min="1284" max="1284" width="17.25" customWidth="1"/>
+    <col min="1285" max="1285" width="20.75" customWidth="1"/>
+    <col min="1286" max="1286" width="33.83203125" customWidth="1"/>
+    <col min="1287" max="1287" width="37.25" customWidth="1"/>
+    <col min="1288" max="1288" width="18.58203125" customWidth="1"/>
+    <col min="1537" max="1537" width="5.83203125" customWidth="1"/>
+    <col min="1538" max="1538" width="62.4140625" customWidth="1"/>
+    <col min="1539" max="1539" width="14.83203125" customWidth="1"/>
+    <col min="1540" max="1540" width="17.25" customWidth="1"/>
+    <col min="1541" max="1541" width="20.75" customWidth="1"/>
+    <col min="1542" max="1542" width="33.83203125" customWidth="1"/>
+    <col min="1543" max="1543" width="37.25" customWidth="1"/>
+    <col min="1544" max="1544" width="18.58203125" customWidth="1"/>
+    <col min="1793" max="1793" width="5.83203125" customWidth="1"/>
+    <col min="1794" max="1794" width="62.4140625" customWidth="1"/>
+    <col min="1795" max="1795" width="14.83203125" customWidth="1"/>
+    <col min="1796" max="1796" width="17.25" customWidth="1"/>
+    <col min="1797" max="1797" width="20.75" customWidth="1"/>
+    <col min="1798" max="1798" width="33.83203125" customWidth="1"/>
+    <col min="1799" max="1799" width="37.25" customWidth="1"/>
+    <col min="1800" max="1800" width="18.58203125" customWidth="1"/>
+    <col min="2049" max="2049" width="5.83203125" customWidth="1"/>
+    <col min="2050" max="2050" width="62.4140625" customWidth="1"/>
+    <col min="2051" max="2051" width="14.83203125" customWidth="1"/>
+    <col min="2052" max="2052" width="17.25" customWidth="1"/>
+    <col min="2053" max="2053" width="20.75" customWidth="1"/>
+    <col min="2054" max="2054" width="33.83203125" customWidth="1"/>
+    <col min="2055" max="2055" width="37.25" customWidth="1"/>
+    <col min="2056" max="2056" width="18.58203125" customWidth="1"/>
+    <col min="2305" max="2305" width="5.83203125" customWidth="1"/>
+    <col min="2306" max="2306" width="62.4140625" customWidth="1"/>
+    <col min="2307" max="2307" width="14.83203125" customWidth="1"/>
+    <col min="2308" max="2308" width="17.25" customWidth="1"/>
+    <col min="2309" max="2309" width="20.75" customWidth="1"/>
+    <col min="2310" max="2310" width="33.83203125" customWidth="1"/>
+    <col min="2311" max="2311" width="37.25" customWidth="1"/>
+    <col min="2312" max="2312" width="18.58203125" customWidth="1"/>
+    <col min="2561" max="2561" width="5.83203125" customWidth="1"/>
+    <col min="2562" max="2562" width="62.4140625" customWidth="1"/>
+    <col min="2563" max="2563" width="14.83203125" customWidth="1"/>
+    <col min="2564" max="2564" width="17.25" customWidth="1"/>
+    <col min="2565" max="2565" width="20.75" customWidth="1"/>
+    <col min="2566" max="2566" width="33.83203125" customWidth="1"/>
+    <col min="2567" max="2567" width="37.25" customWidth="1"/>
+    <col min="2568" max="2568" width="18.58203125" customWidth="1"/>
+    <col min="2817" max="2817" width="5.83203125" customWidth="1"/>
+    <col min="2818" max="2818" width="62.4140625" customWidth="1"/>
+    <col min="2819" max="2819" width="14.83203125" customWidth="1"/>
+    <col min="2820" max="2820" width="17.25" customWidth="1"/>
+    <col min="2821" max="2821" width="20.75" customWidth="1"/>
+    <col min="2822" max="2822" width="33.83203125" customWidth="1"/>
+    <col min="2823" max="2823" width="37.25" customWidth="1"/>
+    <col min="2824" max="2824" width="18.58203125" customWidth="1"/>
+    <col min="3073" max="3073" width="5.83203125" customWidth="1"/>
+    <col min="3074" max="3074" width="62.4140625" customWidth="1"/>
+    <col min="3075" max="3075" width="14.83203125" customWidth="1"/>
+    <col min="3076" max="3076" width="17.25" customWidth="1"/>
+    <col min="3077" max="3077" width="20.75" customWidth="1"/>
+    <col min="3078" max="3078" width="33.83203125" customWidth="1"/>
+    <col min="3079" max="3079" width="37.25" customWidth="1"/>
+    <col min="3080" max="3080" width="18.58203125" customWidth="1"/>
+    <col min="3329" max="3329" width="5.83203125" customWidth="1"/>
+    <col min="3330" max="3330" width="62.4140625" customWidth="1"/>
+    <col min="3331" max="3331" width="14.83203125" customWidth="1"/>
+    <col min="3332" max="3332" width="17.25" customWidth="1"/>
+    <col min="3333" max="3333" width="20.75" customWidth="1"/>
+    <col min="3334" max="3334" width="33.83203125" customWidth="1"/>
+    <col min="3335" max="3335" width="37.25" customWidth="1"/>
+    <col min="3336" max="3336" width="18.58203125" customWidth="1"/>
+    <col min="3585" max="3585" width="5.83203125" customWidth="1"/>
+    <col min="3586" max="3586" width="62.4140625" customWidth="1"/>
+    <col min="3587" max="3587" width="14.83203125" customWidth="1"/>
+    <col min="3588" max="3588" width="17.25" customWidth="1"/>
+    <col min="3589" max="3589" width="20.75" customWidth="1"/>
+    <col min="3590" max="3590" width="33.83203125" customWidth="1"/>
+    <col min="3591" max="3591" width="37.25" customWidth="1"/>
+    <col min="3592" max="3592" width="18.58203125" customWidth="1"/>
+    <col min="3841" max="3841" width="5.83203125" customWidth="1"/>
+    <col min="3842" max="3842" width="62.4140625" customWidth="1"/>
+    <col min="3843" max="3843" width="14.83203125" customWidth="1"/>
+    <col min="3844" max="3844" width="17.25" customWidth="1"/>
+    <col min="3845" max="3845" width="20.75" customWidth="1"/>
+    <col min="3846" max="3846" width="33.83203125" customWidth="1"/>
+    <col min="3847" max="3847" width="37.25" customWidth="1"/>
+    <col min="3848" max="3848" width="18.58203125" customWidth="1"/>
+    <col min="4097" max="4097" width="5.83203125" customWidth="1"/>
+    <col min="4098" max="4098" width="62.4140625" customWidth="1"/>
+    <col min="4099" max="4099" width="14.83203125" customWidth="1"/>
+    <col min="4100" max="4100" width="17.25" customWidth="1"/>
+    <col min="4101" max="4101" width="20.75" customWidth="1"/>
+    <col min="4102" max="4102" width="33.83203125" customWidth="1"/>
+    <col min="4103" max="4103" width="37.25" customWidth="1"/>
+    <col min="4104" max="4104" width="18.58203125" customWidth="1"/>
+    <col min="4353" max="4353" width="5.83203125" customWidth="1"/>
+    <col min="4354" max="4354" width="62.4140625" customWidth="1"/>
+    <col min="4355" max="4355" width="14.83203125" customWidth="1"/>
+    <col min="4356" max="4356" width="17.25" customWidth="1"/>
+    <col min="4357" max="4357" width="20.75" customWidth="1"/>
+    <col min="4358" max="4358" width="33.83203125" customWidth="1"/>
+    <col min="4359" max="4359" width="37.25" customWidth="1"/>
+    <col min="4360" max="4360" width="18.58203125" customWidth="1"/>
+    <col min="4609" max="4609" width="5.83203125" customWidth="1"/>
+    <col min="4610" max="4610" width="62.4140625" customWidth="1"/>
+    <col min="4611" max="4611" width="14.83203125" customWidth="1"/>
+    <col min="4612" max="4612" width="17.25" customWidth="1"/>
+    <col min="4613" max="4613" width="20.75" customWidth="1"/>
+    <col min="4614" max="4614" width="33.83203125" customWidth="1"/>
+    <col min="4615" max="4615" width="37.25" customWidth="1"/>
+    <col min="4616" max="4616" width="18.58203125" customWidth="1"/>
+    <col min="4865" max="4865" width="5.83203125" customWidth="1"/>
+    <col min="4866" max="4866" width="62.4140625" customWidth="1"/>
+    <col min="4867" max="4867" width="14.83203125" customWidth="1"/>
+    <col min="4868" max="4868" width="17.25" customWidth="1"/>
+    <col min="4869" max="4869" width="20.75" customWidth="1"/>
+    <col min="4870" max="4870" width="33.83203125" customWidth="1"/>
+    <col min="4871" max="4871" width="37.25" customWidth="1"/>
+    <col min="4872" max="4872" width="18.58203125" customWidth="1"/>
+    <col min="5121" max="5121" width="5.83203125" customWidth="1"/>
+    <col min="5122" max="5122" width="62.4140625" customWidth="1"/>
+    <col min="5123" max="5123" width="14.83203125" customWidth="1"/>
+    <col min="5124" max="5124" width="17.25" customWidth="1"/>
+    <col min="5125" max="5125" width="20.75" customWidth="1"/>
+    <col min="5126" max="5126" width="33.83203125" customWidth="1"/>
+    <col min="5127" max="5127" width="37.25" customWidth="1"/>
+    <col min="5128" max="5128" width="18.58203125" customWidth="1"/>
+    <col min="5377" max="5377" width="5.83203125" customWidth="1"/>
+    <col min="5378" max="5378" width="62.4140625" customWidth="1"/>
+    <col min="5379" max="5379" width="14.83203125" customWidth="1"/>
+    <col min="5380" max="5380" width="17.25" customWidth="1"/>
+    <col min="5381" max="5381" width="20.75" customWidth="1"/>
+    <col min="5382" max="5382" width="33.83203125" customWidth="1"/>
+    <col min="5383" max="5383" width="37.25" customWidth="1"/>
+    <col min="5384" max="5384" width="18.58203125" customWidth="1"/>
+    <col min="5633" max="5633" width="5.83203125" customWidth="1"/>
+    <col min="5634" max="5634" width="62.4140625" customWidth="1"/>
+    <col min="5635" max="5635" width="14.83203125" customWidth="1"/>
+    <col min="5636" max="5636" width="17.25" customWidth="1"/>
+    <col min="5637" max="5637" width="20.75" customWidth="1"/>
+    <col min="5638" max="5638" width="33.83203125" customWidth="1"/>
+    <col min="5639" max="5639" width="37.25" customWidth="1"/>
+    <col min="5640" max="5640" width="18.58203125" customWidth="1"/>
+    <col min="5889" max="5889" width="5.83203125" customWidth="1"/>
+    <col min="5890" max="5890" width="62.4140625" customWidth="1"/>
+    <col min="5891" max="5891" width="14.83203125" customWidth="1"/>
+    <col min="5892" max="5892" width="17.25" customWidth="1"/>
+    <col min="5893" max="5893" width="20.75" customWidth="1"/>
+    <col min="5894" max="5894" width="33.83203125" customWidth="1"/>
+    <col min="5895" max="5895" width="37.25" customWidth="1"/>
+    <col min="5896" max="5896" width="18.58203125" customWidth="1"/>
+    <col min="6145" max="6145" width="5.83203125" customWidth="1"/>
+    <col min="6146" max="6146" width="62.4140625" customWidth="1"/>
+    <col min="6147" max="6147" width="14.83203125" customWidth="1"/>
+    <col min="6148" max="6148" width="17.25" customWidth="1"/>
+    <col min="6149" max="6149" width="20.75" customWidth="1"/>
+    <col min="6150" max="6150" width="33.83203125" customWidth="1"/>
+    <col min="6151" max="6151" width="37.25" customWidth="1"/>
+    <col min="6152" max="6152" width="18.58203125" customWidth="1"/>
+    <col min="6401" max="6401" width="5.83203125" customWidth="1"/>
+    <col min="6402" max="6402" width="62.4140625" customWidth="1"/>
+    <col min="6403" max="6403" width="14.83203125" customWidth="1"/>
+    <col min="6404" max="6404" width="17.25" customWidth="1"/>
+    <col min="6405" max="6405" width="20.75" customWidth="1"/>
+    <col min="6406" max="6406" width="33.83203125" customWidth="1"/>
+    <col min="6407" max="6407" width="37.25" customWidth="1"/>
+    <col min="6408" max="6408" width="18.58203125" customWidth="1"/>
+    <col min="6657" max="6657" width="5.83203125" customWidth="1"/>
+    <col min="6658" max="6658" width="62.4140625" customWidth="1"/>
+    <col min="6659" max="6659" width="14.83203125" customWidth="1"/>
+    <col min="6660" max="6660" width="17.25" customWidth="1"/>
+    <col min="6661" max="6661" width="20.75" customWidth="1"/>
+    <col min="6662" max="6662" width="33.83203125" customWidth="1"/>
+    <col min="6663" max="6663" width="37.25" customWidth="1"/>
+    <col min="6664" max="6664" width="18.58203125" customWidth="1"/>
+    <col min="6913" max="6913" width="5.83203125" customWidth="1"/>
+    <col min="6914" max="6914" width="62.4140625" customWidth="1"/>
+    <col min="6915" max="6915" width="14.83203125" customWidth="1"/>
+    <col min="6916" max="6916" width="17.25" customWidth="1"/>
+    <col min="6917" max="6917" width="20.75" customWidth="1"/>
+    <col min="6918" max="6918" width="33.83203125" customWidth="1"/>
+    <col min="6919" max="6919" width="37.25" customWidth="1"/>
+    <col min="6920" max="6920" width="18.58203125" customWidth="1"/>
+    <col min="7169" max="7169" width="5.83203125" customWidth="1"/>
+    <col min="7170" max="7170" width="62.4140625" customWidth="1"/>
+    <col min="7171" max="7171" width="14.83203125" customWidth="1"/>
+    <col min="7172" max="7172" width="17.25" customWidth="1"/>
+    <col min="7173" max="7173" width="20.75" customWidth="1"/>
+    <col min="7174" max="7174" width="33.83203125" customWidth="1"/>
+    <col min="7175" max="7175" width="37.25" customWidth="1"/>
+    <col min="7176" max="7176" width="18.58203125" customWidth="1"/>
+    <col min="7425" max="7425" width="5.83203125" customWidth="1"/>
+    <col min="7426" max="7426" width="62.4140625" customWidth="1"/>
+    <col min="7427" max="7427" width="14.83203125" customWidth="1"/>
+    <col min="7428" max="7428" width="17.25" customWidth="1"/>
+    <col min="7429" max="7429" width="20.75" customWidth="1"/>
+    <col min="7430" max="7430" width="33.83203125" customWidth="1"/>
+    <col min="7431" max="7431" width="37.25" customWidth="1"/>
+    <col min="7432" max="7432" width="18.58203125" customWidth="1"/>
+    <col min="7681" max="7681" width="5.83203125" customWidth="1"/>
+    <col min="7682" max="7682" width="62.4140625" customWidth="1"/>
+    <col min="7683" max="7683" width="14.83203125" customWidth="1"/>
+    <col min="7684" max="7684" width="17.25" customWidth="1"/>
+    <col min="7685" max="7685" width="20.75" customWidth="1"/>
+    <col min="7686" max="7686" width="33.83203125" customWidth="1"/>
+    <col min="7687" max="7687" width="37.25" customWidth="1"/>
+    <col min="7688" max="7688" width="18.58203125" customWidth="1"/>
+    <col min="7937" max="7937" width="5.83203125" customWidth="1"/>
+    <col min="7938" max="7938" width="62.4140625" customWidth="1"/>
+    <col min="7939" max="7939" width="14.83203125" customWidth="1"/>
+    <col min="7940" max="7940" width="17.25" customWidth="1"/>
+    <col min="7941" max="7941" width="20.75" customWidth="1"/>
+    <col min="7942" max="7942" width="33.83203125" customWidth="1"/>
+    <col min="7943" max="7943" width="37.25" customWidth="1"/>
+    <col min="7944" max="7944" width="18.58203125" customWidth="1"/>
+    <col min="8193" max="8193" width="5.83203125" customWidth="1"/>
+    <col min="8194" max="8194" width="62.4140625" customWidth="1"/>
+    <col min="8195" max="8195" width="14.83203125" customWidth="1"/>
+    <col min="8196" max="8196" width="17.25" customWidth="1"/>
+    <col min="8197" max="8197" width="20.75" customWidth="1"/>
+    <col min="8198" max="8198" width="33.83203125" customWidth="1"/>
+    <col min="8199" max="8199" width="37.25" customWidth="1"/>
+    <col min="8200" max="8200" width="18.58203125" customWidth="1"/>
+    <col min="8449" max="8449" width="5.83203125" customWidth="1"/>
+    <col min="8450" max="8450" width="62.4140625" customWidth="1"/>
+    <col min="8451" max="8451" width="14.83203125" customWidth="1"/>
+    <col min="8452" max="8452" width="17.25" customWidth="1"/>
+    <col min="8453" max="8453" width="20.75" customWidth="1"/>
+    <col min="8454" max="8454" width="33.83203125" customWidth="1"/>
+    <col min="8455" max="8455" width="37.25" customWidth="1"/>
+    <col min="8456" max="8456" width="18.58203125" customWidth="1"/>
+    <col min="8705" max="8705" width="5.83203125" customWidth="1"/>
+    <col min="8706" max="8706" width="62.4140625" customWidth="1"/>
+    <col min="8707" max="8707" width="14.83203125" customWidth="1"/>
+    <col min="8708" max="8708" width="17.25" customWidth="1"/>
+    <col min="8709" max="8709" width="20.75" customWidth="1"/>
+    <col min="8710" max="8710" width="33.83203125" customWidth="1"/>
+    <col min="8711" max="8711" width="37.25" customWidth="1"/>
+    <col min="8712" max="8712" width="18.58203125" customWidth="1"/>
+    <col min="8961" max="8961" width="5.83203125" customWidth="1"/>
+    <col min="8962" max="8962" width="62.4140625" customWidth="1"/>
+    <col min="8963" max="8963" width="14.83203125" customWidth="1"/>
+    <col min="8964" max="8964" width="17.25" customWidth="1"/>
+    <col min="8965" max="8965" width="20.75" customWidth="1"/>
+    <col min="8966" max="8966" width="33.83203125" customWidth="1"/>
+    <col min="8967" max="8967" width="37.25" customWidth="1"/>
+    <col min="8968" max="8968" width="18.58203125" customWidth="1"/>
+    <col min="9217" max="9217" width="5.83203125" customWidth="1"/>
+    <col min="9218" max="9218" width="62.4140625" customWidth="1"/>
+    <col min="9219" max="9219" width="14.83203125" customWidth="1"/>
+    <col min="9220" max="9220" width="17.25" customWidth="1"/>
+    <col min="9221" max="9221" width="20.75" customWidth="1"/>
+    <col min="9222" max="9222" width="33.83203125" customWidth="1"/>
+    <col min="9223" max="9223" width="37.25" customWidth="1"/>
+    <col min="9224" max="9224" width="18.58203125" customWidth="1"/>
+    <col min="9473" max="9473" width="5.83203125" customWidth="1"/>
+    <col min="9474" max="9474" width="62.4140625" customWidth="1"/>
+    <col min="9475" max="9475" width="14.83203125" customWidth="1"/>
+    <col min="9476" max="9476" width="17.25" customWidth="1"/>
+    <col min="9477" max="9477" width="20.75" customWidth="1"/>
+    <col min="9478" max="9478" width="33.83203125" customWidth="1"/>
+    <col min="9479" max="9479" width="37.25" customWidth="1"/>
+    <col min="9480" max="9480" width="18.58203125" customWidth="1"/>
+    <col min="9729" max="9729" width="5.83203125" customWidth="1"/>
+    <col min="9730" max="9730" width="62.4140625" customWidth="1"/>
+    <col min="9731" max="9731" width="14.83203125" customWidth="1"/>
+    <col min="9732" max="9732" width="17.25" customWidth="1"/>
+    <col min="9733" max="9733" width="20.75" customWidth="1"/>
+    <col min="9734" max="9734" width="33.83203125" customWidth="1"/>
+    <col min="9735" max="9735" width="37.25" customWidth="1"/>
+    <col min="9736" max="9736" width="18.58203125" customWidth="1"/>
+    <col min="9985" max="9985" width="5.83203125" customWidth="1"/>
+    <col min="9986" max="9986" width="62.4140625" customWidth="1"/>
+    <col min="9987" max="9987" width="14.83203125" customWidth="1"/>
+    <col min="9988" max="9988" width="17.25" customWidth="1"/>
+    <col min="9989" max="9989" width="20.75" customWidth="1"/>
+    <col min="9990" max="9990" width="33.83203125" customWidth="1"/>
+    <col min="9991" max="9991" width="37.25" customWidth="1"/>
+    <col min="9992" max="9992" width="18.58203125" customWidth="1"/>
+    <col min="10241" max="10241" width="5.83203125" customWidth="1"/>
+    <col min="10242" max="10242" width="62.4140625" customWidth="1"/>
+    <col min="10243" max="10243" width="14.83203125" customWidth="1"/>
+    <col min="10244" max="10244" width="17.25" customWidth="1"/>
+    <col min="10245" max="10245" width="20.75" customWidth="1"/>
+    <col min="10246" max="10246" width="33.83203125" customWidth="1"/>
+    <col min="10247" max="10247" width="37.25" customWidth="1"/>
+    <col min="10248" max="10248" width="18.58203125" customWidth="1"/>
+    <col min="10497" max="10497" width="5.83203125" customWidth="1"/>
+    <col min="10498" max="10498" width="62.4140625" customWidth="1"/>
+    <col min="10499" max="10499" width="14.83203125" customWidth="1"/>
+    <col min="10500" max="10500" width="17.25" customWidth="1"/>
+    <col min="10501" max="10501" width="20.75" customWidth="1"/>
+    <col min="10502" max="10502" width="33.83203125" customWidth="1"/>
+    <col min="10503" max="10503" width="37.25" customWidth="1"/>
+    <col min="10504" max="10504" width="18.58203125" customWidth="1"/>
+    <col min="10753" max="10753" width="5.83203125" customWidth="1"/>
+    <col min="10754" max="10754" width="62.4140625" customWidth="1"/>
+    <col min="10755" max="10755" width="14.83203125" customWidth="1"/>
+    <col min="10756" max="10756" width="17.25" customWidth="1"/>
+    <col min="10757" max="10757" width="20.75" customWidth="1"/>
+    <col min="10758" max="10758" width="33.83203125" customWidth="1"/>
+    <col min="10759" max="10759" width="37.25" customWidth="1"/>
+    <col min="10760" max="10760" width="18.58203125" customWidth="1"/>
+    <col min="11009" max="11009" width="5.83203125" customWidth="1"/>
+    <col min="11010" max="11010" width="62.4140625" customWidth="1"/>
+    <col min="11011" max="11011" width="14.83203125" customWidth="1"/>
+    <col min="11012" max="11012" width="17.25" customWidth="1"/>
+    <col min="11013" max="11013" width="20.75" customWidth="1"/>
+    <col min="11014" max="11014" width="33.83203125" customWidth="1"/>
+    <col min="11015" max="11015" width="37.25" customWidth="1"/>
+    <col min="11016" max="11016" width="18.58203125" customWidth="1"/>
+    <col min="11265" max="11265" width="5.83203125" customWidth="1"/>
+    <col min="11266" max="11266" width="62.4140625" customWidth="1"/>
+    <col min="11267" max="11267" width="14.83203125" customWidth="1"/>
+    <col min="11268" max="11268" width="17.25" customWidth="1"/>
+    <col min="11269" max="11269" width="20.75" customWidth="1"/>
+    <col min="11270" max="11270" width="33.83203125" customWidth="1"/>
+    <col min="11271" max="11271" width="37.25" customWidth="1"/>
+    <col min="11272" max="11272" width="18.58203125" customWidth="1"/>
+    <col min="11521" max="11521" width="5.83203125" customWidth="1"/>
+    <col min="11522" max="11522" width="62.4140625" customWidth="1"/>
+    <col min="11523" max="11523" width="14.83203125" customWidth="1"/>
+    <col min="11524" max="11524" width="17.25" customWidth="1"/>
+    <col min="11525" max="11525" width="20.75" customWidth="1"/>
+    <col min="11526" max="11526" width="33.83203125" customWidth="1"/>
+    <col min="11527" max="11527" width="37.25" customWidth="1"/>
+    <col min="11528" max="11528" width="18.58203125" customWidth="1"/>
+    <col min="11777" max="11777" width="5.83203125" customWidth="1"/>
+    <col min="11778" max="11778" width="62.4140625" customWidth="1"/>
+    <col min="11779" max="11779" width="14.83203125" customWidth="1"/>
+    <col min="11780" max="11780" width="17.25" customWidth="1"/>
+    <col min="11781" max="11781" width="20.75" customWidth="1"/>
+    <col min="11782" max="11782" width="33.83203125" customWidth="1"/>
+    <col min="11783" max="11783" width="37.25" customWidth="1"/>
+    <col min="11784" max="11784" width="18.58203125" customWidth="1"/>
+    <col min="12033" max="12033" width="5.83203125" customWidth="1"/>
+    <col min="12034" max="12034" width="62.4140625" customWidth="1"/>
+    <col min="12035" max="12035" width="14.83203125" customWidth="1"/>
+    <col min="12036" max="12036" width="17.25" customWidth="1"/>
+    <col min="12037" max="12037" width="20.75" customWidth="1"/>
+    <col min="12038" max="12038" width="33.83203125" customWidth="1"/>
+    <col min="12039" max="12039" width="37.25" customWidth="1"/>
+    <col min="12040" max="12040" width="18.58203125" customWidth="1"/>
+    <col min="12289" max="12289" width="5.83203125" customWidth="1"/>
+    <col min="12290" max="12290" width="62.4140625" customWidth="1"/>
+    <col min="12291" max="12291" width="14.83203125" customWidth="1"/>
+    <col min="12292" max="12292" width="17.25" customWidth="1"/>
+    <col min="12293" max="12293" width="20.75" customWidth="1"/>
+    <col min="12294" max="12294" width="33.83203125" customWidth="1"/>
+    <col min="12295" max="12295" width="37.25" customWidth="1"/>
+    <col min="12296" max="12296" width="18.58203125" customWidth="1"/>
+    <col min="12545" max="12545" width="5.83203125" customWidth="1"/>
+    <col min="12546" max="12546" width="62.4140625" customWidth="1"/>
+    <col min="12547" max="12547" width="14.83203125" customWidth="1"/>
+    <col min="12548" max="12548" width="17.25" customWidth="1"/>
+    <col min="12549" max="12549" width="20.75" customWidth="1"/>
+    <col min="12550" max="12550" width="33.83203125" customWidth="1"/>
+    <col min="12551" max="12551" width="37.25" customWidth="1"/>
+    <col min="12552" max="12552" width="18.58203125" customWidth="1"/>
+    <col min="12801" max="12801" width="5.83203125" customWidth="1"/>
+    <col min="12802" max="12802" width="62.4140625" customWidth="1"/>
+    <col min="12803" max="12803" width="14.83203125" customWidth="1"/>
+    <col min="12804" max="12804" width="17.25" customWidth="1"/>
+    <col min="12805" max="12805" width="20.75" customWidth="1"/>
+    <col min="12806" max="12806" width="33.83203125" customWidth="1"/>
+    <col min="12807" max="12807" width="37.25" customWidth="1"/>
+    <col min="12808" max="12808" width="18.58203125" customWidth="1"/>
+    <col min="13057" max="13057" width="5.83203125" customWidth="1"/>
+    <col min="13058" max="13058" width="62.4140625" customWidth="1"/>
+    <col min="13059" max="13059" width="14.83203125" customWidth="1"/>
+    <col min="13060" max="13060" width="17.25" customWidth="1"/>
+    <col min="13061" max="13061" width="20.75" customWidth="1"/>
+    <col min="13062" max="13062" width="33.83203125" customWidth="1"/>
+    <col min="13063" max="13063" width="37.25" customWidth="1"/>
+    <col min="13064" max="13064" width="18.58203125" customWidth="1"/>
+    <col min="13313" max="13313" width="5.83203125" customWidth="1"/>
+    <col min="13314" max="13314" width="62.4140625" customWidth="1"/>
+    <col min="13315" max="13315" width="14.83203125" customWidth="1"/>
+    <col min="13316" max="13316" width="17.25" customWidth="1"/>
+    <col min="13317" max="13317" width="20.75" customWidth="1"/>
+    <col min="13318" max="13318" width="33.83203125" customWidth="1"/>
+    <col min="13319" max="13319" width="37.25" customWidth="1"/>
+    <col min="13320" max="13320" width="18.58203125" customWidth="1"/>
+    <col min="13569" max="13569" width="5.83203125" customWidth="1"/>
+    <col min="13570" max="13570" width="62.4140625" customWidth="1"/>
+    <col min="13571" max="13571" width="14.83203125" customWidth="1"/>
+    <col min="13572" max="13572" width="17.25" customWidth="1"/>
+    <col min="13573" max="13573" width="20.75" customWidth="1"/>
+    <col min="13574" max="13574" width="33.83203125" customWidth="1"/>
+    <col min="13575" max="13575" width="37.25" customWidth="1"/>
+    <col min="13576" max="13576" width="18.58203125" customWidth="1"/>
+    <col min="13825" max="13825" width="5.83203125" customWidth="1"/>
+    <col min="13826" max="13826" width="62.4140625" customWidth="1"/>
+    <col min="13827" max="13827" width="14.83203125" customWidth="1"/>
+    <col min="13828" max="13828" width="17.25" customWidth="1"/>
+    <col min="13829" max="13829" width="20.75" customWidth="1"/>
+    <col min="13830" max="13830" width="33.83203125" customWidth="1"/>
+    <col min="13831" max="13831" width="37.25" customWidth="1"/>
+    <col min="13832" max="13832" width="18.58203125" customWidth="1"/>
+    <col min="14081" max="14081" width="5.83203125" customWidth="1"/>
+    <col min="14082" max="14082" width="62.4140625" customWidth="1"/>
+    <col min="14083" max="14083" width="14.83203125" customWidth="1"/>
+    <col min="14084" max="14084" width="17.25" customWidth="1"/>
+    <col min="14085" max="14085" width="20.75" customWidth="1"/>
+    <col min="14086" max="14086" width="33.83203125" customWidth="1"/>
+    <col min="14087" max="14087" width="37.25" customWidth="1"/>
+    <col min="14088" max="14088" width="18.58203125" customWidth="1"/>
+    <col min="14337" max="14337" width="5.83203125" customWidth="1"/>
+    <col min="14338" max="14338" width="62.4140625" customWidth="1"/>
+    <col min="14339" max="14339" width="14.83203125" customWidth="1"/>
+    <col min="14340" max="14340" width="17.25" customWidth="1"/>
+    <col min="14341" max="14341" width="20.75" customWidth="1"/>
+    <col min="14342" max="14342" width="33.83203125" customWidth="1"/>
+    <col min="14343" max="14343" width="37.25" customWidth="1"/>
+    <col min="14344" max="14344" width="18.58203125" customWidth="1"/>
+    <col min="14593" max="14593" width="5.83203125" customWidth="1"/>
+    <col min="14594" max="14594" width="62.4140625" customWidth="1"/>
+    <col min="14595" max="14595" width="14.83203125" customWidth="1"/>
+    <col min="14596" max="14596" width="17.25" customWidth="1"/>
+    <col min="14597" max="14597" width="20.75" customWidth="1"/>
+    <col min="14598" max="14598" width="33.83203125" customWidth="1"/>
+    <col min="14599" max="14599" width="37.25" customWidth="1"/>
+    <col min="14600" max="14600" width="18.58203125" customWidth="1"/>
+    <col min="14849" max="14849" width="5.83203125" customWidth="1"/>
+    <col min="14850" max="14850" width="62.4140625" customWidth="1"/>
+    <col min="14851" max="14851" width="14.83203125" customWidth="1"/>
+    <col min="14852" max="14852" width="17.25" customWidth="1"/>
+    <col min="14853" max="14853" width="20.75" customWidth="1"/>
+    <col min="14854" max="14854" width="33.83203125" customWidth="1"/>
+    <col min="14855" max="14855" width="37.25" customWidth="1"/>
+    <col min="14856" max="14856" width="18.58203125" customWidth="1"/>
+    <col min="15105" max="15105" width="5.83203125" customWidth="1"/>
+    <col min="15106" max="15106" width="62.4140625" customWidth="1"/>
+    <col min="15107" max="15107" width="14.83203125" customWidth="1"/>
+    <col min="15108" max="15108" width="17.25" customWidth="1"/>
+    <col min="15109" max="15109" width="20.75" customWidth="1"/>
+    <col min="15110" max="15110" width="33.83203125" customWidth="1"/>
+    <col min="15111" max="15111" width="37.25" customWidth="1"/>
+    <col min="15112" max="15112" width="18.58203125" customWidth="1"/>
+    <col min="15361" max="15361" width="5.83203125" customWidth="1"/>
+    <col min="15362" max="15362" width="62.4140625" customWidth="1"/>
+    <col min="15363" max="15363" width="14.83203125" customWidth="1"/>
+    <col min="15364" max="15364" width="17.25" customWidth="1"/>
+    <col min="15365" max="15365" width="20.75" customWidth="1"/>
+    <col min="15366" max="15366" width="33.83203125" customWidth="1"/>
+    <col min="15367" max="15367" width="37.25" customWidth="1"/>
+    <col min="15368" max="15368" width="18.58203125" customWidth="1"/>
+    <col min="15617" max="15617" width="5.83203125" customWidth="1"/>
+    <col min="15618" max="15618" width="62.4140625" customWidth="1"/>
+    <col min="15619" max="15619" width="14.83203125" customWidth="1"/>
+    <col min="15620" max="15620" width="17.25" customWidth="1"/>
+    <col min="15621" max="15621" width="20.75" customWidth="1"/>
+    <col min="15622" max="15622" width="33.83203125" customWidth="1"/>
+    <col min="15623" max="15623" width="37.25" customWidth="1"/>
+    <col min="15624" max="15624" width="18.58203125" customWidth="1"/>
+    <col min="15873" max="15873" width="5.83203125" customWidth="1"/>
+    <col min="15874" max="15874" width="62.4140625" customWidth="1"/>
+    <col min="15875" max="15875" width="14.83203125" customWidth="1"/>
+    <col min="15876" max="15876" width="17.25" customWidth="1"/>
+    <col min="15877" max="15877" width="20.75" customWidth="1"/>
+    <col min="15878" max="15878" width="33.83203125" customWidth="1"/>
+    <col min="15879" max="15879" width="37.25" customWidth="1"/>
+    <col min="15880" max="15880" width="18.58203125" customWidth="1"/>
+    <col min="16129" max="16129" width="5.83203125" customWidth="1"/>
+    <col min="16130" max="16130" width="62.4140625" customWidth="1"/>
+    <col min="16131" max="16131" width="14.83203125" customWidth="1"/>
+    <col min="16132" max="16132" width="17.25" customWidth="1"/>
+    <col min="16133" max="16133" width="20.75" customWidth="1"/>
+    <col min="16134" max="16134" width="33.83203125" customWidth="1"/>
+    <col min="16135" max="16135" width="37.25" customWidth="1"/>
+    <col min="16136" max="16136" width="18.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1">
@@ -17415,7 +17415,7 @@
       <c r="G2" s="547"/>
       <c r="H2" s="547"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" thickTop="1">
+    <row r="3" spans="1:8" ht="16" thickTop="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -17425,7 +17425,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="4" spans="1:8" ht="15.5">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="548"/>
@@ -17437,7 +17437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="549" t="s">
         <v>22</v>
       </c>
@@ -17449,7 +17449,7 @@
       <c r="G5" s="549"/>
       <c r="H5" s="549"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A6" s="513" t="s">
         <v>2</v>
       </c>
@@ -17473,7 +17473,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A7" s="513"/>
       <c r="B7" s="512"/>
       <c r="C7" s="513"/>
@@ -17487,7 +17487,7 @@
       <c r="G7" s="513"/>
       <c r="H7" s="513"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
+    <row r="8" spans="1:8" ht="15.5">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -17501,7 +17501,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="9" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -17551,7 +17551,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="11" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A11" s="10">
         <v>3</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="12" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A12" s="10">
         <v>4</v>
       </c>
@@ -17599,7 +17599,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="13" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A13" s="10">
         <v>5</v>
       </c>
@@ -17671,7 +17671,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="16" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A16" s="10">
         <v>8</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15.75">
+    <row r="18" spans="1:8" ht="15.5">
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
@@ -17735,7 +17735,7 @@
       <c r="G18" s="11"/>
       <c r="H18" s="282"/>
     </row>
-    <row r="19" spans="1:8" s="8" customFormat="1" ht="78.75">
+    <row r="19" spans="1:8" s="8" customFormat="1" ht="62">
       <c r="A19" s="10">
         <v>1</v>
       </c>
@@ -17761,7 +17761,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="20" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A20" s="10">
         <v>2</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="8" customFormat="1" ht="126">
+    <row r="22" spans="1:8" s="8" customFormat="1" ht="93">
       <c r="A22" s="10">
         <v>4</v>
       </c>
@@ -17837,7 +17837,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="8" customFormat="1" ht="94.5">
+    <row r="23" spans="1:8" s="8" customFormat="1" ht="62">
       <c r="A23" s="10">
         <v>5</v>
       </c>
@@ -17915,7 +17915,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="31.5">
+    <row r="26" spans="1:8" ht="31">
       <c r="A26" s="10">
         <v>8</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="31.5">
+    <row r="27" spans="1:8" ht="31">
       <c r="A27" s="10">
         <v>9</v>
       </c>
@@ -18101,7 +18101,7 @@
       <c r="G35" s="470"/>
       <c r="H35" s="475"/>
     </row>
-    <row r="36" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="36" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A36" s="35" t="s">
         <v>10</v>
       </c>
@@ -18115,7 +18115,7 @@
       <c r="G36" s="442"/>
       <c r="H36" s="37"/>
     </row>
-    <row r="37" spans="1:8" ht="15.75">
+    <row r="37" spans="1:8" ht="15.5">
       <c r="A37" s="35" t="s">
         <v>13</v>
       </c>
@@ -18129,7 +18129,7 @@
       <c r="G37" s="442"/>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" ht="31.5">
+    <row r="38" spans="1:8" ht="31">
       <c r="A38" s="44">
         <v>1</v>
       </c>
@@ -18151,7 +18151,7 @@
       <c r="G38" s="457"/>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="39" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A39" s="10">
         <v>2</v>
       </c>
@@ -18173,7 +18173,7 @@
       <c r="G39" s="543"/>
       <c r="H39" s="14"/>
     </row>
-    <row r="40" spans="1:8" ht="78.75">
+    <row r="40" spans="1:8" ht="77.5">
       <c r="A40" s="44">
         <v>3</v>
       </c>
@@ -18217,7 +18217,7 @@
       <c r="G41" s="446"/>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="42" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A42" s="44">
         <v>5</v>
       </c>
@@ -18257,7 +18257,7 @@
       <c r="G43" s="536"/>
       <c r="H43" s="14"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75">
+    <row r="44" spans="1:8" ht="15.5">
       <c r="A44" s="132"/>
       <c r="B44" s="133"/>
       <c r="C44" s="134"/>
@@ -18279,7 +18279,7 @@
       <c r="G45" s="549"/>
       <c r="H45" s="549"/>
     </row>
-    <row r="46" spans="1:8" ht="15.75">
+    <row r="46" spans="1:8" ht="15">
       <c r="A46" s="447" t="s">
         <v>395</v>
       </c>
@@ -18315,7 +18315,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="48" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A48" s="513"/>
       <c r="B48" s="512"/>
       <c r="C48" s="513"/>
@@ -18329,7 +18329,7 @@
       <c r="G48" s="513"/>
       <c r="H48" s="513"/>
     </row>
-    <row r="49" spans="1:8" ht="15.75">
+    <row r="49" spans="1:8" ht="15.5">
       <c r="A49" s="35" t="s">
         <v>10</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="47.25">
+    <row r="50" spans="1:8" ht="31">
       <c r="A50" s="41">
         <v>1</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="15.75">
+    <row r="51" spans="1:8" ht="15.5">
       <c r="A51" s="41">
         <v>2</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="15.75">
+    <row r="53" spans="1:8" ht="15.5">
       <c r="A53" s="41">
         <v>4</v>
       </c>
@@ -18439,7 +18439,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="31.5">
+    <row r="54" spans="1:8" ht="31">
       <c r="A54" s="41">
         <v>5</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75">
+    <row r="56" spans="1:8" ht="15.5">
       <c r="A56" s="41">
         <v>7</v>
       </c>
@@ -18509,7 +18509,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="31.5">
+    <row r="57" spans="1:8" ht="31">
       <c r="A57" s="41">
         <v>8</v>
       </c>
@@ -18533,7 +18533,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15.75">
+    <row r="58" spans="1:8" ht="15.5">
       <c r="A58" s="41">
         <v>9</v>
       </c>
@@ -18557,7 +18557,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="31.5">
+    <row r="59" spans="1:8" ht="31">
       <c r="A59" s="41">
         <v>10</v>
       </c>
@@ -18605,7 +18605,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="31.5">
+    <row r="61" spans="1:8" ht="15.5">
       <c r="A61" s="41">
         <v>12</v>
       </c>
@@ -18629,7 +18629,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="31.5">
+    <row r="62" spans="1:8" ht="31">
       <c r="A62" s="41">
         <v>13</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="31.5">
+    <row r="63" spans="1:8" ht="31">
       <c r="A63" s="41">
         <v>14</v>
       </c>
@@ -18677,7 +18677,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="31.5">
+    <row r="64" spans="1:8" ht="31">
       <c r="A64" s="41">
         <v>15</v>
       </c>
@@ -18701,7 +18701,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="47.25">
+    <row r="65" spans="1:8" ht="31">
       <c r="A65" s="41">
         <v>16</v>
       </c>
@@ -18725,7 +18725,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="78.75">
+    <row r="66" spans="1:8" ht="77.5">
       <c r="A66" s="41">
         <v>17</v>
       </c>
@@ -18751,7 +18751,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="15.75">
+    <row r="67" spans="1:8" ht="15.5">
       <c r="A67" s="41">
         <v>18</v>
       </c>
@@ -18871,7 +18871,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="72" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A72" s="41">
         <v>23</v>
       </c>
@@ -18895,7 +18895,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="73" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A73" s="41">
         <v>24</v>
       </c>
@@ -18919,7 +18919,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="62" customFormat="1" ht="31.5">
+    <row r="74" spans="1:8" s="62" customFormat="1" ht="31">
       <c r="A74" s="41">
         <v>25</v>
       </c>
@@ -18943,7 +18943,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:8" s="62" customFormat="1" ht="15.75">
+    <row r="75" spans="1:8" s="62" customFormat="1" ht="15.5">
       <c r="A75" s="104">
         <v>26</v>
       </c>
@@ -18965,7 +18965,7 @@
       <c r="G75" s="281"/>
       <c r="H75" s="147"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75">
+    <row r="76" spans="1:8" ht="15.5">
       <c r="A76" s="58" t="s">
         <v>13</v>
       </c>
@@ -19029,7 +19029,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="31.5">
+    <row r="79" spans="1:8" ht="31">
       <c r="A79" s="44">
         <v>3</v>
       </c>
@@ -19075,7 +19075,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="81" spans="1:8" s="8" customFormat="1" ht="47.25">
+    <row r="81" spans="1:8" s="8" customFormat="1" ht="46.5">
       <c r="A81" s="147">
         <v>5</v>
       </c>
@@ -19143,7 +19143,7 @@
       <c r="G84" s="509"/>
       <c r="H84" s="437"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75">
+    <row r="85" spans="1:8" ht="15.5">
       <c r="A85" s="107"/>
       <c r="B85" s="130"/>
       <c r="C85" s="126"/>
@@ -19153,7 +19153,7 @@
       <c r="G85" s="131"/>
       <c r="H85" s="128"/>
     </row>
-    <row r="86" spans="1:8" ht="15.75">
+    <row r="86" spans="1:8" ht="15.5">
       <c r="A86" s="113" t="s">
         <v>396</v>
       </c>
@@ -19201,7 +19201,7 @@
       <c r="G88" s="449"/>
       <c r="H88" s="433"/>
     </row>
-    <row r="89" spans="1:8" ht="15.75">
+    <row r="89" spans="1:8" ht="15.5">
       <c r="A89" s="68" t="s">
         <v>10</v>
       </c>
@@ -19303,7 +19303,7 @@
       <c r="G93" s="442"/>
       <c r="H93" s="37"/>
     </row>
-    <row r="94" spans="1:8" ht="15.75">
+    <row r="94" spans="1:8" ht="15.5">
       <c r="A94" s="35" t="s">
         <v>13</v>
       </c>
@@ -19339,7 +19339,7 @@
       <c r="G95" s="457"/>
       <c r="H95" s="37"/>
     </row>
-    <row r="96" spans="1:8" s="151" customFormat="1" ht="31.5">
+    <row r="96" spans="1:8" s="151" customFormat="1" ht="31">
       <c r="A96" s="147">
         <v>2</v>
       </c>
@@ -19357,7 +19357,7 @@
       <c r="G96" s="519"/>
       <c r="H96" s="150"/>
     </row>
-    <row r="97" spans="1:8" s="52" customFormat="1" ht="47.25">
+    <row r="97" spans="1:8" s="52" customFormat="1" ht="46.5">
       <c r="A97" s="44">
         <v>3</v>
       </c>
@@ -19375,7 +19375,7 @@
       <c r="G97" s="446"/>
       <c r="H97" s="50"/>
     </row>
-    <row r="98" spans="1:8" ht="15.75">
+    <row r="98" spans="1:8" ht="15.5">
       <c r="A98" s="44"/>
       <c r="B98" s="53"/>
       <c r="C98" s="44"/>
@@ -19397,7 +19397,7 @@
       <c r="G99" s="521"/>
       <c r="H99" s="522"/>
     </row>
-    <row r="100" spans="1:8" ht="15.75">
+    <row r="100" spans="1:8" ht="15">
       <c r="A100" s="447" t="s">
         <v>395</v>
       </c>
@@ -19447,7 +19447,7 @@
       <c r="G102" s="513"/>
       <c r="H102" s="513"/>
     </row>
-    <row r="103" spans="1:8" ht="15.75">
+    <row r="103" spans="1:8" ht="15.5">
       <c r="A103" s="285" t="s">
         <v>10</v>
       </c>
@@ -19463,7 +19463,7 @@
       <c r="G103" s="297"/>
       <c r="H103" s="297"/>
     </row>
-    <row r="104" spans="1:8" ht="31.5">
+    <row r="104" spans="1:8" ht="31">
       <c r="A104" s="44">
         <v>1</v>
       </c>
@@ -19559,7 +19559,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="40" customFormat="1" ht="63">
+    <row r="108" spans="1:8" s="40" customFormat="1" ht="62">
       <c r="A108" s="44" t="s">
         <v>346</v>
       </c>
@@ -19593,7 +19593,7 @@
       <c r="G109" s="46"/>
       <c r="H109" s="16"/>
     </row>
-    <row r="110" spans="1:8" s="40" customFormat="1" ht="47.25">
+    <row r="110" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A110" s="44">
         <v>5</v>
       </c>
@@ -19641,7 +19641,7 @@
       <c r="G112" s="155"/>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" spans="1:8" ht="63">
+    <row r="113" spans="1:8" ht="46.5">
       <c r="A113" s="44">
         <v>6</v>
       </c>
@@ -19773,7 +19773,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="119" spans="1:8" s="162" customFormat="1" ht="63">
+    <row r="119" spans="1:8" s="162" customFormat="1" ht="46.5">
       <c r="A119" s="48">
         <v>2</v>
       </c>
@@ -19825,7 +19825,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="121" spans="1:8" s="8" customFormat="1" ht="78.75">
+    <row r="121" spans="1:8" s="8" customFormat="1" ht="77.5">
       <c r="A121" s="48">
         <v>5</v>
       </c>
@@ -19877,7 +19877,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="123" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A123" s="286" t="s">
         <v>174</v>
       </c>
@@ -19923,7 +19923,7 @@
       <c r="G125" s="534"/>
       <c r="H125" s="534"/>
     </row>
-    <row r="126" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="126" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A126" s="110" t="s">
         <v>339</v>
       </c>
@@ -19971,7 +19971,7 @@
       <c r="G128" s="470"/>
       <c r="H128" s="475"/>
     </row>
-    <row r="129" spans="1:12" s="40" customFormat="1" ht="15.75">
+    <row r="129" spans="1:12" s="40" customFormat="1" ht="15.5">
       <c r="A129" s="301" t="s">
         <v>10</v>
       </c>
@@ -19985,7 +19985,7 @@
       <c r="G129" s="530"/>
       <c r="H129" s="297"/>
     </row>
-    <row r="130" spans="1:12" s="160" customFormat="1" ht="31.5">
+    <row r="130" spans="1:12" s="160" customFormat="1" ht="31">
       <c r="A130" s="177">
         <v>1</v>
       </c>
@@ -20008,7 +20008,7 @@
       <c r="H130" s="175"/>
       <c r="L130" s="176"/>
     </row>
-    <row r="131" spans="1:12" s="160" customFormat="1" ht="31.5">
+    <row r="131" spans="1:12" s="160" customFormat="1" ht="31">
       <c r="A131" s="177">
         <v>2</v>
       </c>
@@ -20030,7 +20030,7 @@
       <c r="G131" s="524"/>
       <c r="H131" s="175"/>
     </row>
-    <row r="132" spans="1:12" s="160" customFormat="1" ht="31.5">
+    <row r="132" spans="1:12" s="160" customFormat="1" ht="31">
       <c r="A132" s="177">
         <v>3</v>
       </c>
@@ -20074,7 +20074,7 @@
       <c r="G133" s="524"/>
       <c r="H133" s="166"/>
     </row>
-    <row r="134" spans="1:12" s="160" customFormat="1" ht="15.75">
+    <row r="134" spans="1:12" s="160" customFormat="1" ht="15.5">
       <c r="A134" s="177">
         <v>5</v>
       </c>
@@ -20118,7 +20118,7 @@
       <c r="G135" s="443"/>
       <c r="H135" s="172"/>
     </row>
-    <row r="136" spans="1:12" ht="15.75">
+    <row r="136" spans="1:12" ht="15.5">
       <c r="A136" s="301" t="s">
         <v>13</v>
       </c>
@@ -20132,7 +20132,7 @@
       <c r="G136" s="530"/>
       <c r="H136" s="304"/>
     </row>
-    <row r="137" spans="1:12" s="70" customFormat="1" ht="78.75">
+    <row r="137" spans="1:12" s="70" customFormat="1" ht="77.5">
       <c r="A137" s="44">
         <v>1</v>
       </c>
@@ -20154,7 +20154,7 @@
       <c r="G137" s="457"/>
       <c r="H137" s="182"/>
     </row>
-    <row r="138" spans="1:12" s="160" customFormat="1" ht="63">
+    <row r="138" spans="1:12" s="160" customFormat="1" ht="46.5">
       <c r="A138" s="177">
         <v>2</v>
       </c>
@@ -20176,7 +20176,7 @@
       <c r="G138" s="466"/>
       <c r="H138" s="161"/>
     </row>
-    <row r="139" spans="1:12" s="160" customFormat="1" ht="63">
+    <row r="139" spans="1:12" s="160" customFormat="1" ht="46.5">
       <c r="A139" s="177">
         <v>3</v>
       </c>
@@ -20194,7 +20194,7 @@
       <c r="G139" s="503"/>
       <c r="H139" s="174"/>
     </row>
-    <row r="140" spans="1:12" ht="15.75">
+    <row r="140" spans="1:12" ht="15.5">
       <c r="A140" s="283"/>
       <c r="B140" s="284"/>
       <c r="C140" s="179"/>
@@ -20216,7 +20216,7 @@
       <c r="G141" s="526"/>
       <c r="H141" s="527"/>
     </row>
-    <row r="142" spans="1:12" ht="15.75">
+    <row r="142" spans="1:12" ht="15">
       <c r="A142" s="447" t="s">
         <v>178</v>
       </c>
@@ -20228,7 +20228,7 @@
       <c r="G142" s="447"/>
       <c r="H142" s="447"/>
     </row>
-    <row r="143" spans="1:12" s="34" customFormat="1" ht="15.75">
+    <row r="143" spans="1:12" s="34" customFormat="1" ht="15.5">
       <c r="A143" s="431" t="s">
         <v>2</v>
       </c>
@@ -20252,7 +20252,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="144" spans="1:12" s="34" customFormat="1" ht="15.75">
+    <row r="144" spans="1:12" s="34" customFormat="1" ht="15.5">
       <c r="A144" s="432"/>
       <c r="B144" s="532"/>
       <c r="C144" s="432"/>
@@ -20266,7 +20266,7 @@
       <c r="G144" s="432"/>
       <c r="H144" s="432"/>
     </row>
-    <row r="145" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="145" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A145" s="285" t="s">
         <v>10</v>
       </c>
@@ -20306,7 +20306,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="147" spans="1:8" s="40" customFormat="1" ht="47.25">
+    <row r="147" spans="1:8" s="40" customFormat="1" ht="46.5">
       <c r="A147" s="41">
         <v>2</v>
       </c>
@@ -20354,7 +20354,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="149" spans="1:8" s="40" customFormat="1" ht="47.25">
+    <row r="149" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A149" s="48" t="s">
         <v>75</v>
       </c>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="H151" s="39"/>
     </row>
-    <row r="152" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="152" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A152" s="44" t="s">
         <v>85</v>
       </c>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="H152" s="39"/>
     </row>
-    <row r="153" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="153" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A153" s="48" t="s">
         <v>88</v>
       </c>
@@ -20464,7 +20464,7 @@
       </c>
       <c r="H153" s="39"/>
     </row>
-    <row r="154" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="154" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A154" s="44" t="s">
         <v>92</v>
       </c>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="H154" s="39"/>
     </row>
-    <row r="155" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="155" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A155" s="48" t="s">
         <v>94</v>
       </c>
@@ -20508,7 +20508,7 @@
       </c>
       <c r="H155" s="39"/>
     </row>
-    <row r="156" spans="1:8" s="40" customFormat="1" ht="47.25">
+    <row r="156" spans="1:8" s="40" customFormat="1" ht="46.5">
       <c r="A156" s="44" t="s">
         <v>96</v>
       </c>
@@ -20530,7 +20530,7 @@
       </c>
       <c r="H156" s="39"/>
     </row>
-    <row r="157" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="157" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A157" s="44" t="s">
         <v>100</v>
       </c>
@@ -20552,7 +20552,7 @@
       </c>
       <c r="H157" s="39"/>
     </row>
-    <row r="158" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="158" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A158" s="57" t="s">
         <v>316</v>
       </c>
@@ -20574,7 +20574,7 @@
       </c>
       <c r="H158" s="51"/>
     </row>
-    <row r="159" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="159" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A159" s="57" t="s">
         <v>319</v>
       </c>
@@ -20596,7 +20596,7 @@
       </c>
       <c r="H159" s="51"/>
     </row>
-    <row r="160" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="160" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A160" s="57" t="s">
         <v>322</v>
       </c>
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H160" s="51"/>
     </row>
-    <row r="161" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="161" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A161" s="48" t="s">
         <v>325</v>
       </c>
@@ -20640,7 +20640,7 @@
       </c>
       <c r="H161" s="51"/>
     </row>
-    <row r="162" spans="1:8" s="52" customFormat="1" ht="63">
+    <row r="162" spans="1:8" s="52" customFormat="1" ht="46.5">
       <c r="A162" s="44" t="s">
         <v>328</v>
       </c>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="H162" s="51"/>
     </row>
-    <row r="163" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="163" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A163" s="44" t="s">
         <v>331</v>
       </c>
@@ -20746,7 +20746,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="167" spans="1:8" s="52" customFormat="1" ht="63">
+    <row r="167" spans="1:8" s="52" customFormat="1" ht="62">
       <c r="A167" s="44">
         <v>2</v>
       </c>
@@ -20820,7 +20820,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="170" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="170" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A170" s="286" t="s">
         <v>174</v>
       </c>
@@ -20866,7 +20866,7 @@
       <c r="G172" s="509"/>
       <c r="H172" s="437"/>
     </row>
-    <row r="173" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="173" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A173" s="110" t="s">
         <v>179</v>
       </c>
@@ -20914,7 +20914,7 @@
       <c r="G175" s="470"/>
       <c r="H175" s="475"/>
     </row>
-    <row r="176" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="176" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A176" s="35" t="s">
         <v>10</v>
       </c>
@@ -20930,7 +20930,7 @@
       <c r="G176" s="442"/>
       <c r="H176" s="37"/>
     </row>
-    <row r="177" spans="1:10" s="40" customFormat="1" ht="15.75">
+    <row r="177" spans="1:10" s="40" customFormat="1" ht="15.5">
       <c r="A177" s="48">
         <v>1</v>
       </c>
@@ -20950,7 +20950,7 @@
       <c r="G177" s="460"/>
       <c r="H177" s="37"/>
     </row>
-    <row r="178" spans="1:10" s="40" customFormat="1" ht="15.75">
+    <row r="178" spans="1:10" s="40" customFormat="1" ht="15.5">
       <c r="A178" s="48">
         <v>2</v>
       </c>
@@ -20970,7 +20970,7 @@
       <c r="G178" s="460"/>
       <c r="H178" s="37"/>
     </row>
-    <row r="179" spans="1:10" s="40" customFormat="1" ht="15.75">
+    <row r="179" spans="1:10" s="40" customFormat="1" ht="15.5">
       <c r="A179" s="48">
         <v>3</v>
       </c>
@@ -21096,7 +21096,7 @@
       <c r="G185" s="457"/>
       <c r="H185" s="51"/>
     </row>
-    <row r="186" spans="1:10" s="52" customFormat="1" ht="31.5">
+    <row r="186" spans="1:10" s="52" customFormat="1" ht="31">
       <c r="A186" s="44">
         <v>3</v>
       </c>
@@ -21116,7 +21116,7 @@
       <c r="G186" s="457"/>
       <c r="H186" s="51"/>
     </row>
-    <row r="187" spans="1:10" s="40" customFormat="1" ht="15.75">
+    <row r="187" spans="1:10" s="40" customFormat="1" ht="15.5">
       <c r="A187" s="147"/>
       <c r="B187" s="185"/>
       <c r="C187" s="44"/>
@@ -21402,7 +21402,7 @@
     <mergeCell ref="C124:H124"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="7" manualBreakCount="7">
     <brk id="44" max="16383" man="1"/>
     <brk id="93" max="16383" man="1"/>
@@ -21422,522 +21422,522 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J159"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.85546875" customWidth="1"/>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" style="90" customWidth="1"/>
-    <col min="6" max="6" width="52.5703125" customWidth="1"/>
-    <col min="7" max="7" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.58203125" customWidth="1"/>
+    <col min="3" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="5" width="11.25" style="90" customWidth="1"/>
+    <col min="6" max="6" width="52.58203125" customWidth="1"/>
+    <col min="7" max="7" width="43.75" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="257" max="257" width="5.85546875" customWidth="1"/>
-    <col min="258" max="258" width="62.42578125" customWidth="1"/>
-    <col min="259" max="259" width="14.85546875" customWidth="1"/>
-    <col min="260" max="260" width="17.28515625" customWidth="1"/>
-    <col min="261" max="261" width="20.7109375" customWidth="1"/>
-    <col min="262" max="262" width="33.85546875" customWidth="1"/>
-    <col min="263" max="263" width="37.28515625" customWidth="1"/>
-    <col min="264" max="264" width="18.5703125" customWidth="1"/>
-    <col min="513" max="513" width="5.85546875" customWidth="1"/>
-    <col min="514" max="514" width="62.42578125" customWidth="1"/>
-    <col min="515" max="515" width="14.85546875" customWidth="1"/>
-    <col min="516" max="516" width="17.28515625" customWidth="1"/>
-    <col min="517" max="517" width="20.7109375" customWidth="1"/>
-    <col min="518" max="518" width="33.85546875" customWidth="1"/>
-    <col min="519" max="519" width="37.28515625" customWidth="1"/>
-    <col min="520" max="520" width="18.5703125" customWidth="1"/>
-    <col min="769" max="769" width="5.85546875" customWidth="1"/>
-    <col min="770" max="770" width="62.42578125" customWidth="1"/>
-    <col min="771" max="771" width="14.85546875" customWidth="1"/>
-    <col min="772" max="772" width="17.28515625" customWidth="1"/>
-    <col min="773" max="773" width="20.7109375" customWidth="1"/>
-    <col min="774" max="774" width="33.85546875" customWidth="1"/>
-    <col min="775" max="775" width="37.28515625" customWidth="1"/>
-    <col min="776" max="776" width="18.5703125" customWidth="1"/>
-    <col min="1025" max="1025" width="5.85546875" customWidth="1"/>
-    <col min="1026" max="1026" width="62.42578125" customWidth="1"/>
-    <col min="1027" max="1027" width="14.85546875" customWidth="1"/>
-    <col min="1028" max="1028" width="17.28515625" customWidth="1"/>
-    <col min="1029" max="1029" width="20.7109375" customWidth="1"/>
-    <col min="1030" max="1030" width="33.85546875" customWidth="1"/>
-    <col min="1031" max="1031" width="37.28515625" customWidth="1"/>
-    <col min="1032" max="1032" width="18.5703125" customWidth="1"/>
-    <col min="1281" max="1281" width="5.85546875" customWidth="1"/>
-    <col min="1282" max="1282" width="62.42578125" customWidth="1"/>
-    <col min="1283" max="1283" width="14.85546875" customWidth="1"/>
-    <col min="1284" max="1284" width="17.28515625" customWidth="1"/>
-    <col min="1285" max="1285" width="20.7109375" customWidth="1"/>
-    <col min="1286" max="1286" width="33.85546875" customWidth="1"/>
-    <col min="1287" max="1287" width="37.28515625" customWidth="1"/>
-    <col min="1288" max="1288" width="18.5703125" customWidth="1"/>
-    <col min="1537" max="1537" width="5.85546875" customWidth="1"/>
-    <col min="1538" max="1538" width="62.42578125" customWidth="1"/>
-    <col min="1539" max="1539" width="14.85546875" customWidth="1"/>
-    <col min="1540" max="1540" width="17.28515625" customWidth="1"/>
-    <col min="1541" max="1541" width="20.7109375" customWidth="1"/>
-    <col min="1542" max="1542" width="33.85546875" customWidth="1"/>
-    <col min="1543" max="1543" width="37.28515625" customWidth="1"/>
-    <col min="1544" max="1544" width="18.5703125" customWidth="1"/>
-    <col min="1793" max="1793" width="5.85546875" customWidth="1"/>
-    <col min="1794" max="1794" width="62.42578125" customWidth="1"/>
-    <col min="1795" max="1795" width="14.85546875" customWidth="1"/>
-    <col min="1796" max="1796" width="17.28515625" customWidth="1"/>
-    <col min="1797" max="1797" width="20.7109375" customWidth="1"/>
-    <col min="1798" max="1798" width="33.85546875" customWidth="1"/>
-    <col min="1799" max="1799" width="37.28515625" customWidth="1"/>
-    <col min="1800" max="1800" width="18.5703125" customWidth="1"/>
-    <col min="2049" max="2049" width="5.85546875" customWidth="1"/>
-    <col min="2050" max="2050" width="62.42578125" customWidth="1"/>
-    <col min="2051" max="2051" width="14.85546875" customWidth="1"/>
-    <col min="2052" max="2052" width="17.28515625" customWidth="1"/>
-    <col min="2053" max="2053" width="20.7109375" customWidth="1"/>
-    <col min="2054" max="2054" width="33.85546875" customWidth="1"/>
-    <col min="2055" max="2055" width="37.28515625" customWidth="1"/>
-    <col min="2056" max="2056" width="18.5703125" customWidth="1"/>
-    <col min="2305" max="2305" width="5.85546875" customWidth="1"/>
-    <col min="2306" max="2306" width="62.42578125" customWidth="1"/>
-    <col min="2307" max="2307" width="14.85546875" customWidth="1"/>
-    <col min="2308" max="2308" width="17.28515625" customWidth="1"/>
-    <col min="2309" max="2309" width="20.7109375" customWidth="1"/>
-    <col min="2310" max="2310" width="33.85546875" customWidth="1"/>
-    <col min="2311" max="2311" width="37.28515625" customWidth="1"/>
-    <col min="2312" max="2312" width="18.5703125" customWidth="1"/>
-    <col min="2561" max="2561" width="5.85546875" customWidth="1"/>
-    <col min="2562" max="2562" width="62.42578125" customWidth="1"/>
-    <col min="2563" max="2563" width="14.85546875" customWidth="1"/>
-    <col min="2564" max="2564" width="17.28515625" customWidth="1"/>
-    <col min="2565" max="2565" width="20.7109375" customWidth="1"/>
-    <col min="2566" max="2566" width="33.85546875" customWidth="1"/>
-    <col min="2567" max="2567" width="37.28515625" customWidth="1"/>
-    <col min="2568" max="2568" width="18.5703125" customWidth="1"/>
-    <col min="2817" max="2817" width="5.85546875" customWidth="1"/>
-    <col min="2818" max="2818" width="62.42578125" customWidth="1"/>
-    <col min="2819" max="2819" width="14.85546875" customWidth="1"/>
-    <col min="2820" max="2820" width="17.28515625" customWidth="1"/>
-    <col min="2821" max="2821" width="20.7109375" customWidth="1"/>
-    <col min="2822" max="2822" width="33.85546875" customWidth="1"/>
-    <col min="2823" max="2823" width="37.28515625" customWidth="1"/>
-    <col min="2824" max="2824" width="18.5703125" customWidth="1"/>
-    <col min="3073" max="3073" width="5.85546875" customWidth="1"/>
-    <col min="3074" max="3074" width="62.42578125" customWidth="1"/>
-    <col min="3075" max="3075" width="14.85546875" customWidth="1"/>
-    <col min="3076" max="3076" width="17.28515625" customWidth="1"/>
-    <col min="3077" max="3077" width="20.7109375" customWidth="1"/>
-    <col min="3078" max="3078" width="33.85546875" customWidth="1"/>
-    <col min="3079" max="3079" width="37.28515625" customWidth="1"/>
-    <col min="3080" max="3080" width="18.5703125" customWidth="1"/>
-    <col min="3329" max="3329" width="5.85546875" customWidth="1"/>
-    <col min="3330" max="3330" width="62.42578125" customWidth="1"/>
-    <col min="3331" max="3331" width="14.85546875" customWidth="1"/>
-    <col min="3332" max="3332" width="17.28515625" customWidth="1"/>
-    <col min="3333" max="3333" width="20.7109375" customWidth="1"/>
-    <col min="3334" max="3334" width="33.85546875" customWidth="1"/>
-    <col min="3335" max="3335" width="37.28515625" customWidth="1"/>
-    <col min="3336" max="3336" width="18.5703125" customWidth="1"/>
-    <col min="3585" max="3585" width="5.85546875" customWidth="1"/>
-    <col min="3586" max="3586" width="62.42578125" customWidth="1"/>
-    <col min="3587" max="3587" width="14.85546875" customWidth="1"/>
-    <col min="3588" max="3588" width="17.28515625" customWidth="1"/>
-    <col min="3589" max="3589" width="20.7109375" customWidth="1"/>
-    <col min="3590" max="3590" width="33.85546875" customWidth="1"/>
-    <col min="3591" max="3591" width="37.28515625" customWidth="1"/>
-    <col min="3592" max="3592" width="18.5703125" customWidth="1"/>
-    <col min="3841" max="3841" width="5.85546875" customWidth="1"/>
-    <col min="3842" max="3842" width="62.42578125" customWidth="1"/>
-    <col min="3843" max="3843" width="14.85546875" customWidth="1"/>
-    <col min="3844" max="3844" width="17.28515625" customWidth="1"/>
-    <col min="3845" max="3845" width="20.7109375" customWidth="1"/>
-    <col min="3846" max="3846" width="33.85546875" customWidth="1"/>
-    <col min="3847" max="3847" width="37.28515625" customWidth="1"/>
-    <col min="3848" max="3848" width="18.5703125" customWidth="1"/>
-    <col min="4097" max="4097" width="5.85546875" customWidth="1"/>
-    <col min="4098" max="4098" width="62.42578125" customWidth="1"/>
-    <col min="4099" max="4099" width="14.85546875" customWidth="1"/>
-    <col min="4100" max="4100" width="17.28515625" customWidth="1"/>
-    <col min="4101" max="4101" width="20.7109375" customWidth="1"/>
-    <col min="4102" max="4102" width="33.85546875" customWidth="1"/>
-    <col min="4103" max="4103" width="37.28515625" customWidth="1"/>
-    <col min="4104" max="4104" width="18.5703125" customWidth="1"/>
-    <col min="4353" max="4353" width="5.85546875" customWidth="1"/>
-    <col min="4354" max="4354" width="62.42578125" customWidth="1"/>
-    <col min="4355" max="4355" width="14.85546875" customWidth="1"/>
-    <col min="4356" max="4356" width="17.28515625" customWidth="1"/>
-    <col min="4357" max="4357" width="20.7109375" customWidth="1"/>
-    <col min="4358" max="4358" width="33.85546875" customWidth="1"/>
-    <col min="4359" max="4359" width="37.28515625" customWidth="1"/>
-    <col min="4360" max="4360" width="18.5703125" customWidth="1"/>
-    <col min="4609" max="4609" width="5.85546875" customWidth="1"/>
-    <col min="4610" max="4610" width="62.42578125" customWidth="1"/>
-    <col min="4611" max="4611" width="14.85546875" customWidth="1"/>
-    <col min="4612" max="4612" width="17.28515625" customWidth="1"/>
-    <col min="4613" max="4613" width="20.7109375" customWidth="1"/>
-    <col min="4614" max="4614" width="33.85546875" customWidth="1"/>
-    <col min="4615" max="4615" width="37.28515625" customWidth="1"/>
-    <col min="4616" max="4616" width="18.5703125" customWidth="1"/>
-    <col min="4865" max="4865" width="5.85546875" customWidth="1"/>
-    <col min="4866" max="4866" width="62.42578125" customWidth="1"/>
-    <col min="4867" max="4867" width="14.85546875" customWidth="1"/>
-    <col min="4868" max="4868" width="17.28515625" customWidth="1"/>
-    <col min="4869" max="4869" width="20.7109375" customWidth="1"/>
-    <col min="4870" max="4870" width="33.85546875" customWidth="1"/>
-    <col min="4871" max="4871" width="37.28515625" customWidth="1"/>
-    <col min="4872" max="4872" width="18.5703125" customWidth="1"/>
-    <col min="5121" max="5121" width="5.85546875" customWidth="1"/>
-    <col min="5122" max="5122" width="62.42578125" customWidth="1"/>
-    <col min="5123" max="5123" width="14.85546875" customWidth="1"/>
-    <col min="5124" max="5124" width="17.28515625" customWidth="1"/>
-    <col min="5125" max="5125" width="20.7109375" customWidth="1"/>
-    <col min="5126" max="5126" width="33.85546875" customWidth="1"/>
-    <col min="5127" max="5127" width="37.28515625" customWidth="1"/>
-    <col min="5128" max="5128" width="18.5703125" customWidth="1"/>
-    <col min="5377" max="5377" width="5.85546875" customWidth="1"/>
-    <col min="5378" max="5378" width="62.42578125" customWidth="1"/>
-    <col min="5379" max="5379" width="14.85546875" customWidth="1"/>
-    <col min="5380" max="5380" width="17.28515625" customWidth="1"/>
-    <col min="5381" max="5381" width="20.7109375" customWidth="1"/>
-    <col min="5382" max="5382" width="33.85546875" customWidth="1"/>
-    <col min="5383" max="5383" width="37.28515625" customWidth="1"/>
-    <col min="5384" max="5384" width="18.5703125" customWidth="1"/>
-    <col min="5633" max="5633" width="5.85546875" customWidth="1"/>
-    <col min="5634" max="5634" width="62.42578125" customWidth="1"/>
-    <col min="5635" max="5635" width="14.85546875" customWidth="1"/>
-    <col min="5636" max="5636" width="17.28515625" customWidth="1"/>
-    <col min="5637" max="5637" width="20.7109375" customWidth="1"/>
-    <col min="5638" max="5638" width="33.85546875" customWidth="1"/>
-    <col min="5639" max="5639" width="37.28515625" customWidth="1"/>
-    <col min="5640" max="5640" width="18.5703125" customWidth="1"/>
-    <col min="5889" max="5889" width="5.85546875" customWidth="1"/>
-    <col min="5890" max="5890" width="62.42578125" customWidth="1"/>
-    <col min="5891" max="5891" width="14.85546875" customWidth="1"/>
-    <col min="5892" max="5892" width="17.28515625" customWidth="1"/>
-    <col min="5893" max="5893" width="20.7109375" customWidth="1"/>
-    <col min="5894" max="5894" width="33.85546875" customWidth="1"/>
-    <col min="5895" max="5895" width="37.28515625" customWidth="1"/>
-    <col min="5896" max="5896" width="18.5703125" customWidth="1"/>
-    <col min="6145" max="6145" width="5.85546875" customWidth="1"/>
-    <col min="6146" max="6146" width="62.42578125" customWidth="1"/>
-    <col min="6147" max="6147" width="14.85546875" customWidth="1"/>
-    <col min="6148" max="6148" width="17.28515625" customWidth="1"/>
-    <col min="6149" max="6149" width="20.7109375" customWidth="1"/>
-    <col min="6150" max="6150" width="33.85546875" customWidth="1"/>
-    <col min="6151" max="6151" width="37.28515625" customWidth="1"/>
-    <col min="6152" max="6152" width="18.5703125" customWidth="1"/>
-    <col min="6401" max="6401" width="5.85546875" customWidth="1"/>
-    <col min="6402" max="6402" width="62.42578125" customWidth="1"/>
-    <col min="6403" max="6403" width="14.85546875" customWidth="1"/>
-    <col min="6404" max="6404" width="17.28515625" customWidth="1"/>
-    <col min="6405" max="6405" width="20.7109375" customWidth="1"/>
-    <col min="6406" max="6406" width="33.85546875" customWidth="1"/>
-    <col min="6407" max="6407" width="37.28515625" customWidth="1"/>
-    <col min="6408" max="6408" width="18.5703125" customWidth="1"/>
-    <col min="6657" max="6657" width="5.85546875" customWidth="1"/>
-    <col min="6658" max="6658" width="62.42578125" customWidth="1"/>
-    <col min="6659" max="6659" width="14.85546875" customWidth="1"/>
-    <col min="6660" max="6660" width="17.28515625" customWidth="1"/>
-    <col min="6661" max="6661" width="20.7109375" customWidth="1"/>
-    <col min="6662" max="6662" width="33.85546875" customWidth="1"/>
-    <col min="6663" max="6663" width="37.28515625" customWidth="1"/>
-    <col min="6664" max="6664" width="18.5703125" customWidth="1"/>
-    <col min="6913" max="6913" width="5.85546875" customWidth="1"/>
-    <col min="6914" max="6914" width="62.42578125" customWidth="1"/>
-    <col min="6915" max="6915" width="14.85546875" customWidth="1"/>
-    <col min="6916" max="6916" width="17.28515625" customWidth="1"/>
-    <col min="6917" max="6917" width="20.7109375" customWidth="1"/>
-    <col min="6918" max="6918" width="33.85546875" customWidth="1"/>
-    <col min="6919" max="6919" width="37.28515625" customWidth="1"/>
-    <col min="6920" max="6920" width="18.5703125" customWidth="1"/>
-    <col min="7169" max="7169" width="5.85546875" customWidth="1"/>
-    <col min="7170" max="7170" width="62.42578125" customWidth="1"/>
-    <col min="7171" max="7171" width="14.85546875" customWidth="1"/>
-    <col min="7172" max="7172" width="17.28515625" customWidth="1"/>
-    <col min="7173" max="7173" width="20.7109375" customWidth="1"/>
-    <col min="7174" max="7174" width="33.85546875" customWidth="1"/>
-    <col min="7175" max="7175" width="37.28515625" customWidth="1"/>
-    <col min="7176" max="7176" width="18.5703125" customWidth="1"/>
-    <col min="7425" max="7425" width="5.85546875" customWidth="1"/>
-    <col min="7426" max="7426" width="62.42578125" customWidth="1"/>
-    <col min="7427" max="7427" width="14.85546875" customWidth="1"/>
-    <col min="7428" max="7428" width="17.28515625" customWidth="1"/>
-    <col min="7429" max="7429" width="20.7109375" customWidth="1"/>
-    <col min="7430" max="7430" width="33.85546875" customWidth="1"/>
-    <col min="7431" max="7431" width="37.28515625" customWidth="1"/>
-    <col min="7432" max="7432" width="18.5703125" customWidth="1"/>
-    <col min="7681" max="7681" width="5.85546875" customWidth="1"/>
-    <col min="7682" max="7682" width="62.42578125" customWidth="1"/>
-    <col min="7683" max="7683" width="14.85546875" customWidth="1"/>
-    <col min="7684" max="7684" width="17.28515625" customWidth="1"/>
-    <col min="7685" max="7685" width="20.7109375" customWidth="1"/>
-    <col min="7686" max="7686" width="33.85546875" customWidth="1"/>
-    <col min="7687" max="7687" width="37.28515625" customWidth="1"/>
-    <col min="7688" max="7688" width="18.5703125" customWidth="1"/>
-    <col min="7937" max="7937" width="5.85546875" customWidth="1"/>
-    <col min="7938" max="7938" width="62.42578125" customWidth="1"/>
-    <col min="7939" max="7939" width="14.85546875" customWidth="1"/>
-    <col min="7940" max="7940" width="17.28515625" customWidth="1"/>
-    <col min="7941" max="7941" width="20.7109375" customWidth="1"/>
-    <col min="7942" max="7942" width="33.85546875" customWidth="1"/>
-    <col min="7943" max="7943" width="37.28515625" customWidth="1"/>
-    <col min="7944" max="7944" width="18.5703125" customWidth="1"/>
-    <col min="8193" max="8193" width="5.85546875" customWidth="1"/>
-    <col min="8194" max="8194" width="62.42578125" customWidth="1"/>
-    <col min="8195" max="8195" width="14.85546875" customWidth="1"/>
-    <col min="8196" max="8196" width="17.28515625" customWidth="1"/>
-    <col min="8197" max="8197" width="20.7109375" customWidth="1"/>
-    <col min="8198" max="8198" width="33.85546875" customWidth="1"/>
-    <col min="8199" max="8199" width="37.28515625" customWidth="1"/>
-    <col min="8200" max="8200" width="18.5703125" customWidth="1"/>
-    <col min="8449" max="8449" width="5.85546875" customWidth="1"/>
-    <col min="8450" max="8450" width="62.42578125" customWidth="1"/>
-    <col min="8451" max="8451" width="14.85546875" customWidth="1"/>
-    <col min="8452" max="8452" width="17.28515625" customWidth="1"/>
-    <col min="8453" max="8453" width="20.7109375" customWidth="1"/>
-    <col min="8454" max="8454" width="33.85546875" customWidth="1"/>
-    <col min="8455" max="8455" width="37.28515625" customWidth="1"/>
-    <col min="8456" max="8456" width="18.5703125" customWidth="1"/>
-    <col min="8705" max="8705" width="5.85546875" customWidth="1"/>
-    <col min="8706" max="8706" width="62.42578125" customWidth="1"/>
-    <col min="8707" max="8707" width="14.85546875" customWidth="1"/>
-    <col min="8708" max="8708" width="17.28515625" customWidth="1"/>
-    <col min="8709" max="8709" width="20.7109375" customWidth="1"/>
-    <col min="8710" max="8710" width="33.85546875" customWidth="1"/>
-    <col min="8711" max="8711" width="37.28515625" customWidth="1"/>
-    <col min="8712" max="8712" width="18.5703125" customWidth="1"/>
-    <col min="8961" max="8961" width="5.85546875" customWidth="1"/>
-    <col min="8962" max="8962" width="62.42578125" customWidth="1"/>
-    <col min="8963" max="8963" width="14.85546875" customWidth="1"/>
-    <col min="8964" max="8964" width="17.28515625" customWidth="1"/>
-    <col min="8965" max="8965" width="20.7109375" customWidth="1"/>
-    <col min="8966" max="8966" width="33.85546875" customWidth="1"/>
-    <col min="8967" max="8967" width="37.28515625" customWidth="1"/>
-    <col min="8968" max="8968" width="18.5703125" customWidth="1"/>
-    <col min="9217" max="9217" width="5.85546875" customWidth="1"/>
-    <col min="9218" max="9218" width="62.42578125" customWidth="1"/>
-    <col min="9219" max="9219" width="14.85546875" customWidth="1"/>
-    <col min="9220" max="9220" width="17.28515625" customWidth="1"/>
-    <col min="9221" max="9221" width="20.7109375" customWidth="1"/>
-    <col min="9222" max="9222" width="33.85546875" customWidth="1"/>
-    <col min="9223" max="9223" width="37.28515625" customWidth="1"/>
-    <col min="9224" max="9224" width="18.5703125" customWidth="1"/>
-    <col min="9473" max="9473" width="5.85546875" customWidth="1"/>
-    <col min="9474" max="9474" width="62.42578125" customWidth="1"/>
-    <col min="9475" max="9475" width="14.85546875" customWidth="1"/>
-    <col min="9476" max="9476" width="17.28515625" customWidth="1"/>
-    <col min="9477" max="9477" width="20.7109375" customWidth="1"/>
-    <col min="9478" max="9478" width="33.85546875" customWidth="1"/>
-    <col min="9479" max="9479" width="37.28515625" customWidth="1"/>
-    <col min="9480" max="9480" width="18.5703125" customWidth="1"/>
-    <col min="9729" max="9729" width="5.85546875" customWidth="1"/>
-    <col min="9730" max="9730" width="62.42578125" customWidth="1"/>
-    <col min="9731" max="9731" width="14.85546875" customWidth="1"/>
-    <col min="9732" max="9732" width="17.28515625" customWidth="1"/>
-    <col min="9733" max="9733" width="20.7109375" customWidth="1"/>
-    <col min="9734" max="9734" width="33.85546875" customWidth="1"/>
-    <col min="9735" max="9735" width="37.28515625" customWidth="1"/>
-    <col min="9736" max="9736" width="18.5703125" customWidth="1"/>
-    <col min="9985" max="9985" width="5.85546875" customWidth="1"/>
-    <col min="9986" max="9986" width="62.42578125" customWidth="1"/>
-    <col min="9987" max="9987" width="14.85546875" customWidth="1"/>
-    <col min="9988" max="9988" width="17.28515625" customWidth="1"/>
-    <col min="9989" max="9989" width="20.7109375" customWidth="1"/>
-    <col min="9990" max="9990" width="33.85546875" customWidth="1"/>
-    <col min="9991" max="9991" width="37.28515625" customWidth="1"/>
-    <col min="9992" max="9992" width="18.5703125" customWidth="1"/>
-    <col min="10241" max="10241" width="5.85546875" customWidth="1"/>
-    <col min="10242" max="10242" width="62.42578125" customWidth="1"/>
-    <col min="10243" max="10243" width="14.85546875" customWidth="1"/>
-    <col min="10244" max="10244" width="17.28515625" customWidth="1"/>
-    <col min="10245" max="10245" width="20.7109375" customWidth="1"/>
-    <col min="10246" max="10246" width="33.85546875" customWidth="1"/>
-    <col min="10247" max="10247" width="37.28515625" customWidth="1"/>
-    <col min="10248" max="10248" width="18.5703125" customWidth="1"/>
-    <col min="10497" max="10497" width="5.85546875" customWidth="1"/>
-    <col min="10498" max="10498" width="62.42578125" customWidth="1"/>
-    <col min="10499" max="10499" width="14.85546875" customWidth="1"/>
-    <col min="10500" max="10500" width="17.28515625" customWidth="1"/>
-    <col min="10501" max="10501" width="20.7109375" customWidth="1"/>
-    <col min="10502" max="10502" width="33.85546875" customWidth="1"/>
-    <col min="10503" max="10503" width="37.28515625" customWidth="1"/>
-    <col min="10504" max="10504" width="18.5703125" customWidth="1"/>
-    <col min="10753" max="10753" width="5.85546875" customWidth="1"/>
-    <col min="10754" max="10754" width="62.42578125" customWidth="1"/>
-    <col min="10755" max="10755" width="14.85546875" customWidth="1"/>
-    <col min="10756" max="10756" width="17.28515625" customWidth="1"/>
-    <col min="10757" max="10757" width="20.7109375" customWidth="1"/>
-    <col min="10758" max="10758" width="33.85546875" customWidth="1"/>
-    <col min="10759" max="10759" width="37.28515625" customWidth="1"/>
-    <col min="10760" max="10760" width="18.5703125" customWidth="1"/>
-    <col min="11009" max="11009" width="5.85546875" customWidth="1"/>
-    <col min="11010" max="11010" width="62.42578125" customWidth="1"/>
-    <col min="11011" max="11011" width="14.85546875" customWidth="1"/>
-    <col min="11012" max="11012" width="17.28515625" customWidth="1"/>
-    <col min="11013" max="11013" width="20.7109375" customWidth="1"/>
-    <col min="11014" max="11014" width="33.85546875" customWidth="1"/>
-    <col min="11015" max="11015" width="37.28515625" customWidth="1"/>
-    <col min="11016" max="11016" width="18.5703125" customWidth="1"/>
-    <col min="11265" max="11265" width="5.85546875" customWidth="1"/>
-    <col min="11266" max="11266" width="62.42578125" customWidth="1"/>
-    <col min="11267" max="11267" width="14.85546875" customWidth="1"/>
-    <col min="11268" max="11268" width="17.28515625" customWidth="1"/>
-    <col min="11269" max="11269" width="20.7109375" customWidth="1"/>
-    <col min="11270" max="11270" width="33.85546875" customWidth="1"/>
-    <col min="11271" max="11271" width="37.28515625" customWidth="1"/>
-    <col min="11272" max="11272" width="18.5703125" customWidth="1"/>
-    <col min="11521" max="11521" width="5.85546875" customWidth="1"/>
-    <col min="11522" max="11522" width="62.42578125" customWidth="1"/>
-    <col min="11523" max="11523" width="14.85546875" customWidth="1"/>
-    <col min="11524" max="11524" width="17.28515625" customWidth="1"/>
-    <col min="11525" max="11525" width="20.7109375" customWidth="1"/>
-    <col min="11526" max="11526" width="33.85546875" customWidth="1"/>
-    <col min="11527" max="11527" width="37.28515625" customWidth="1"/>
-    <col min="11528" max="11528" width="18.5703125" customWidth="1"/>
-    <col min="11777" max="11777" width="5.85546875" customWidth="1"/>
-    <col min="11778" max="11778" width="62.42578125" customWidth="1"/>
-    <col min="11779" max="11779" width="14.85546875" customWidth="1"/>
-    <col min="11780" max="11780" width="17.28515625" customWidth="1"/>
-    <col min="11781" max="11781" width="20.7109375" customWidth="1"/>
-    <col min="11782" max="11782" width="33.85546875" customWidth="1"/>
-    <col min="11783" max="11783" width="37.28515625" customWidth="1"/>
-    <col min="11784" max="11784" width="18.5703125" customWidth="1"/>
-    <col min="12033" max="12033" width="5.85546875" customWidth="1"/>
-    <col min="12034" max="12034" width="62.42578125" customWidth="1"/>
-    <col min="12035" max="12035" width="14.85546875" customWidth="1"/>
-    <col min="12036" max="12036" width="17.28515625" customWidth="1"/>
-    <col min="12037" max="12037" width="20.7109375" customWidth="1"/>
-    <col min="12038" max="12038" width="33.85546875" customWidth="1"/>
-    <col min="12039" max="12039" width="37.28515625" customWidth="1"/>
-    <col min="12040" max="12040" width="18.5703125" customWidth="1"/>
-    <col min="12289" max="12289" width="5.85546875" customWidth="1"/>
-    <col min="12290" max="12290" width="62.42578125" customWidth="1"/>
-    <col min="12291" max="12291" width="14.85546875" customWidth="1"/>
-    <col min="12292" max="12292" width="17.28515625" customWidth="1"/>
-    <col min="12293" max="12293" width="20.7109375" customWidth="1"/>
-    <col min="12294" max="12294" width="33.85546875" customWidth="1"/>
-    <col min="12295" max="12295" width="37.28515625" customWidth="1"/>
-    <col min="12296" max="12296" width="18.5703125" customWidth="1"/>
-    <col min="12545" max="12545" width="5.85546875" customWidth="1"/>
-    <col min="12546" max="12546" width="62.42578125" customWidth="1"/>
-    <col min="12547" max="12547" width="14.85546875" customWidth="1"/>
-    <col min="12548" max="12548" width="17.28515625" customWidth="1"/>
-    <col min="12549" max="12549" width="20.7109375" customWidth="1"/>
-    <col min="12550" max="12550" width="33.85546875" customWidth="1"/>
-    <col min="12551" max="12551" width="37.28515625" customWidth="1"/>
-    <col min="12552" max="12552" width="18.5703125" customWidth="1"/>
-    <col min="12801" max="12801" width="5.85546875" customWidth="1"/>
-    <col min="12802" max="12802" width="62.42578125" customWidth="1"/>
-    <col min="12803" max="12803" width="14.85546875" customWidth="1"/>
-    <col min="12804" max="12804" width="17.28515625" customWidth="1"/>
-    <col min="12805" max="12805" width="20.7109375" customWidth="1"/>
-    <col min="12806" max="12806" width="33.85546875" customWidth="1"/>
-    <col min="12807" max="12807" width="37.28515625" customWidth="1"/>
-    <col min="12808" max="12808" width="18.5703125" customWidth="1"/>
-    <col min="13057" max="13057" width="5.85546875" customWidth="1"/>
-    <col min="13058" max="13058" width="62.42578125" customWidth="1"/>
-    <col min="13059" max="13059" width="14.85546875" customWidth="1"/>
-    <col min="13060" max="13060" width="17.28515625" customWidth="1"/>
-    <col min="13061" max="13061" width="20.7109375" customWidth="1"/>
-    <col min="13062" max="13062" width="33.85546875" customWidth="1"/>
-    <col min="13063" max="13063" width="37.28515625" customWidth="1"/>
-    <col min="13064" max="13064" width="18.5703125" customWidth="1"/>
-    <col min="13313" max="13313" width="5.85546875" customWidth="1"/>
-    <col min="13314" max="13314" width="62.42578125" customWidth="1"/>
-    <col min="13315" max="13315" width="14.85546875" customWidth="1"/>
-    <col min="13316" max="13316" width="17.28515625" customWidth="1"/>
-    <col min="13317" max="13317" width="20.7109375" customWidth="1"/>
-    <col min="13318" max="13318" width="33.85546875" customWidth="1"/>
-    <col min="13319" max="13319" width="37.28515625" customWidth="1"/>
-    <col min="13320" max="13320" width="18.5703125" customWidth="1"/>
-    <col min="13569" max="13569" width="5.85546875" customWidth="1"/>
-    <col min="13570" max="13570" width="62.42578125" customWidth="1"/>
-    <col min="13571" max="13571" width="14.85546875" customWidth="1"/>
-    <col min="13572" max="13572" width="17.28515625" customWidth="1"/>
-    <col min="13573" max="13573" width="20.7109375" customWidth="1"/>
-    <col min="13574" max="13574" width="33.85546875" customWidth="1"/>
-    <col min="13575" max="13575" width="37.28515625" customWidth="1"/>
-    <col min="13576" max="13576" width="18.5703125" customWidth="1"/>
-    <col min="13825" max="13825" width="5.85546875" customWidth="1"/>
-    <col min="13826" max="13826" width="62.42578125" customWidth="1"/>
-    <col min="13827" max="13827" width="14.85546875" customWidth="1"/>
-    <col min="13828" max="13828" width="17.28515625" customWidth="1"/>
-    <col min="13829" max="13829" width="20.7109375" customWidth="1"/>
-    <col min="13830" max="13830" width="33.85546875" customWidth="1"/>
-    <col min="13831" max="13831" width="37.28515625" customWidth="1"/>
-    <col min="13832" max="13832" width="18.5703125" customWidth="1"/>
-    <col min="14081" max="14081" width="5.85546875" customWidth="1"/>
-    <col min="14082" max="14082" width="62.42578125" customWidth="1"/>
-    <col min="14083" max="14083" width="14.85546875" customWidth="1"/>
-    <col min="14084" max="14084" width="17.28515625" customWidth="1"/>
-    <col min="14085" max="14085" width="20.7109375" customWidth="1"/>
-    <col min="14086" max="14086" width="33.85546875" customWidth="1"/>
-    <col min="14087" max="14087" width="37.28515625" customWidth="1"/>
-    <col min="14088" max="14088" width="18.5703125" customWidth="1"/>
-    <col min="14337" max="14337" width="5.85546875" customWidth="1"/>
-    <col min="14338" max="14338" width="62.42578125" customWidth="1"/>
-    <col min="14339" max="14339" width="14.85546875" customWidth="1"/>
-    <col min="14340" max="14340" width="17.28515625" customWidth="1"/>
-    <col min="14341" max="14341" width="20.7109375" customWidth="1"/>
-    <col min="14342" max="14342" width="33.85546875" customWidth="1"/>
-    <col min="14343" max="14343" width="37.28515625" customWidth="1"/>
-    <col min="14344" max="14344" width="18.5703125" customWidth="1"/>
-    <col min="14593" max="14593" width="5.85546875" customWidth="1"/>
-    <col min="14594" max="14594" width="62.42578125" customWidth="1"/>
-    <col min="14595" max="14595" width="14.85546875" customWidth="1"/>
-    <col min="14596" max="14596" width="17.28515625" customWidth="1"/>
-    <col min="14597" max="14597" width="20.7109375" customWidth="1"/>
-    <col min="14598" max="14598" width="33.85546875" customWidth="1"/>
-    <col min="14599" max="14599" width="37.28515625" customWidth="1"/>
-    <col min="14600" max="14600" width="18.5703125" customWidth="1"/>
-    <col min="14849" max="14849" width="5.85546875" customWidth="1"/>
-    <col min="14850" max="14850" width="62.42578125" customWidth="1"/>
-    <col min="14851" max="14851" width="14.85546875" customWidth="1"/>
-    <col min="14852" max="14852" width="17.28515625" customWidth="1"/>
-    <col min="14853" max="14853" width="20.7109375" customWidth="1"/>
-    <col min="14854" max="14854" width="33.85546875" customWidth="1"/>
-    <col min="14855" max="14855" width="37.28515625" customWidth="1"/>
-    <col min="14856" max="14856" width="18.5703125" customWidth="1"/>
-    <col min="15105" max="15105" width="5.85546875" customWidth="1"/>
-    <col min="15106" max="15106" width="62.42578125" customWidth="1"/>
-    <col min="15107" max="15107" width="14.85546875" customWidth="1"/>
-    <col min="15108" max="15108" width="17.28515625" customWidth="1"/>
-    <col min="15109" max="15109" width="20.7109375" customWidth="1"/>
-    <col min="15110" max="15110" width="33.85546875" customWidth="1"/>
-    <col min="15111" max="15111" width="37.28515625" customWidth="1"/>
-    <col min="15112" max="15112" width="18.5703125" customWidth="1"/>
-    <col min="15361" max="15361" width="5.85546875" customWidth="1"/>
-    <col min="15362" max="15362" width="62.42578125" customWidth="1"/>
-    <col min="15363" max="15363" width="14.85546875" customWidth="1"/>
-    <col min="15364" max="15364" width="17.28515625" customWidth="1"/>
-    <col min="15365" max="15365" width="20.7109375" customWidth="1"/>
-    <col min="15366" max="15366" width="33.85546875" customWidth="1"/>
-    <col min="15367" max="15367" width="37.28515625" customWidth="1"/>
-    <col min="15368" max="15368" width="18.5703125" customWidth="1"/>
-    <col min="15617" max="15617" width="5.85546875" customWidth="1"/>
-    <col min="15618" max="15618" width="62.42578125" customWidth="1"/>
-    <col min="15619" max="15619" width="14.85546875" customWidth="1"/>
-    <col min="15620" max="15620" width="17.28515625" customWidth="1"/>
-    <col min="15621" max="15621" width="20.7109375" customWidth="1"/>
-    <col min="15622" max="15622" width="33.85546875" customWidth="1"/>
-    <col min="15623" max="15623" width="37.28515625" customWidth="1"/>
-    <col min="15624" max="15624" width="18.5703125" customWidth="1"/>
-    <col min="15873" max="15873" width="5.85546875" customWidth="1"/>
-    <col min="15874" max="15874" width="62.42578125" customWidth="1"/>
-    <col min="15875" max="15875" width="14.85546875" customWidth="1"/>
-    <col min="15876" max="15876" width="17.28515625" customWidth="1"/>
-    <col min="15877" max="15877" width="20.7109375" customWidth="1"/>
-    <col min="15878" max="15878" width="33.85546875" customWidth="1"/>
-    <col min="15879" max="15879" width="37.28515625" customWidth="1"/>
-    <col min="15880" max="15880" width="18.5703125" customWidth="1"/>
-    <col min="16129" max="16129" width="5.85546875" customWidth="1"/>
-    <col min="16130" max="16130" width="62.42578125" customWidth="1"/>
-    <col min="16131" max="16131" width="14.85546875" customWidth="1"/>
-    <col min="16132" max="16132" width="17.28515625" customWidth="1"/>
-    <col min="16133" max="16133" width="20.7109375" customWidth="1"/>
-    <col min="16134" max="16134" width="33.85546875" customWidth="1"/>
-    <col min="16135" max="16135" width="37.28515625" customWidth="1"/>
-    <col min="16136" max="16136" width="18.5703125" customWidth="1"/>
+    <col min="257" max="257" width="5.83203125" customWidth="1"/>
+    <col min="258" max="258" width="62.4140625" customWidth="1"/>
+    <col min="259" max="259" width="14.83203125" customWidth="1"/>
+    <col min="260" max="260" width="17.25" customWidth="1"/>
+    <col min="261" max="261" width="20.75" customWidth="1"/>
+    <col min="262" max="262" width="33.83203125" customWidth="1"/>
+    <col min="263" max="263" width="37.25" customWidth="1"/>
+    <col min="264" max="264" width="18.58203125" customWidth="1"/>
+    <col min="513" max="513" width="5.83203125" customWidth="1"/>
+    <col min="514" max="514" width="62.4140625" customWidth="1"/>
+    <col min="515" max="515" width="14.83203125" customWidth="1"/>
+    <col min="516" max="516" width="17.25" customWidth="1"/>
+    <col min="517" max="517" width="20.75" customWidth="1"/>
+    <col min="518" max="518" width="33.83203125" customWidth="1"/>
+    <col min="519" max="519" width="37.25" customWidth="1"/>
+    <col min="520" max="520" width="18.58203125" customWidth="1"/>
+    <col min="769" max="769" width="5.83203125" customWidth="1"/>
+    <col min="770" max="770" width="62.4140625" customWidth="1"/>
+    <col min="771" max="771" width="14.83203125" customWidth="1"/>
+    <col min="772" max="772" width="17.25" customWidth="1"/>
+    <col min="773" max="773" width="20.75" customWidth="1"/>
+    <col min="774" max="774" width="33.83203125" customWidth="1"/>
+    <col min="775" max="775" width="37.25" customWidth="1"/>
+    <col min="776" max="776" width="18.58203125" customWidth="1"/>
+    <col min="1025" max="1025" width="5.83203125" customWidth="1"/>
+    <col min="1026" max="1026" width="62.4140625" customWidth="1"/>
+    <col min="1027" max="1027" width="14.83203125" customWidth="1"/>
+    <col min="1028" max="1028" width="17.25" customWidth="1"/>
+    <col min="1029" max="1029" width="20.75" customWidth="1"/>
+    <col min="1030" max="1030" width="33.83203125" customWidth="1"/>
+    <col min="1031" max="1031" width="37.25" customWidth="1"/>
+    <col min="1032" max="1032" width="18.58203125" customWidth="1"/>
+    <col min="1281" max="1281" width="5.83203125" customWidth="1"/>
+    <col min="1282" max="1282" width="62.4140625" customWidth="1"/>
+    <col min="1283" max="1283" width="14.83203125" customWidth="1"/>
+    <col min="1284" max="1284" width="17.25" customWidth="1"/>
+    <col min="1285" max="1285" width="20.75" customWidth="1"/>
+    <col min="1286" max="1286" width="33.83203125" customWidth="1"/>
+    <col min="1287" max="1287" width="37.25" customWidth="1"/>
+    <col min="1288" max="1288" width="18.58203125" customWidth="1"/>
+    <col min="1537" max="1537" width="5.83203125" customWidth="1"/>
+    <col min="1538" max="1538" width="62.4140625" customWidth="1"/>
+    <col min="1539" max="1539" width="14.83203125" customWidth="1"/>
+    <col min="1540" max="1540" width="17.25" customWidth="1"/>
+    <col min="1541" max="1541" width="20.75" customWidth="1"/>
+    <col min="1542" max="1542" width="33.83203125" customWidth="1"/>
+    <col min="1543" max="1543" width="37.25" customWidth="1"/>
+    <col min="1544" max="1544" width="18.58203125" customWidth="1"/>
+    <col min="1793" max="1793" width="5.83203125" customWidth="1"/>
+    <col min="1794" max="1794" width="62.4140625" customWidth="1"/>
+    <col min="1795" max="1795" width="14.83203125" customWidth="1"/>
+    <col min="1796" max="1796" width="17.25" customWidth="1"/>
+    <col min="1797" max="1797" width="20.75" customWidth="1"/>
+    <col min="1798" max="1798" width="33.83203125" customWidth="1"/>
+    <col min="1799" max="1799" width="37.25" customWidth="1"/>
+    <col min="1800" max="1800" width="18.58203125" customWidth="1"/>
+    <col min="2049" max="2049" width="5.83203125" customWidth="1"/>
+    <col min="2050" max="2050" width="62.4140625" customWidth="1"/>
+    <col min="2051" max="2051" width="14.83203125" customWidth="1"/>
+    <col min="2052" max="2052" width="17.25" customWidth="1"/>
+    <col min="2053" max="2053" width="20.75" customWidth="1"/>
+    <col min="2054" max="2054" width="33.83203125" customWidth="1"/>
+    <col min="2055" max="2055" width="37.25" customWidth="1"/>
+    <col min="2056" max="2056" width="18.58203125" customWidth="1"/>
+    <col min="2305" max="2305" width="5.83203125" customWidth="1"/>
+    <col min="2306" max="2306" width="62.4140625" customWidth="1"/>
+    <col min="2307" max="2307" width="14.83203125" customWidth="1"/>
+    <col min="2308" max="2308" width="17.25" customWidth="1"/>
+    <col min="2309" max="2309" width="20.75" customWidth="1"/>
+    <col min="2310" max="2310" width="33.83203125" customWidth="1"/>
+    <col min="2311" max="2311" width="37.25" customWidth="1"/>
+    <col min="2312" max="2312" width="18.58203125" customWidth="1"/>
+    <col min="2561" max="2561" width="5.83203125" customWidth="1"/>
+    <col min="2562" max="2562" width="62.4140625" customWidth="1"/>
+    <col min="2563" max="2563" width="14.83203125" customWidth="1"/>
+    <col min="2564" max="2564" width="17.25" customWidth="1"/>
+    <col min="2565" max="2565" width="20.75" customWidth="1"/>
+    <col min="2566" max="2566" width="33.83203125" customWidth="1"/>
+    <col min="2567" max="2567" width="37.25" customWidth="1"/>
+    <col min="2568" max="2568" width="18.58203125" customWidth="1"/>
+    <col min="2817" max="2817" width="5.83203125" customWidth="1"/>
+    <col min="2818" max="2818" width="62.4140625" customWidth="1"/>
+    <col min="2819" max="2819" width="14.83203125" customWidth="1"/>
+    <col min="2820" max="2820" width="17.25" customWidth="1"/>
+    <col min="2821" max="2821" width="20.75" customWidth="1"/>
+    <col min="2822" max="2822" width="33.83203125" customWidth="1"/>
+    <col min="2823" max="2823" width="37.25" customWidth="1"/>
+    <col min="2824" max="2824" width="18.58203125" customWidth="1"/>
+    <col min="3073" max="3073" width="5.83203125" customWidth="1"/>
+    <col min="3074" max="3074" width="62.4140625" customWidth="1"/>
+    <col min="3075" max="3075" width="14.83203125" customWidth="1"/>
+    <col min="3076" max="3076" width="17.25" customWidth="1"/>
+    <col min="3077" max="3077" width="20.75" customWidth="1"/>
+    <col min="3078" max="3078" width="33.83203125" customWidth="1"/>
+    <col min="3079" max="3079" width="37.25" customWidth="1"/>
+    <col min="3080" max="3080" width="18.58203125" customWidth="1"/>
+    <col min="3329" max="3329" width="5.83203125" customWidth="1"/>
+    <col min="3330" max="3330" width="62.4140625" customWidth="1"/>
+    <col min="3331" max="3331" width="14.83203125" customWidth="1"/>
+    <col min="3332" max="3332" width="17.25" customWidth="1"/>
+    <col min="3333" max="3333" width="20.75" customWidth="1"/>
+    <col min="3334" max="3334" width="33.83203125" customWidth="1"/>
+    <col min="3335" max="3335" width="37.25" customWidth="1"/>
+    <col min="3336" max="3336" width="18.58203125" customWidth="1"/>
+    <col min="3585" max="3585" width="5.83203125" customWidth="1"/>
+    <col min="3586" max="3586" width="62.4140625" customWidth="1"/>
+    <col min="3587" max="3587" width="14.83203125" customWidth="1"/>
+    <col min="3588" max="3588" width="17.25" customWidth="1"/>
+    <col min="3589" max="3589" width="20.75" customWidth="1"/>
+    <col min="3590" max="3590" width="33.83203125" customWidth="1"/>
+    <col min="3591" max="3591" width="37.25" customWidth="1"/>
+    <col min="3592" max="3592" width="18.58203125" customWidth="1"/>
+    <col min="3841" max="3841" width="5.83203125" customWidth="1"/>
+    <col min="3842" max="3842" width="62.4140625" customWidth="1"/>
+    <col min="3843" max="3843" width="14.83203125" customWidth="1"/>
+    <col min="3844" max="3844" width="17.25" customWidth="1"/>
+    <col min="3845" max="3845" width="20.75" customWidth="1"/>
+    <col min="3846" max="3846" width="33.83203125" customWidth="1"/>
+    <col min="3847" max="3847" width="37.25" customWidth="1"/>
+    <col min="3848" max="3848" width="18.58203125" customWidth="1"/>
+    <col min="4097" max="4097" width="5.83203125" customWidth="1"/>
+    <col min="4098" max="4098" width="62.4140625" customWidth="1"/>
+    <col min="4099" max="4099" width="14.83203125" customWidth="1"/>
+    <col min="4100" max="4100" width="17.25" customWidth="1"/>
+    <col min="4101" max="4101" width="20.75" customWidth="1"/>
+    <col min="4102" max="4102" width="33.83203125" customWidth="1"/>
+    <col min="4103" max="4103" width="37.25" customWidth="1"/>
+    <col min="4104" max="4104" width="18.58203125" customWidth="1"/>
+    <col min="4353" max="4353" width="5.83203125" customWidth="1"/>
+    <col min="4354" max="4354" width="62.4140625" customWidth="1"/>
+    <col min="4355" max="4355" width="14.83203125" customWidth="1"/>
+    <col min="4356" max="4356" width="17.25" customWidth="1"/>
+    <col min="4357" max="4357" width="20.75" customWidth="1"/>
+    <col min="4358" max="4358" width="33.83203125" customWidth="1"/>
+    <col min="4359" max="4359" width="37.25" customWidth="1"/>
+    <col min="4360" max="4360" width="18.58203125" customWidth="1"/>
+    <col min="4609" max="4609" width="5.83203125" customWidth="1"/>
+    <col min="4610" max="4610" width="62.4140625" customWidth="1"/>
+    <col min="4611" max="4611" width="14.83203125" customWidth="1"/>
+    <col min="4612" max="4612" width="17.25" customWidth="1"/>
+    <col min="4613" max="4613" width="20.75" customWidth="1"/>
+    <col min="4614" max="4614" width="33.83203125" customWidth="1"/>
+    <col min="4615" max="4615" width="37.25" customWidth="1"/>
+    <col min="4616" max="4616" width="18.58203125" customWidth="1"/>
+    <col min="4865" max="4865" width="5.83203125" customWidth="1"/>
+    <col min="4866" max="4866" width="62.4140625" customWidth="1"/>
+    <col min="4867" max="4867" width="14.83203125" customWidth="1"/>
+    <col min="4868" max="4868" width="17.25" customWidth="1"/>
+    <col min="4869" max="4869" width="20.75" customWidth="1"/>
+    <col min="4870" max="4870" width="33.83203125" customWidth="1"/>
+    <col min="4871" max="4871" width="37.25" customWidth="1"/>
+    <col min="4872" max="4872" width="18.58203125" customWidth="1"/>
+    <col min="5121" max="5121" width="5.83203125" customWidth="1"/>
+    <col min="5122" max="5122" width="62.4140625" customWidth="1"/>
+    <col min="5123" max="5123" width="14.83203125" customWidth="1"/>
+    <col min="5124" max="5124" width="17.25" customWidth="1"/>
+    <col min="5125" max="5125" width="20.75" customWidth="1"/>
+    <col min="5126" max="5126" width="33.83203125" customWidth="1"/>
+    <col min="5127" max="5127" width="37.25" customWidth="1"/>
+    <col min="5128" max="5128" width="18.58203125" customWidth="1"/>
+    <col min="5377" max="5377" width="5.83203125" customWidth="1"/>
+    <col min="5378" max="5378" width="62.4140625" customWidth="1"/>
+    <col min="5379" max="5379" width="14.83203125" customWidth="1"/>
+    <col min="5380" max="5380" width="17.25" customWidth="1"/>
+    <col min="5381" max="5381" width="20.75" customWidth="1"/>
+    <col min="5382" max="5382" width="33.83203125" customWidth="1"/>
+    <col min="5383" max="5383" width="37.25" customWidth="1"/>
+    <col min="5384" max="5384" width="18.58203125" customWidth="1"/>
+    <col min="5633" max="5633" width="5.83203125" customWidth="1"/>
+    <col min="5634" max="5634" width="62.4140625" customWidth="1"/>
+    <col min="5635" max="5635" width="14.83203125" customWidth="1"/>
+    <col min="5636" max="5636" width="17.25" customWidth="1"/>
+    <col min="5637" max="5637" width="20.75" customWidth="1"/>
+    <col min="5638" max="5638" width="33.83203125" customWidth="1"/>
+    <col min="5639" max="5639" width="37.25" customWidth="1"/>
+    <col min="5640" max="5640" width="18.58203125" customWidth="1"/>
+    <col min="5889" max="5889" width="5.83203125" customWidth="1"/>
+    <col min="5890" max="5890" width="62.4140625" customWidth="1"/>
+    <col min="5891" max="5891" width="14.83203125" customWidth="1"/>
+    <col min="5892" max="5892" width="17.25" customWidth="1"/>
+    <col min="5893" max="5893" width="20.75" customWidth="1"/>
+    <col min="5894" max="5894" width="33.83203125" customWidth="1"/>
+    <col min="5895" max="5895" width="37.25" customWidth="1"/>
+    <col min="5896" max="5896" width="18.58203125" customWidth="1"/>
+    <col min="6145" max="6145" width="5.83203125" customWidth="1"/>
+    <col min="6146" max="6146" width="62.4140625" customWidth="1"/>
+    <col min="6147" max="6147" width="14.83203125" customWidth="1"/>
+    <col min="6148" max="6148" width="17.25" customWidth="1"/>
+    <col min="6149" max="6149" width="20.75" customWidth="1"/>
+    <col min="6150" max="6150" width="33.83203125" customWidth="1"/>
+    <col min="6151" max="6151" width="37.25" customWidth="1"/>
+    <col min="6152" max="6152" width="18.58203125" customWidth="1"/>
+    <col min="6401" max="6401" width="5.83203125" customWidth="1"/>
+    <col min="6402" max="6402" width="62.4140625" customWidth="1"/>
+    <col min="6403" max="6403" width="14.83203125" customWidth="1"/>
+    <col min="6404" max="6404" width="17.25" customWidth="1"/>
+    <col min="6405" max="6405" width="20.75" customWidth="1"/>
+    <col min="6406" max="6406" width="33.83203125" customWidth="1"/>
+    <col min="6407" max="6407" width="37.25" customWidth="1"/>
+    <col min="6408" max="6408" width="18.58203125" customWidth="1"/>
+    <col min="6657" max="6657" width="5.83203125" customWidth="1"/>
+    <col min="6658" max="6658" width="62.4140625" customWidth="1"/>
+    <col min="6659" max="6659" width="14.83203125" customWidth="1"/>
+    <col min="6660" max="6660" width="17.25" customWidth="1"/>
+    <col min="6661" max="6661" width="20.75" customWidth="1"/>
+    <col min="6662" max="6662" width="33.83203125" customWidth="1"/>
+    <col min="6663" max="6663" width="37.25" customWidth="1"/>
+    <col min="6664" max="6664" width="18.58203125" customWidth="1"/>
+    <col min="6913" max="6913" width="5.83203125" customWidth="1"/>
+    <col min="6914" max="6914" width="62.4140625" customWidth="1"/>
+    <col min="6915" max="6915" width="14.83203125" customWidth="1"/>
+    <col min="6916" max="6916" width="17.25" customWidth="1"/>
+    <col min="6917" max="6917" width="20.75" customWidth="1"/>
+    <col min="6918" max="6918" width="33.83203125" customWidth="1"/>
+    <col min="6919" max="6919" width="37.25" customWidth="1"/>
+    <col min="6920" max="6920" width="18.58203125" customWidth="1"/>
+    <col min="7169" max="7169" width="5.83203125" customWidth="1"/>
+    <col min="7170" max="7170" width="62.4140625" customWidth="1"/>
+    <col min="7171" max="7171" width="14.83203125" customWidth="1"/>
+    <col min="7172" max="7172" width="17.25" customWidth="1"/>
+    <col min="7173" max="7173" width="20.75" customWidth="1"/>
+    <col min="7174" max="7174" width="33.83203125" customWidth="1"/>
+    <col min="7175" max="7175" width="37.25" customWidth="1"/>
+    <col min="7176" max="7176" width="18.58203125" customWidth="1"/>
+    <col min="7425" max="7425" width="5.83203125" customWidth="1"/>
+    <col min="7426" max="7426" width="62.4140625" customWidth="1"/>
+    <col min="7427" max="7427" width="14.83203125" customWidth="1"/>
+    <col min="7428" max="7428" width="17.25" customWidth="1"/>
+    <col min="7429" max="7429" width="20.75" customWidth="1"/>
+    <col min="7430" max="7430" width="33.83203125" customWidth="1"/>
+    <col min="7431" max="7431" width="37.25" customWidth="1"/>
+    <col min="7432" max="7432" width="18.58203125" customWidth="1"/>
+    <col min="7681" max="7681" width="5.83203125" customWidth="1"/>
+    <col min="7682" max="7682" width="62.4140625" customWidth="1"/>
+    <col min="7683" max="7683" width="14.83203125" customWidth="1"/>
+    <col min="7684" max="7684" width="17.25" customWidth="1"/>
+    <col min="7685" max="7685" width="20.75" customWidth="1"/>
+    <col min="7686" max="7686" width="33.83203125" customWidth="1"/>
+    <col min="7687" max="7687" width="37.25" customWidth="1"/>
+    <col min="7688" max="7688" width="18.58203125" customWidth="1"/>
+    <col min="7937" max="7937" width="5.83203125" customWidth="1"/>
+    <col min="7938" max="7938" width="62.4140625" customWidth="1"/>
+    <col min="7939" max="7939" width="14.83203125" customWidth="1"/>
+    <col min="7940" max="7940" width="17.25" customWidth="1"/>
+    <col min="7941" max="7941" width="20.75" customWidth="1"/>
+    <col min="7942" max="7942" width="33.83203125" customWidth="1"/>
+    <col min="7943" max="7943" width="37.25" customWidth="1"/>
+    <col min="7944" max="7944" width="18.58203125" customWidth="1"/>
+    <col min="8193" max="8193" width="5.83203125" customWidth="1"/>
+    <col min="8194" max="8194" width="62.4140625" customWidth="1"/>
+    <col min="8195" max="8195" width="14.83203125" customWidth="1"/>
+    <col min="8196" max="8196" width="17.25" customWidth="1"/>
+    <col min="8197" max="8197" width="20.75" customWidth="1"/>
+    <col min="8198" max="8198" width="33.83203125" customWidth="1"/>
+    <col min="8199" max="8199" width="37.25" customWidth="1"/>
+    <col min="8200" max="8200" width="18.58203125" customWidth="1"/>
+    <col min="8449" max="8449" width="5.83203125" customWidth="1"/>
+    <col min="8450" max="8450" width="62.4140625" customWidth="1"/>
+    <col min="8451" max="8451" width="14.83203125" customWidth="1"/>
+    <col min="8452" max="8452" width="17.25" customWidth="1"/>
+    <col min="8453" max="8453" width="20.75" customWidth="1"/>
+    <col min="8454" max="8454" width="33.83203125" customWidth="1"/>
+    <col min="8455" max="8455" width="37.25" customWidth="1"/>
+    <col min="8456" max="8456" width="18.58203125" customWidth="1"/>
+    <col min="8705" max="8705" width="5.83203125" customWidth="1"/>
+    <col min="8706" max="8706" width="62.4140625" customWidth="1"/>
+    <col min="8707" max="8707" width="14.83203125" customWidth="1"/>
+    <col min="8708" max="8708" width="17.25" customWidth="1"/>
+    <col min="8709" max="8709" width="20.75" customWidth="1"/>
+    <col min="8710" max="8710" width="33.83203125" customWidth="1"/>
+    <col min="8711" max="8711" width="37.25" customWidth="1"/>
+    <col min="8712" max="8712" width="18.58203125" customWidth="1"/>
+    <col min="8961" max="8961" width="5.83203125" customWidth="1"/>
+    <col min="8962" max="8962" width="62.4140625" customWidth="1"/>
+    <col min="8963" max="8963" width="14.83203125" customWidth="1"/>
+    <col min="8964" max="8964" width="17.25" customWidth="1"/>
+    <col min="8965" max="8965" width="20.75" customWidth="1"/>
+    <col min="8966" max="8966" width="33.83203125" customWidth="1"/>
+    <col min="8967" max="8967" width="37.25" customWidth="1"/>
+    <col min="8968" max="8968" width="18.58203125" customWidth="1"/>
+    <col min="9217" max="9217" width="5.83203125" customWidth="1"/>
+    <col min="9218" max="9218" width="62.4140625" customWidth="1"/>
+    <col min="9219" max="9219" width="14.83203125" customWidth="1"/>
+    <col min="9220" max="9220" width="17.25" customWidth="1"/>
+    <col min="9221" max="9221" width="20.75" customWidth="1"/>
+    <col min="9222" max="9222" width="33.83203125" customWidth="1"/>
+    <col min="9223" max="9223" width="37.25" customWidth="1"/>
+    <col min="9224" max="9224" width="18.58203125" customWidth="1"/>
+    <col min="9473" max="9473" width="5.83203125" customWidth="1"/>
+    <col min="9474" max="9474" width="62.4140625" customWidth="1"/>
+    <col min="9475" max="9475" width="14.83203125" customWidth="1"/>
+    <col min="9476" max="9476" width="17.25" customWidth="1"/>
+    <col min="9477" max="9477" width="20.75" customWidth="1"/>
+    <col min="9478" max="9478" width="33.83203125" customWidth="1"/>
+    <col min="9479" max="9479" width="37.25" customWidth="1"/>
+    <col min="9480" max="9480" width="18.58203125" customWidth="1"/>
+    <col min="9729" max="9729" width="5.83203125" customWidth="1"/>
+    <col min="9730" max="9730" width="62.4140625" customWidth="1"/>
+    <col min="9731" max="9731" width="14.83203125" customWidth="1"/>
+    <col min="9732" max="9732" width="17.25" customWidth="1"/>
+    <col min="9733" max="9733" width="20.75" customWidth="1"/>
+    <col min="9734" max="9734" width="33.83203125" customWidth="1"/>
+    <col min="9735" max="9735" width="37.25" customWidth="1"/>
+    <col min="9736" max="9736" width="18.58203125" customWidth="1"/>
+    <col min="9985" max="9985" width="5.83203125" customWidth="1"/>
+    <col min="9986" max="9986" width="62.4140625" customWidth="1"/>
+    <col min="9987" max="9987" width="14.83203125" customWidth="1"/>
+    <col min="9988" max="9988" width="17.25" customWidth="1"/>
+    <col min="9989" max="9989" width="20.75" customWidth="1"/>
+    <col min="9990" max="9990" width="33.83203125" customWidth="1"/>
+    <col min="9991" max="9991" width="37.25" customWidth="1"/>
+    <col min="9992" max="9992" width="18.58203125" customWidth="1"/>
+    <col min="10241" max="10241" width="5.83203125" customWidth="1"/>
+    <col min="10242" max="10242" width="62.4140625" customWidth="1"/>
+    <col min="10243" max="10243" width="14.83203125" customWidth="1"/>
+    <col min="10244" max="10244" width="17.25" customWidth="1"/>
+    <col min="10245" max="10245" width="20.75" customWidth="1"/>
+    <col min="10246" max="10246" width="33.83203125" customWidth="1"/>
+    <col min="10247" max="10247" width="37.25" customWidth="1"/>
+    <col min="10248" max="10248" width="18.58203125" customWidth="1"/>
+    <col min="10497" max="10497" width="5.83203125" customWidth="1"/>
+    <col min="10498" max="10498" width="62.4140625" customWidth="1"/>
+    <col min="10499" max="10499" width="14.83203125" customWidth="1"/>
+    <col min="10500" max="10500" width="17.25" customWidth="1"/>
+    <col min="10501" max="10501" width="20.75" customWidth="1"/>
+    <col min="10502" max="10502" width="33.83203125" customWidth="1"/>
+    <col min="10503" max="10503" width="37.25" customWidth="1"/>
+    <col min="10504" max="10504" width="18.58203125" customWidth="1"/>
+    <col min="10753" max="10753" width="5.83203125" customWidth="1"/>
+    <col min="10754" max="10754" width="62.4140625" customWidth="1"/>
+    <col min="10755" max="10755" width="14.83203125" customWidth="1"/>
+    <col min="10756" max="10756" width="17.25" customWidth="1"/>
+    <col min="10757" max="10757" width="20.75" customWidth="1"/>
+    <col min="10758" max="10758" width="33.83203125" customWidth="1"/>
+    <col min="10759" max="10759" width="37.25" customWidth="1"/>
+    <col min="10760" max="10760" width="18.58203125" customWidth="1"/>
+    <col min="11009" max="11009" width="5.83203125" customWidth="1"/>
+    <col min="11010" max="11010" width="62.4140625" customWidth="1"/>
+    <col min="11011" max="11011" width="14.83203125" customWidth="1"/>
+    <col min="11012" max="11012" width="17.25" customWidth="1"/>
+    <col min="11013" max="11013" width="20.75" customWidth="1"/>
+    <col min="11014" max="11014" width="33.83203125" customWidth="1"/>
+    <col min="11015" max="11015" width="37.25" customWidth="1"/>
+    <col min="11016" max="11016" width="18.58203125" customWidth="1"/>
+    <col min="11265" max="11265" width="5.83203125" customWidth="1"/>
+    <col min="11266" max="11266" width="62.4140625" customWidth="1"/>
+    <col min="11267" max="11267" width="14.83203125" customWidth="1"/>
+    <col min="11268" max="11268" width="17.25" customWidth="1"/>
+    <col min="11269" max="11269" width="20.75" customWidth="1"/>
+    <col min="11270" max="11270" width="33.83203125" customWidth="1"/>
+    <col min="11271" max="11271" width="37.25" customWidth="1"/>
+    <col min="11272" max="11272" width="18.58203125" customWidth="1"/>
+    <col min="11521" max="11521" width="5.83203125" customWidth="1"/>
+    <col min="11522" max="11522" width="62.4140625" customWidth="1"/>
+    <col min="11523" max="11523" width="14.83203125" customWidth="1"/>
+    <col min="11524" max="11524" width="17.25" customWidth="1"/>
+    <col min="11525" max="11525" width="20.75" customWidth="1"/>
+    <col min="11526" max="11526" width="33.83203125" customWidth="1"/>
+    <col min="11527" max="11527" width="37.25" customWidth="1"/>
+    <col min="11528" max="11528" width="18.58203125" customWidth="1"/>
+    <col min="11777" max="11777" width="5.83203125" customWidth="1"/>
+    <col min="11778" max="11778" width="62.4140625" customWidth="1"/>
+    <col min="11779" max="11779" width="14.83203125" customWidth="1"/>
+    <col min="11780" max="11780" width="17.25" customWidth="1"/>
+    <col min="11781" max="11781" width="20.75" customWidth="1"/>
+    <col min="11782" max="11782" width="33.83203125" customWidth="1"/>
+    <col min="11783" max="11783" width="37.25" customWidth="1"/>
+    <col min="11784" max="11784" width="18.58203125" customWidth="1"/>
+    <col min="12033" max="12033" width="5.83203125" customWidth="1"/>
+    <col min="12034" max="12034" width="62.4140625" customWidth="1"/>
+    <col min="12035" max="12035" width="14.83203125" customWidth="1"/>
+    <col min="12036" max="12036" width="17.25" customWidth="1"/>
+    <col min="12037" max="12037" width="20.75" customWidth="1"/>
+    <col min="12038" max="12038" width="33.83203125" customWidth="1"/>
+    <col min="12039" max="12039" width="37.25" customWidth="1"/>
+    <col min="12040" max="12040" width="18.58203125" customWidth="1"/>
+    <col min="12289" max="12289" width="5.83203125" customWidth="1"/>
+    <col min="12290" max="12290" width="62.4140625" customWidth="1"/>
+    <col min="12291" max="12291" width="14.83203125" customWidth="1"/>
+    <col min="12292" max="12292" width="17.25" customWidth="1"/>
+    <col min="12293" max="12293" width="20.75" customWidth="1"/>
+    <col min="12294" max="12294" width="33.83203125" customWidth="1"/>
+    <col min="12295" max="12295" width="37.25" customWidth="1"/>
+    <col min="12296" max="12296" width="18.58203125" customWidth="1"/>
+    <col min="12545" max="12545" width="5.83203125" customWidth="1"/>
+    <col min="12546" max="12546" width="62.4140625" customWidth="1"/>
+    <col min="12547" max="12547" width="14.83203125" customWidth="1"/>
+    <col min="12548" max="12548" width="17.25" customWidth="1"/>
+    <col min="12549" max="12549" width="20.75" customWidth="1"/>
+    <col min="12550" max="12550" width="33.83203125" customWidth="1"/>
+    <col min="12551" max="12551" width="37.25" customWidth="1"/>
+    <col min="12552" max="12552" width="18.58203125" customWidth="1"/>
+    <col min="12801" max="12801" width="5.83203125" customWidth="1"/>
+    <col min="12802" max="12802" width="62.4140625" customWidth="1"/>
+    <col min="12803" max="12803" width="14.83203125" customWidth="1"/>
+    <col min="12804" max="12804" width="17.25" customWidth="1"/>
+    <col min="12805" max="12805" width="20.75" customWidth="1"/>
+    <col min="12806" max="12806" width="33.83203125" customWidth="1"/>
+    <col min="12807" max="12807" width="37.25" customWidth="1"/>
+    <col min="12808" max="12808" width="18.58203125" customWidth="1"/>
+    <col min="13057" max="13057" width="5.83203125" customWidth="1"/>
+    <col min="13058" max="13058" width="62.4140625" customWidth="1"/>
+    <col min="13059" max="13059" width="14.83203125" customWidth="1"/>
+    <col min="13060" max="13060" width="17.25" customWidth="1"/>
+    <col min="13061" max="13061" width="20.75" customWidth="1"/>
+    <col min="13062" max="13062" width="33.83203125" customWidth="1"/>
+    <col min="13063" max="13063" width="37.25" customWidth="1"/>
+    <col min="13064" max="13064" width="18.58203125" customWidth="1"/>
+    <col min="13313" max="13313" width="5.83203125" customWidth="1"/>
+    <col min="13314" max="13314" width="62.4140625" customWidth="1"/>
+    <col min="13315" max="13315" width="14.83203125" customWidth="1"/>
+    <col min="13316" max="13316" width="17.25" customWidth="1"/>
+    <col min="13317" max="13317" width="20.75" customWidth="1"/>
+    <col min="13318" max="13318" width="33.83203125" customWidth="1"/>
+    <col min="13319" max="13319" width="37.25" customWidth="1"/>
+    <col min="13320" max="13320" width="18.58203125" customWidth="1"/>
+    <col min="13569" max="13569" width="5.83203125" customWidth="1"/>
+    <col min="13570" max="13570" width="62.4140625" customWidth="1"/>
+    <col min="13571" max="13571" width="14.83203125" customWidth="1"/>
+    <col min="13572" max="13572" width="17.25" customWidth="1"/>
+    <col min="13573" max="13573" width="20.75" customWidth="1"/>
+    <col min="13574" max="13574" width="33.83203125" customWidth="1"/>
+    <col min="13575" max="13575" width="37.25" customWidth="1"/>
+    <col min="13576" max="13576" width="18.58203125" customWidth="1"/>
+    <col min="13825" max="13825" width="5.83203125" customWidth="1"/>
+    <col min="13826" max="13826" width="62.4140625" customWidth="1"/>
+    <col min="13827" max="13827" width="14.83203125" customWidth="1"/>
+    <col min="13828" max="13828" width="17.25" customWidth="1"/>
+    <col min="13829" max="13829" width="20.75" customWidth="1"/>
+    <col min="13830" max="13830" width="33.83203125" customWidth="1"/>
+    <col min="13831" max="13831" width="37.25" customWidth="1"/>
+    <col min="13832" max="13832" width="18.58203125" customWidth="1"/>
+    <col min="14081" max="14081" width="5.83203125" customWidth="1"/>
+    <col min="14082" max="14082" width="62.4140625" customWidth="1"/>
+    <col min="14083" max="14083" width="14.83203125" customWidth="1"/>
+    <col min="14084" max="14084" width="17.25" customWidth="1"/>
+    <col min="14085" max="14085" width="20.75" customWidth="1"/>
+    <col min="14086" max="14086" width="33.83203125" customWidth="1"/>
+    <col min="14087" max="14087" width="37.25" customWidth="1"/>
+    <col min="14088" max="14088" width="18.58203125" customWidth="1"/>
+    <col min="14337" max="14337" width="5.83203125" customWidth="1"/>
+    <col min="14338" max="14338" width="62.4140625" customWidth="1"/>
+    <col min="14339" max="14339" width="14.83203125" customWidth="1"/>
+    <col min="14340" max="14340" width="17.25" customWidth="1"/>
+    <col min="14341" max="14341" width="20.75" customWidth="1"/>
+    <col min="14342" max="14342" width="33.83203125" customWidth="1"/>
+    <col min="14343" max="14343" width="37.25" customWidth="1"/>
+    <col min="14344" max="14344" width="18.58203125" customWidth="1"/>
+    <col min="14593" max="14593" width="5.83203125" customWidth="1"/>
+    <col min="14594" max="14594" width="62.4140625" customWidth="1"/>
+    <col min="14595" max="14595" width="14.83203125" customWidth="1"/>
+    <col min="14596" max="14596" width="17.25" customWidth="1"/>
+    <col min="14597" max="14597" width="20.75" customWidth="1"/>
+    <col min="14598" max="14598" width="33.83203125" customWidth="1"/>
+    <col min="14599" max="14599" width="37.25" customWidth="1"/>
+    <col min="14600" max="14600" width="18.58203125" customWidth="1"/>
+    <col min="14849" max="14849" width="5.83203125" customWidth="1"/>
+    <col min="14850" max="14850" width="62.4140625" customWidth="1"/>
+    <col min="14851" max="14851" width="14.83203125" customWidth="1"/>
+    <col min="14852" max="14852" width="17.25" customWidth="1"/>
+    <col min="14853" max="14853" width="20.75" customWidth="1"/>
+    <col min="14854" max="14854" width="33.83203125" customWidth="1"/>
+    <col min="14855" max="14855" width="37.25" customWidth="1"/>
+    <col min="14856" max="14856" width="18.58203125" customWidth="1"/>
+    <col min="15105" max="15105" width="5.83203125" customWidth="1"/>
+    <col min="15106" max="15106" width="62.4140625" customWidth="1"/>
+    <col min="15107" max="15107" width="14.83203125" customWidth="1"/>
+    <col min="15108" max="15108" width="17.25" customWidth="1"/>
+    <col min="15109" max="15109" width="20.75" customWidth="1"/>
+    <col min="15110" max="15110" width="33.83203125" customWidth="1"/>
+    <col min="15111" max="15111" width="37.25" customWidth="1"/>
+    <col min="15112" max="15112" width="18.58203125" customWidth="1"/>
+    <col min="15361" max="15361" width="5.83203125" customWidth="1"/>
+    <col min="15362" max="15362" width="62.4140625" customWidth="1"/>
+    <col min="15363" max="15363" width="14.83203125" customWidth="1"/>
+    <col min="15364" max="15364" width="17.25" customWidth="1"/>
+    <col min="15365" max="15365" width="20.75" customWidth="1"/>
+    <col min="15366" max="15366" width="33.83203125" customWidth="1"/>
+    <col min="15367" max="15367" width="37.25" customWidth="1"/>
+    <col min="15368" max="15368" width="18.58203125" customWidth="1"/>
+    <col min="15617" max="15617" width="5.83203125" customWidth="1"/>
+    <col min="15618" max="15618" width="62.4140625" customWidth="1"/>
+    <col min="15619" max="15619" width="14.83203125" customWidth="1"/>
+    <col min="15620" max="15620" width="17.25" customWidth="1"/>
+    <col min="15621" max="15621" width="20.75" customWidth="1"/>
+    <col min="15622" max="15622" width="33.83203125" customWidth="1"/>
+    <col min="15623" max="15623" width="37.25" customWidth="1"/>
+    <col min="15624" max="15624" width="18.58203125" customWidth="1"/>
+    <col min="15873" max="15873" width="5.83203125" customWidth="1"/>
+    <col min="15874" max="15874" width="62.4140625" customWidth="1"/>
+    <col min="15875" max="15875" width="14.83203125" customWidth="1"/>
+    <col min="15876" max="15876" width="17.25" customWidth="1"/>
+    <col min="15877" max="15877" width="20.75" customWidth="1"/>
+    <col min="15878" max="15878" width="33.83203125" customWidth="1"/>
+    <col min="15879" max="15879" width="37.25" customWidth="1"/>
+    <col min="15880" max="15880" width="18.58203125" customWidth="1"/>
+    <col min="16129" max="16129" width="5.83203125" customWidth="1"/>
+    <col min="16130" max="16130" width="62.4140625" customWidth="1"/>
+    <col min="16131" max="16131" width="14.83203125" customWidth="1"/>
+    <col min="16132" max="16132" width="17.25" customWidth="1"/>
+    <col min="16133" max="16133" width="20.75" customWidth="1"/>
+    <col min="16134" max="16134" width="33.83203125" customWidth="1"/>
+    <col min="16135" max="16135" width="37.25" customWidth="1"/>
+    <col min="16136" max="16136" width="18.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75">
+    <row r="1" spans="1:8" ht="17.5">
       <c r="A1" s="567" t="s">
         <v>0</v>
       </c>
@@ -21951,7 +21951,7 @@
       <c r="G1" s="568"/>
       <c r="H1" s="568"/>
     </row>
-    <row r="2" spans="1:8" ht="16.5" thickBot="1">
+    <row r="2" spans="1:8" ht="15.5" thickBot="1">
       <c r="A2" s="569" t="s">
         <v>18</v>
       </c>
@@ -21965,7 +21965,7 @@
       <c r="G2" s="569"/>
       <c r="H2" s="569"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" thickTop="1">
+    <row r="3" spans="1:8" ht="16" thickTop="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -21975,7 +21975,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75">
+    <row r="4" spans="1:8" ht="15.5">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="C4" s="548"/>
@@ -21987,7 +21987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75">
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="573" t="s">
         <v>22</v>
       </c>
@@ -21999,7 +21999,7 @@
       <c r="G5" s="573"/>
       <c r="H5" s="573"/>
     </row>
-    <row r="6" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="6" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A6" s="513" t="s">
         <v>2</v>
       </c>
@@ -22023,7 +22023,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="7" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A7" s="513"/>
       <c r="B7" s="512"/>
       <c r="C7" s="513"/>
@@ -22037,7 +22037,7 @@
       <c r="G7" s="513"/>
       <c r="H7" s="513"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75">
+    <row r="8" spans="1:8" ht="15.5">
       <c r="A8" s="5" t="s">
         <v>10</v>
       </c>
@@ -22073,7 +22073,7 @@
       <c r="G9" s="17"/>
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="10" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A10" s="10">
         <v>2</v>
       </c>
@@ -22097,7 +22097,7 @@
       </c>
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="11" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A11" s="10">
         <v>3</v>
       </c>
@@ -22119,7 +22119,7 @@
       <c r="G11" s="17"/>
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="12" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A12" s="10">
         <v>4</v>
       </c>
@@ -22141,7 +22141,7 @@
       <c r="G12" s="17"/>
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="13" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A13" s="10">
         <v>5</v>
       </c>
@@ -22163,7 +22163,7 @@
       <c r="G13" s="17"/>
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="14" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A14" s="10">
         <v>6</v>
       </c>
@@ -22207,7 +22207,7 @@
       <c r="G15" s="17"/>
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="16" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A16" s="10">
         <v>8</v>
       </c>
@@ -22229,7 +22229,7 @@
       <c r="G16" s="17"/>
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" ht="63">
+    <row r="17" spans="1:8" s="8" customFormat="1" ht="62">
       <c r="A17" s="10">
         <v>9</v>
       </c>
@@ -22271,7 +22271,7 @@
       <c r="G18" s="17"/>
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75">
+    <row r="19" spans="1:8" ht="15.5">
       <c r="A19" s="5" t="s">
         <v>13</v>
       </c>
@@ -22285,7 +22285,7 @@
       <c r="G19" s="11"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="20" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A20" s="10">
         <v>1</v>
       </c>
@@ -22325,7 +22325,7 @@
       </c>
       <c r="H21" s="13"/>
     </row>
-    <row r="22" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="22" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A22" s="10">
         <v>3</v>
       </c>
@@ -22343,7 +22343,7 @@
       <c r="G22" s="11"/>
       <c r="H22" s="13"/>
     </row>
-    <row r="23" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="23" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A23" s="10">
         <v>4</v>
       </c>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="H24" s="14"/>
     </row>
-    <row r="25" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="25" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A25" s="10">
         <v>6</v>
       </c>
@@ -22407,7 +22407,7 @@
       </c>
       <c r="H25" s="14"/>
     </row>
-    <row r="26" spans="1:8" s="52" customFormat="1" ht="63">
+    <row r="26" spans="1:8" s="52" customFormat="1" ht="62">
       <c r="A26" s="10">
         <v>7</v>
       </c>
@@ -22431,7 +22431,7 @@
       </c>
       <c r="H26" s="51"/>
     </row>
-    <row r="27" spans="1:8" s="52" customFormat="1" ht="63">
+    <row r="27" spans="1:8" s="52" customFormat="1" ht="62">
       <c r="A27" s="10">
         <v>8</v>
       </c>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="H27" s="51"/>
     </row>
-    <row r="28" spans="1:8" s="8" customFormat="1" ht="47.25">
+    <row r="28" spans="1:8" s="8" customFormat="1" ht="46.5">
       <c r="A28" s="10">
         <v>9</v>
       </c>
@@ -22477,7 +22477,7 @@
       </c>
       <c r="H28" s="14"/>
     </row>
-    <row r="29" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="29" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A29" s="36" t="s">
         <v>174</v>
       </c>
@@ -22491,7 +22491,7 @@
       <c r="G29" s="50"/>
       <c r="H29" s="99"/>
     </row>
-    <row r="30" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="30" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A30" s="104">
         <v>1</v>
       </c>
@@ -22505,7 +22505,7 @@
       <c r="G30" s="541"/>
       <c r="H30" s="541"/>
     </row>
-    <row r="31" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="31" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A31" s="41">
         <v>2</v>
       </c>
@@ -22519,7 +22519,7 @@
       <c r="G31" s="564"/>
       <c r="H31" s="564"/>
     </row>
-    <row r="32" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="32" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A32" s="110" t="s">
         <v>110</v>
       </c>
@@ -22567,7 +22567,7 @@
       <c r="G34" s="470"/>
       <c r="H34" s="475"/>
     </row>
-    <row r="35" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="35" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A35" s="35" t="s">
         <v>10</v>
       </c>
@@ -22581,7 +22581,7 @@
       <c r="G35" s="442"/>
       <c r="H35" s="37"/>
     </row>
-    <row r="36" spans="1:8" ht="15.75">
+    <row r="36" spans="1:8" ht="15.5">
       <c r="A36" s="35" t="s">
         <v>13</v>
       </c>
@@ -22595,7 +22595,7 @@
       <c r="G36" s="442"/>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" ht="31.5">
+    <row r="37" spans="1:8" ht="31">
       <c r="A37" s="44">
         <v>1</v>
       </c>
@@ -22649,7 +22649,7 @@
       <c r="G39" s="457"/>
       <c r="H39" s="98"/>
     </row>
-    <row r="40" spans="1:8" ht="15.75">
+    <row r="40" spans="1:8" ht="15.5">
       <c r="A40" s="132"/>
       <c r="B40" s="133"/>
       <c r="C40" s="134"/>
@@ -22659,7 +22659,7 @@
       <c r="G40" s="136"/>
       <c r="H40" s="137"/>
     </row>
-    <row r="41" spans="1:8" ht="16.5" thickBot="1">
+    <row r="41" spans="1:8" ht="16" thickBot="1">
       <c r="A41" s="132"/>
       <c r="B41" s="133"/>
       <c r="C41" s="134"/>
@@ -22681,7 +22681,7 @@
       <c r="G42" s="575"/>
       <c r="H42" s="576"/>
     </row>
-    <row r="43" spans="1:8" ht="15.75">
+    <row r="43" spans="1:8" ht="15">
       <c r="A43" s="463" t="s">
         <v>178</v>
       </c>
@@ -22693,7 +22693,7 @@
       <c r="G43" s="464"/>
       <c r="H43" s="465"/>
     </row>
-    <row r="44" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="44" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A44" s="565" t="s">
         <v>2</v>
       </c>
@@ -22717,7 +22717,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="1" customFormat="1" ht="15.75">
+    <row r="45" spans="1:8" s="1" customFormat="1" ht="15.5">
       <c r="A45" s="566"/>
       <c r="B45" s="572"/>
       <c r="C45" s="566"/>
@@ -22731,7 +22731,7 @@
       <c r="G45" s="566"/>
       <c r="H45" s="566"/>
     </row>
-    <row r="46" spans="1:8" ht="15.75">
+    <row r="46" spans="1:8" ht="15.5">
       <c r="A46" s="35" t="s">
         <v>10</v>
       </c>
@@ -22745,7 +22745,7 @@
       <c r="G46" s="38"/>
       <c r="H46" s="39"/>
     </row>
-    <row r="47" spans="1:8" s="62" customFormat="1" ht="47.25">
+    <row r="47" spans="1:8" s="62" customFormat="1" ht="46.5">
       <c r="A47" s="48">
         <v>1</v>
       </c>
@@ -22770,7 +22770,7 @@
         <v>49995000</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="48" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A48" s="48">
         <v>2</v>
       </c>
@@ -22816,7 +22816,7 @@
         <v>16550000</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="8" customFormat="1" ht="47.25">
+    <row r="50" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A50" s="48">
         <v>4</v>
       </c>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="H50" s="50"/>
     </row>
-    <row r="51" spans="1:8" s="8" customFormat="1" ht="47.25">
+    <row r="51" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A51" s="48">
         <v>5</v>
       </c>
@@ -22862,7 +22862,7 @@
       <c r="G51" s="42"/>
       <c r="H51" s="50"/>
     </row>
-    <row r="52" spans="1:8" s="62" customFormat="1" ht="31.5">
+    <row r="52" spans="1:8" s="62" customFormat="1" ht="31">
       <c r="A52" s="48">
         <v>6</v>
       </c>
@@ -22884,7 +22884,7 @@
       <c r="G52" s="67"/>
       <c r="H52" s="50"/>
     </row>
-    <row r="53" spans="1:8" s="62" customFormat="1" ht="31.5">
+    <row r="53" spans="1:8" s="62" customFormat="1" ht="31">
       <c r="A53" s="48">
         <v>7</v>
       </c>
@@ -22906,7 +22906,7 @@
       <c r="G53" s="67"/>
       <c r="H53" s="50"/>
     </row>
-    <row r="54" spans="1:8" s="62" customFormat="1" ht="31.5">
+    <row r="54" spans="1:8" s="62" customFormat="1" ht="15.5">
       <c r="A54" s="48">
         <v>8</v>
       </c>
@@ -22928,7 +22928,7 @@
       <c r="G54" s="67"/>
       <c r="H54" s="50"/>
     </row>
-    <row r="55" spans="1:8" s="8" customFormat="1" ht="31.5">
+    <row r="55" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A55" s="48">
         <v>9</v>
       </c>
@@ -22950,7 +22950,7 @@
       <c r="G55" s="50"/>
       <c r="H55" s="50"/>
     </row>
-    <row r="56" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="56" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A56" s="44"/>
       <c r="B56" s="15"/>
       <c r="C56" s="49"/>
@@ -22960,7 +22960,7 @@
       <c r="G56" s="50"/>
       <c r="H56" s="50"/>
     </row>
-    <row r="57" spans="1:8" ht="15.75">
+    <row r="57" spans="1:8" ht="15.5">
       <c r="A57" s="58" t="s">
         <v>13</v>
       </c>
@@ -22974,7 +22974,7 @@
       <c r="G57" s="56"/>
       <c r="H57" s="37"/>
     </row>
-    <row r="58" spans="1:8" s="8" customFormat="1" ht="47.25">
+    <row r="58" spans="1:8" s="8" customFormat="1" ht="31">
       <c r="A58" s="48">
         <v>1</v>
       </c>
@@ -22996,7 +22996,7 @@
       <c r="G58" s="50"/>
       <c r="H58" s="50"/>
     </row>
-    <row r="59" spans="1:8" s="62" customFormat="1" ht="63">
+    <row r="59" spans="1:8" s="62" customFormat="1" ht="62">
       <c r="A59" s="48">
         <v>2</v>
       </c>
@@ -23020,7 +23020,7 @@
       </c>
       <c r="H59" s="50"/>
     </row>
-    <row r="60" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="60" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A60" s="44"/>
       <c r="B60" s="15"/>
       <c r="C60" s="49"/>
@@ -23030,7 +23030,7 @@
       <c r="G60" s="50"/>
       <c r="H60" s="50"/>
     </row>
-    <row r="61" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="61" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A61" s="36" t="s">
         <v>174</v>
       </c>
@@ -23044,7 +23044,7 @@
       <c r="G61" s="50"/>
       <c r="H61" s="99"/>
     </row>
-    <row r="62" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="62" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A62" s="104">
         <v>1</v>
       </c>
@@ -23060,7 +23060,7 @@
       <c r="G62" s="541"/>
       <c r="H62" s="541"/>
     </row>
-    <row r="63" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="63" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A63" s="104">
         <v>2</v>
       </c>
@@ -23076,7 +23076,7 @@
       <c r="G63" s="564"/>
       <c r="H63" s="564"/>
     </row>
-    <row r="64" spans="1:8" ht="15.75">
+    <row r="64" spans="1:8" ht="15.5">
       <c r="A64" s="107"/>
       <c r="B64" s="130"/>
       <c r="C64" s="126"/>
@@ -23086,7 +23086,7 @@
       <c r="G64" s="131"/>
       <c r="H64" s="128"/>
     </row>
-    <row r="65" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="65" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A65" s="105"/>
       <c r="B65" s="106"/>
       <c r="C65" s="107"/>
@@ -23096,7 +23096,7 @@
       <c r="G65" s="107"/>
       <c r="H65" s="111"/>
     </row>
-    <row r="66" spans="1:8" ht="15.75">
+    <row r="66" spans="1:8" ht="15.5">
       <c r="A66" s="113" t="s">
         <v>179</v>
       </c>
@@ -23144,7 +23144,7 @@
       <c r="G68" s="449"/>
       <c r="H68" s="433"/>
     </row>
-    <row r="69" spans="1:8" ht="15.75">
+    <row r="69" spans="1:8" ht="15.5">
       <c r="A69" s="68" t="s">
         <v>10</v>
       </c>
@@ -23160,7 +23160,7 @@
       <c r="G69" s="458"/>
       <c r="H69" s="112"/>
     </row>
-    <row r="70" spans="1:8" ht="47.25">
+    <row r="70" spans="1:8" ht="46.5">
       <c r="A70" s="48">
         <v>1</v>
       </c>
@@ -23192,7 +23192,7 @@
       <c r="G71" s="460"/>
       <c r="H71" s="37"/>
     </row>
-    <row r="72" spans="1:8" ht="15.75">
+    <row r="72" spans="1:8" ht="15.5">
       <c r="A72" s="44">
         <v>3</v>
       </c>
@@ -23208,7 +23208,7 @@
       <c r="G72" s="460"/>
       <c r="H72" s="37"/>
     </row>
-    <row r="73" spans="1:8" ht="15.75">
+    <row r="73" spans="1:8" ht="15.5">
       <c r="A73" s="48">
         <v>4</v>
       </c>
@@ -23224,7 +23224,7 @@
       <c r="G73" s="460"/>
       <c r="H73" s="37"/>
     </row>
-    <row r="74" spans="1:8" ht="47.25">
+    <row r="74" spans="1:8" ht="46.5">
       <c r="A74" s="48">
         <v>5</v>
       </c>
@@ -23240,7 +23240,7 @@
       <c r="G74" s="442"/>
       <c r="H74" s="37"/>
     </row>
-    <row r="75" spans="1:8" ht="31.5">
+    <row r="75" spans="1:8" ht="31">
       <c r="A75" s="48">
         <v>6</v>
       </c>
@@ -23258,7 +23258,7 @@
       <c r="G75" s="442"/>
       <c r="H75" s="37"/>
     </row>
-    <row r="76" spans="1:8" ht="15.75">
+    <row r="76" spans="1:8" ht="15.5">
       <c r="A76" s="35" t="s">
         <v>13</v>
       </c>
@@ -23272,7 +23272,7 @@
       <c r="G76" s="442"/>
       <c r="H76" s="37"/>
     </row>
-    <row r="77" spans="1:8" ht="31.5">
+    <row r="77" spans="1:8" ht="31">
       <c r="A77" s="44">
         <v>1</v>
       </c>
@@ -23288,7 +23288,7 @@
       <c r="G77" s="442"/>
       <c r="H77" s="37"/>
     </row>
-    <row r="78" spans="1:8" ht="31.5">
+    <row r="78" spans="1:8" ht="31">
       <c r="A78" s="44">
         <v>2</v>
       </c>
@@ -23306,7 +23306,7 @@
       <c r="G78" s="442"/>
       <c r="H78" s="37"/>
     </row>
-    <row r="79" spans="1:8" ht="31.5">
+    <row r="79" spans="1:8" ht="31">
       <c r="A79" s="44">
         <v>3</v>
       </c>
@@ -23324,7 +23324,7 @@
       <c r="G79" s="442"/>
       <c r="H79" s="37"/>
     </row>
-    <row r="80" spans="1:8" ht="31.5">
+    <row r="80" spans="1:8" ht="31">
       <c r="A80" s="44">
         <v>4</v>
       </c>
@@ -23354,7 +23354,7 @@
       <c r="G81" s="101"/>
       <c r="H81" s="103"/>
     </row>
-    <row r="82" spans="1:8" ht="15.75">
+    <row r="82" spans="1:8" ht="15">
       <c r="A82" s="463" t="s">
         <v>178</v>
       </c>
@@ -23404,7 +23404,7 @@
       <c r="G84" s="513"/>
       <c r="H84" s="513"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75">
+    <row r="85" spans="1:8" ht="15.5">
       <c r="A85" s="5" t="s">
         <v>10</v>
       </c>
@@ -23420,7 +23420,7 @@
       <c r="G85" s="4"/>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" ht="31.5">
+    <row r="86" spans="1:8" ht="15.5">
       <c r="A86" s="10">
         <v>1</v>
       </c>
@@ -23434,7 +23434,7 @@
       <c r="G86" s="17"/>
       <c r="H86" s="9"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75">
+    <row r="87" spans="1:8" ht="15.5">
       <c r="A87" s="10">
         <v>2</v>
       </c>
@@ -23448,7 +23448,7 @@
       <c r="G87" s="11"/>
       <c r="H87" s="9"/>
     </row>
-    <row r="88" spans="1:8" ht="15.75">
+    <row r="88" spans="1:8" ht="15.5">
       <c r="A88" s="10">
         <v>3</v>
       </c>
@@ -23462,7 +23462,7 @@
       <c r="G88" s="11"/>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" ht="31.5">
+    <row r="89" spans="1:8" ht="31">
       <c r="A89" s="10">
         <v>4</v>
       </c>
@@ -23476,7 +23476,7 @@
       <c r="G89" s="11"/>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" ht="31.5">
+    <row r="90" spans="1:8" ht="31">
       <c r="A90" s="10">
         <v>5</v>
       </c>
@@ -23492,7 +23492,7 @@
       <c r="G90" s="11"/>
       <c r="H90" s="12"/>
     </row>
-    <row r="91" spans="1:8" ht="15.75">
+    <row r="91" spans="1:8" ht="15.5">
       <c r="A91" s="10">
         <v>6</v>
       </c>
@@ -23534,7 +23534,7 @@
       <c r="G93" s="11"/>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" s="8" customFormat="1" ht="126">
+    <row r="94" spans="1:8" s="8" customFormat="1" ht="124">
       <c r="A94" s="10">
         <v>1</v>
       </c>
@@ -23550,7 +23550,7 @@
       <c r="G94" s="17"/>
       <c r="H94" s="14"/>
     </row>
-    <row r="95" spans="1:8" ht="15.75">
+    <row r="95" spans="1:8" ht="15.5">
       <c r="A95" s="10">
         <v>2</v>
       </c>
@@ -23564,7 +23564,7 @@
       <c r="G95" s="17"/>
       <c r="H95" s="14"/>
     </row>
-    <row r="96" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="96" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A96" s="36" t="s">
         <v>174</v>
       </c>
@@ -23578,7 +23578,7 @@
       <c r="G96" s="50"/>
       <c r="H96" s="99"/>
     </row>
-    <row r="97" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="97" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A97" s="104">
         <v>1</v>
       </c>
@@ -23594,7 +23594,7 @@
       <c r="G97" s="578"/>
       <c r="H97" s="578"/>
     </row>
-    <row r="98" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="98" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A98" s="104">
         <v>2</v>
       </c>
@@ -23608,7 +23608,7 @@
       <c r="G98" s="578"/>
       <c r="H98" s="578"/>
     </row>
-    <row r="99" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="99" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A99" s="110" t="s">
         <v>110</v>
       </c>
@@ -23656,7 +23656,7 @@
       <c r="G101" s="470"/>
       <c r="H101" s="475"/>
     </row>
-    <row r="102" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="102" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A102" s="35" t="s">
         <v>10</v>
       </c>
@@ -23672,7 +23672,7 @@
       <c r="G102" s="442"/>
       <c r="H102" s="37"/>
     </row>
-    <row r="103" spans="1:8" ht="15.75">
+    <row r="103" spans="1:8" ht="15.5">
       <c r="A103" s="35" t="s">
         <v>13</v>
       </c>
@@ -23688,7 +23688,7 @@
       <c r="G103" s="442"/>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" ht="16.5" thickBot="1">
+    <row r="104" spans="1:8" ht="16" thickBot="1">
       <c r="A104" s="124"/>
       <c r="B104" s="125"/>
       <c r="C104" s="126"/>
@@ -23710,7 +23710,7 @@
       <c r="G105" s="119"/>
       <c r="H105" s="121"/>
     </row>
-    <row r="106" spans="1:8" ht="15.75">
+    <row r="106" spans="1:8" ht="15">
       <c r="A106" s="463" t="s">
         <v>178</v>
       </c>
@@ -23722,7 +23722,7 @@
       <c r="G106" s="464"/>
       <c r="H106" s="465"/>
     </row>
-    <row r="107" spans="1:8" s="34" customFormat="1" ht="15.75">
+    <row r="107" spans="1:8" s="34" customFormat="1" ht="15.5">
       <c r="A107" s="431" t="s">
         <v>2</v>
       </c>
@@ -23746,7 +23746,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="34" customFormat="1" ht="15.75">
+    <row r="108" spans="1:8" s="34" customFormat="1" ht="15.5">
       <c r="A108" s="432"/>
       <c r="B108" s="532"/>
       <c r="C108" s="432"/>
@@ -23760,7 +23760,7 @@
       <c r="G108" s="432"/>
       <c r="H108" s="432"/>
     </row>
-    <row r="109" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="109" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A109" s="35" t="s">
         <v>10</v>
       </c>
@@ -23774,7 +23774,7 @@
       <c r="G109" s="38"/>
       <c r="H109" s="39"/>
     </row>
-    <row r="110" spans="1:8" s="40" customFormat="1" ht="47.25">
+    <row r="110" spans="1:8" s="40" customFormat="1" ht="46.5">
       <c r="A110" s="41">
         <v>1</v>
       </c>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="H110" s="39"/>
     </row>
-    <row r="111" spans="1:8" s="40" customFormat="1" ht="63">
+    <row r="111" spans="1:8" s="40" customFormat="1" ht="46.5">
       <c r="A111" s="41">
         <v>2</v>
       </c>
@@ -23822,7 +23822,7 @@
       </c>
       <c r="H111" s="39"/>
     </row>
-    <row r="112" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="112" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A112" s="41">
         <v>3</v>
       </c>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="H113" s="51"/>
     </row>
-    <row r="114" spans="1:8" s="52" customFormat="1" ht="47.25">
+    <row r="114" spans="1:8" s="52" customFormat="1" ht="46.5">
       <c r="A114" s="44" t="s">
         <v>78</v>
       </c>
@@ -23886,7 +23886,7 @@
       </c>
       <c r="H114" s="51"/>
     </row>
-    <row r="115" spans="1:8" s="52" customFormat="1" ht="47.25">
+    <row r="115" spans="1:8" s="52" customFormat="1" ht="46.5">
       <c r="A115" s="48" t="s">
         <v>82</v>
       </c>
@@ -23910,7 +23910,7 @@
       </c>
       <c r="H115" s="51"/>
     </row>
-    <row r="116" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="116" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A116" s="44" t="s">
         <v>85</v>
       </c>
@@ -24054,7 +24054,7 @@
       </c>
       <c r="H121" s="51"/>
     </row>
-    <row r="122" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="122" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A122" s="57"/>
       <c r="B122" s="53"/>
       <c r="C122" s="43"/>
@@ -24064,7 +24064,7 @@
       <c r="G122" s="50"/>
       <c r="H122" s="51"/>
     </row>
-    <row r="123" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="123" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A123" s="58" t="s">
         <v>13</v>
       </c>
@@ -24078,7 +24078,7 @@
       <c r="G123" s="56"/>
       <c r="H123" s="61"/>
     </row>
-    <row r="124" spans="1:8" s="40" customFormat="1" ht="94.5">
+    <row r="124" spans="1:8" s="40" customFormat="1" ht="93">
       <c r="A124" s="44">
         <v>1</v>
       </c>
@@ -24130,7 +24130,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="126" spans="1:8" s="52" customFormat="1" ht="31.5">
+    <row r="126" spans="1:8" s="52" customFormat="1" ht="31">
       <c r="A126" s="44">
         <v>3</v>
       </c>
@@ -24152,7 +24152,7 @@
       <c r="G126" s="50"/>
       <c r="H126" s="51"/>
     </row>
-    <row r="127" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="127" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A127" s="44"/>
       <c r="B127" s="15" t="s">
         <v>16</v>
@@ -24164,7 +24164,7 @@
       <c r="G127" s="50"/>
       <c r="H127" s="51"/>
     </row>
-    <row r="128" spans="1:8" s="52" customFormat="1" ht="15.75">
+    <row r="128" spans="1:8" s="52" customFormat="1" ht="15.5">
       <c r="A128" s="44"/>
       <c r="B128" s="15" t="s">
         <v>16</v>
@@ -24176,7 +24176,7 @@
       <c r="G128" s="50"/>
       <c r="H128" s="51"/>
     </row>
-    <row r="129" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="129" spans="1:8" s="8" customFormat="1" ht="15.5">
       <c r="A129" s="36" t="s">
         <v>174</v>
       </c>
@@ -24190,7 +24190,7 @@
       <c r="G129" s="50"/>
       <c r="H129" s="99"/>
     </row>
-    <row r="130" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="130" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A130" s="104">
         <v>1</v>
       </c>
@@ -24206,7 +24206,7 @@
       <c r="G130" s="541"/>
       <c r="H130" s="541"/>
     </row>
-    <row r="131" spans="1:8" s="8" customFormat="1" ht="15.75">
+    <row r="131" spans="1:8" s="8" customFormat="1" ht="15">
       <c r="A131" s="104">
         <v>2</v>
       </c>
@@ -24222,7 +24222,7 @@
       <c r="G131" s="564"/>
       <c r="H131" s="564"/>
     </row>
-    <row r="132" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="132" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A132" s="110" t="s">
         <v>179</v>
       </c>
@@ -24270,7 +24270,7 @@
       <c r="G134" s="470"/>
       <c r="H134" s="475"/>
     </row>
-    <row r="135" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="135" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A135" s="35" t="s">
         <v>10</v>
       </c>
@@ -24286,7 +24286,7 @@
       <c r="G135" s="442"/>
       <c r="H135" s="37"/>
     </row>
-    <row r="136" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="136" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A136" s="48">
         <v>1</v>
       </c>
@@ -24302,7 +24302,7 @@
       <c r="G136" s="460"/>
       <c r="H136" s="37"/>
     </row>
-    <row r="137" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="137" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A137" s="48">
         <v>2</v>
       </c>
@@ -24318,7 +24318,7 @@
       <c r="G137" s="460"/>
       <c r="H137" s="37"/>
     </row>
-    <row r="138" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="138" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A138" s="48">
         <v>3</v>
       </c>
@@ -24334,7 +24334,7 @@
       <c r="G138" s="460"/>
       <c r="H138" s="37"/>
     </row>
-    <row r="139" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="139" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A139" s="48">
         <v>4</v>
       </c>
@@ -24350,7 +24350,7 @@
       <c r="G139" s="460"/>
       <c r="H139" s="37"/>
     </row>
-    <row r="140" spans="1:8" s="40" customFormat="1" ht="31.5">
+    <row r="140" spans="1:8" s="40" customFormat="1" ht="31">
       <c r="A140" s="48">
         <v>5</v>
       </c>
@@ -24368,7 +24368,7 @@
       <c r="G140" s="446"/>
       <c r="H140" s="37"/>
     </row>
-    <row r="141" spans="1:8" s="40" customFormat="1" ht="15.75">
+    <row r="141" spans="1:8" s="40" customFormat="1" ht="15.5">
       <c r="A141" s="35" t="s">
         <v>13</v>
       </c>
@@ -24448,7 +24448,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="145" spans="1:10" s="40" customFormat="1" ht="31.5">
+    <row r="145" spans="1:10" s="40" customFormat="1" ht="31">
       <c r="A145" s="44">
         <v>4</v>
       </c>
@@ -24736,7 +24736,7 @@
     <mergeCell ref="F142:G142"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="66" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="41" max="16383" man="1"/>
     <brk id="80" max="16383" man="1"/>
